--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17717,6 +17717,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B668" t="n">
+        <v>23298733</v>
+      </c>
+      <c r="C668" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="E668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="G668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H668" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17743,6 +17743,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B669" t="n">
+        <v>7969925</v>
+      </c>
+      <c r="C669" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="G669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H669" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17769,6 +17769,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B670" t="n">
+        <v>24136718</v>
+      </c>
+      <c r="C670" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="G670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H670" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17795,6 +17795,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B671" t="n">
+        <v>14495546</v>
+      </c>
+      <c r="C671" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="E671" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="G671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H671" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -397,9 +394,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -420,11 +414,8 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -446,11 +437,8 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +460,8 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +483,8 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -524,11 +506,8 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -550,11 +529,8 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -576,11 +552,8 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
+      <c r="G8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -602,11 +575,8 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -628,11 +598,8 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+      <c r="G10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -654,11 +621,8 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
+      <c r="G11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -680,11 +644,8 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -706,11 +667,8 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -732,11 +690,8 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H14" t="s">
-        <v>8</v>
+      <c r="G14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -758,11 +713,8 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -784,11 +736,8 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
+      <c r="G16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -810,11 +759,8 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+      <c r="G17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -836,11 +782,8 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -862,11 +805,8 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -888,11 +828,8 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+      <c r="G20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -914,11 +851,8 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H21" t="s">
-        <v>8</v>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -940,11 +874,8 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
+      <c r="G22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -966,11 +897,8 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
+      <c r="G23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -992,11 +920,8 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1018,11 +943,8 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
+      <c r="G25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1044,11 +966,8 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>8</v>
+      <c r="G26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1070,11 +989,8 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.019845999777317</v>
-      </c>
-      <c r="H27" t="s">
-        <v>8</v>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1096,11 +1012,8 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H28" t="s">
-        <v>8</v>
+      <c r="G28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1122,11 +1035,8 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>8</v>
+      <c r="G29" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1148,11 +1058,8 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.01923399977386</v>
-      </c>
-      <c r="H30" t="s">
-        <v>8</v>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1174,11 +1081,8 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+      <c r="G31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1200,11 +1104,8 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+      <c r="G32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1127,8 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1252,11 +1150,8 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="G34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1278,11 +1173,8 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1304,11 +1196,8 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H36" t="s">
-        <v>8</v>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1330,11 +1219,8 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H37" t="s">
-        <v>8</v>
+      <c r="G37" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1356,11 +1242,8 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H38" t="s">
-        <v>8</v>
+      <c r="G38" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1382,11 +1265,8 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H39" t="s">
-        <v>8</v>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1408,11 +1288,8 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
+      <c r="G40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1434,11 +1311,8 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
+      <c r="G41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1460,11 +1334,8 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1486,11 +1357,8 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H43" t="s">
-        <v>8</v>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1512,11 +1380,8 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H44" t="s">
-        <v>8</v>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1538,11 +1403,8 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H45" t="s">
-        <v>8</v>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1564,11 +1426,8 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H46" t="s">
-        <v>8</v>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1590,11 +1449,8 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H47" t="s">
-        <v>8</v>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1616,11 +1472,8 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H48" t="s">
-        <v>8</v>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1642,11 +1495,8 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H49" t="s">
-        <v>8</v>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1668,11 +1518,8 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H50" t="s">
-        <v>8</v>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1694,11 +1541,8 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H51" t="s">
-        <v>8</v>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1720,11 +1564,8 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H52" t="s">
-        <v>8</v>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1746,11 +1587,8 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H53" t="s">
-        <v>8</v>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,11 +1610,8 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H54" t="s">
-        <v>8</v>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1798,11 +1633,8 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H55" t="s">
-        <v>8</v>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1824,11 +1656,8 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H56" t="s">
-        <v>8</v>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1850,11 +1679,8 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H57" t="s">
-        <v>8</v>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1876,11 +1702,8 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H58" t="s">
-        <v>8</v>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1902,11 +1725,8 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H59" t="s">
-        <v>8</v>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1928,11 +1748,8 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H60" t="s">
-        <v>8</v>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1954,11 +1771,8 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1980,11 +1794,8 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H62" t="s">
-        <v>8</v>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2006,11 +1817,8 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H63" t="s">
-        <v>8</v>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2032,11 +1840,8 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H64" t="s">
-        <v>8</v>
+      <c r="G64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2058,11 +1863,8 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H65" t="s">
-        <v>8</v>
+      <c r="G65" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2084,11 +1886,8 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H66" t="s">
-        <v>8</v>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2110,11 +1909,8 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H67" t="s">
-        <v>8</v>
+      <c r="G67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2136,11 +1932,8 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H68" t="s">
-        <v>8</v>
+      <c r="G68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2162,11 +1955,8 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H69" t="s">
-        <v>8</v>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -2188,11 +1978,8 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H70" t="s">
-        <v>8</v>
+      <c r="G70" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2214,11 +2001,8 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H71" t="s">
-        <v>8</v>
+      <c r="G71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2240,11 +2024,8 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H72" t="s">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2266,11 +2047,8 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H73" t="s">
-        <v>8</v>
+      <c r="G73" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -2292,11 +2070,8 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="G74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2318,11 +2093,8 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H75" t="s">
-        <v>8</v>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2344,11 +2116,8 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="G76" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2370,11 +2139,8 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H77" t="s">
-        <v>8</v>
+      <c r="G77" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2396,11 +2162,8 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2422,11 +2185,8 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H79" t="s">
-        <v>8</v>
+      <c r="G79" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2448,11 +2208,8 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+      <c r="G80" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2474,11 +2231,8 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H81" t="s">
-        <v>8</v>
+      <c r="G81" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2500,11 +2254,8 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+      <c r="G82" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2526,11 +2277,8 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H83" t="s">
-        <v>8</v>
+      <c r="G83" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2552,11 +2300,8 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H84" t="s">
-        <v>8</v>
+      <c r="G84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2578,11 +2323,8 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H85" t="s">
-        <v>8</v>
+      <c r="G85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2604,11 +2346,8 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H86" t="s">
-        <v>8</v>
+      <c r="G86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -2630,11 +2369,8 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>8</v>
+      <c r="G87" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2656,11 +2392,8 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>8</v>
+      <c r="G88" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2682,11 +2415,8 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H89" t="s">
-        <v>8</v>
+      <c r="G89" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -2708,11 +2438,8 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="G90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2734,11 +2461,8 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H91" t="s">
-        <v>8</v>
+      <c r="G91" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2760,11 +2484,8 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="G92" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2786,11 +2507,8 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H93" t="s">
-        <v>8</v>
+      <c r="G93" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -2812,11 +2530,8 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H94" t="s">
-        <v>8</v>
+      <c r="G94" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2838,11 +2553,8 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="G95" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2864,11 +2576,8 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H96" t="s">
-        <v>8</v>
+      <c r="G96" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2890,11 +2599,8 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+      <c r="G97" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -2916,11 +2622,8 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H98" t="s">
-        <v>8</v>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2942,11 +2645,8 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="G99" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2668,8 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H100" t="s">
-        <v>8</v>
+      <c r="G100" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2994,11 +2691,8 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H101" t="s">
-        <v>8</v>
+      <c r="G101" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3020,11 +2714,8 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H102" t="s">
-        <v>8</v>
+      <c r="G102" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3046,11 +2737,8 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="G103" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3072,11 +2760,8 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H104" t="s">
-        <v>8</v>
+      <c r="G104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3098,11 +2783,8 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H105" t="s">
-        <v>8</v>
+      <c r="G105" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3124,11 +2806,8 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H106" t="s">
-        <v>8</v>
+      <c r="G106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3150,11 +2829,8 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H107" t="s">
-        <v>8</v>
+      <c r="G107" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3176,11 +2852,8 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+      <c r="G108" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3202,11 +2875,8 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H109" t="s">
-        <v>8</v>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3228,11 +2898,8 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H110" t="s">
-        <v>8</v>
+      <c r="G110" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -3254,11 +2921,8 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H111" t="s">
-        <v>8</v>
+      <c r="G111" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -3280,11 +2944,8 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H112" t="s">
-        <v>8</v>
+      <c r="G112" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3306,11 +2967,8 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+      <c r="G113" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3332,11 +2990,8 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H114" t="s">
-        <v>8</v>
+      <c r="G114" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3358,11 +3013,8 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H115" t="s">
-        <v>8</v>
+      <c r="G115" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3384,11 +3036,8 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+      <c r="G116" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3410,11 +3059,8 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H117" t="s">
-        <v>8</v>
+      <c r="G117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3436,11 +3082,8 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H118" t="s">
-        <v>8</v>
+      <c r="G118" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3462,11 +3105,8 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H119" t="s">
-        <v>8</v>
+      <c r="G119" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -3488,11 +3128,8 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H120" t="s">
-        <v>8</v>
+      <c r="G120" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -3514,11 +3151,8 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
+      <c r="G121" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -3540,11 +3174,8 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H122" t="s">
-        <v>8</v>
+      <c r="G122" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -3566,11 +3197,8 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H123" t="s">
-        <v>8</v>
+      <c r="G123" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3592,11 +3220,8 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H124" t="s">
-        <v>8</v>
+      <c r="G124" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -3618,11 +3243,8 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H125" t="s">
-        <v>8</v>
+      <c r="G125" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -3644,11 +3266,8 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H126" t="s">
-        <v>8</v>
+      <c r="G126" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -3670,11 +3289,8 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H127" t="s">
-        <v>8</v>
+      <c r="G127" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3696,11 +3312,8 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H128" t="s">
-        <v>8</v>
+      <c r="G128" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="129">
@@ -3722,11 +3335,8 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H129" t="s">
-        <v>8</v>
+      <c r="G129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -3748,11 +3358,8 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H130" t="s">
-        <v>8</v>
+      <c r="G130" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3774,11 +3381,8 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H131" t="s">
-        <v>8</v>
+      <c r="G131" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -3800,11 +3404,8 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H132" t="s">
-        <v>8</v>
+      <c r="G132" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -3826,11 +3427,8 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H133" t="s">
-        <v>8</v>
+      <c r="G133" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -3852,11 +3450,8 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H134" t="s">
-        <v>8</v>
+      <c r="G134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3878,11 +3473,8 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H135" t="s">
-        <v>8</v>
+      <c r="G135" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="136">
@@ -3904,11 +3496,8 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H136" t="s">
-        <v>8</v>
+      <c r="G136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -3930,11 +3519,8 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H137" t="s">
-        <v>8</v>
+      <c r="G137" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3956,11 +3542,8 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H138" t="s">
-        <v>8</v>
+      <c r="G138" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3982,11 +3565,8 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>8</v>
+      <c r="G139" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -4008,11 +3588,8 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H140" t="s">
-        <v>8</v>
+      <c r="G140" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -4034,11 +3611,8 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H141" t="s">
-        <v>8</v>
+      <c r="G141" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -4060,11 +3634,8 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H142" t="s">
-        <v>8</v>
+      <c r="G142" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="143">
@@ -4086,11 +3657,8 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H143" t="s">
-        <v>8</v>
+      <c r="G143" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4112,11 +3680,8 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H144" t="s">
-        <v>8</v>
+      <c r="G144" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -4138,11 +3703,8 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H145" t="s">
-        <v>8</v>
+      <c r="G145" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -4164,11 +3726,8 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H146" t="s">
-        <v>8</v>
+      <c r="G146" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -4190,11 +3749,8 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H147" t="s">
-        <v>8</v>
+      <c r="G147" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -4216,11 +3772,8 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H148" t="s">
-        <v>8</v>
+      <c r="G148" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -4242,11 +3795,8 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H149" t="s">
-        <v>8</v>
+      <c r="G149" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -4268,11 +3818,8 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H150" t="s">
-        <v>8</v>
+      <c r="G150" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -4294,11 +3841,8 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H151" t="s">
-        <v>8</v>
+      <c r="G151" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -4320,11 +3864,8 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H152" t="s">
-        <v>8</v>
+      <c r="G152" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -4346,11 +3887,8 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>8</v>
+      <c r="G153" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4372,11 +3910,8 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H154" t="s">
-        <v>8</v>
+      <c r="G154" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -4398,11 +3933,8 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H155" t="s">
-        <v>8</v>
+      <c r="G155" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -4424,11 +3956,8 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H156" t="s">
-        <v>8</v>
+      <c r="G156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -4450,11 +3979,8 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H157" t="s">
-        <v>8</v>
+      <c r="G157" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -4476,11 +4002,8 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H158" t="s">
-        <v>8</v>
+      <c r="G158" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -4502,11 +4025,8 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H159" t="s">
-        <v>8</v>
+      <c r="G159" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -4528,11 +4048,8 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H160" t="s">
-        <v>8</v>
+      <c r="G160" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -4554,11 +4071,8 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H161" t="s">
-        <v>8</v>
+      <c r="G161" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -4580,11 +4094,8 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H162" t="s">
-        <v>8</v>
+      <c r="G162" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -4606,11 +4117,8 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H163" t="s">
-        <v>8</v>
+      <c r="G163" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4632,11 +4140,8 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H164" t="s">
-        <v>8</v>
+      <c r="G164" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4658,11 +4163,8 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H165" t="s">
-        <v>8</v>
+      <c r="G165" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -4684,11 +4186,8 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H166" t="s">
-        <v>8</v>
+      <c r="G166" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -4710,11 +4209,8 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H167" t="s">
-        <v>8</v>
+      <c r="G167" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4736,11 +4232,8 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H168" t="s">
-        <v>8</v>
+      <c r="G168" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -4762,11 +4255,8 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H169" t="s">
-        <v>8</v>
+      <c r="G169" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4788,11 +4278,8 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H170" t="s">
-        <v>8</v>
+      <c r="G170" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4814,11 +4301,8 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H171" t="s">
-        <v>8</v>
+      <c r="G171" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4840,11 +4324,8 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H172" t="s">
-        <v>8</v>
+      <c r="G172" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -4866,11 +4347,8 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H173" t="s">
-        <v>8</v>
+      <c r="G173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4370,8 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H174" t="s">
-        <v>8</v>
+      <c r="G174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4918,11 +4393,8 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H175" t="s">
-        <v>8</v>
+      <c r="G175" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -4944,11 +4416,8 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H176" t="s">
-        <v>8</v>
+      <c r="G176" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -4970,11 +4439,8 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H177" t="s">
-        <v>8</v>
+      <c r="G177" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -4996,11 +4462,8 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H178" t="s">
-        <v>8</v>
+      <c r="G178" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -5022,11 +4485,8 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H179" t="s">
-        <v>8</v>
+      <c r="G179" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="180">
@@ -5048,11 +4508,8 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H180" t="s">
-        <v>8</v>
+      <c r="G180" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -5074,11 +4531,8 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H181" t="s">
-        <v>8</v>
+      <c r="G181" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182">
@@ -5100,11 +4554,8 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H182" t="s">
-        <v>8</v>
+      <c r="G182" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -5126,11 +4577,8 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H183" t="s">
-        <v>8</v>
+      <c r="G183" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -5152,11 +4600,8 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H184" t="s">
-        <v>8</v>
+      <c r="G184" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -5178,11 +4623,8 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H185" t="s">
-        <v>8</v>
+      <c r="G185" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5204,11 +4646,8 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H186" t="s">
-        <v>8</v>
+      <c r="G186" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -5230,11 +4669,8 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H187" t="s">
-        <v>8</v>
+      <c r="G187" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5256,11 +4692,8 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H188" t="s">
-        <v>8</v>
+      <c r="G188" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5282,11 +4715,8 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H189" t="s">
-        <v>8</v>
+      <c r="G189" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -5308,11 +4738,8 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H190" t="s">
-        <v>8</v>
+      <c r="G190" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -5334,11 +4761,8 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H191" t="s">
-        <v>8</v>
+      <c r="G191" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -5360,11 +4784,8 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H192" t="s">
-        <v>8</v>
+      <c r="G192" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -5386,11 +4807,8 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H193" t="s">
-        <v>8</v>
+      <c r="G193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -5412,11 +4830,8 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H194" t="s">
-        <v>8</v>
+      <c r="G194" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -5438,11 +4853,8 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H195" t="s">
-        <v>8</v>
+      <c r="G195" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -5464,11 +4876,8 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H196" t="s">
-        <v>8</v>
+      <c r="G196" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -5490,11 +4899,8 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H197" t="s">
-        <v>8</v>
+      <c r="G197" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -5516,11 +4922,8 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H198" t="s">
-        <v>8</v>
+      <c r="G198" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -5542,11 +4945,8 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H199" t="s">
-        <v>8</v>
+      <c r="G199" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -5568,11 +4968,8 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H200" t="s">
-        <v>8</v>
+      <c r="G200" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -5594,11 +4991,8 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H201" t="s">
-        <v>8</v>
+      <c r="G201" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5620,11 +5014,8 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H202" t="s">
-        <v>8</v>
+      <c r="G202" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -5646,11 +5037,8 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H203" t="s">
-        <v>8</v>
+      <c r="G203" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -5672,11 +5060,8 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H204" t="s">
-        <v>8</v>
+      <c r="G204" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -5698,11 +5083,8 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H205" t="s">
-        <v>8</v>
+      <c r="G205" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -5724,11 +5106,8 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H206" t="s">
-        <v>8</v>
+      <c r="G206" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -5750,11 +5129,8 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H207" t="s">
-        <v>8</v>
+      <c r="G207" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -5776,11 +5152,8 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H208" t="s">
-        <v>8</v>
+      <c r="G208" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -5802,11 +5175,8 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H209" t="s">
-        <v>8</v>
+      <c r="G209" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5828,11 +5198,8 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H210" t="s">
-        <v>8</v>
+      <c r="G210" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -5854,11 +5221,8 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H211" t="s">
-        <v>8</v>
+      <c r="G211" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -5880,11 +5244,8 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H212" t="s">
-        <v>8</v>
+      <c r="G212" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5906,11 +5267,8 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H213" t="s">
-        <v>8</v>
+      <c r="G213" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -5932,11 +5290,8 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H214" t="s">
-        <v>8</v>
+      <c r="G214" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -5958,11 +5313,8 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H215" t="s">
-        <v>8</v>
+      <c r="G215" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -5984,11 +5336,8 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H216" t="s">
-        <v>8</v>
+      <c r="G216" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -6010,11 +5359,8 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H217" t="s">
-        <v>8</v>
+      <c r="G217" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -6036,11 +5382,8 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H218" t="s">
-        <v>8</v>
+      <c r="G218" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -6062,11 +5405,8 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H219" t="s">
-        <v>8</v>
+      <c r="G219" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -6088,11 +5428,8 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H220" t="s">
-        <v>8</v>
+      <c r="G220" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -6114,11 +5451,8 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H221" t="s">
-        <v>8</v>
+      <c r="G221" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -6140,11 +5474,8 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H222" t="s">
-        <v>8</v>
+      <c r="G222" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -6166,11 +5497,8 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H223" t="s">
-        <v>8</v>
+      <c r="G223" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -6192,11 +5520,8 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H224" t="s">
-        <v>8</v>
+      <c r="G224" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -6218,11 +5543,8 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H225" t="s">
-        <v>8</v>
+      <c r="G225" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="226">
@@ -6244,11 +5566,8 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H226" t="s">
-        <v>8</v>
+      <c r="G226" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -6270,11 +5589,8 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H227" t="s">
-        <v>8</v>
+      <c r="G227" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -6296,11 +5612,8 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H228" t="s">
-        <v>8</v>
+      <c r="G228" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -6322,11 +5635,8 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H229" t="s">
-        <v>8</v>
+      <c r="G229" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -6348,11 +5658,8 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H230" t="s">
-        <v>8</v>
+      <c r="G230" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -6374,11 +5681,8 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H231" t="s">
-        <v>8</v>
+      <c r="G231" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -6400,11 +5704,8 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H232" t="s">
-        <v>8</v>
+      <c r="G232" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -6426,11 +5727,8 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H233" t="s">
-        <v>8</v>
+      <c r="G233" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -6452,11 +5750,8 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H234" t="s">
-        <v>8</v>
+      <c r="G234" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -6478,11 +5773,8 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H235" t="s">
-        <v>8</v>
+      <c r="G235" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -6504,11 +5796,8 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H236" t="s">
-        <v>8</v>
+      <c r="G236" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -6530,11 +5819,8 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H237" t="s">
-        <v>8</v>
+      <c r="G237" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -6556,11 +5842,8 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H238" t="s">
-        <v>8</v>
+      <c r="G238" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -6582,11 +5865,8 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H239" t="s">
-        <v>8</v>
+      <c r="G239" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -6608,11 +5888,8 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H240" t="s">
-        <v>8</v>
+      <c r="G240" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6634,11 +5911,8 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H241" t="s">
-        <v>8</v>
+      <c r="G241" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -6660,11 +5934,8 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H242" t="s">
-        <v>8</v>
+      <c r="G242" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="243">
@@ -6686,11 +5957,8 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H243" t="s">
-        <v>8</v>
+      <c r="G243" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -6712,11 +5980,8 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H244" t="s">
-        <v>8</v>
+      <c r="G244" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6738,11 +6003,8 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H245" t="s">
-        <v>8</v>
+      <c r="G245" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -6764,11 +6026,8 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H246" t="s">
-        <v>8</v>
+      <c r="G246" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -6790,11 +6049,8 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H247" t="s">
-        <v>8</v>
+      <c r="G247" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -6816,11 +6072,8 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H248" t="s">
-        <v>8</v>
+      <c r="G248" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6842,11 +6095,8 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H249" t="s">
-        <v>8</v>
+      <c r="G249" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -6868,11 +6118,8 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H250" t="s">
-        <v>8</v>
+      <c r="G250" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -6894,11 +6141,8 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H251" t="s">
-        <v>8</v>
+      <c r="G251" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6920,11 +6164,8 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H252" t="s">
-        <v>8</v>
+      <c r="G252" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6946,11 +6187,8 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H253" t="s">
-        <v>8</v>
+      <c r="G253" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -6972,11 +6210,8 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H254" t="s">
-        <v>8</v>
+      <c r="G254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -6998,11 +6233,8 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H255" t="s">
-        <v>8</v>
+      <c r="G255" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -7024,11 +6256,8 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H256" t="s">
-        <v>8</v>
+      <c r="G256" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -7050,11 +6279,8 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H257" t="s">
-        <v>8</v>
+      <c r="G257" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -7076,11 +6302,8 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H258" t="s">
-        <v>8</v>
+      <c r="G258" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -7102,11 +6325,8 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H259" t="s">
-        <v>8</v>
+      <c r="G259" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -7128,11 +6348,8 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H260" t="s">
-        <v>8</v>
+      <c r="G260" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -7154,11 +6371,8 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H261" t="s">
-        <v>8</v>
+      <c r="G261" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -7180,11 +6394,8 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H262" t="s">
-        <v>8</v>
+      <c r="G262" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -7206,11 +6417,8 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H263" t="s">
-        <v>8</v>
+      <c r="G263" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -7232,11 +6440,8 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H264" t="s">
-        <v>8</v>
+      <c r="G264" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -7258,11 +6463,8 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H265" t="s">
-        <v>8</v>
+      <c r="G265" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7284,11 +6486,8 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H266" t="s">
-        <v>8</v>
+      <c r="G266" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -7310,11 +6509,8 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H267" t="s">
-        <v>8</v>
+      <c r="G267" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7336,11 +6532,8 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H268" t="s">
-        <v>8</v>
+      <c r="G268" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -7362,11 +6555,8 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H269" t="s">
-        <v>8</v>
+      <c r="G269" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -7388,11 +6578,8 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H270" t="s">
-        <v>8</v>
+      <c r="G270" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -7414,11 +6601,8 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H271" t="s">
-        <v>8</v>
+      <c r="G271" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -7440,11 +6624,8 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H272" t="s">
-        <v>8</v>
+      <c r="G272" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -7466,11 +6647,8 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H273" t="s">
-        <v>8</v>
+      <c r="G273" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -7492,11 +6670,8 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H274" t="s">
-        <v>8</v>
+      <c r="G274" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -7518,11 +6693,8 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H275" t="s">
-        <v>8</v>
+      <c r="G275" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -7544,11 +6716,8 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H276" t="s">
-        <v>8</v>
+      <c r="G276" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7570,11 +6739,8 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H277" t="s">
-        <v>8</v>
+      <c r="G277" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -7596,11 +6762,8 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H278" t="s">
-        <v>8</v>
+      <c r="G278" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -7622,11 +6785,8 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H279" t="s">
-        <v>8</v>
+      <c r="G279" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -7648,11 +6808,8 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H280" t="s">
-        <v>8</v>
+      <c r="G280" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -7674,11 +6831,8 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H281" t="s">
-        <v>8</v>
+      <c r="G281" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -7700,11 +6854,8 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H282" t="s">
-        <v>8</v>
+      <c r="G282" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -7726,11 +6877,8 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H283" t="s">
-        <v>8</v>
+      <c r="G283" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -7752,11 +6900,8 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H284" t="s">
-        <v>8</v>
+      <c r="G284" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -7778,11 +6923,8 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H285" t="s">
-        <v>8</v>
+      <c r="G285" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7804,11 +6946,8 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H286" t="s">
-        <v>8</v>
+      <c r="G286" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -7830,11 +6969,8 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H287" t="s">
-        <v>8</v>
+      <c r="G287" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -7856,11 +6992,8 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H288" t="s">
-        <v>8</v>
+      <c r="G288" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -7882,11 +7015,8 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H289" t="s">
-        <v>8</v>
+      <c r="G289" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -7908,11 +7038,8 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H290" t="s">
-        <v>8</v>
+      <c r="G290" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -7934,11 +7061,8 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H291" t="s">
-        <v>8</v>
+      <c r="G291" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -7960,11 +7084,8 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H292" t="s">
-        <v>8</v>
+      <c r="G292" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -7986,11 +7107,8 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H293" t="s">
-        <v>8</v>
+      <c r="G293" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -8012,11 +7130,8 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H294" t="s">
-        <v>8</v>
+      <c r="G294" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -8038,11 +7153,8 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H295" t="s">
-        <v>8</v>
+      <c r="G295" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -8064,11 +7176,8 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H296" t="s">
-        <v>8</v>
+      <c r="G296" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -8090,11 +7199,8 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H297" t="s">
-        <v>8</v>
+      <c r="G297" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -8116,11 +7222,8 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H298" t="s">
-        <v>8</v>
+      <c r="G298" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -8142,11 +7245,8 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H299" t="s">
-        <v>8</v>
+      <c r="G299" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -8168,11 +7268,8 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H300" t="s">
-        <v>8</v>
+      <c r="G300" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -8194,11 +7291,8 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H301" t="s">
-        <v>8</v>
+      <c r="G301" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -8220,11 +7314,8 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H302" t="s">
-        <v>8</v>
+      <c r="G302" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -8246,11 +7337,8 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H303" t="s">
-        <v>8</v>
+      <c r="G303" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -8272,11 +7360,8 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H304" t="s">
-        <v>8</v>
+      <c r="G304" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -8298,11 +7383,8 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H305" t="s">
-        <v>8</v>
+      <c r="G305" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -8324,11 +7406,8 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H306" t="s">
-        <v>8</v>
+      <c r="G306" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -8350,11 +7429,8 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H307" t="s">
-        <v>8</v>
+      <c r="G307" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -8376,11 +7452,8 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H308" t="s">
-        <v>8</v>
+      <c r="G308" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -8402,11 +7475,8 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H309" t="s">
-        <v>8</v>
+      <c r="G309" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -8428,11 +7498,8 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H310" t="s">
-        <v>8</v>
+      <c r="G310" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -8454,11 +7521,8 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H311" t="s">
-        <v>8</v>
+      <c r="G311" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -8480,11 +7544,8 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H312" t="s">
-        <v>8</v>
+      <c r="G312" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -8506,11 +7567,8 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H313" t="s">
-        <v>8</v>
+      <c r="G313" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -8532,11 +7590,8 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H314" t="s">
-        <v>8</v>
+      <c r="G314" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -8558,11 +7613,8 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H315" t="s">
-        <v>8</v>
+      <c r="G315" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -8584,11 +7636,8 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H316" t="s">
-        <v>8</v>
+      <c r="G316" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -8610,11 +7659,8 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H317" t="s">
-        <v>8</v>
+      <c r="G317" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -8636,11 +7682,8 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H318" t="s">
-        <v>8</v>
+      <c r="G318" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -8662,11 +7705,8 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H319" t="s">
-        <v>8</v>
+      <c r="G319" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -8688,11 +7728,8 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H320" t="s">
-        <v>8</v>
+      <c r="G320" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -8714,11 +7751,8 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H321" t="s">
-        <v>8</v>
+      <c r="G321" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -8740,11 +7774,8 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H322" t="s">
-        <v>8</v>
+      <c r="G322" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -8766,11 +7797,8 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H323" t="s">
-        <v>8</v>
+      <c r="G323" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -8792,11 +7820,8 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H324" t="s">
-        <v>8</v>
+      <c r="G324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -8818,11 +7843,8 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H325" t="s">
-        <v>8</v>
+      <c r="G325" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -8844,11 +7866,8 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H326" t="s">
-        <v>8</v>
+      <c r="G326" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -8870,11 +7889,8 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H327" t="s">
-        <v>8</v>
+      <c r="G327" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -8896,11 +7912,8 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H328" t="s">
-        <v>8</v>
+      <c r="G328" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -8922,11 +7935,8 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H329" t="s">
-        <v>8</v>
+      <c r="G329" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8948,11 +7958,8 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H330" t="s">
-        <v>8</v>
+      <c r="G330" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -8974,11 +7981,8 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H331" t="s">
-        <v>8</v>
+      <c r="G331" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -9000,11 +8004,8 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H332" t="s">
-        <v>8</v>
+      <c r="G332" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9026,11 +8027,8 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H333" t="s">
-        <v>8</v>
+      <c r="G333" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -9052,11 +8050,8 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H334" t="s">
-        <v>8</v>
+      <c r="G334" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -9078,11 +8073,8 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H335" t="s">
-        <v>8</v>
+      <c r="G335" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -9104,11 +8096,8 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H336" t="s">
-        <v>8</v>
+      <c r="G336" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -9130,11 +8119,8 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H337" t="s">
-        <v>8</v>
+      <c r="G337" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -9156,11 +8142,8 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H338" t="s">
-        <v>8</v>
+      <c r="G338" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -9182,11 +8165,8 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H339" t="s">
-        <v>8</v>
+      <c r="G339" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9208,11 +8188,8 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H340" t="s">
-        <v>8</v>
+      <c r="G340" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -9234,11 +8211,8 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H341" t="s">
-        <v>8</v>
+      <c r="G341" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -9260,11 +8234,8 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H342" t="s">
-        <v>8</v>
+      <c r="G342" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -9286,11 +8257,8 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H343" t="s">
-        <v>8</v>
+      <c r="G343" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -9312,11 +8280,8 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H344" t="s">
-        <v>8</v>
+      <c r="G344" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -9338,11 +8303,8 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H345" t="s">
-        <v>8</v>
+      <c r="G345" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -9364,11 +8326,8 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H346" t="s">
-        <v>8</v>
+      <c r="G346" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -9390,11 +8349,8 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H347" t="s">
-        <v>8</v>
+      <c r="G347" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -9416,11 +8372,8 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H348" t="s">
-        <v>8</v>
+      <c r="G348" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -9442,11 +8395,8 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H349" t="s">
-        <v>8</v>
+      <c r="G349" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -9468,11 +8418,8 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H350" t="s">
-        <v>8</v>
+      <c r="G350" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -9494,11 +8441,8 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H351" t="s">
-        <v>8</v>
+      <c r="G351" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -9520,11 +8464,8 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H352" t="s">
-        <v>8</v>
+      <c r="G352" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -9546,11 +8487,8 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H353" t="s">
-        <v>8</v>
+      <c r="G353" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -9572,11 +8510,8 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H354" t="s">
-        <v>8</v>
+      <c r="G354" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -9598,11 +8533,8 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H355" t="s">
-        <v>8</v>
+      <c r="G355" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -9624,11 +8556,8 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H356" t="s">
-        <v>8</v>
+      <c r="G356" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -9650,11 +8579,8 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H357" t="s">
-        <v>8</v>
+      <c r="G357" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -9676,11 +8602,8 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H358" t="s">
-        <v>8</v>
+      <c r="G358" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -9702,11 +8625,8 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H359" t="s">
-        <v>8</v>
+      <c r="G359" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -9728,11 +8648,8 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H360" t="s">
-        <v>8</v>
+      <c r="G360" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -9754,11 +8671,8 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H361" t="s">
-        <v>8</v>
+      <c r="G361" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -9780,11 +8694,8 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H362" t="s">
-        <v>8</v>
+      <c r="G362" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -9806,11 +8717,8 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H363" t="s">
-        <v>8</v>
+      <c r="G363" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -9832,11 +8740,8 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H364" t="s">
-        <v>8</v>
+      <c r="G364" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -9858,11 +8763,8 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H365" t="s">
-        <v>8</v>
+      <c r="G365" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -9884,11 +8786,8 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H366" t="s">
-        <v>8</v>
+      <c r="G366" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -9910,11 +8809,8 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H367" t="s">
-        <v>8</v>
+      <c r="G367" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -9936,11 +8832,8 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H368" t="s">
-        <v>8</v>
+      <c r="G368" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="369">
@@ -9962,11 +8855,8 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H369" t="s">
-        <v>8</v>
+      <c r="G369" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -9988,11 +8878,8 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H370" t="s">
-        <v>8</v>
+      <c r="G370" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -10014,11 +8901,8 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H371" t="s">
-        <v>8</v>
+      <c r="G371" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -10040,11 +8924,8 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H372" t="s">
-        <v>8</v>
+      <c r="G372" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="373">
@@ -10066,11 +8947,8 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H373" t="s">
-        <v>8</v>
+      <c r="G373" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -10092,11 +8970,8 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H374" t="s">
-        <v>8</v>
+      <c r="G374" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -10118,11 +8993,8 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H375" t="s">
-        <v>8</v>
+      <c r="G375" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -10144,11 +9016,8 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H376" t="s">
-        <v>8</v>
+      <c r="G376" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="377">
@@ -10170,11 +9039,8 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H377" t="s">
-        <v>8</v>
+      <c r="G377" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="378">
@@ -10196,11 +9062,8 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H378" t="s">
-        <v>8</v>
+      <c r="G378" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="379">
@@ -10222,11 +9085,8 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H379" t="s">
-        <v>8</v>
+      <c r="G379" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="380">
@@ -10248,11 +9108,8 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H380" t="s">
-        <v>8</v>
+      <c r="G380" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="381">
@@ -10274,11 +9131,8 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H381" t="s">
-        <v>8</v>
+      <c r="G381" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -10300,11 +9154,8 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H382" t="s">
-        <v>8</v>
+      <c r="G382" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -10326,11 +9177,8 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H383" t="s">
-        <v>8</v>
+      <c r="G383" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -10352,11 +9200,8 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H384" t="s">
-        <v>8</v>
+      <c r="G384" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -10378,11 +9223,8 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H385" t="s">
-        <v>8</v>
+      <c r="G385" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -10404,11 +9246,8 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H386" t="s">
-        <v>8</v>
+      <c r="G386" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -10430,11 +9269,8 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H387" t="s">
-        <v>8</v>
+      <c r="G387" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -10456,11 +9292,8 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H388" t="s">
-        <v>8</v>
+      <c r="G388" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -10482,11 +9315,8 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H389" t="s">
-        <v>8</v>
+      <c r="G389" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -10508,11 +9338,8 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H390" t="s">
-        <v>8</v>
+      <c r="G390" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -10534,11 +9361,8 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H391" t="s">
-        <v>8</v>
+      <c r="G391" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -10560,11 +9384,8 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H392" t="s">
-        <v>8</v>
+      <c r="G392" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -10586,11 +9407,8 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H393" t="s">
-        <v>8</v>
+      <c r="G393" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="394">
@@ -10612,11 +9430,8 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H394" t="s">
-        <v>8</v>
+      <c r="G394" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="395">
@@ -10638,11 +9453,8 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H395" t="s">
-        <v>8</v>
+      <c r="G395" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="396">
@@ -10664,11 +9476,8 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H396" t="s">
-        <v>8</v>
+      <c r="G396" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -10690,11 +9499,8 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H397" t="s">
-        <v>8</v>
+      <c r="G397" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="398">
@@ -10716,11 +9522,8 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H398" t="s">
-        <v>8</v>
+      <c r="G398" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -10742,11 +9545,8 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H399" t="s">
-        <v>8</v>
+      <c r="G399" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -10768,11 +9568,8 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H400" t="s">
-        <v>8</v>
+      <c r="G400" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="401">
@@ -10794,11 +9591,8 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H401" t="s">
-        <v>8</v>
+      <c r="G401" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -10820,11 +9614,8 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H402" t="s">
-        <v>8</v>
+      <c r="G402" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -10846,11 +9637,8 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H403" t="s">
-        <v>8</v>
+      <c r="G403" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="404">
@@ -10872,11 +9660,8 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H404" t="s">
-        <v>8</v>
+      <c r="G404" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -10898,11 +9683,8 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H405" t="s">
-        <v>8</v>
+      <c r="G405" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -10924,11 +9706,8 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H406" t="s">
-        <v>8</v>
+      <c r="G406" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -10950,11 +9729,8 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H407" t="s">
-        <v>8</v>
+      <c r="G407" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -10976,11 +9752,8 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H408" t="s">
-        <v>8</v>
+      <c r="G408" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="409">
@@ -11002,11 +9775,8 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H409" t="s">
-        <v>8</v>
+      <c r="G409" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -11028,11 +9798,8 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H410" t="s">
-        <v>8</v>
+      <c r="G410" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11054,11 +9821,8 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H411" t="s">
-        <v>8</v>
+      <c r="G411" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -11080,11 +9844,8 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H412" t="s">
-        <v>8</v>
+      <c r="G412" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -11106,11 +9867,8 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H413" t="s">
-        <v>8</v>
+      <c r="G413" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="414">
@@ -11132,11 +9890,8 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H414" t="s">
-        <v>8</v>
+      <c r="G414" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -11158,11 +9913,8 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H415" t="s">
-        <v>8</v>
+      <c r="G415" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="416">
@@ -11184,11 +9936,8 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H416" t="s">
-        <v>8</v>
+      <c r="G416" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -11210,11 +9959,8 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H417" t="s">
-        <v>8</v>
+      <c r="G417" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="418">
@@ -11236,11 +9982,8 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H418" t="s">
-        <v>8</v>
+      <c r="G418" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -11262,11 +10005,8 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H419" t="s">
-        <v>8</v>
+      <c r="G419" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -11288,11 +10028,8 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H420" t="s">
-        <v>8</v>
+      <c r="G420" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="421">
@@ -11314,11 +10051,8 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="n">
-        <v>0.018673000857234</v>
-      </c>
-      <c r="H421" t="s">
-        <v>8</v>
+      <c r="G421" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="422">
@@ -11340,11 +10074,8 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H422" t="s">
-        <v>8</v>
+      <c r="G422" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -11366,11 +10097,8 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H423" t="s">
-        <v>8</v>
+      <c r="G423" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -11392,11 +10120,8 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H424" t="s">
-        <v>8</v>
+      <c r="G424" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -11418,11 +10143,8 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H425" t="s">
-        <v>8</v>
+      <c r="G425" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -11444,11 +10166,8 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H426" t="s">
-        <v>8</v>
+      <c r="G426" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -11470,11 +10189,8 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H427" t="s">
-        <v>8</v>
+      <c r="G427" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -11496,11 +10212,8 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H428" t="s">
-        <v>8</v>
+      <c r="G428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429">
@@ -11522,11 +10235,8 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H429" t="s">
-        <v>8</v>
+      <c r="G429" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -11548,11 +10258,8 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H430" t="s">
-        <v>8</v>
+      <c r="G430" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -11574,11 +10281,8 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H431" t="s">
-        <v>8</v>
+      <c r="G431" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -11600,11 +10304,8 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H432" t="s">
-        <v>8</v>
+      <c r="G432" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="433">
@@ -11626,11 +10327,8 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H433" t="s">
-        <v>8</v>
+      <c r="G433" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="434">
@@ -11652,11 +10350,8 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H434" t="s">
-        <v>8</v>
+      <c r="G434" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="435">
@@ -11678,11 +10373,8 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H435" t="s">
-        <v>8</v>
+      <c r="G435" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -11704,11 +10396,8 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H436" t="s">
-        <v>8</v>
+      <c r="G436" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -11730,11 +10419,8 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H437" t="s">
-        <v>8</v>
+      <c r="G437" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="438">
@@ -11756,11 +10442,8 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H438" t="s">
-        <v>8</v>
+      <c r="G438" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -11782,11 +10465,8 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H439" t="s">
-        <v>8</v>
+      <c r="G439" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -11808,11 +10488,8 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H440" t="s">
-        <v>8</v>
+      <c r="G440" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="441">
@@ -11834,11 +10511,8 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H441" t="s">
-        <v>8</v>
+      <c r="G441" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -11860,11 +10534,8 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H442" t="s">
-        <v>8</v>
+      <c r="G442" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -11886,11 +10557,8 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H443" t="s">
-        <v>8</v>
+      <c r="G443" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="444">
@@ -11912,11 +10580,8 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H444" t="s">
-        <v>8</v>
+      <c r="G444" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="445">
@@ -11938,11 +10603,8 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H445" t="s">
-        <v>8</v>
+      <c r="G445" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="446">
@@ -11964,11 +10626,8 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H446" t="s">
-        <v>8</v>
+      <c r="G446" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="447">
@@ -11990,11 +10649,8 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H447" t="s">
-        <v>8</v>
+      <c r="G447" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -12016,11 +10672,8 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H448" t="s">
-        <v>8</v>
+      <c r="G448" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -12042,11 +10695,8 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H449" t="s">
-        <v>8</v>
+      <c r="G449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -12068,11 +10718,8 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H450" t="s">
-        <v>8</v>
+      <c r="G450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451">
@@ -12094,11 +10741,8 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H451" t="s">
-        <v>8</v>
+      <c r="G451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -12120,11 +10764,8 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H452" t="s">
-        <v>8</v>
+      <c r="G452" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -12146,11 +10787,8 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H453" t="s">
-        <v>8</v>
+      <c r="G453" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -12172,11 +10810,8 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H454" t="s">
-        <v>8</v>
+      <c r="G454" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -12198,11 +10833,8 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H455" t="s">
-        <v>8</v>
+      <c r="G455" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -12224,11 +10856,8 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H456" t="s">
-        <v>8</v>
+      <c r="G456" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -12250,11 +10879,8 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H457" t="s">
-        <v>8</v>
+      <c r="G457" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -12276,11 +10902,8 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H458" t="s">
-        <v>8</v>
+      <c r="G458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -12302,11 +10925,8 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H459" t="s">
-        <v>8</v>
+      <c r="G459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -12328,11 +10948,8 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H460" t="s">
-        <v>8</v>
+      <c r="G460" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -12354,11 +10971,8 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H461" t="s">
-        <v>8</v>
+      <c r="G461" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -12380,11 +10994,8 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H462" t="s">
-        <v>8</v>
+      <c r="G462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -12406,11 +11017,8 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H463" t="s">
-        <v>8</v>
+      <c r="G463" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -12432,11 +11040,8 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H464" t="s">
-        <v>8</v>
+      <c r="G464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -12458,11 +11063,8 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H465" t="s">
-        <v>8</v>
+      <c r="G465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -12484,11 +11086,8 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H466" t="s">
-        <v>8</v>
+      <c r="G466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -12510,11 +11109,8 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H467" t="s">
-        <v>8</v>
+      <c r="G467" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="468">
@@ -12536,11 +11132,8 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H468" t="s">
-        <v>8</v>
+      <c r="G468" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -12562,11 +11155,8 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H469" t="s">
-        <v>8</v>
+      <c r="G469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -12588,11 +11178,8 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H470" t="s">
-        <v>8</v>
+      <c r="G470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471">
@@ -12614,11 +11201,8 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H471" t="s">
-        <v>8</v>
+      <c r="G471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -12640,11 +11224,8 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H472" t="s">
-        <v>8</v>
+      <c r="G472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -12666,11 +11247,8 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H473" t="s">
-        <v>8</v>
+      <c r="G473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474">
@@ -12692,11 +11270,8 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H474" t="s">
-        <v>8</v>
+      <c r="G474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -12718,11 +11293,8 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H475" t="s">
-        <v>8</v>
+      <c r="G475" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="476">
@@ -12744,11 +11316,8 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H476" t="s">
-        <v>8</v>
+      <c r="G476" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="477">
@@ -12770,11 +11339,8 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H477" t="s">
-        <v>8</v>
+      <c r="G477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478">
@@ -12796,11 +11362,8 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H478" t="s">
-        <v>8</v>
+      <c r="G478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -12822,11 +11385,8 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H479" t="s">
-        <v>8</v>
+      <c r="G479" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="480">
@@ -12848,11 +11408,8 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H480" t="s">
-        <v>8</v>
+      <c r="G480" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="481">
@@ -12874,11 +11431,8 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H481" t="s">
-        <v>8</v>
+      <c r="G481" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -12900,11 +11454,8 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H482" t="s">
-        <v>8</v>
+      <c r="G482" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -12926,11 +11477,8 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H483" t="s">
-        <v>8</v>
+      <c r="G483" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -12952,11 +11500,8 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H484" t="s">
-        <v>8</v>
+      <c r="G484" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="485">
@@ -12978,11 +11523,8 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H485" t="s">
-        <v>8</v>
+      <c r="G485" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="486">
@@ -13004,11 +11546,8 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H486" t="s">
-        <v>8</v>
+      <c r="G486" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -13030,11 +11569,8 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H487" t="s">
-        <v>8</v>
+      <c r="G487" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="488">
@@ -13056,11 +11592,8 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H488" t="s">
-        <v>8</v>
+      <c r="G488" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -13082,11 +11615,8 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H489" t="s">
-        <v>8</v>
+      <c r="G489" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="490">
@@ -13108,11 +11638,8 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H490" t="s">
-        <v>8</v>
+      <c r="G490" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -13134,11 +11661,8 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H491" t="s">
-        <v>8</v>
+      <c r="G491" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -13160,11 +11684,8 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H492" t="s">
-        <v>8</v>
+      <c r="G492" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="493">
@@ -13186,11 +11707,8 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H493" t="s">
-        <v>8</v>
+      <c r="G493" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="494">
@@ -13212,11 +11730,8 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H494" t="s">
-        <v>8</v>
+      <c r="G494" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="495">
@@ -13238,11 +11753,8 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H495" t="s">
-        <v>8</v>
+      <c r="G495" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="496">
@@ -13264,11 +11776,8 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H496" t="s">
-        <v>8</v>
+      <c r="G496" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -13290,11 +11799,8 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H497" t="s">
-        <v>8</v>
+      <c r="G497" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -13316,11 +11822,8 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H498" t="s">
-        <v>8</v>
+      <c r="G498" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -13342,11 +11845,8 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H499" t="s">
-        <v>8</v>
+      <c r="G499" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -13368,11 +11868,8 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H500" t="s">
-        <v>8</v>
+      <c r="G500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -13394,11 +11891,8 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H501" t="s">
-        <v>8</v>
+      <c r="G501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -13420,11 +11914,8 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H502" t="s">
-        <v>8</v>
+      <c r="G502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -13446,11 +11937,8 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H503" t="s">
-        <v>8</v>
+      <c r="G503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -13472,11 +11960,8 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H504" t="s">
-        <v>8</v>
+      <c r="G504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505">
@@ -13498,11 +11983,8 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H505" t="s">
-        <v>8</v>
+      <c r="G505" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -13524,11 +12006,8 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="n">
-        <v>0.0154079999774694</v>
-      </c>
-      <c r="H506" t="s">
-        <v>8</v>
+      <c r="G506" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="507">
@@ -13550,11 +12029,8 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H507" t="s">
-        <v>8</v>
+      <c r="G507" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -13576,11 +12052,8 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H508" t="s">
-        <v>8</v>
+      <c r="G508" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -13602,11 +12075,8 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H509" t="s">
-        <v>8</v>
+      <c r="G509" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="510">
@@ -13628,11 +12098,8 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H510" t="s">
-        <v>8</v>
+      <c r="G510" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="511">
@@ -13654,11 +12121,8 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H511" t="s">
-        <v>8</v>
+      <c r="G511" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -13680,11 +12144,8 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H512" t="s">
-        <v>8</v>
+      <c r="G512" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="513">
@@ -13706,11 +12167,8 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H513" t="s">
-        <v>8</v>
+      <c r="G513" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -13732,11 +12190,8 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>8</v>
+      <c r="G514" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -13758,11 +12213,8 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H515" t="s">
-        <v>8</v>
+      <c r="G515" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -13784,11 +12236,8 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H516" t="s">
-        <v>8</v>
+      <c r="G516" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="517">
@@ -13810,11 +12259,8 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H517" t="s">
-        <v>8</v>
+      <c r="G517" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -13836,11 +12282,8 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H518" t="s">
-        <v>8</v>
+      <c r="G518" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -13862,11 +12305,8 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H519" t="s">
-        <v>8</v>
+      <c r="G519" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -13888,11 +12328,8 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H520" t="s">
-        <v>8</v>
+      <c r="G520" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -13914,11 +12351,8 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H521" t="s">
-        <v>8</v>
+      <c r="G521" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="522">
@@ -13940,11 +12374,8 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H522" t="s">
-        <v>8</v>
+      <c r="G522" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -13966,11 +12397,8 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H523" t="s">
-        <v>8</v>
+      <c r="G523" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -13992,11 +12420,8 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H524" t="s">
-        <v>8</v>
+      <c r="G524" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="525">
@@ -14018,11 +12443,8 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H525" t="s">
-        <v>8</v>
+      <c r="G525" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -14044,11 +12466,8 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H526" t="s">
-        <v>8</v>
+      <c r="G526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527">
@@ -14070,11 +12489,8 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H527" t="s">
-        <v>8</v>
+      <c r="G527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528">
@@ -14096,11 +12512,8 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H528" t="s">
-        <v>8</v>
+      <c r="G528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529">
@@ -14122,11 +12535,8 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H529" t="s">
-        <v>8</v>
+      <c r="G529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -14148,11 +12558,8 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H530" t="s">
-        <v>8</v>
+      <c r="G530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -14174,11 +12581,8 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H531" t="s">
-        <v>8</v>
+      <c r="G531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532">
@@ -14200,11 +12604,8 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H532" t="s">
-        <v>8</v>
+      <c r="G532" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="533">
@@ -14226,11 +12627,8 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H533" t="s">
-        <v>8</v>
+      <c r="G533" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -14252,11 +12650,8 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H534" t="s">
-        <v>8</v>
+      <c r="G534" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="535">
@@ -14278,11 +12673,8 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H535" t="s">
-        <v>8</v>
+      <c r="G535" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -14304,11 +12696,8 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H536" t="s">
-        <v>8</v>
+      <c r="G536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537">
@@ -14330,11 +12719,8 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H537" t="s">
-        <v>8</v>
+      <c r="G537" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="538">
@@ -14356,11 +12742,8 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H538" t="s">
-        <v>8</v>
+      <c r="G538" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="539">
@@ -14382,11 +12765,8 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H539" t="s">
-        <v>8</v>
+      <c r="G539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540">
@@ -14408,11 +12788,8 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H540" t="s">
-        <v>8</v>
+      <c r="G540" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -14434,11 +12811,8 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H541" t="s">
-        <v>8</v>
+      <c r="G541" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="542">
@@ -14460,11 +12834,8 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H542" t="s">
-        <v>8</v>
+      <c r="G542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -14486,11 +12857,8 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H543" t="s">
-        <v>8</v>
+      <c r="G543" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -14512,11 +12880,8 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H544" t="s">
-        <v>8</v>
+      <c r="G544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545">
@@ -14538,11 +12903,8 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H545" t="s">
-        <v>8</v>
+      <c r="G545" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="546">
@@ -14564,11 +12926,8 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H546" t="s">
-        <v>8</v>
+      <c r="G546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547">
@@ -14590,11 +12949,8 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H547" t="s">
-        <v>8</v>
+      <c r="G547" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="548">
@@ -14616,11 +12972,8 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H548" t="s">
-        <v>8</v>
+      <c r="G548" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -14642,11 +12995,8 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H549" t="s">
-        <v>8</v>
+      <c r="G549" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -14668,11 +13018,8 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H550" t="s">
-        <v>8</v>
+      <c r="G550" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -14694,11 +13041,8 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H551" t="s">
-        <v>8</v>
+      <c r="G551" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="552">
@@ -14720,11 +13064,8 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H552" t="s">
-        <v>8</v>
+      <c r="G552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -14746,11 +13087,8 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H553" t="s">
-        <v>8</v>
+      <c r="G553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -14772,11 +13110,8 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H554" t="s">
-        <v>8</v>
+      <c r="G554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -14798,11 +13133,8 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H555" t="s">
-        <v>8</v>
+      <c r="G555" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="556">
@@ -14824,11 +13156,8 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H556" t="s">
-        <v>8</v>
+      <c r="G556" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="557">
@@ -14850,11 +13179,8 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H557" t="s">
-        <v>8</v>
+      <c r="G557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -14876,11 +13202,8 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H558" t="s">
-        <v>8</v>
+      <c r="G558" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="559">
@@ -14902,11 +13225,8 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H559" t="s">
-        <v>8</v>
+      <c r="G559" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="560">
@@ -14928,11 +13248,8 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H560" t="s">
-        <v>8</v>
+      <c r="G560" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -14954,11 +13271,8 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H561" t="s">
-        <v>8</v>
+      <c r="G561" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="562">
@@ -14980,11 +13294,8 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H562" t="s">
-        <v>8</v>
+      <c r="G562" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="563">
@@ -15006,11 +13317,8 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H563" t="s">
-        <v>8</v>
+      <c r="G563" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="564">
@@ -15032,11 +13340,8 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H564" t="s">
-        <v>8</v>
+      <c r="G564" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -15058,11 +13363,8 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H565" t="s">
-        <v>8</v>
+      <c r="G565" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="566">
@@ -15084,11 +13386,8 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H566" t="s">
-        <v>8</v>
+      <c r="G566" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -15110,11 +13409,8 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H567" t="s">
-        <v>8</v>
+      <c r="G567" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="568">
@@ -15136,11 +13432,8 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H568" t="s">
-        <v>8</v>
+      <c r="G568" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -15162,11 +13455,8 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H569" t="s">
-        <v>8</v>
+      <c r="G569" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="570">
@@ -15188,11 +13478,8 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H570" t="s">
-        <v>8</v>
+      <c r="G570" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -15214,11 +13501,8 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H571" t="s">
-        <v>8</v>
+      <c r="G571" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="572">
@@ -15240,11 +13524,8 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H572" t="s">
-        <v>8</v>
+      <c r="G572" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -15266,11 +13547,8 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H573" t="s">
-        <v>8</v>
+      <c r="G573" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="574">
@@ -15292,11 +13570,8 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H574" t="s">
-        <v>8</v>
+      <c r="G574" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -15318,11 +13593,8 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H575" t="s">
-        <v>8</v>
+      <c r="G575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -15344,11 +13616,8 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H576" t="s">
-        <v>8</v>
+      <c r="G576" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -15370,11 +13639,8 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H577" t="s">
-        <v>8</v>
+      <c r="G577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -15396,11 +13662,8 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="n">
-        <v>0.0175000000745058</v>
-      </c>
-      <c r="H578" t="s">
-        <v>8</v>
+      <c r="G578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579">
@@ -15422,11 +13685,8 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H579" t="s">
-        <v>8</v>
+      <c r="G579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580">
@@ -15448,11 +13708,8 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H580" t="s">
-        <v>8</v>
+      <c r="G580" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="581">
@@ -15474,11 +13731,8 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H581" t="s">
-        <v>8</v>
+      <c r="G581" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="582">
@@ -15500,11 +13754,8 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H582" t="s">
-        <v>8</v>
+      <c r="G582" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -15526,11 +13777,8 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H583" t="s">
-        <v>8</v>
+      <c r="G583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -15552,11 +13800,8 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H584" t="s">
-        <v>8</v>
+      <c r="G584" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="585">
@@ -15578,11 +13823,8 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H585" t="s">
-        <v>8</v>
+      <c r="G585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586">
@@ -15604,11 +13846,8 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H586" t="s">
-        <v>8</v>
+      <c r="G586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -15630,11 +13869,8 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H587" t="s">
-        <v>8</v>
+      <c r="G587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588">
@@ -15656,11 +13892,8 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H588" t="s">
-        <v>8</v>
+      <c r="G588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589">
@@ -15682,11 +13915,8 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H589" t="s">
-        <v>8</v>
+      <c r="G589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590">
@@ -15708,11 +13938,8 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="n">
-        <v>0.0171000007539988</v>
-      </c>
-      <c r="H590" t="s">
-        <v>8</v>
+      <c r="G590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591">
@@ -15734,11 +13961,8 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H591" t="s">
-        <v>8</v>
+      <c r="G591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592">
@@ -15760,11 +13984,8 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H592" t="s">
-        <v>8</v>
+      <c r="G592" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="593">
@@ -15786,11 +14007,8 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H593" t="s">
-        <v>8</v>
+      <c r="G593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594">
@@ -15812,11 +14030,8 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="n">
-        <v>0.0215000007301569</v>
-      </c>
-      <c r="H594" t="s">
-        <v>8</v>
+      <c r="G594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595">
@@ -15838,11 +14053,8 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="n">
-        <v>0.0203000009059906</v>
-      </c>
-      <c r="H595" t="s">
-        <v>8</v>
+      <c r="G595" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="596">
@@ -15864,11 +14076,8 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H596" t="s">
-        <v>8</v>
+      <c r="G596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597">
@@ -15890,11 +14099,8 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H597" t="s">
-        <v>8</v>
+      <c r="G597" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="598">
@@ -15916,11 +14122,8 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H598" t="s">
-        <v>8</v>
+      <c r="G598" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="599">
@@ -15942,11 +14145,8 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H599" t="s">
-        <v>8</v>
+      <c r="G599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600">
@@ -15968,11 +14168,8 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="n">
-        <v>0.0183000005781651</v>
-      </c>
-      <c r="H600" t="s">
-        <v>8</v>
+      <c r="G600" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="601">
@@ -15994,11 +14191,8 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H601" t="s">
-        <v>8</v>
+      <c r="G601" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="602">
@@ -16020,11 +14214,8 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H602" t="s">
-        <v>8</v>
+      <c r="G602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603">
@@ -16046,11 +14237,8 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H603" t="s">
-        <v>8</v>
+      <c r="G603" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="604">
@@ -16072,11 +14260,8 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="n">
-        <v>0.0196000002324581</v>
-      </c>
-      <c r="H604" t="s">
-        <v>8</v>
+      <c r="G604" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="605">
@@ -16098,11 +14283,8 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="n">
-        <v>0.0192000009119511</v>
-      </c>
-      <c r="H605" t="s">
-        <v>8</v>
+      <c r="G605" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="606">
@@ -16124,11 +14306,8 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H606" t="s">
-        <v>8</v>
+      <c r="G606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607">
@@ -16150,11 +14329,8 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H607" t="s">
-        <v>8</v>
+      <c r="G607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608">
@@ -16176,11 +14352,8 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H608" t="s">
-        <v>8</v>
+      <c r="G608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609">
@@ -16202,11 +14375,8 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="n">
-        <v>0.0181000009179115</v>
-      </c>
-      <c r="H609" t="s">
-        <v>8</v>
+      <c r="G609" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="610">
@@ -16228,11 +14398,8 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H610" t="s">
-        <v>8</v>
+      <c r="G610" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="611">
@@ -16254,11 +14421,8 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H611" t="s">
-        <v>8</v>
+      <c r="G611" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="612">
@@ -16280,11 +14444,8 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H612" t="s">
-        <v>8</v>
+      <c r="G612" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="613">
@@ -16306,11 +14467,8 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H613" t="s">
-        <v>8</v>
+      <c r="G613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614">
@@ -16332,11 +14490,8 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H614" t="s">
-        <v>8</v>
+      <c r="G614" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -16358,11 +14513,8 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H615" t="s">
-        <v>8</v>
+      <c r="G615" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="616">
@@ -16384,11 +14536,8 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H616" t="s">
-        <v>8</v>
+      <c r="G616" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -16410,11 +14559,8 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H617" t="s">
-        <v>8</v>
+      <c r="G617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618">
@@ -16436,11 +14582,8 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H618" t="s">
-        <v>8</v>
+      <c r="G618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619">
@@ -16462,11 +14605,8 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H619" t="s">
-        <v>8</v>
+      <c r="G619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620">
@@ -16488,11 +14628,8 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H620" t="s">
-        <v>8</v>
+      <c r="G620" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="621">
@@ -16514,11 +14651,8 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H621" t="s">
-        <v>8</v>
+      <c r="G621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622">
@@ -16540,11 +14674,8 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H622" t="s">
-        <v>8</v>
+      <c r="G622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623">
@@ -16566,11 +14697,8 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H623" t="s">
-        <v>8</v>
+      <c r="G623" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="624">
@@ -16592,11 +14720,8 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H624" t="s">
-        <v>8</v>
+      <c r="G624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625">
@@ -16618,11 +14743,8 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H625" t="s">
-        <v>8</v>
+      <c r="G625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -16644,11 +14766,8 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H626" t="s">
-        <v>8</v>
+      <c r="G626" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="627">
@@ -16670,11 +14789,8 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H627" t="s">
-        <v>8</v>
+      <c r="G627" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="628">
@@ -16696,11 +14812,8 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H628" t="s">
-        <v>8</v>
+      <c r="G628" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="629">
@@ -16722,11 +14835,8 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H629" t="s">
-        <v>8</v>
+      <c r="G629" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="630">
@@ -16748,11 +14858,8 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H630" t="s">
-        <v>8</v>
+      <c r="G630" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -16774,11 +14881,8 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H631" t="s">
-        <v>8</v>
+      <c r="G631" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="632">
@@ -16800,11 +14904,8 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H632" t="s">
-        <v>8</v>
+      <c r="G632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633">
@@ -16826,11 +14927,8 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="n">
-        <v>0.0172000005841255</v>
-      </c>
-      <c r="H633" t="s">
-        <v>8</v>
+      <c r="G633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -16852,11 +14950,8 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H634" t="s">
-        <v>8</v>
+      <c r="G634" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -16878,11 +14973,8 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H635" t="s">
-        <v>8</v>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -16904,11 +14996,8 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H636" t="s">
-        <v>8</v>
+      <c r="G636" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="637">
@@ -16930,11 +15019,8 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H637" t="s">
-        <v>8</v>
+      <c r="G637" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="638">
@@ -16956,11 +15042,8 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H638" t="s">
-        <v>8</v>
+      <c r="G638" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="639">
@@ -16982,11 +15065,8 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H639" t="s">
-        <v>8</v>
+      <c r="G639" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="640">
@@ -17008,11 +15088,8 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H640" t="s">
-        <v>8</v>
+      <c r="G640" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="641">
@@ -17034,11 +15111,8 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H641" t="s">
-        <v>8</v>
+      <c r="G641" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -17060,11 +15134,8 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H642" t="s">
-        <v>8</v>
+      <c r="G642" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -17086,11 +15157,8 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H643" t="s">
-        <v>8</v>
+      <c r="G643" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="644">
@@ -17112,11 +15180,8 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H644" t="s">
-        <v>8</v>
+      <c r="G644" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -17138,11 +15203,8 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H645" t="s">
-        <v>8</v>
+      <c r="G645" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -17164,11 +15226,8 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H646" t="s">
-        <v>8</v>
+      <c r="G646" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="647">
@@ -17190,11 +15249,8 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H647" t="s">
-        <v>8</v>
+      <c r="G647" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -17216,11 +15272,8 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H648" t="s">
-        <v>8</v>
+      <c r="G648" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -17242,11 +15295,8 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H649" t="s">
-        <v>8</v>
+      <c r="G649" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="650">
@@ -17268,11 +15318,8 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H650" t="s">
-        <v>8</v>
+      <c r="G650" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="651">
@@ -17294,11 +15341,8 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H651" t="s">
-        <v>8</v>
+      <c r="G651" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="652">
@@ -17320,11 +15364,8 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H652" t="s">
-        <v>8</v>
+      <c r="G652" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="653">
@@ -17346,11 +15387,8 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H653" t="s">
-        <v>8</v>
+      <c r="G653" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -17372,11 +15410,8 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H654" t="s">
-        <v>8</v>
+      <c r="G654" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="655">
@@ -17398,11 +15433,8 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H655" t="s">
-        <v>8</v>
+      <c r="G655" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="656">
@@ -17424,11 +15456,8 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H656" t="s">
-        <v>8</v>
+      <c r="G656" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="657">
@@ -17450,11 +15479,8 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H657" t="s">
-        <v>8</v>
+      <c r="G657" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="658">
@@ -17476,11 +15502,8 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H658" t="s">
-        <v>8</v>
+      <c r="G658" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -17502,11 +15525,8 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H659" t="s">
-        <v>8</v>
+      <c r="G659" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -17528,11 +15548,8 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H660" t="s">
-        <v>8</v>
+      <c r="G660" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -17554,11 +15571,8 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H661" t="s">
-        <v>8</v>
+      <c r="G661" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="662">
@@ -17580,11 +15594,8 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H662" t="s">
-        <v>8</v>
+      <c r="G662" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="663">
@@ -17606,11 +15617,8 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H663" t="s">
-        <v>8</v>
+      <c r="G663" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="664">
@@ -17632,11 +15640,8 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H664" t="s">
-        <v>8</v>
+      <c r="G664" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="665">
@@ -17658,11 +15663,8 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H665" t="s">
-        <v>8</v>
+      <c r="G665" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="666">
@@ -17684,11 +15686,8 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H666" t="s">
-        <v>8</v>
+      <c r="G666" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="667">
@@ -17710,11 +15709,8 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H667" t="s">
-        <v>8</v>
+      <c r="G667" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="668">
@@ -17736,11 +15732,8 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H668" t="s">
-        <v>8</v>
+      <c r="G668" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="669">
@@ -17762,11 +15755,8 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H669" t="s">
-        <v>8</v>
+      <c r="G669" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -17788,37 +15778,31 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H670" t="s">
-        <v>8</v>
+      <c r="G670" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46283.2916666667</v>
       </c>
       <c r="B671" t="n">
-        <v>14495546</v>
+        <v>3578243</v>
       </c>
       <c r="C671" t="n">
-        <v>0.0206000003963709</v>
+        <v>0.0204000007361174</v>
       </c>
       <c r="D671" t="n">
-        <v>0.0196000002324581</v>
+        <v>0.0199999995529652</v>
       </c>
       <c r="E671" t="n">
-        <v>0.0199999995529652</v>
+        <v>0.0204000007361174</v>
       </c>
       <c r="F671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="G671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H671" t="s">
-        <v>8</v>
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="G671" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -394,6 +397,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -414,8 +420,11 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -437,8 +446,11 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +472,11 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -483,8 +498,11 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -506,8 +524,11 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -529,8 +550,11 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -552,8 +576,11 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -575,8 +602,11 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -598,8 +628,11 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -621,8 +654,11 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +680,11 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -667,8 +706,11 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -690,8 +732,11 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -713,8 +758,11 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -736,8 +784,11 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -759,8 +810,11 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -782,8 +836,11 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,8 +862,11 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -828,8 +888,11 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -851,8 +914,11 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -874,8 +940,11 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -897,8 +966,11 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -920,8 +992,11 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -943,8 +1018,11 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -966,8 +1044,11 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -989,8 +1070,11 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" t="n">
+        <v>0.019845999777317</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1012,8 +1096,11 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1035,8 +1122,11 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1058,8 +1148,11 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
+      <c r="G30" t="n">
+        <v>0.01923399977386</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1081,8 +1174,11 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1104,8 +1200,11 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1127,8 +1226,11 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1150,8 +1252,11 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1173,8 +1278,11 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1196,8 +1304,11 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1219,8 +1330,11 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1242,8 +1356,11 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1265,8 +1382,11 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1288,8 +1408,11 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1311,8 +1434,11 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1334,8 +1460,11 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="G42" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1357,8 +1486,11 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1380,8 +1512,11 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,8 +1538,11 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -1426,8 +1564,11 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1449,8 +1590,11 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1472,8 +1616,11 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1495,8 +1642,11 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1518,8 +1668,11 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1541,8 +1694,11 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1564,8 +1720,11 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1587,8 +1746,11 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -1610,8 +1772,11 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1633,8 +1798,11 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1656,8 +1824,11 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1679,8 +1850,11 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -1702,8 +1876,11 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1725,8 +1902,11 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1748,8 +1928,11 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="s">
-        <v>7</v>
+      <c r="G60" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1771,8 +1954,11 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="s">
-        <v>7</v>
+      <c r="G61" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1794,8 +1980,11 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="s">
-        <v>7</v>
+      <c r="G62" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1817,8 +2006,11 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1840,8 +2032,11 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1863,8 +2058,11 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1886,8 +2084,11 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1909,8 +2110,11 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1932,8 +2136,11 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -1955,8 +2162,11 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1978,8 +2188,11 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -2001,8 +2214,11 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2024,8 +2240,11 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2047,8 +2266,11 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -2070,8 +2292,11 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -2093,8 +2318,11 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -2116,8 +2344,11 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2139,8 +2370,11 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -2162,8 +2396,11 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -2185,8 +2422,11 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2208,8 +2448,11 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
+      <c r="G80" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -2231,8 +2474,11 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2254,8 +2500,11 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2277,8 +2526,11 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2300,8 +2552,11 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2323,8 +2578,11 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2346,8 +2604,11 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -2369,8 +2630,11 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -2392,8 +2656,11 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2415,8 +2682,11 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -2438,8 +2708,11 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2461,8 +2734,11 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2484,8 +2760,11 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2507,8 +2786,11 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2530,8 +2812,11 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2553,8 +2838,11 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2576,8 +2864,11 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2599,8 +2890,11 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="s">
-        <v>7</v>
+      <c r="G97" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2622,8 +2916,11 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="s">
-        <v>7</v>
+      <c r="G98" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -2645,8 +2942,11 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -2668,8 +2968,11 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -2691,8 +2994,11 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2714,8 +3020,11 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2737,8 +3046,11 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -2760,8 +3072,11 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -2783,8 +3098,11 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2806,8 +3124,11 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="s">
-        <v>7</v>
+      <c r="G106" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -2829,8 +3150,11 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -2852,8 +3176,11 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -2875,8 +3202,11 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2898,8 +3228,11 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -2921,8 +3254,11 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -2944,8 +3280,11 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -2967,8 +3306,11 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2990,8 +3332,11 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3013,8 +3358,11 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -3036,8 +3384,11 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -3059,8 +3410,11 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -3082,8 +3436,11 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3105,8 +3462,11 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -3128,8 +3488,11 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -3151,8 +3514,11 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="G121" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3174,8 +3540,11 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -3197,8 +3566,11 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H123" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3220,8 +3592,11 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -3243,8 +3618,11 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H125" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3266,8 +3644,11 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H126" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -3289,8 +3670,11 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H127" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3312,8 +3696,11 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H128" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -3335,8 +3722,11 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H129" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -3358,8 +3748,11 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H130" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -3381,8 +3774,11 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H131" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132">
@@ -3404,8 +3800,11 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H132" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -3427,8 +3826,11 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H133" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134">
@@ -3450,8 +3852,11 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -3473,8 +3878,11 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="s">
-        <v>7</v>
+      <c r="G135" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136">
@@ -3496,8 +3904,11 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="s">
-        <v>7</v>
+      <c r="G136" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137">
@@ -3519,8 +3930,11 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="s">
-        <v>7</v>
+      <c r="G137" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -3542,8 +3956,11 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3565,8 +3982,11 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140">
@@ -3588,8 +4008,11 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141">
@@ -3611,8 +4034,11 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -3634,8 +4060,11 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,8 +4086,11 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
@@ -3680,8 +4112,11 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -3703,8 +4138,11 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146">
@@ -3726,8 +4164,11 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3749,8 +4190,11 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148">
@@ -3772,8 +4216,11 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3795,8 +4242,11 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
+      <c r="G149" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150">
@@ -3818,8 +4268,11 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -3841,8 +4294,11 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
@@ -3864,8 +4320,11 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="s">
-        <v>7</v>
+      <c r="G152" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3887,8 +4346,11 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="s">
-        <v>7</v>
+      <c r="G153" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,8 +4372,11 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3933,8 +4398,11 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156">
@@ -3956,8 +4424,11 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -3979,8 +4450,11 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158">
@@ -4002,8 +4476,11 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -4025,8 +4502,11 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
+      <c r="G159" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -4048,8 +4528,11 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="s">
-        <v>7</v>
+      <c r="G160" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161">
@@ -4071,8 +4554,11 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="s">
-        <v>7</v>
+      <c r="G161" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162">
@@ -4094,8 +4580,11 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="s">
-        <v>7</v>
+      <c r="G162" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -4117,8 +4606,11 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="s">
-        <v>7</v>
+      <c r="G163" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -4140,8 +4632,11 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="s">
-        <v>7</v>
+      <c r="G164" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -4163,8 +4658,11 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="s">
-        <v>7</v>
+      <c r="G165" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -4186,8 +4684,11 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -4209,8 +4710,11 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -4232,8 +4736,11 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169">
@@ -4255,8 +4762,11 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4278,8 +4788,11 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H170" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -4301,8 +4814,11 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="s">
-        <v>7</v>
+      <c r="G171" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4324,8 +4840,11 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="s">
-        <v>7</v>
+      <c r="G172" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H172" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4347,8 +4866,11 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H173" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4370,8 +4892,11 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
+      <c r="G174" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H174" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -4393,8 +4918,11 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
+      <c r="G175" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H175" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176">
@@ -4416,8 +4944,11 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="s">
-        <v>7</v>
+      <c r="G176" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H176" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -4439,8 +4970,11 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="s">
-        <v>7</v>
+      <c r="G177" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H177" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -4462,8 +4996,11 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H178" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4485,8 +5022,11 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
+      <c r="G179" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H179" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4508,8 +5048,11 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="s">
-        <v>7</v>
+      <c r="G180" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H180" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
@@ -4531,8 +5074,11 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="s">
-        <v>7</v>
+      <c r="G181" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H181" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182">
@@ -4554,8 +5100,11 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="s">
-        <v>7</v>
+      <c r="G182" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H182" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183">
@@ -4577,8 +5126,11 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="s">
-        <v>7</v>
+      <c r="G183" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H183" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
@@ -4600,8 +5152,11 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="s">
-        <v>7</v>
+      <c r="G184" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185">
@@ -4623,8 +5178,11 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="s">
-        <v>7</v>
+      <c r="G185" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H185" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186">
@@ -4646,8 +5204,11 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="s">
-        <v>7</v>
+      <c r="G186" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H186" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187">
@@ -4669,8 +5230,11 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="s">
-        <v>7</v>
+      <c r="G187" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H187" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4692,8 +5256,11 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="s">
-        <v>7</v>
+      <c r="G188" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H188" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189">
@@ -4715,8 +5282,11 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="s">
-        <v>7</v>
+      <c r="G189" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H189" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4738,8 +5308,11 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="s">
-        <v>7</v>
+      <c r="G190" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H190" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4761,8 +5334,11 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="s">
-        <v>7</v>
+      <c r="G191" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H191" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -4784,8 +5360,11 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="s">
-        <v>7</v>
+      <c r="G192" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H192" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4807,8 +5386,11 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="s">
-        <v>7</v>
+      <c r="G193" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H193" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194">
@@ -4830,8 +5412,11 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="s">
-        <v>7</v>
+      <c r="G194" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H194" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195">
@@ -4853,8 +5438,11 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="s">
-        <v>7</v>
+      <c r="G195" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H195" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -4876,8 +5464,11 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="s">
-        <v>7</v>
+      <c r="G196" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H196" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -4899,8 +5490,11 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="s">
-        <v>7</v>
+      <c r="G197" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -4922,8 +5516,11 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="s">
-        <v>7</v>
+      <c r="G198" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H198" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199">
@@ -4945,8 +5542,11 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="s">
-        <v>7</v>
+      <c r="G199" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H199" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -4968,8 +5568,11 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="s">
-        <v>7</v>
+      <c r="G200" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H200" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201">
@@ -4991,8 +5594,11 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="s">
-        <v>7</v>
+      <c r="G201" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H201" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -5014,8 +5620,11 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="s">
-        <v>7</v>
+      <c r="G202" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H202" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -5037,8 +5646,11 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="s">
-        <v>7</v>
+      <c r="G203" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -5060,8 +5672,11 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="s">
-        <v>7</v>
+      <c r="G204" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H204" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -5083,8 +5698,11 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="s">
-        <v>7</v>
+      <c r="G205" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H205" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -5106,8 +5724,11 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="s">
-        <v>7</v>
+      <c r="G206" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H206" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207">
@@ -5129,8 +5750,11 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="s">
-        <v>7</v>
+      <c r="G207" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H207" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -5152,8 +5776,11 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="s">
-        <v>7</v>
+      <c r="G208" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H208" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209">
@@ -5175,8 +5802,11 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="s">
-        <v>7</v>
+      <c r="G209" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H209" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -5198,8 +5828,11 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="s">
-        <v>7</v>
+      <c r="G210" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H210" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5221,8 +5854,11 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="s">
-        <v>7</v>
+      <c r="G211" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H211" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -5244,8 +5880,11 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="s">
-        <v>7</v>
+      <c r="G212" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H212" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213">
@@ -5267,8 +5906,11 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="s">
-        <v>7</v>
+      <c r="G213" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H213" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214">
@@ -5290,8 +5932,11 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="s">
-        <v>7</v>
+      <c r="G214" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H214" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5313,8 +5958,11 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="s">
-        <v>7</v>
+      <c r="G215" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H215" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5336,8 +5984,11 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="s">
-        <v>7</v>
+      <c r="G216" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H216" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -5359,8 +6010,11 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="s">
-        <v>7</v>
+      <c r="G217" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H217" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5382,8 +6036,11 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="s">
-        <v>7</v>
+      <c r="G218" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H218" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -5405,8 +6062,11 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="s">
-        <v>7</v>
+      <c r="G219" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H219" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -5428,8 +6088,11 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="s">
-        <v>7</v>
+      <c r="G220" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H220" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -5451,8 +6114,11 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="s">
-        <v>7</v>
+      <c r="G221" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H221" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222">
@@ -5474,8 +6140,11 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="s">
-        <v>7</v>
+      <c r="G222" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H222" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -5497,8 +6166,11 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="s">
-        <v>7</v>
+      <c r="G223" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H223" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224">
@@ -5520,8 +6192,11 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="s">
-        <v>7</v>
+      <c r="G224" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H224" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225">
@@ -5543,8 +6218,11 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="s">
-        <v>7</v>
+      <c r="G225" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H225" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -5566,8 +6244,11 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="s">
-        <v>7</v>
+      <c r="G226" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H226" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5589,8 +6270,11 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="s">
-        <v>7</v>
+      <c r="G227" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H227" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5612,8 +6296,11 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="s">
-        <v>7</v>
+      <c r="G228" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H228" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229">
@@ -5635,8 +6322,11 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="s">
-        <v>7</v>
+      <c r="G229" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H229" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5658,8 +6348,11 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="s">
-        <v>7</v>
+      <c r="G230" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H230" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5681,8 +6374,11 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="s">
-        <v>7</v>
+      <c r="G231" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H231" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5704,8 +6400,11 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="s">
-        <v>7</v>
+      <c r="G232" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H232" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5727,8 +6426,11 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="s">
-        <v>7</v>
+      <c r="G233" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H233" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234">
@@ -5750,8 +6452,11 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="s">
-        <v>7</v>
+      <c r="G234" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H234" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -5773,8 +6478,11 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="s">
-        <v>7</v>
+      <c r="G235" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H235" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -5796,8 +6504,11 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="s">
-        <v>7</v>
+      <c r="G236" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H236" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -5819,8 +6530,11 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="s">
-        <v>7</v>
+      <c r="G237" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H237" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -5842,8 +6556,11 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="s">
-        <v>7</v>
+      <c r="G238" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H238" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239">
@@ -5865,8 +6582,11 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="s">
-        <v>7</v>
+      <c r="G239" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H239" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5888,8 +6608,11 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="s">
-        <v>7</v>
+      <c r="G240" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H240" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -5911,8 +6634,11 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="s">
-        <v>7</v>
+      <c r="G241" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H241" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -5934,8 +6660,11 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="s">
-        <v>7</v>
+      <c r="G242" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H242" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5957,8 +6686,11 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="s">
-        <v>7</v>
+      <c r="G243" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H243" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -5980,8 +6712,11 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="s">
-        <v>7</v>
+      <c r="G244" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H244" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -6003,8 +6738,11 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="s">
-        <v>7</v>
+      <c r="G245" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H245" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6026,8 +6764,11 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="s">
-        <v>7</v>
+      <c r="G246" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H246" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -6049,8 +6790,11 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="s">
-        <v>7</v>
+      <c r="G247" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H247" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -6072,8 +6816,11 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="s">
-        <v>7</v>
+      <c r="G248" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H248" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -6095,8 +6842,11 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="s">
-        <v>7</v>
+      <c r="G249" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H249" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -6118,8 +6868,11 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="s">
-        <v>7</v>
+      <c r="G250" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H250" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251">
@@ -6141,8 +6894,11 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="s">
-        <v>7</v>
+      <c r="G251" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H251" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6164,8 +6920,11 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="s">
-        <v>7</v>
+      <c r="G252" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H252" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6187,8 +6946,11 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="s">
-        <v>7</v>
+      <c r="G253" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H253" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6210,8 +6972,11 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="s">
-        <v>7</v>
+      <c r="G254" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H254" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6233,8 +6998,11 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="s">
-        <v>7</v>
+      <c r="G255" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6256,8 +7024,11 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="s">
-        <v>7</v>
+      <c r="G256" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257">
@@ -6279,8 +7050,11 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="s">
-        <v>7</v>
+      <c r="G257" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6302,8 +7076,11 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="s">
-        <v>7</v>
+      <c r="G258" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259">
@@ -6325,8 +7102,11 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="s">
-        <v>7</v>
+      <c r="G259" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H259" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260">
@@ -6348,8 +7128,11 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="s">
-        <v>7</v>
+      <c r="G260" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H260" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261">
@@ -6371,8 +7154,11 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="s">
-        <v>7</v>
+      <c r="G261" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H261" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -6394,8 +7180,11 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="s">
-        <v>7</v>
+      <c r="G262" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H262" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263">
@@ -6417,8 +7206,11 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="s">
-        <v>7</v>
+      <c r="G263" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H263" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264">
@@ -6440,8 +7232,11 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="s">
-        <v>7</v>
+      <c r="G264" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H264" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265">
@@ -6463,8 +7258,11 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="s">
-        <v>7</v>
+      <c r="G265" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H265" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -6486,8 +7284,11 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="s">
-        <v>7</v>
+      <c r="G266" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H266" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6509,8 +7310,11 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="s">
-        <v>7</v>
+      <c r="G267" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H267" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -6532,8 +7336,11 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="s">
-        <v>7</v>
+      <c r="G268" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H268" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -6555,8 +7362,11 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="s">
-        <v>7</v>
+      <c r="G269" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H269" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -6578,8 +7388,11 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="s">
-        <v>7</v>
+      <c r="G270" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H270" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271">
@@ -6601,8 +7414,11 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="s">
-        <v>7</v>
+      <c r="G271" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H271" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -6624,8 +7440,11 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="s">
-        <v>7</v>
+      <c r="G272" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H272" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -6647,8 +7466,11 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
+      <c r="G273" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H273" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6670,8 +7492,11 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="s">
-        <v>7</v>
+      <c r="G274" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H274" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -6693,8 +7518,11 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="s">
-        <v>7</v>
+      <c r="G275" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H275" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6716,8 +7544,11 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="s">
-        <v>7</v>
+      <c r="G276" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H276" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6739,8 +7570,11 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="s">
-        <v>7</v>
+      <c r="G277" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H277" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6762,8 +7596,11 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="s">
-        <v>7</v>
+      <c r="G278" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H278" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6785,8 +7622,11 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="s">
-        <v>7</v>
+      <c r="G279" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H279" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -6808,8 +7648,11 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="s">
-        <v>7</v>
+      <c r="G280" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H280" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -6831,8 +7674,11 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="s">
-        <v>7</v>
+      <c r="G281" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H281" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6854,8 +7700,11 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="s">
-        <v>7</v>
+      <c r="G282" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H282" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -6877,8 +7726,11 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="s">
-        <v>7</v>
+      <c r="G283" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H283" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284">
@@ -6900,8 +7752,11 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="s">
-        <v>7</v>
+      <c r="G284" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H284" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -6923,8 +7778,11 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="s">
-        <v>7</v>
+      <c r="G285" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H285" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6946,8 +7804,11 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="s">
-        <v>7</v>
+      <c r="G286" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H286" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6969,8 +7830,11 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="s">
-        <v>7</v>
+      <c r="G287" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H287" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6992,8 +7856,11 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="s">
-        <v>7</v>
+      <c r="G288" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H288" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -7015,8 +7882,11 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="s">
-        <v>7</v>
+      <c r="G289" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H289" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -7038,8 +7908,11 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="s">
-        <v>7</v>
+      <c r="G290" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H290" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7061,8 +7934,11 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="s">
-        <v>7</v>
+      <c r="G291" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H291" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -7084,8 +7960,11 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="s">
-        <v>7</v>
+      <c r="G292" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H292" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -7107,8 +7986,11 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="s">
-        <v>7</v>
+      <c r="G293" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H293" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -7130,8 +8012,11 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="s">
-        <v>7</v>
+      <c r="G294" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H294" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295">
@@ -7153,8 +8038,11 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="s">
-        <v>7</v>
+      <c r="G295" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H295" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -7176,8 +8064,11 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="s">
-        <v>7</v>
+      <c r="G296" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H296" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -7199,8 +8090,11 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="s">
-        <v>7</v>
+      <c r="G297" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H297" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -7222,8 +8116,11 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="s">
-        <v>7</v>
+      <c r="G298" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -7245,8 +8142,11 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="s">
-        <v>7</v>
+      <c r="G299" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H299" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -7268,8 +8168,11 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="s">
-        <v>7</v>
+      <c r="G300" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H300" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -7291,8 +8194,11 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="s">
-        <v>7</v>
+      <c r="G301" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H301" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7314,8 +8220,11 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="s">
-        <v>7</v>
+      <c r="G302" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H302" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -7337,8 +8246,11 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="s">
-        <v>7</v>
+      <c r="G303" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H303" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7360,8 +8272,11 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="s">
-        <v>7</v>
+      <c r="G304" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H304" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305">
@@ -7383,8 +8298,11 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="s">
-        <v>7</v>
+      <c r="G305" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H305" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -7406,8 +8324,11 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="s">
-        <v>7</v>
+      <c r="G306" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H306" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307">
@@ -7429,8 +8350,11 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="s">
-        <v>7</v>
+      <c r="G307" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H307" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308">
@@ -7452,8 +8376,11 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="s">
-        <v>7</v>
+      <c r="G308" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H308" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309">
@@ -7475,8 +8402,11 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="s">
-        <v>7</v>
+      <c r="G309" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H309" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310">
@@ -7498,8 +8428,11 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="s">
-        <v>7</v>
+      <c r="G310" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H310" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -7521,8 +8454,11 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="s">
-        <v>7</v>
+      <c r="G311" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H311" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -7544,8 +8480,11 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="s">
-        <v>7</v>
+      <c r="G312" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H312" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -7567,8 +8506,11 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="s">
-        <v>7</v>
+      <c r="G313" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H313" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7590,8 +8532,11 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="s">
-        <v>7</v>
+      <c r="G314" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H314" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315">
@@ -7613,8 +8558,11 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="s">
-        <v>7</v>
+      <c r="G315" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H315" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -7636,8 +8584,11 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="s">
-        <v>7</v>
+      <c r="G316" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H316" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -7659,8 +8610,11 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="s">
-        <v>7</v>
+      <c r="G317" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H317" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7682,8 +8636,11 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="s">
-        <v>7</v>
+      <c r="G318" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H318" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319">
@@ -7705,8 +8662,11 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="s">
-        <v>7</v>
+      <c r="G319" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H319" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -7728,8 +8688,11 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="s">
-        <v>7</v>
+      <c r="G320" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H320" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -7751,8 +8714,11 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="s">
-        <v>7</v>
+      <c r="G321" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H321" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -7774,8 +8740,11 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="s">
-        <v>7</v>
+      <c r="G322" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H322" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -7797,8 +8766,11 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="s">
-        <v>7</v>
+      <c r="G323" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H323" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7820,8 +8792,11 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="s">
-        <v>7</v>
+      <c r="G324" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H324" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7843,8 +8818,11 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="s">
-        <v>7</v>
+      <c r="G325" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H325" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -7866,8 +8844,11 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="s">
-        <v>7</v>
+      <c r="G326" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H326" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327">
@@ -7889,8 +8870,11 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="s">
-        <v>7</v>
+      <c r="G327" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H327" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7912,8 +8896,11 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="s">
-        <v>7</v>
+      <c r="G328" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H328" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329">
@@ -7935,8 +8922,11 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="s">
-        <v>7</v>
+      <c r="G329" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H329" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7958,8 +8948,11 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="s">
-        <v>7</v>
+      <c r="G330" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H330" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -7981,8 +8974,11 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="s">
-        <v>7</v>
+      <c r="G331" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332">
@@ -8004,8 +9000,11 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="s">
-        <v>7</v>
+      <c r="G332" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H332" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8027,8 +9026,11 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="s">
-        <v>7</v>
+      <c r="G333" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H333" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -8050,8 +9052,11 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="s">
-        <v>7</v>
+      <c r="G334" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H334" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -8073,8 +9078,11 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="s">
-        <v>7</v>
+      <c r="G335" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H335" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -8096,8 +9104,11 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="s">
-        <v>7</v>
+      <c r="G336" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H336" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8119,8 +9130,11 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="s">
-        <v>7</v>
+      <c r="G337" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H337" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338">
@@ -8142,8 +9156,11 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="s">
-        <v>7</v>
+      <c r="G338" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H338" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339">
@@ -8165,8 +9182,11 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="s">
-        <v>7</v>
+      <c r="G339" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H339" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -8188,8 +9208,11 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="s">
-        <v>7</v>
+      <c r="G340" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H340" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -8211,8 +9234,11 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="s">
-        <v>7</v>
+      <c r="G341" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H341" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342">
@@ -8234,8 +9260,11 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="s">
-        <v>7</v>
+      <c r="G342" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H342" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343">
@@ -8257,8 +9286,11 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="s">
-        <v>7</v>
+      <c r="G343" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H343" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344">
@@ -8280,8 +9312,11 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="s">
-        <v>7</v>
+      <c r="G344" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H344" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -8303,8 +9338,11 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="s">
-        <v>7</v>
+      <c r="G345" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H345" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -8326,8 +9364,11 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="s">
-        <v>7</v>
+      <c r="G346" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H346" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -8349,8 +9390,11 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="s">
-        <v>7</v>
+      <c r="G347" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H347" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348">
@@ -8372,8 +9416,11 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="s">
-        <v>7</v>
+      <c r="G348" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H348" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349">
@@ -8395,8 +9442,11 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="s">
-        <v>7</v>
+      <c r="G349" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H349" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -8418,8 +9468,11 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="s">
-        <v>7</v>
+      <c r="G350" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H350" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351">
@@ -8441,8 +9494,11 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="s">
-        <v>7</v>
+      <c r="G351" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H351" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8464,8 +9520,11 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="s">
-        <v>7</v>
+      <c r="G352" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H352" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -8487,8 +9546,11 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="s">
-        <v>7</v>
+      <c r="G353" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H353" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354">
@@ -8510,8 +9572,11 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="s">
-        <v>7</v>
+      <c r="G354" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H354" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8533,8 +9598,11 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="s">
-        <v>7</v>
+      <c r="G355" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H355" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -8556,8 +9624,11 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="s">
-        <v>7</v>
+      <c r="G356" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H356" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8579,8 +9650,11 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="s">
-        <v>7</v>
+      <c r="G357" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H357" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -8602,8 +9676,11 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="s">
-        <v>7</v>
+      <c r="G358" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H358" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359">
@@ -8625,8 +9702,11 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="s">
-        <v>7</v>
+      <c r="G359" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H359" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8648,8 +9728,11 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="s">
-        <v>7</v>
+      <c r="G360" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H360" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361">
@@ -8671,8 +9754,11 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="s">
-        <v>7</v>
+      <c r="G361" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H361" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362">
@@ -8694,8 +9780,11 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="s">
-        <v>7</v>
+      <c r="G362" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H362" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -8717,8 +9806,11 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="s">
-        <v>7</v>
+      <c r="G363" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H363" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8740,8 +9832,11 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="s">
-        <v>7</v>
+      <c r="G364" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H364" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8763,8 +9858,11 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="s">
-        <v>7</v>
+      <c r="G365" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H365" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8786,8 +9884,11 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="s">
-        <v>7</v>
+      <c r="G366" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H366" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8809,8 +9910,11 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="s">
-        <v>7</v>
+      <c r="G367" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H367" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8832,8 +9936,11 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="s">
-        <v>7</v>
+      <c r="G368" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H368" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -8855,8 +9962,11 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="s">
-        <v>7</v>
+      <c r="G369" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H369" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8878,8 +9988,11 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="s">
-        <v>7</v>
+      <c r="G370" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H370" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8901,8 +10014,11 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="s">
-        <v>7</v>
+      <c r="G371" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H371" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8924,8 +10040,11 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="s">
-        <v>7</v>
+      <c r="G372" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H372" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -8947,8 +10066,11 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="s">
-        <v>7</v>
+      <c r="G373" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H373" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8970,8 +10092,11 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="s">
-        <v>7</v>
+      <c r="G374" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H374" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8993,8 +10118,11 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="s">
-        <v>7</v>
+      <c r="G375" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H375" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -9016,8 +10144,11 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="s">
-        <v>7</v>
+      <c r="G376" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H376" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -9039,8 +10170,11 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="s">
-        <v>7</v>
+      <c r="G377" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H377" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -9062,8 +10196,11 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="s">
-        <v>7</v>
+      <c r="G378" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H378" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -9085,8 +10222,11 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="s">
-        <v>7</v>
+      <c r="G379" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H379" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -9108,8 +10248,11 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="s">
-        <v>7</v>
+      <c r="G380" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H380" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -9131,8 +10274,11 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="s">
-        <v>7</v>
+      <c r="G381" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H381" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -9154,8 +10300,11 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="s">
-        <v>7</v>
+      <c r="G382" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H382" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -9177,8 +10326,11 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="s">
-        <v>7</v>
+      <c r="G383" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H383" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -9200,8 +10352,11 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="s">
-        <v>7</v>
+      <c r="G384" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H384" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -9223,8 +10378,11 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="s">
-        <v>7</v>
+      <c r="G385" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H385" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -9246,8 +10404,11 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="s">
-        <v>7</v>
+      <c r="G386" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H386" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -9269,8 +10430,11 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="s">
-        <v>7</v>
+      <c r="G387" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H387" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -9292,8 +10456,11 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="s">
-        <v>7</v>
+      <c r="G388" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H388" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -9315,8 +10482,11 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="s">
-        <v>7</v>
+      <c r="G389" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H389" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -9338,8 +10508,11 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="s">
-        <v>7</v>
+      <c r="G390" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H390" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -9361,8 +10534,11 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="s">
-        <v>7</v>
+      <c r="G391" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H391" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -9384,8 +10560,11 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="s">
-        <v>7</v>
+      <c r="G392" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H392" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -9407,8 +10586,11 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="s">
-        <v>7</v>
+      <c r="G393" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H393" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -9430,8 +10612,11 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="s">
-        <v>7</v>
+      <c r="G394" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H394" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -9453,8 +10638,11 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="s">
-        <v>7</v>
+      <c r="G395" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H395" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -9476,8 +10664,11 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="s">
-        <v>7</v>
+      <c r="G396" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H396" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -9499,8 +10690,11 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="s">
-        <v>7</v>
+      <c r="G397" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H397" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -9522,8 +10716,11 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="s">
-        <v>7</v>
+      <c r="G398" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H398" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -9545,8 +10742,11 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="s">
-        <v>7</v>
+      <c r="G399" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H399" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -9568,8 +10768,11 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="s">
-        <v>7</v>
+      <c r="G400" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H400" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -9591,8 +10794,11 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="s">
-        <v>7</v>
+      <c r="G401" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H401" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -9614,8 +10820,11 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="s">
-        <v>7</v>
+      <c r="G402" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H402" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9637,8 +10846,11 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="s">
-        <v>7</v>
+      <c r="G403" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H403" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9660,8 +10872,11 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="s">
-        <v>7</v>
+      <c r="G404" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H404" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -9683,8 +10898,11 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="s">
-        <v>7</v>
+      <c r="G405" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H405" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9706,8 +10924,11 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="s">
-        <v>7</v>
+      <c r="G406" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H406" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -9729,8 +10950,11 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="s">
-        <v>7</v>
+      <c r="G407" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H407" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9752,8 +10976,11 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="s">
-        <v>7</v>
+      <c r="G408" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H408" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -9775,8 +11002,11 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="s">
-        <v>7</v>
+      <c r="G409" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H409" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9798,8 +11028,11 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="s">
-        <v>7</v>
+      <c r="G410" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H410" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9821,8 +11054,11 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="s">
-        <v>7</v>
+      <c r="G411" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H411" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9844,8 +11080,11 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="s">
-        <v>7</v>
+      <c r="G412" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H412" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9867,8 +11106,11 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="s">
-        <v>7</v>
+      <c r="G413" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H413" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -9890,8 +11132,11 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="s">
-        <v>7</v>
+      <c r="G414" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H414" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9913,8 +11158,11 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="s">
-        <v>7</v>
+      <c r="G415" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H415" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9936,8 +11184,11 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="s">
-        <v>7</v>
+      <c r="G416" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H416" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -9959,8 +11210,11 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="s">
-        <v>7</v>
+      <c r="G417" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H417" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -9982,8 +11236,11 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="s">
-        <v>7</v>
+      <c r="G418" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H418" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -10005,8 +11262,11 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="s">
-        <v>7</v>
+      <c r="G419" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H419" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -10028,8 +11288,11 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="s">
-        <v>7</v>
+      <c r="G420" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H420" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -10051,8 +11314,11 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="s">
-        <v>7</v>
+      <c r="G421" t="n">
+        <v>0.018673000857234</v>
+      </c>
+      <c r="H421" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -10074,8 +11340,11 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="s">
-        <v>7</v>
+      <c r="G422" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H422" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -10097,8 +11366,11 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="s">
-        <v>7</v>
+      <c r="G423" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H423" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -10120,8 +11392,11 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="s">
-        <v>7</v>
+      <c r="G424" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H424" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -10143,8 +11418,11 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="s">
-        <v>7</v>
+      <c r="G425" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H425" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -10166,8 +11444,11 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="s">
-        <v>7</v>
+      <c r="G426" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H426" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -10189,8 +11470,11 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="s">
-        <v>7</v>
+      <c r="G427" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H427" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -10212,8 +11496,11 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="s">
-        <v>7</v>
+      <c r="G428" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H428" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -10235,8 +11522,11 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="s">
-        <v>7</v>
+      <c r="G429" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H429" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -10258,8 +11548,11 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="s">
-        <v>7</v>
+      <c r="G430" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H430" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -10281,8 +11574,11 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="s">
-        <v>7</v>
+      <c r="G431" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H431" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -10304,8 +11600,11 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="s">
-        <v>7</v>
+      <c r="G432" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H432" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -10327,8 +11626,11 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="s">
-        <v>7</v>
+      <c r="G433" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H433" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -10350,8 +11652,11 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="s">
-        <v>7</v>
+      <c r="G434" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H434" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -10373,8 +11678,11 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="s">
-        <v>7</v>
+      <c r="G435" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H435" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -10396,8 +11704,11 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="s">
-        <v>7</v>
+      <c r="G436" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H436" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -10419,8 +11730,11 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="s">
-        <v>7</v>
+      <c r="G437" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H437" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -10442,8 +11756,11 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="s">
-        <v>7</v>
+      <c r="G438" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H438" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -10465,8 +11782,11 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="s">
-        <v>7</v>
+      <c r="G439" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H439" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -10488,8 +11808,11 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="s">
-        <v>7</v>
+      <c r="G440" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H440" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -10511,8 +11834,11 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="s">
-        <v>7</v>
+      <c r="G441" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H441" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -10534,8 +11860,11 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="s">
-        <v>7</v>
+      <c r="G442" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H442" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -10557,8 +11886,11 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="s">
-        <v>7</v>
+      <c r="G443" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H443" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -10580,8 +11912,11 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="s">
-        <v>7</v>
+      <c r="G444" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H444" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -10603,8 +11938,11 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="s">
-        <v>7</v>
+      <c r="G445" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H445" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -10626,8 +11964,11 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="s">
-        <v>7</v>
+      <c r="G446" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H446" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -10649,8 +11990,11 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="s">
-        <v>7</v>
+      <c r="G447" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H447" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -10672,8 +12016,11 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="s">
-        <v>7</v>
+      <c r="G448" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H448" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -10695,8 +12042,11 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="s">
-        <v>7</v>
+      <c r="G449" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H449" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -10718,8 +12068,11 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="s">
-        <v>7</v>
+      <c r="G450" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H450" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -10741,8 +12094,11 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="s">
-        <v>7</v>
+      <c r="G451" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H451" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10764,8 +12120,11 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="s">
-        <v>7</v>
+      <c r="G452" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H452" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10787,8 +12146,11 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="s">
-        <v>7</v>
+      <c r="G453" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H453" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -10810,8 +12172,11 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="s">
-        <v>7</v>
+      <c r="G454" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H454" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10833,8 +12198,11 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="s">
-        <v>7</v>
+      <c r="G455" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H455" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10856,8 +12224,11 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="s">
-        <v>7</v>
+      <c r="G456" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H456" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10879,8 +12250,11 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="s">
-        <v>7</v>
+      <c r="G457" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H457" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -10902,8 +12276,11 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="s">
-        <v>7</v>
+      <c r="G458" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H458" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -10925,8 +12302,11 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="s">
-        <v>7</v>
+      <c r="G459" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H459" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -10948,8 +12328,11 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="s">
-        <v>7</v>
+      <c r="G460" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H460" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -10971,8 +12354,11 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="s">
-        <v>7</v>
+      <c r="G461" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H461" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10994,8 +12380,11 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="s">
-        <v>7</v>
+      <c r="G462" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H462" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -11017,8 +12406,11 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="s">
-        <v>7</v>
+      <c r="G463" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H463" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -11040,8 +12432,11 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="s">
-        <v>7</v>
+      <c r="G464" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H464" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -11063,8 +12458,11 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="s">
-        <v>7</v>
+      <c r="G465" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H465" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -11086,8 +12484,11 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="s">
-        <v>7</v>
+      <c r="G466" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H466" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -11109,8 +12510,11 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="s">
-        <v>7</v>
+      <c r="G467" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H467" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -11132,8 +12536,11 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="s">
-        <v>7</v>
+      <c r="G468" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H468" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -11155,8 +12562,11 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="s">
-        <v>7</v>
+      <c r="G469" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -11178,8 +12588,11 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="s">
-        <v>7</v>
+      <c r="G470" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H470" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -11201,8 +12614,11 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="s">
-        <v>7</v>
+      <c r="G471" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H471" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -11224,8 +12640,11 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="s">
-        <v>7</v>
+      <c r="G472" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H472" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -11247,8 +12666,11 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="s">
-        <v>7</v>
+      <c r="G473" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H473" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -11270,8 +12692,11 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="s">
-        <v>7</v>
+      <c r="G474" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H474" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -11293,8 +12718,11 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="s">
-        <v>7</v>
+      <c r="G475" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H475" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -11316,8 +12744,11 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="s">
-        <v>7</v>
+      <c r="G476" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H476" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -11339,8 +12770,11 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="s">
-        <v>7</v>
+      <c r="G477" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H477" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -11362,8 +12796,11 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="s">
-        <v>7</v>
+      <c r="G478" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H478" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -11385,8 +12822,11 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="s">
-        <v>7</v>
+      <c r="G479" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H479" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -11408,8 +12848,11 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="s">
-        <v>7</v>
+      <c r="G480" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H480" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -11431,8 +12874,11 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="s">
-        <v>7</v>
+      <c r="G481" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H481" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -11454,8 +12900,11 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="s">
-        <v>7</v>
+      <c r="G482" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H482" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -11477,8 +12926,11 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="s">
-        <v>7</v>
+      <c r="G483" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H483" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -11500,8 +12952,11 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="s">
-        <v>7</v>
+      <c r="G484" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H484" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -11523,8 +12978,11 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="s">
-        <v>7</v>
+      <c r="G485" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H485" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -11546,8 +13004,11 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="s">
-        <v>7</v>
+      <c r="G486" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H486" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -11569,8 +13030,11 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="s">
-        <v>7</v>
+      <c r="G487" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H487" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="488">
@@ -11592,8 +13056,11 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="s">
-        <v>7</v>
+      <c r="G488" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H488" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -11615,8 +13082,11 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="s">
-        <v>7</v>
+      <c r="G489" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H489" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -11638,8 +13108,11 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="s">
-        <v>7</v>
+      <c r="G490" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H490" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -11661,8 +13134,11 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="s">
-        <v>7</v>
+      <c r="G491" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H491" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -11684,8 +13160,11 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="s">
-        <v>7</v>
+      <c r="G492" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H492" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -11707,8 +13186,11 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="s">
-        <v>7</v>
+      <c r="G493" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H493" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -11730,8 +13212,11 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="s">
-        <v>7</v>
+      <c r="G494" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H494" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -11753,8 +13238,11 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="s">
-        <v>7</v>
+      <c r="G495" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H495" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="496">
@@ -11776,8 +13264,11 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="s">
-        <v>7</v>
+      <c r="G496" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H496" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -11799,8 +13290,11 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="s">
-        <v>7</v>
+      <c r="G497" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H497" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="498">
@@ -11822,8 +13316,11 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="s">
-        <v>7</v>
+      <c r="G498" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H498" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="499">
@@ -11845,8 +13342,11 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="s">
-        <v>7</v>
+      <c r="G499" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H499" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="500">
@@ -11868,8 +13368,11 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="s">
-        <v>7</v>
+      <c r="G500" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H500" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="501">
@@ -11891,8 +13394,11 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="s">
-        <v>7</v>
+      <c r="G501" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H501" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="502">
@@ -11914,8 +13420,11 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="s">
-        <v>7</v>
+      <c r="G502" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H502" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="503">
@@ -11937,8 +13446,11 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="s">
-        <v>7</v>
+      <c r="G503" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H503" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="504">
@@ -11960,8 +13472,11 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="s">
-        <v>7</v>
+      <c r="G504" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H504" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11983,8 +13498,11 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="s">
-        <v>7</v>
+      <c r="G505" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H505" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -12006,8 +13524,11 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="s">
-        <v>7</v>
+      <c r="G506" t="n">
+        <v>0.0154079999774694</v>
+      </c>
+      <c r="H506" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="507">
@@ -12029,8 +13550,11 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="s">
-        <v>7</v>
+      <c r="G507" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H507" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="508">
@@ -12052,8 +13576,11 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="s">
-        <v>7</v>
+      <c r="G508" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H508" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -12075,8 +13602,11 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="s">
-        <v>7</v>
+      <c r="G509" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H509" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -12098,8 +13628,11 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="s">
-        <v>7</v>
+      <c r="G510" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H510" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="511">
@@ -12121,8 +13654,11 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="s">
-        <v>7</v>
+      <c r="G511" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H511" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="512">
@@ -12144,8 +13680,11 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="s">
-        <v>7</v>
+      <c r="G512" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H512" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -12167,8 +13706,11 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="s">
-        <v>7</v>
+      <c r="G513" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H513" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -12190,8 +13732,11 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="s">
-        <v>7</v>
+      <c r="G514" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H514" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="515">
@@ -12213,8 +13758,11 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="s">
-        <v>7</v>
+      <c r="G515" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H515" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="516">
@@ -12236,8 +13784,11 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="s">
-        <v>7</v>
+      <c r="G516" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H516" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="517">
@@ -12259,8 +13810,11 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="s">
-        <v>7</v>
+      <c r="G517" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H517" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="518">
@@ -12282,8 +13836,11 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="s">
-        <v>7</v>
+      <c r="G518" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H518" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="519">
@@ -12305,8 +13862,11 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="s">
-        <v>7</v>
+      <c r="G519" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H519" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -12328,8 +13888,11 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="s">
-        <v>7</v>
+      <c r="G520" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H520" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="521">
@@ -12351,8 +13914,11 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="s">
-        <v>7</v>
+      <c r="G521" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H521" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="522">
@@ -12374,8 +13940,11 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="s">
-        <v>7</v>
+      <c r="G522" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H522" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="523">
@@ -12397,8 +13966,11 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="s">
-        <v>7</v>
+      <c r="G523" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H523" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="524">
@@ -12420,8 +13992,11 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="s">
-        <v>7</v>
+      <c r="G524" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H524" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="525">
@@ -12443,8 +14018,11 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="s">
-        <v>7</v>
+      <c r="G525" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H525" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -12466,8 +14044,11 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="s">
-        <v>7</v>
+      <c r="G526" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H526" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="527">
@@ -12489,8 +14070,11 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="s">
-        <v>7</v>
+      <c r="G527" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H527" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="528">
@@ -12512,8 +14096,11 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="s">
-        <v>7</v>
+      <c r="G528" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H528" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="529">
@@ -12535,8 +14122,11 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="s">
-        <v>7</v>
+      <c r="G529" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H529" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="530">
@@ -12558,8 +14148,11 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="s">
-        <v>7</v>
+      <c r="G530" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H530" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -12581,8 +14174,11 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="s">
-        <v>7</v>
+      <c r="G531" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H531" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -12604,8 +14200,11 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="s">
-        <v>7</v>
+      <c r="G532" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H532" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="533">
@@ -12627,8 +14226,11 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="s">
-        <v>7</v>
+      <c r="G533" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H533" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="534">
@@ -12650,8 +14252,11 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="s">
-        <v>7</v>
+      <c r="G534" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H534" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="535">
@@ -12673,8 +14278,11 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="s">
-        <v>7</v>
+      <c r="G535" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H535" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="536">
@@ -12696,8 +14304,11 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="s">
-        <v>7</v>
+      <c r="G536" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H536" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -12719,8 +14330,11 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="s">
-        <v>7</v>
+      <c r="G537" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H537" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="538">
@@ -12742,8 +14356,11 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="s">
-        <v>7</v>
+      <c r="G538" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H538" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="539">
@@ -12765,8 +14382,11 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="s">
-        <v>7</v>
+      <c r="G539" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H539" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="540">
@@ -12788,8 +14408,11 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="s">
-        <v>7</v>
+      <c r="G540" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H540" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="541">
@@ -12811,8 +14434,11 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="s">
-        <v>7</v>
+      <c r="G541" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H541" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="542">
@@ -12834,8 +14460,11 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="s">
-        <v>7</v>
+      <c r="G542" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H542" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="543">
@@ -12857,8 +14486,11 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="s">
-        <v>7</v>
+      <c r="G543" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H543" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="544">
@@ -12880,8 +14512,11 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="s">
-        <v>7</v>
+      <c r="G544" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H544" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="545">
@@ -12903,8 +14538,11 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="s">
-        <v>7</v>
+      <c r="G545" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H545" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="546">
@@ -12926,8 +14564,11 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="s">
-        <v>7</v>
+      <c r="G546" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H546" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="547">
@@ -12949,8 +14590,11 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="s">
-        <v>7</v>
+      <c r="G547" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H547" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="548">
@@ -12972,8 +14616,11 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="s">
-        <v>7</v>
+      <c r="G548" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H548" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -12995,8 +14642,11 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="s">
-        <v>7</v>
+      <c r="G549" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H549" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="550">
@@ -13018,8 +14668,11 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="s">
-        <v>7</v>
+      <c r="G550" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H550" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="551">
@@ -13041,8 +14694,11 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="s">
-        <v>7</v>
+      <c r="G551" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H551" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="552">
@@ -13064,8 +14720,11 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="s">
-        <v>7</v>
+      <c r="G552" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H552" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="553">
@@ -13087,8 +14746,11 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="s">
-        <v>7</v>
+      <c r="G553" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H553" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="554">
@@ -13110,8 +14772,11 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="s">
-        <v>7</v>
+      <c r="G554" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H554" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -13133,8 +14798,11 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="s">
-        <v>7</v>
+      <c r="G555" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H555" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -13156,8 +14824,11 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="s">
-        <v>7</v>
+      <c r="G556" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H556" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="557">
@@ -13179,8 +14850,11 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="s">
-        <v>7</v>
+      <c r="G557" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H557" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="558">
@@ -13202,8 +14876,11 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="s">
-        <v>7</v>
+      <c r="G558" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H558" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="559">
@@ -13225,8 +14902,11 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="s">
-        <v>7</v>
+      <c r="G559" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H559" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -13248,8 +14928,11 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="s">
-        <v>7</v>
+      <c r="G560" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H560" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="561">
@@ -13271,8 +14954,11 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="s">
-        <v>7</v>
+      <c r="G561" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H561" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="562">
@@ -13294,8 +14980,11 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="s">
-        <v>7</v>
+      <c r="G562" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H562" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="563">
@@ -13317,8 +15006,11 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="s">
-        <v>7</v>
+      <c r="G563" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H563" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="564">
@@ -13340,8 +15032,11 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="s">
-        <v>7</v>
+      <c r="G564" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H564" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="565">
@@ -13363,8 +15058,11 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="s">
-        <v>7</v>
+      <c r="G565" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H565" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -13386,8 +15084,11 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="s">
-        <v>7</v>
+      <c r="G566" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H566" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="567">
@@ -13409,8 +15110,11 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="s">
-        <v>7</v>
+      <c r="G567" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H567" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="568">
@@ -13432,8 +15136,11 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="s">
-        <v>7</v>
+      <c r="G568" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H568" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="569">
@@ -13455,8 +15162,11 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="s">
-        <v>7</v>
+      <c r="G569" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H569" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="570">
@@ -13478,8 +15188,11 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="s">
-        <v>7</v>
+      <c r="G570" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H570" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="571">
@@ -13501,8 +15214,11 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="s">
-        <v>7</v>
+      <c r="G571" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H571" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="572">
@@ -13524,8 +15240,11 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="s">
-        <v>7</v>
+      <c r="G572" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H572" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="573">
@@ -13547,8 +15266,11 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="s">
-        <v>7</v>
+      <c r="G573" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H573" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="574">
@@ -13570,8 +15292,11 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="s">
-        <v>7</v>
+      <c r="G574" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H574" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="575">
@@ -13593,8 +15318,11 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="s">
-        <v>7</v>
+      <c r="G575" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H575" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="576">
@@ -13616,8 +15344,11 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="s">
-        <v>7</v>
+      <c r="G576" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H576" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="577">
@@ -13639,8 +15370,11 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="s">
-        <v>7</v>
+      <c r="G577" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H577" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="578">
@@ -13662,8 +15396,11 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="s">
-        <v>7</v>
+      <c r="G578" t="n">
+        <v>0.0175000000745058</v>
+      </c>
+      <c r="H578" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="579">
@@ -13685,8 +15422,11 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="s">
-        <v>7</v>
+      <c r="G579" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H579" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="580">
@@ -13708,8 +15448,11 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="s">
-        <v>7</v>
+      <c r="G580" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H580" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="581">
@@ -13731,8 +15474,11 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="s">
-        <v>7</v>
+      <c r="G581" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H581" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="582">
@@ -13754,8 +15500,11 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="s">
-        <v>7</v>
+      <c r="G582" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H582" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="583">
@@ -13777,8 +15526,11 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="s">
-        <v>7</v>
+      <c r="G583" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H583" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="584">
@@ -13800,8 +15552,11 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="s">
-        <v>7</v>
+      <c r="G584" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H584" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="585">
@@ -13823,8 +15578,11 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="s">
-        <v>7</v>
+      <c r="G585" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H585" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="586">
@@ -13846,8 +15604,11 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="s">
-        <v>7</v>
+      <c r="G586" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H586" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="587">
@@ -13869,8 +15630,11 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="s">
-        <v>7</v>
+      <c r="G587" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H587" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="588">
@@ -13892,8 +15656,11 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="s">
-        <v>7</v>
+      <c r="G588" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H588" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="589">
@@ -13915,8 +15682,11 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="s">
-        <v>7</v>
+      <c r="G589" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H589" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="590">
@@ -13938,8 +15708,11 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="s">
-        <v>7</v>
+      <c r="G590" t="n">
+        <v>0.0171000007539988</v>
+      </c>
+      <c r="H590" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -13961,8 +15734,11 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="s">
-        <v>7</v>
+      <c r="G591" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H591" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="592">
@@ -13984,8 +15760,11 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="s">
-        <v>7</v>
+      <c r="G592" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H592" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="593">
@@ -14007,8 +15786,11 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="s">
-        <v>7</v>
+      <c r="G593" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H593" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="594">
@@ -14030,8 +15812,11 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="s">
-        <v>7</v>
+      <c r="G594" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="H594" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="595">
@@ -14053,8 +15838,11 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="s">
-        <v>7</v>
+      <c r="G595" t="n">
+        <v>0.0203000009059906</v>
+      </c>
+      <c r="H595" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="596">
@@ -14076,8 +15864,11 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="s">
-        <v>7</v>
+      <c r="G596" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H596" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -14099,8 +15890,11 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="s">
-        <v>7</v>
+      <c r="G597" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H597" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="598">
@@ -14122,8 +15916,11 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="s">
-        <v>7</v>
+      <c r="G598" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H598" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="599">
@@ -14145,8 +15942,11 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="s">
-        <v>7</v>
+      <c r="G599" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H599" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="600">
@@ -14168,8 +15968,11 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="s">
-        <v>7</v>
+      <c r="G600" t="n">
+        <v>0.0183000005781651</v>
+      </c>
+      <c r="H600" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="601">
@@ -14191,8 +15994,11 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="s">
-        <v>7</v>
+      <c r="G601" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H601" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="602">
@@ -14214,8 +16020,11 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="s">
-        <v>7</v>
+      <c r="G602" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H602" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="603">
@@ -14237,8 +16046,11 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="s">
-        <v>7</v>
+      <c r="G603" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H603" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="604">
@@ -14260,8 +16072,11 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="s">
-        <v>7</v>
+      <c r="G604" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="H604" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="605">
@@ -14283,8 +16098,11 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="s">
-        <v>7</v>
+      <c r="G605" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H605" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="606">
@@ -14306,8 +16124,11 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="s">
-        <v>7</v>
+      <c r="G606" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H606" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="607">
@@ -14329,8 +16150,11 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="s">
-        <v>7</v>
+      <c r="G607" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H607" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="608">
@@ -14352,8 +16176,11 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="s">
-        <v>7</v>
+      <c r="G608" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H608" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="609">
@@ -14375,8 +16202,11 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="s">
-        <v>7</v>
+      <c r="G609" t="n">
+        <v>0.0181000009179115</v>
+      </c>
+      <c r="H609" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="610">
@@ -14398,8 +16228,11 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="s">
-        <v>7</v>
+      <c r="G610" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H610" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="611">
@@ -14421,8 +16254,11 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="s">
-        <v>7</v>
+      <c r="G611" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H611" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="612">
@@ -14444,8 +16280,11 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="s">
-        <v>7</v>
+      <c r="G612" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H612" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="613">
@@ -14467,8 +16306,11 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="s">
-        <v>7</v>
+      <c r="G613" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H613" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="614">
@@ -14490,8 +16332,11 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="s">
-        <v>7</v>
+      <c r="G614" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H614" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="615">
@@ -14513,8 +16358,11 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="s">
-        <v>7</v>
+      <c r="G615" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H615" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="616">
@@ -14536,8 +16384,11 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="s">
-        <v>7</v>
+      <c r="G616" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H616" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="617">
@@ -14559,8 +16410,11 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="s">
-        <v>7</v>
+      <c r="G617" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H617" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="618">
@@ -14582,8 +16436,11 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="s">
-        <v>7</v>
+      <c r="G618" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H618" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="619">
@@ -14605,8 +16462,11 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="s">
-        <v>7</v>
+      <c r="G619" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H619" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="620">
@@ -14628,8 +16488,11 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="s">
-        <v>7</v>
+      <c r="G620" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H620" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="621">
@@ -14651,8 +16514,11 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="s">
-        <v>7</v>
+      <c r="G621" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H621" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="622">
@@ -14674,8 +16540,11 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="s">
-        <v>7</v>
+      <c r="G622" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H622" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="623">
@@ -14697,8 +16566,11 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="s">
-        <v>7</v>
+      <c r="G623" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H623" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="624">
@@ -14720,8 +16592,11 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="s">
-        <v>7</v>
+      <c r="G624" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H624" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="625">
@@ -14743,8 +16618,11 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="s">
-        <v>7</v>
+      <c r="G625" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H625" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="626">
@@ -14766,8 +16644,11 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="s">
-        <v>7</v>
+      <c r="G626" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H626" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="627">
@@ -14789,8 +16670,11 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="s">
-        <v>7</v>
+      <c r="G627" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H627" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="628">
@@ -14812,8 +16696,11 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="s">
-        <v>7</v>
+      <c r="G628" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H628" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="629">
@@ -14835,8 +16722,11 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="s">
-        <v>7</v>
+      <c r="G629" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H629" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="630">
@@ -14858,8 +16748,11 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="s">
-        <v>7</v>
+      <c r="G630" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H630" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="631">
@@ -14881,8 +16774,11 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="s">
-        <v>7</v>
+      <c r="G631" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H631" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="632">
@@ -14904,8 +16800,11 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="s">
-        <v>7</v>
+      <c r="G632" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H632" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="633">
@@ -14927,8 +16826,11 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="s">
-        <v>7</v>
+      <c r="G633" t="n">
+        <v>0.0172000005841255</v>
+      </c>
+      <c r="H633" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="634">
@@ -14950,8 +16852,11 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="s">
-        <v>7</v>
+      <c r="G634" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H634" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="635">
@@ -14973,8 +16878,11 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="s">
-        <v>7</v>
+      <c r="G635" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H635" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="636">
@@ -14996,8 +16904,11 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="s">
-        <v>7</v>
+      <c r="G636" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H636" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="637">
@@ -15019,8 +16930,11 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="s">
-        <v>7</v>
+      <c r="G637" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H637" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="638">
@@ -15042,8 +16956,11 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="s">
-        <v>7</v>
+      <c r="G638" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H638" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="639">
@@ -15065,8 +16982,11 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="s">
-        <v>7</v>
+      <c r="G639" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H639" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="640">
@@ -15088,8 +17008,11 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="s">
-        <v>7</v>
+      <c r="G640" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H640" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="641">
@@ -15111,8 +17034,11 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="s">
-        <v>7</v>
+      <c r="G641" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H641" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="642">
@@ -15134,8 +17060,11 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="s">
-        <v>7</v>
+      <c r="G642" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H642" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="643">
@@ -15157,8 +17086,11 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="s">
-        <v>7</v>
+      <c r="G643" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H643" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="644">
@@ -15180,8 +17112,11 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="s">
-        <v>7</v>
+      <c r="G644" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H644" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="645">
@@ -15203,8 +17138,11 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="s">
-        <v>7</v>
+      <c r="G645" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H645" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="646">
@@ -15226,8 +17164,11 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="s">
-        <v>7</v>
+      <c r="G646" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H646" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="647">
@@ -15249,8 +17190,11 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="s">
-        <v>7</v>
+      <c r="G647" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H647" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="648">
@@ -15272,8 +17216,11 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="s">
-        <v>7</v>
+      <c r="G648" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H648" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="649">
@@ -15295,8 +17242,11 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="s">
-        <v>7</v>
+      <c r="G649" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H649" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="650">
@@ -15318,8 +17268,11 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="s">
-        <v>7</v>
+      <c r="G650" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H650" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="651">
@@ -15341,8 +17294,11 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="s">
-        <v>7</v>
+      <c r="G651" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H651" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="652">
@@ -15364,8 +17320,11 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="s">
-        <v>7</v>
+      <c r="G652" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H652" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="653">
@@ -15387,8 +17346,11 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="s">
-        <v>7</v>
+      <c r="G653" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H653" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="654">
@@ -15410,8 +17372,11 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="s">
-        <v>7</v>
+      <c r="G654" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H654" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="655">
@@ -15433,8 +17398,11 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="s">
-        <v>7</v>
+      <c r="G655" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H655" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="656">
@@ -15456,8 +17424,11 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="s">
-        <v>7</v>
+      <c r="G656" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H656" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="657">
@@ -15479,8 +17450,11 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="s">
-        <v>7</v>
+      <c r="G657" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H657" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="658">
@@ -15502,8 +17476,11 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="s">
-        <v>7</v>
+      <c r="G658" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H658" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="659">
@@ -15525,8 +17502,11 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="s">
-        <v>7</v>
+      <c r="G659" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H659" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="660">
@@ -15548,8 +17528,11 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="s">
-        <v>7</v>
+      <c r="G660" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H660" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="661">
@@ -15571,8 +17554,11 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="s">
-        <v>7</v>
+      <c r="G661" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H661" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="662">
@@ -15594,8 +17580,11 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="s">
-        <v>7</v>
+      <c r="G662" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H662" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="663">
@@ -15617,8 +17606,11 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="s">
-        <v>7</v>
+      <c r="G663" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H663" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="664">
@@ -15640,8 +17632,11 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="s">
-        <v>7</v>
+      <c r="G664" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H664" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="665">
@@ -15663,8 +17658,11 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="s">
-        <v>7</v>
+      <c r="G665" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H665" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="666">
@@ -15686,8 +17684,11 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="s">
-        <v>7</v>
+      <c r="G666" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H666" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="667">
@@ -15709,8 +17710,11 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="s">
-        <v>7</v>
+      <c r="G667" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H667" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="668">
@@ -15732,8 +17736,11 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="s">
-        <v>7</v>
+      <c r="G668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H668" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="669">
@@ -15755,8 +17762,11 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="s">
-        <v>7</v>
+      <c r="G669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H669" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="670">
@@ -15778,31 +17788,89 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="s">
-        <v>7</v>
+      <c r="G670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H670" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B671" t="n">
+        <v>14495546</v>
+      </c>
+      <c r="C671" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="E671" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="G671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H671" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B671" t="n">
+      <c r="B672" t="n">
         <v>3578243</v>
       </c>
-      <c r="C671" t="n">
+      <c r="C672" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="D671" t="n">
+      <c r="D672" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="E671" t="n">
+      <c r="E672" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="F671" t="n">
+      <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G671" t="s">
-        <v>7</v>
+      <c r="G672" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="H672" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B673" t="n">
+        <v>10267153</v>
+      </c>
+      <c r="C673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="D673" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="G673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H673" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17873,6 +17873,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B674" t="n">
+        <v>1961429</v>
+      </c>
+      <c r="C674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="E674" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="G674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="H674" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17899,6 +17899,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B675" t="n">
+        <v>6149894</v>
+      </c>
+      <c r="C675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="G675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="H675" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17925,6 +17925,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B676" t="n">
+        <v>18524689</v>
+      </c>
+      <c r="C676" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0.0209999997168779</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="G676" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="H676" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -17951,6 +17951,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B677" t="n">
+        <v>4981016</v>
+      </c>
+      <c r="C677" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H677" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -397,9 +394,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -420,11 +414,8 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -446,11 +437,8 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +460,8 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +483,8 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -524,11 +506,8 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -550,11 +529,8 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -576,11 +552,8 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
+      <c r="G8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -602,11 +575,8 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -628,11 +598,8 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+      <c r="G10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -654,11 +621,8 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
+      <c r="G11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -680,11 +644,8 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -706,11 +667,8 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -732,11 +690,8 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H14" t="s">
-        <v>8</v>
+      <c r="G14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -758,11 +713,8 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -784,11 +736,8 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
+      <c r="G16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -810,11 +759,8 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+      <c r="G17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -836,11 +782,8 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -862,11 +805,8 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -888,11 +828,8 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+      <c r="G20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -914,11 +851,8 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H21" t="s">
-        <v>8</v>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -940,11 +874,8 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
+      <c r="G22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -966,11 +897,8 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
+      <c r="G23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -992,11 +920,8 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1018,11 +943,8 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
+      <c r="G25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1044,11 +966,8 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>8</v>
+      <c r="G26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1070,11 +989,8 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.019845999777317</v>
-      </c>
-      <c r="H27" t="s">
-        <v>8</v>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1096,11 +1012,8 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H28" t="s">
-        <v>8</v>
+      <c r="G28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1122,11 +1035,8 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>8</v>
+      <c r="G29" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1148,11 +1058,8 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.01923399977386</v>
-      </c>
-      <c r="H30" t="s">
-        <v>8</v>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1174,11 +1081,8 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+      <c r="G31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1200,11 +1104,8 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+      <c r="G32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1127,8 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1252,11 +1150,8 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="G34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1278,11 +1173,8 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1304,11 +1196,8 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H36" t="s">
-        <v>8</v>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1330,11 +1219,8 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H37" t="s">
-        <v>8</v>
+      <c r="G37" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1356,11 +1242,8 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H38" t="s">
-        <v>8</v>
+      <c r="G38" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1382,11 +1265,8 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H39" t="s">
-        <v>8</v>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1408,11 +1288,8 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
+      <c r="G40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1434,11 +1311,8 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
+      <c r="G41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1460,11 +1334,8 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1486,11 +1357,8 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H43" t="s">
-        <v>8</v>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1512,11 +1380,8 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H44" t="s">
-        <v>8</v>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1538,11 +1403,8 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H45" t="s">
-        <v>8</v>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1564,11 +1426,8 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H46" t="s">
-        <v>8</v>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1590,11 +1449,8 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H47" t="s">
-        <v>8</v>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1616,11 +1472,8 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H48" t="s">
-        <v>8</v>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1642,11 +1495,8 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H49" t="s">
-        <v>8</v>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1668,11 +1518,8 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H50" t="s">
-        <v>8</v>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1694,11 +1541,8 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H51" t="s">
-        <v>8</v>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1720,11 +1564,8 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H52" t="s">
-        <v>8</v>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1746,11 +1587,8 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H53" t="s">
-        <v>8</v>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,11 +1610,8 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H54" t="s">
-        <v>8</v>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1798,11 +1633,8 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H55" t="s">
-        <v>8</v>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1824,11 +1656,8 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H56" t="s">
-        <v>8</v>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1850,11 +1679,8 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H57" t="s">
-        <v>8</v>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1876,11 +1702,8 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H58" t="s">
-        <v>8</v>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1902,11 +1725,8 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H59" t="s">
-        <v>8</v>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1928,11 +1748,8 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H60" t="s">
-        <v>8</v>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1954,11 +1771,8 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1980,11 +1794,8 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H62" t="s">
-        <v>8</v>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2006,11 +1817,8 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H63" t="s">
-        <v>8</v>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2032,11 +1840,8 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H64" t="s">
-        <v>8</v>
+      <c r="G64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2058,11 +1863,8 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H65" t="s">
-        <v>8</v>
+      <c r="G65" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2084,11 +1886,8 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H66" t="s">
-        <v>8</v>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2110,11 +1909,8 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H67" t="s">
-        <v>8</v>
+      <c r="G67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2136,11 +1932,8 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H68" t="s">
-        <v>8</v>
+      <c r="G68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2162,11 +1955,8 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H69" t="s">
-        <v>8</v>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -2188,11 +1978,8 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H70" t="s">
-        <v>8</v>
+      <c r="G70" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2214,11 +2001,8 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H71" t="s">
-        <v>8</v>
+      <c r="G71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2240,11 +2024,8 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H72" t="s">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2266,11 +2047,8 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H73" t="s">
-        <v>8</v>
+      <c r="G73" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -2292,11 +2070,8 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="G74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2318,11 +2093,8 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H75" t="s">
-        <v>8</v>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2344,11 +2116,8 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="G76" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2370,11 +2139,8 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H77" t="s">
-        <v>8</v>
+      <c r="G77" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2396,11 +2162,8 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2422,11 +2185,8 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H79" t="s">
-        <v>8</v>
+      <c r="G79" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2448,11 +2208,8 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+      <c r="G80" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2474,11 +2231,8 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H81" t="s">
-        <v>8</v>
+      <c r="G81" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2500,11 +2254,8 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+      <c r="G82" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2526,11 +2277,8 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H83" t="s">
-        <v>8</v>
+      <c r="G83" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2552,11 +2300,8 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H84" t="s">
-        <v>8</v>
+      <c r="G84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2578,11 +2323,8 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H85" t="s">
-        <v>8</v>
+      <c r="G85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2604,11 +2346,8 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H86" t="s">
-        <v>8</v>
+      <c r="G86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -2630,11 +2369,8 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>8</v>
+      <c r="G87" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2656,11 +2392,8 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>8</v>
+      <c r="G88" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2682,11 +2415,8 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H89" t="s">
-        <v>8</v>
+      <c r="G89" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -2708,11 +2438,8 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="G90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2734,11 +2461,8 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H91" t="s">
-        <v>8</v>
+      <c r="G91" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2760,11 +2484,8 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="G92" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2786,11 +2507,8 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H93" t="s">
-        <v>8</v>
+      <c r="G93" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -2812,11 +2530,8 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H94" t="s">
-        <v>8</v>
+      <c r="G94" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2838,11 +2553,8 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="G95" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2864,11 +2576,8 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H96" t="s">
-        <v>8</v>
+      <c r="G96" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2890,11 +2599,8 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+      <c r="G97" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -2916,11 +2622,8 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H98" t="s">
-        <v>8</v>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2942,11 +2645,8 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="G99" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2668,8 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H100" t="s">
-        <v>8</v>
+      <c r="G100" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2994,11 +2691,8 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H101" t="s">
-        <v>8</v>
+      <c r="G101" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3020,11 +2714,8 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H102" t="s">
-        <v>8</v>
+      <c r="G102" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3046,11 +2737,8 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="G103" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3072,11 +2760,8 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H104" t="s">
-        <v>8</v>
+      <c r="G104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3098,11 +2783,8 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H105" t="s">
-        <v>8</v>
+      <c r="G105" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3124,11 +2806,8 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H106" t="s">
-        <v>8</v>
+      <c r="G106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3150,11 +2829,8 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H107" t="s">
-        <v>8</v>
+      <c r="G107" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3176,11 +2852,8 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+      <c r="G108" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3202,11 +2875,8 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H109" t="s">
-        <v>8</v>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3228,11 +2898,8 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H110" t="s">
-        <v>8</v>
+      <c r="G110" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -3254,11 +2921,8 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H111" t="s">
-        <v>8</v>
+      <c r="G111" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -3280,11 +2944,8 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H112" t="s">
-        <v>8</v>
+      <c r="G112" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3306,11 +2967,8 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+      <c r="G113" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3332,11 +2990,8 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H114" t="s">
-        <v>8</v>
+      <c r="G114" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3358,11 +3013,8 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H115" t="s">
-        <v>8</v>
+      <c r="G115" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3384,11 +3036,8 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+      <c r="G116" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3410,11 +3059,8 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H117" t="s">
-        <v>8</v>
+      <c r="G117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3436,11 +3082,8 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H118" t="s">
-        <v>8</v>
+      <c r="G118" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3462,11 +3105,8 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H119" t="s">
-        <v>8</v>
+      <c r="G119" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -3488,11 +3128,8 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H120" t="s">
-        <v>8</v>
+      <c r="G120" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -3514,11 +3151,8 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
+      <c r="G121" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -3540,11 +3174,8 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H122" t="s">
-        <v>8</v>
+      <c r="G122" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -3566,11 +3197,8 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H123" t="s">
-        <v>8</v>
+      <c r="G123" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3592,11 +3220,8 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H124" t="s">
-        <v>8</v>
+      <c r="G124" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -3618,11 +3243,8 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H125" t="s">
-        <v>8</v>
+      <c r="G125" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -3644,11 +3266,8 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H126" t="s">
-        <v>8</v>
+      <c r="G126" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -3670,11 +3289,8 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H127" t="s">
-        <v>8</v>
+      <c r="G127" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3696,11 +3312,8 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H128" t="s">
-        <v>8</v>
+      <c r="G128" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="129">
@@ -3722,11 +3335,8 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H129" t="s">
-        <v>8</v>
+      <c r="G129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -3748,11 +3358,8 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H130" t="s">
-        <v>8</v>
+      <c r="G130" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3774,11 +3381,8 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H131" t="s">
-        <v>8</v>
+      <c r="G131" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -3800,11 +3404,8 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H132" t="s">
-        <v>8</v>
+      <c r="G132" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -3826,11 +3427,8 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H133" t="s">
-        <v>8</v>
+      <c r="G133" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -3852,11 +3450,8 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H134" t="s">
-        <v>8</v>
+      <c r="G134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3878,11 +3473,8 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H135" t="s">
-        <v>8</v>
+      <c r="G135" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="136">
@@ -3904,11 +3496,8 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H136" t="s">
-        <v>8</v>
+      <c r="G136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -3930,11 +3519,8 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H137" t="s">
-        <v>8</v>
+      <c r="G137" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3956,11 +3542,8 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H138" t="s">
-        <v>8</v>
+      <c r="G138" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3982,11 +3565,8 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>8</v>
+      <c r="G139" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -4008,11 +3588,8 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H140" t="s">
-        <v>8</v>
+      <c r="G140" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -4034,11 +3611,8 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H141" t="s">
-        <v>8</v>
+      <c r="G141" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -4060,11 +3634,8 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H142" t="s">
-        <v>8</v>
+      <c r="G142" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="143">
@@ -4086,11 +3657,8 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H143" t="s">
-        <v>8</v>
+      <c r="G143" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4112,11 +3680,8 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H144" t="s">
-        <v>8</v>
+      <c r="G144" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -4138,11 +3703,8 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H145" t="s">
-        <v>8</v>
+      <c r="G145" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -4164,11 +3726,8 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H146" t="s">
-        <v>8</v>
+      <c r="G146" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -4190,11 +3749,8 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H147" t="s">
-        <v>8</v>
+      <c r="G147" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -4216,11 +3772,8 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H148" t="s">
-        <v>8</v>
+      <c r="G148" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -4242,11 +3795,8 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H149" t="s">
-        <v>8</v>
+      <c r="G149" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -4268,11 +3818,8 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H150" t="s">
-        <v>8</v>
+      <c r="G150" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -4294,11 +3841,8 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H151" t="s">
-        <v>8</v>
+      <c r="G151" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -4320,11 +3864,8 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H152" t="s">
-        <v>8</v>
+      <c r="G152" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -4346,11 +3887,8 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>8</v>
+      <c r="G153" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4372,11 +3910,8 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H154" t="s">
-        <v>8</v>
+      <c r="G154" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -4398,11 +3933,8 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H155" t="s">
-        <v>8</v>
+      <c r="G155" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -4424,11 +3956,8 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H156" t="s">
-        <v>8</v>
+      <c r="G156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -4450,11 +3979,8 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H157" t="s">
-        <v>8</v>
+      <c r="G157" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -4476,11 +4002,8 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H158" t="s">
-        <v>8</v>
+      <c r="G158" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -4502,11 +4025,8 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H159" t="s">
-        <v>8</v>
+      <c r="G159" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -4528,11 +4048,8 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H160" t="s">
-        <v>8</v>
+      <c r="G160" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -4554,11 +4071,8 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H161" t="s">
-        <v>8</v>
+      <c r="G161" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -4580,11 +4094,8 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H162" t="s">
-        <v>8</v>
+      <c r="G162" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -4606,11 +4117,8 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H163" t="s">
-        <v>8</v>
+      <c r="G163" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4632,11 +4140,8 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H164" t="s">
-        <v>8</v>
+      <c r="G164" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4658,11 +4163,8 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H165" t="s">
-        <v>8</v>
+      <c r="G165" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -4684,11 +4186,8 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H166" t="s">
-        <v>8</v>
+      <c r="G166" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -4710,11 +4209,8 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H167" t="s">
-        <v>8</v>
+      <c r="G167" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4736,11 +4232,8 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H168" t="s">
-        <v>8</v>
+      <c r="G168" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -4762,11 +4255,8 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H169" t="s">
-        <v>8</v>
+      <c r="G169" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4788,11 +4278,8 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H170" t="s">
-        <v>8</v>
+      <c r="G170" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4814,11 +4301,8 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H171" t="s">
-        <v>8</v>
+      <c r="G171" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4840,11 +4324,8 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H172" t="s">
-        <v>8</v>
+      <c r="G172" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -4866,11 +4347,8 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H173" t="s">
-        <v>8</v>
+      <c r="G173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4370,8 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H174" t="s">
-        <v>8</v>
+      <c r="G174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4918,11 +4393,8 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H175" t="s">
-        <v>8</v>
+      <c r="G175" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -4944,11 +4416,8 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H176" t="s">
-        <v>8</v>
+      <c r="G176" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -4970,11 +4439,8 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H177" t="s">
-        <v>8</v>
+      <c r="G177" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -4996,11 +4462,8 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H178" t="s">
-        <v>8</v>
+      <c r="G178" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -5022,11 +4485,8 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H179" t="s">
-        <v>8</v>
+      <c r="G179" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="180">
@@ -5048,11 +4508,8 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H180" t="s">
-        <v>8</v>
+      <c r="G180" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -5074,11 +4531,8 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H181" t="s">
-        <v>8</v>
+      <c r="G181" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182">
@@ -5100,11 +4554,8 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H182" t="s">
-        <v>8</v>
+      <c r="G182" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -5126,11 +4577,8 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H183" t="s">
-        <v>8</v>
+      <c r="G183" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -5152,11 +4600,8 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H184" t="s">
-        <v>8</v>
+      <c r="G184" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -5178,11 +4623,8 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H185" t="s">
-        <v>8</v>
+      <c r="G185" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5204,11 +4646,8 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H186" t="s">
-        <v>8</v>
+      <c r="G186" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -5230,11 +4669,8 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H187" t="s">
-        <v>8</v>
+      <c r="G187" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5256,11 +4692,8 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H188" t="s">
-        <v>8</v>
+      <c r="G188" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5282,11 +4715,8 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H189" t="s">
-        <v>8</v>
+      <c r="G189" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -5308,11 +4738,8 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H190" t="s">
-        <v>8</v>
+      <c r="G190" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -5334,11 +4761,8 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H191" t="s">
-        <v>8</v>
+      <c r="G191" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -5360,11 +4784,8 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H192" t="s">
-        <v>8</v>
+      <c r="G192" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -5386,11 +4807,8 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H193" t="s">
-        <v>8</v>
+      <c r="G193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -5412,11 +4830,8 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H194" t="s">
-        <v>8</v>
+      <c r="G194" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -5438,11 +4853,8 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H195" t="s">
-        <v>8</v>
+      <c r="G195" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -5464,11 +4876,8 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H196" t="s">
-        <v>8</v>
+      <c r="G196" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -5490,11 +4899,8 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H197" t="s">
-        <v>8</v>
+      <c r="G197" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -5516,11 +4922,8 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H198" t="s">
-        <v>8</v>
+      <c r="G198" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -5542,11 +4945,8 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H199" t="s">
-        <v>8</v>
+      <c r="G199" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -5568,11 +4968,8 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H200" t="s">
-        <v>8</v>
+      <c r="G200" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -5594,11 +4991,8 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H201" t="s">
-        <v>8</v>
+      <c r="G201" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5620,11 +5014,8 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H202" t="s">
-        <v>8</v>
+      <c r="G202" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -5646,11 +5037,8 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H203" t="s">
-        <v>8</v>
+      <c r="G203" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -5672,11 +5060,8 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H204" t="s">
-        <v>8</v>
+      <c r="G204" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -5698,11 +5083,8 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H205" t="s">
-        <v>8</v>
+      <c r="G205" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -5724,11 +5106,8 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H206" t="s">
-        <v>8</v>
+      <c r="G206" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -5750,11 +5129,8 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H207" t="s">
-        <v>8</v>
+      <c r="G207" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -5776,11 +5152,8 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H208" t="s">
-        <v>8</v>
+      <c r="G208" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -5802,11 +5175,8 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H209" t="s">
-        <v>8</v>
+      <c r="G209" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5828,11 +5198,8 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H210" t="s">
-        <v>8</v>
+      <c r="G210" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -5854,11 +5221,8 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H211" t="s">
-        <v>8</v>
+      <c r="G211" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -5880,11 +5244,8 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H212" t="s">
-        <v>8</v>
+      <c r="G212" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5906,11 +5267,8 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H213" t="s">
-        <v>8</v>
+      <c r="G213" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -5932,11 +5290,8 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H214" t="s">
-        <v>8</v>
+      <c r="G214" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -5958,11 +5313,8 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H215" t="s">
-        <v>8</v>
+      <c r="G215" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -5984,11 +5336,8 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H216" t="s">
-        <v>8</v>
+      <c r="G216" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -6010,11 +5359,8 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H217" t="s">
-        <v>8</v>
+      <c r="G217" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -6036,11 +5382,8 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H218" t="s">
-        <v>8</v>
+      <c r="G218" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -6062,11 +5405,8 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H219" t="s">
-        <v>8</v>
+      <c r="G219" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -6088,11 +5428,8 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H220" t="s">
-        <v>8</v>
+      <c r="G220" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -6114,11 +5451,8 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H221" t="s">
-        <v>8</v>
+      <c r="G221" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -6140,11 +5474,8 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H222" t="s">
-        <v>8</v>
+      <c r="G222" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -6166,11 +5497,8 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H223" t="s">
-        <v>8</v>
+      <c r="G223" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -6192,11 +5520,8 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H224" t="s">
-        <v>8</v>
+      <c r="G224" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -6218,11 +5543,8 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H225" t="s">
-        <v>8</v>
+      <c r="G225" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="226">
@@ -6244,11 +5566,8 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H226" t="s">
-        <v>8</v>
+      <c r="G226" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -6270,11 +5589,8 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H227" t="s">
-        <v>8</v>
+      <c r="G227" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -6296,11 +5612,8 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H228" t="s">
-        <v>8</v>
+      <c r="G228" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -6322,11 +5635,8 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H229" t="s">
-        <v>8</v>
+      <c r="G229" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -6348,11 +5658,8 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H230" t="s">
-        <v>8</v>
+      <c r="G230" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -6374,11 +5681,8 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H231" t="s">
-        <v>8</v>
+      <c r="G231" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -6400,11 +5704,8 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H232" t="s">
-        <v>8</v>
+      <c r="G232" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -6426,11 +5727,8 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H233" t="s">
-        <v>8</v>
+      <c r="G233" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -6452,11 +5750,8 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H234" t="s">
-        <v>8</v>
+      <c r="G234" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -6478,11 +5773,8 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H235" t="s">
-        <v>8</v>
+      <c r="G235" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -6504,11 +5796,8 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H236" t="s">
-        <v>8</v>
+      <c r="G236" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -6530,11 +5819,8 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H237" t="s">
-        <v>8</v>
+      <c r="G237" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -6556,11 +5842,8 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H238" t="s">
-        <v>8</v>
+      <c r="G238" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -6582,11 +5865,8 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H239" t="s">
-        <v>8</v>
+      <c r="G239" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -6608,11 +5888,8 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H240" t="s">
-        <v>8</v>
+      <c r="G240" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6634,11 +5911,8 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H241" t="s">
-        <v>8</v>
+      <c r="G241" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -6660,11 +5934,8 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H242" t="s">
-        <v>8</v>
+      <c r="G242" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="243">
@@ -6686,11 +5957,8 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H243" t="s">
-        <v>8</v>
+      <c r="G243" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -6712,11 +5980,8 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H244" t="s">
-        <v>8</v>
+      <c r="G244" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6738,11 +6003,8 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H245" t="s">
-        <v>8</v>
+      <c r="G245" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -6764,11 +6026,8 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H246" t="s">
-        <v>8</v>
+      <c r="G246" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -6790,11 +6049,8 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H247" t="s">
-        <v>8</v>
+      <c r="G247" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -6816,11 +6072,8 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H248" t="s">
-        <v>8</v>
+      <c r="G248" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6842,11 +6095,8 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H249" t="s">
-        <v>8</v>
+      <c r="G249" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -6868,11 +6118,8 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H250" t="s">
-        <v>8</v>
+      <c r="G250" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -6894,11 +6141,8 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H251" t="s">
-        <v>8</v>
+      <c r="G251" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6920,11 +6164,8 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H252" t="s">
-        <v>8</v>
+      <c r="G252" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6946,11 +6187,8 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H253" t="s">
-        <v>8</v>
+      <c r="G253" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -6972,11 +6210,8 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H254" t="s">
-        <v>8</v>
+      <c r="G254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -6998,11 +6233,8 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H255" t="s">
-        <v>8</v>
+      <c r="G255" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -7024,11 +6256,8 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H256" t="s">
-        <v>8</v>
+      <c r="G256" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -7050,11 +6279,8 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H257" t="s">
-        <v>8</v>
+      <c r="G257" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -7076,11 +6302,8 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H258" t="s">
-        <v>8</v>
+      <c r="G258" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -7102,11 +6325,8 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H259" t="s">
-        <v>8</v>
+      <c r="G259" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -7128,11 +6348,8 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H260" t="s">
-        <v>8</v>
+      <c r="G260" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -7154,11 +6371,8 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H261" t="s">
-        <v>8</v>
+      <c r="G261" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -7180,11 +6394,8 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H262" t="s">
-        <v>8</v>
+      <c r="G262" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -7206,11 +6417,8 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H263" t="s">
-        <v>8</v>
+      <c r="G263" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -7232,11 +6440,8 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H264" t="s">
-        <v>8</v>
+      <c r="G264" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -7258,11 +6463,8 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H265" t="s">
-        <v>8</v>
+      <c r="G265" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7284,11 +6486,8 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H266" t="s">
-        <v>8</v>
+      <c r="G266" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -7310,11 +6509,8 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H267" t="s">
-        <v>8</v>
+      <c r="G267" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7336,11 +6532,8 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H268" t="s">
-        <v>8</v>
+      <c r="G268" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -7362,11 +6555,8 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H269" t="s">
-        <v>8</v>
+      <c r="G269" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -7388,11 +6578,8 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H270" t="s">
-        <v>8</v>
+      <c r="G270" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -7414,11 +6601,8 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H271" t="s">
-        <v>8</v>
+      <c r="G271" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -7440,11 +6624,8 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H272" t="s">
-        <v>8</v>
+      <c r="G272" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -7466,11 +6647,8 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H273" t="s">
-        <v>8</v>
+      <c r="G273" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -7492,11 +6670,8 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H274" t="s">
-        <v>8</v>
+      <c r="G274" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -7518,11 +6693,8 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H275" t="s">
-        <v>8</v>
+      <c r="G275" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -7544,11 +6716,8 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H276" t="s">
-        <v>8</v>
+      <c r="G276" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7570,11 +6739,8 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H277" t="s">
-        <v>8</v>
+      <c r="G277" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -7596,11 +6762,8 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H278" t="s">
-        <v>8</v>
+      <c r="G278" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -7622,11 +6785,8 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H279" t="s">
-        <v>8</v>
+      <c r="G279" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -7648,11 +6808,8 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H280" t="s">
-        <v>8</v>
+      <c r="G280" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -7674,11 +6831,8 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H281" t="s">
-        <v>8</v>
+      <c r="G281" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -7700,11 +6854,8 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H282" t="s">
-        <v>8</v>
+      <c r="G282" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -7726,11 +6877,8 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H283" t="s">
-        <v>8</v>
+      <c r="G283" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -7752,11 +6900,8 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H284" t="s">
-        <v>8</v>
+      <c r="G284" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -7778,11 +6923,8 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H285" t="s">
-        <v>8</v>
+      <c r="G285" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7804,11 +6946,8 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H286" t="s">
-        <v>8</v>
+      <c r="G286" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -7830,11 +6969,8 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H287" t="s">
-        <v>8</v>
+      <c r="G287" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -7856,11 +6992,8 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H288" t="s">
-        <v>8</v>
+      <c r="G288" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -7882,11 +7015,8 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H289" t="s">
-        <v>8</v>
+      <c r="G289" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -7908,11 +7038,8 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H290" t="s">
-        <v>8</v>
+      <c r="G290" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -7934,11 +7061,8 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H291" t="s">
-        <v>8</v>
+      <c r="G291" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -7960,11 +7084,8 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H292" t="s">
-        <v>8</v>
+      <c r="G292" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -7986,11 +7107,8 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H293" t="s">
-        <v>8</v>
+      <c r="G293" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -8012,11 +7130,8 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H294" t="s">
-        <v>8</v>
+      <c r="G294" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -8038,11 +7153,8 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H295" t="s">
-        <v>8</v>
+      <c r="G295" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -8064,11 +7176,8 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H296" t="s">
-        <v>8</v>
+      <c r="G296" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -8090,11 +7199,8 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H297" t="s">
-        <v>8</v>
+      <c r="G297" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -8116,11 +7222,8 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H298" t="s">
-        <v>8</v>
+      <c r="G298" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -8142,11 +7245,8 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H299" t="s">
-        <v>8</v>
+      <c r="G299" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -8168,11 +7268,8 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H300" t="s">
-        <v>8</v>
+      <c r="G300" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -8194,11 +7291,8 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H301" t="s">
-        <v>8</v>
+      <c r="G301" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -8220,11 +7314,8 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H302" t="s">
-        <v>8</v>
+      <c r="G302" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -8246,11 +7337,8 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H303" t="s">
-        <v>8</v>
+      <c r="G303" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -8272,11 +7360,8 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H304" t="s">
-        <v>8</v>
+      <c r="G304" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -8298,11 +7383,8 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H305" t="s">
-        <v>8</v>
+      <c r="G305" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -8324,11 +7406,8 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H306" t="s">
-        <v>8</v>
+      <c r="G306" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -8350,11 +7429,8 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H307" t="s">
-        <v>8</v>
+      <c r="G307" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -8376,11 +7452,8 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H308" t="s">
-        <v>8</v>
+      <c r="G308" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -8402,11 +7475,8 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H309" t="s">
-        <v>8</v>
+      <c r="G309" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -8428,11 +7498,8 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H310" t="s">
-        <v>8</v>
+      <c r="G310" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -8454,11 +7521,8 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H311" t="s">
-        <v>8</v>
+      <c r="G311" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -8480,11 +7544,8 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H312" t="s">
-        <v>8</v>
+      <c r="G312" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -8506,11 +7567,8 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H313" t="s">
-        <v>8</v>
+      <c r="G313" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -8532,11 +7590,8 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H314" t="s">
-        <v>8</v>
+      <c r="G314" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -8558,11 +7613,8 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H315" t="s">
-        <v>8</v>
+      <c r="G315" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -8584,11 +7636,8 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H316" t="s">
-        <v>8</v>
+      <c r="G316" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -8610,11 +7659,8 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H317" t="s">
-        <v>8</v>
+      <c r="G317" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -8636,11 +7682,8 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H318" t="s">
-        <v>8</v>
+      <c r="G318" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -8662,11 +7705,8 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H319" t="s">
-        <v>8</v>
+      <c r="G319" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -8688,11 +7728,8 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H320" t="s">
-        <v>8</v>
+      <c r="G320" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -8714,11 +7751,8 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H321" t="s">
-        <v>8</v>
+      <c r="G321" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -8740,11 +7774,8 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H322" t="s">
-        <v>8</v>
+      <c r="G322" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -8766,11 +7797,8 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H323" t="s">
-        <v>8</v>
+      <c r="G323" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -8792,11 +7820,8 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H324" t="s">
-        <v>8</v>
+      <c r="G324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -8818,11 +7843,8 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H325" t="s">
-        <v>8</v>
+      <c r="G325" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -8844,11 +7866,8 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H326" t="s">
-        <v>8</v>
+      <c r="G326" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -8870,11 +7889,8 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H327" t="s">
-        <v>8</v>
+      <c r="G327" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -8896,11 +7912,8 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H328" t="s">
-        <v>8</v>
+      <c r="G328" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -8922,11 +7935,8 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H329" t="s">
-        <v>8</v>
+      <c r="G329" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8948,11 +7958,8 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H330" t="s">
-        <v>8</v>
+      <c r="G330" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -8974,11 +7981,8 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H331" t="s">
-        <v>8</v>
+      <c r="G331" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -9000,11 +8004,8 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H332" t="s">
-        <v>8</v>
+      <c r="G332" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9026,11 +8027,8 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H333" t="s">
-        <v>8</v>
+      <c r="G333" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -9052,11 +8050,8 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H334" t="s">
-        <v>8</v>
+      <c r="G334" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -9078,11 +8073,8 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H335" t="s">
-        <v>8</v>
+      <c r="G335" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -9104,11 +8096,8 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H336" t="s">
-        <v>8</v>
+      <c r="G336" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -9130,11 +8119,8 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H337" t="s">
-        <v>8</v>
+      <c r="G337" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -9156,11 +8142,8 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H338" t="s">
-        <v>8</v>
+      <c r="G338" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -9182,11 +8165,8 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H339" t="s">
-        <v>8</v>
+      <c r="G339" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9208,11 +8188,8 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H340" t="s">
-        <v>8</v>
+      <c r="G340" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -9234,11 +8211,8 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H341" t="s">
-        <v>8</v>
+      <c r="G341" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -9260,11 +8234,8 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H342" t="s">
-        <v>8</v>
+      <c r="G342" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -9286,11 +8257,8 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H343" t="s">
-        <v>8</v>
+      <c r="G343" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -9312,11 +8280,8 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H344" t="s">
-        <v>8</v>
+      <c r="G344" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -9338,11 +8303,8 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H345" t="s">
-        <v>8</v>
+      <c r="G345" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -9364,11 +8326,8 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H346" t="s">
-        <v>8</v>
+      <c r="G346" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -9390,11 +8349,8 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H347" t="s">
-        <v>8</v>
+      <c r="G347" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -9416,11 +8372,8 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H348" t="s">
-        <v>8</v>
+      <c r="G348" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -9442,11 +8395,8 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H349" t="s">
-        <v>8</v>
+      <c r="G349" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -9468,11 +8418,8 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H350" t="s">
-        <v>8</v>
+      <c r="G350" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -9494,11 +8441,8 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H351" t="s">
-        <v>8</v>
+      <c r="G351" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -9520,11 +8464,8 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H352" t="s">
-        <v>8</v>
+      <c r="G352" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -9546,11 +8487,8 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H353" t="s">
-        <v>8</v>
+      <c r="G353" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -9572,11 +8510,8 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H354" t="s">
-        <v>8</v>
+      <c r="G354" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -9598,11 +8533,8 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H355" t="s">
-        <v>8</v>
+      <c r="G355" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -9624,11 +8556,8 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H356" t="s">
-        <v>8</v>
+      <c r="G356" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -9650,11 +8579,8 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H357" t="s">
-        <v>8</v>
+      <c r="G357" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -9676,11 +8602,8 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H358" t="s">
-        <v>8</v>
+      <c r="G358" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -9702,11 +8625,8 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H359" t="s">
-        <v>8</v>
+      <c r="G359" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -9728,11 +8648,8 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H360" t="s">
-        <v>8</v>
+      <c r="G360" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -9754,11 +8671,8 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H361" t="s">
-        <v>8</v>
+      <c r="G361" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -9780,11 +8694,8 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H362" t="s">
-        <v>8</v>
+      <c r="G362" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -9806,11 +8717,8 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H363" t="s">
-        <v>8</v>
+      <c r="G363" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -9832,11 +8740,8 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H364" t="s">
-        <v>8</v>
+      <c r="G364" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -9858,11 +8763,8 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H365" t="s">
-        <v>8</v>
+      <c r="G365" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -9884,11 +8786,8 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H366" t="s">
-        <v>8</v>
+      <c r="G366" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -9910,11 +8809,8 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H367" t="s">
-        <v>8</v>
+      <c r="G367" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -9936,11 +8832,8 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H368" t="s">
-        <v>8</v>
+      <c r="G368" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="369">
@@ -9962,11 +8855,8 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H369" t="s">
-        <v>8</v>
+      <c r="G369" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -9988,11 +8878,8 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H370" t="s">
-        <v>8</v>
+      <c r="G370" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -10014,11 +8901,8 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H371" t="s">
-        <v>8</v>
+      <c r="G371" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -10040,11 +8924,8 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H372" t="s">
-        <v>8</v>
+      <c r="G372" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="373">
@@ -10066,11 +8947,8 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H373" t="s">
-        <v>8</v>
+      <c r="G373" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -10092,11 +8970,8 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H374" t="s">
-        <v>8</v>
+      <c r="G374" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -10118,11 +8993,8 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H375" t="s">
-        <v>8</v>
+      <c r="G375" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -10144,11 +9016,8 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H376" t="s">
-        <v>8</v>
+      <c r="G376" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="377">
@@ -10170,11 +9039,8 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H377" t="s">
-        <v>8</v>
+      <c r="G377" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="378">
@@ -10196,11 +9062,8 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H378" t="s">
-        <v>8</v>
+      <c r="G378" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="379">
@@ -10222,11 +9085,8 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H379" t="s">
-        <v>8</v>
+      <c r="G379" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="380">
@@ -10248,11 +9108,8 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H380" t="s">
-        <v>8</v>
+      <c r="G380" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="381">
@@ -10274,11 +9131,8 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H381" t="s">
-        <v>8</v>
+      <c r="G381" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -10300,11 +9154,8 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H382" t="s">
-        <v>8</v>
+      <c r="G382" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -10326,11 +9177,8 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H383" t="s">
-        <v>8</v>
+      <c r="G383" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -10352,11 +9200,8 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H384" t="s">
-        <v>8</v>
+      <c r="G384" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -10378,11 +9223,8 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H385" t="s">
-        <v>8</v>
+      <c r="G385" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -10404,11 +9246,8 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H386" t="s">
-        <v>8</v>
+      <c r="G386" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -10430,11 +9269,8 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H387" t="s">
-        <v>8</v>
+      <c r="G387" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -10456,11 +9292,8 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H388" t="s">
-        <v>8</v>
+      <c r="G388" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -10482,11 +9315,8 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H389" t="s">
-        <v>8</v>
+      <c r="G389" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -10508,11 +9338,8 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H390" t="s">
-        <v>8</v>
+      <c r="G390" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -10534,11 +9361,8 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H391" t="s">
-        <v>8</v>
+      <c r="G391" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -10560,11 +9384,8 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H392" t="s">
-        <v>8</v>
+      <c r="G392" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -10586,11 +9407,8 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H393" t="s">
-        <v>8</v>
+      <c r="G393" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="394">
@@ -10612,11 +9430,8 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H394" t="s">
-        <v>8</v>
+      <c r="G394" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="395">
@@ -10638,11 +9453,8 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H395" t="s">
-        <v>8</v>
+      <c r="G395" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="396">
@@ -10664,11 +9476,8 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H396" t="s">
-        <v>8</v>
+      <c r="G396" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -10690,11 +9499,8 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H397" t="s">
-        <v>8</v>
+      <c r="G397" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="398">
@@ -10716,11 +9522,8 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H398" t="s">
-        <v>8</v>
+      <c r="G398" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -10742,11 +9545,8 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H399" t="s">
-        <v>8</v>
+      <c r="G399" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -10768,11 +9568,8 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H400" t="s">
-        <v>8</v>
+      <c r="G400" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="401">
@@ -10794,11 +9591,8 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H401" t="s">
-        <v>8</v>
+      <c r="G401" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -10820,11 +9614,8 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H402" t="s">
-        <v>8</v>
+      <c r="G402" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -10846,11 +9637,8 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H403" t="s">
-        <v>8</v>
+      <c r="G403" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="404">
@@ -10872,11 +9660,8 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H404" t="s">
-        <v>8</v>
+      <c r="G404" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -10898,11 +9683,8 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H405" t="s">
-        <v>8</v>
+      <c r="G405" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -10924,11 +9706,8 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H406" t="s">
-        <v>8</v>
+      <c r="G406" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -10950,11 +9729,8 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H407" t="s">
-        <v>8</v>
+      <c r="G407" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -10976,11 +9752,8 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H408" t="s">
-        <v>8</v>
+      <c r="G408" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="409">
@@ -11002,11 +9775,8 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H409" t="s">
-        <v>8</v>
+      <c r="G409" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -11028,11 +9798,8 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H410" t="s">
-        <v>8</v>
+      <c r="G410" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11054,11 +9821,8 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H411" t="s">
-        <v>8</v>
+      <c r="G411" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -11080,11 +9844,8 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H412" t="s">
-        <v>8</v>
+      <c r="G412" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -11106,11 +9867,8 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H413" t="s">
-        <v>8</v>
+      <c r="G413" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="414">
@@ -11132,11 +9890,8 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H414" t="s">
-        <v>8</v>
+      <c r="G414" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -11158,11 +9913,8 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H415" t="s">
-        <v>8</v>
+      <c r="G415" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="416">
@@ -11184,11 +9936,8 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H416" t="s">
-        <v>8</v>
+      <c r="G416" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -11210,11 +9959,8 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H417" t="s">
-        <v>8</v>
+      <c r="G417" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="418">
@@ -11236,11 +9982,8 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H418" t="s">
-        <v>8</v>
+      <c r="G418" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -11262,11 +10005,8 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H419" t="s">
-        <v>8</v>
+      <c r="G419" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -11288,11 +10028,8 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H420" t="s">
-        <v>8</v>
+      <c r="G420" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="421">
@@ -11314,11 +10051,8 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="n">
-        <v>0.018673000857234</v>
-      </c>
-      <c r="H421" t="s">
-        <v>8</v>
+      <c r="G421" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="422">
@@ -11340,11 +10074,8 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H422" t="s">
-        <v>8</v>
+      <c r="G422" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -11366,11 +10097,8 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H423" t="s">
-        <v>8</v>
+      <c r="G423" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -11392,11 +10120,8 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H424" t="s">
-        <v>8</v>
+      <c r="G424" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -11418,11 +10143,8 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H425" t="s">
-        <v>8</v>
+      <c r="G425" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -11444,11 +10166,8 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H426" t="s">
-        <v>8</v>
+      <c r="G426" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -11470,11 +10189,8 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H427" t="s">
-        <v>8</v>
+      <c r="G427" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -11496,11 +10212,8 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H428" t="s">
-        <v>8</v>
+      <c r="G428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429">
@@ -11522,11 +10235,8 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H429" t="s">
-        <v>8</v>
+      <c r="G429" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -11548,11 +10258,8 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H430" t="s">
-        <v>8</v>
+      <c r="G430" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -11574,11 +10281,8 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H431" t="s">
-        <v>8</v>
+      <c r="G431" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -11600,11 +10304,8 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H432" t="s">
-        <v>8</v>
+      <c r="G432" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="433">
@@ -11626,11 +10327,8 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H433" t="s">
-        <v>8</v>
+      <c r="G433" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="434">
@@ -11652,11 +10350,8 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H434" t="s">
-        <v>8</v>
+      <c r="G434" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="435">
@@ -11678,11 +10373,8 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H435" t="s">
-        <v>8</v>
+      <c r="G435" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -11704,11 +10396,8 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H436" t="s">
-        <v>8</v>
+      <c r="G436" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -11730,11 +10419,8 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H437" t="s">
-        <v>8</v>
+      <c r="G437" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="438">
@@ -11756,11 +10442,8 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H438" t="s">
-        <v>8</v>
+      <c r="G438" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -11782,11 +10465,8 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H439" t="s">
-        <v>8</v>
+      <c r="G439" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -11808,11 +10488,8 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H440" t="s">
-        <v>8</v>
+      <c r="G440" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="441">
@@ -11834,11 +10511,8 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H441" t="s">
-        <v>8</v>
+      <c r="G441" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -11860,11 +10534,8 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H442" t="s">
-        <v>8</v>
+      <c r="G442" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -11886,11 +10557,8 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H443" t="s">
-        <v>8</v>
+      <c r="G443" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="444">
@@ -11912,11 +10580,8 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H444" t="s">
-        <v>8</v>
+      <c r="G444" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="445">
@@ -11938,11 +10603,8 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H445" t="s">
-        <v>8</v>
+      <c r="G445" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="446">
@@ -11964,11 +10626,8 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H446" t="s">
-        <v>8</v>
+      <c r="G446" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="447">
@@ -11990,11 +10649,8 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H447" t="s">
-        <v>8</v>
+      <c r="G447" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -12016,11 +10672,8 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H448" t="s">
-        <v>8</v>
+      <c r="G448" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -12042,11 +10695,8 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H449" t="s">
-        <v>8</v>
+      <c r="G449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -12068,11 +10718,8 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H450" t="s">
-        <v>8</v>
+      <c r="G450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451">
@@ -12094,11 +10741,8 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H451" t="s">
-        <v>8</v>
+      <c r="G451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -12120,11 +10764,8 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H452" t="s">
-        <v>8</v>
+      <c r="G452" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -12146,11 +10787,8 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H453" t="s">
-        <v>8</v>
+      <c r="G453" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -12172,11 +10810,8 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H454" t="s">
-        <v>8</v>
+      <c r="G454" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -12198,11 +10833,8 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H455" t="s">
-        <v>8</v>
+      <c r="G455" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -12224,11 +10856,8 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H456" t="s">
-        <v>8</v>
+      <c r="G456" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -12250,11 +10879,8 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H457" t="s">
-        <v>8</v>
+      <c r="G457" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -12276,11 +10902,8 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H458" t="s">
-        <v>8</v>
+      <c r="G458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -12302,11 +10925,8 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H459" t="s">
-        <v>8</v>
+      <c r="G459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -12328,11 +10948,8 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H460" t="s">
-        <v>8</v>
+      <c r="G460" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -12354,11 +10971,8 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H461" t="s">
-        <v>8</v>
+      <c r="G461" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -12380,11 +10994,8 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H462" t="s">
-        <v>8</v>
+      <c r="G462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -12406,11 +11017,8 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H463" t="s">
-        <v>8</v>
+      <c r="G463" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -12432,11 +11040,8 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H464" t="s">
-        <v>8</v>
+      <c r="G464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -12458,11 +11063,8 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H465" t="s">
-        <v>8</v>
+      <c r="G465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -12484,11 +11086,8 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H466" t="s">
-        <v>8</v>
+      <c r="G466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -12510,11 +11109,8 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H467" t="s">
-        <v>8</v>
+      <c r="G467" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="468">
@@ -12536,11 +11132,8 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H468" t="s">
-        <v>8</v>
+      <c r="G468" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -12562,11 +11155,8 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H469" t="s">
-        <v>8</v>
+      <c r="G469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -12588,11 +11178,8 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H470" t="s">
-        <v>8</v>
+      <c r="G470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471">
@@ -12614,11 +11201,8 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H471" t="s">
-        <v>8</v>
+      <c r="G471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -12640,11 +11224,8 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H472" t="s">
-        <v>8</v>
+      <c r="G472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -12666,11 +11247,8 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H473" t="s">
-        <v>8</v>
+      <c r="G473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474">
@@ -12692,11 +11270,8 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H474" t="s">
-        <v>8</v>
+      <c r="G474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -12718,11 +11293,8 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H475" t="s">
-        <v>8</v>
+      <c r="G475" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="476">
@@ -12744,11 +11316,8 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H476" t="s">
-        <v>8</v>
+      <c r="G476" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="477">
@@ -12770,11 +11339,8 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H477" t="s">
-        <v>8</v>
+      <c r="G477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478">
@@ -12796,11 +11362,8 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H478" t="s">
-        <v>8</v>
+      <c r="G478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -12822,11 +11385,8 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H479" t="s">
-        <v>8</v>
+      <c r="G479" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="480">
@@ -12848,11 +11408,8 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H480" t="s">
-        <v>8</v>
+      <c r="G480" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="481">
@@ -12874,11 +11431,8 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H481" t="s">
-        <v>8</v>
+      <c r="G481" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -12900,11 +11454,8 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H482" t="s">
-        <v>8</v>
+      <c r="G482" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -12926,11 +11477,8 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H483" t="s">
-        <v>8</v>
+      <c r="G483" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -12952,11 +11500,8 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H484" t="s">
-        <v>8</v>
+      <c r="G484" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="485">
@@ -12978,11 +11523,8 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H485" t="s">
-        <v>8</v>
+      <c r="G485" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="486">
@@ -13004,11 +11546,8 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H486" t="s">
-        <v>8</v>
+      <c r="G486" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -13030,11 +11569,8 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H487" t="s">
-        <v>8</v>
+      <c r="G487" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="488">
@@ -13056,11 +11592,8 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H488" t="s">
-        <v>8</v>
+      <c r="G488" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -13082,11 +11615,8 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H489" t="s">
-        <v>8</v>
+      <c r="G489" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="490">
@@ -13108,11 +11638,8 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H490" t="s">
-        <v>8</v>
+      <c r="G490" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -13134,11 +11661,8 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H491" t="s">
-        <v>8</v>
+      <c r="G491" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -13160,11 +11684,8 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H492" t="s">
-        <v>8</v>
+      <c r="G492" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="493">
@@ -13186,11 +11707,8 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H493" t="s">
-        <v>8</v>
+      <c r="G493" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="494">
@@ -13212,11 +11730,8 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H494" t="s">
-        <v>8</v>
+      <c r="G494" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="495">
@@ -13238,11 +11753,8 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H495" t="s">
-        <v>8</v>
+      <c r="G495" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="496">
@@ -13264,11 +11776,8 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H496" t="s">
-        <v>8</v>
+      <c r="G496" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -13290,11 +11799,8 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H497" t="s">
-        <v>8</v>
+      <c r="G497" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -13316,11 +11822,8 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H498" t="s">
-        <v>8</v>
+      <c r="G498" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -13342,11 +11845,8 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H499" t="s">
-        <v>8</v>
+      <c r="G499" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -13368,11 +11868,8 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H500" t="s">
-        <v>8</v>
+      <c r="G500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -13394,11 +11891,8 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H501" t="s">
-        <v>8</v>
+      <c r="G501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -13420,11 +11914,8 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H502" t="s">
-        <v>8</v>
+      <c r="G502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -13446,11 +11937,8 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H503" t="s">
-        <v>8</v>
+      <c r="G503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -13472,11 +11960,8 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H504" t="s">
-        <v>8</v>
+      <c r="G504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505">
@@ -13498,11 +11983,8 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H505" t="s">
-        <v>8</v>
+      <c r="G505" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -13524,11 +12006,8 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="n">
-        <v>0.0154079999774694</v>
-      </c>
-      <c r="H506" t="s">
-        <v>8</v>
+      <c r="G506" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="507">
@@ -13550,11 +12029,8 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H507" t="s">
-        <v>8</v>
+      <c r="G507" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -13576,11 +12052,8 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H508" t="s">
-        <v>8</v>
+      <c r="G508" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -13602,11 +12075,8 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H509" t="s">
-        <v>8</v>
+      <c r="G509" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="510">
@@ -13628,11 +12098,8 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H510" t="s">
-        <v>8</v>
+      <c r="G510" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="511">
@@ -13654,11 +12121,8 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H511" t="s">
-        <v>8</v>
+      <c r="G511" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -13680,11 +12144,8 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H512" t="s">
-        <v>8</v>
+      <c r="G512" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="513">
@@ -13706,11 +12167,8 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H513" t="s">
-        <v>8</v>
+      <c r="G513" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -13732,11 +12190,8 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>8</v>
+      <c r="G514" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -13758,11 +12213,8 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H515" t="s">
-        <v>8</v>
+      <c r="G515" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -13784,11 +12236,8 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H516" t="s">
-        <v>8</v>
+      <c r="G516" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="517">
@@ -13810,11 +12259,8 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H517" t="s">
-        <v>8</v>
+      <c r="G517" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -13836,11 +12282,8 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H518" t="s">
-        <v>8</v>
+      <c r="G518" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -13862,11 +12305,8 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H519" t="s">
-        <v>8</v>
+      <c r="G519" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -13888,11 +12328,8 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H520" t="s">
-        <v>8</v>
+      <c r="G520" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -13914,11 +12351,8 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H521" t="s">
-        <v>8</v>
+      <c r="G521" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="522">
@@ -13940,11 +12374,8 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H522" t="s">
-        <v>8</v>
+      <c r="G522" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -13966,11 +12397,8 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H523" t="s">
-        <v>8</v>
+      <c r="G523" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -13992,11 +12420,8 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H524" t="s">
-        <v>8</v>
+      <c r="G524" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="525">
@@ -14018,11 +12443,8 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H525" t="s">
-        <v>8</v>
+      <c r="G525" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -14044,11 +12466,8 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H526" t="s">
-        <v>8</v>
+      <c r="G526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527">
@@ -14070,11 +12489,8 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H527" t="s">
-        <v>8</v>
+      <c r="G527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528">
@@ -14096,11 +12512,8 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H528" t="s">
-        <v>8</v>
+      <c r="G528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529">
@@ -14122,11 +12535,8 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H529" t="s">
-        <v>8</v>
+      <c r="G529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -14148,11 +12558,8 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H530" t="s">
-        <v>8</v>
+      <c r="G530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -14174,11 +12581,8 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H531" t="s">
-        <v>8</v>
+      <c r="G531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532">
@@ -14200,11 +12604,8 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H532" t="s">
-        <v>8</v>
+      <c r="G532" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="533">
@@ -14226,11 +12627,8 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H533" t="s">
-        <v>8</v>
+      <c r="G533" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -14252,11 +12650,8 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H534" t="s">
-        <v>8</v>
+      <c r="G534" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="535">
@@ -14278,11 +12673,8 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H535" t="s">
-        <v>8</v>
+      <c r="G535" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -14304,11 +12696,8 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H536" t="s">
-        <v>8</v>
+      <c r="G536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537">
@@ -14330,11 +12719,8 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H537" t="s">
-        <v>8</v>
+      <c r="G537" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="538">
@@ -14356,11 +12742,8 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H538" t="s">
-        <v>8</v>
+      <c r="G538" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="539">
@@ -14382,11 +12765,8 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H539" t="s">
-        <v>8</v>
+      <c r="G539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540">
@@ -14408,11 +12788,8 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H540" t="s">
-        <v>8</v>
+      <c r="G540" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -14434,11 +12811,8 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H541" t="s">
-        <v>8</v>
+      <c r="G541" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="542">
@@ -14460,11 +12834,8 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H542" t="s">
-        <v>8</v>
+      <c r="G542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -14486,11 +12857,8 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H543" t="s">
-        <v>8</v>
+      <c r="G543" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -14512,11 +12880,8 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H544" t="s">
-        <v>8</v>
+      <c r="G544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545">
@@ -14538,11 +12903,8 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H545" t="s">
-        <v>8</v>
+      <c r="G545" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="546">
@@ -14564,11 +12926,8 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H546" t="s">
-        <v>8</v>
+      <c r="G546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547">
@@ -14590,11 +12949,8 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H547" t="s">
-        <v>8</v>
+      <c r="G547" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="548">
@@ -14616,11 +12972,8 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H548" t="s">
-        <v>8</v>
+      <c r="G548" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -14642,11 +12995,8 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H549" t="s">
-        <v>8</v>
+      <c r="G549" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -14668,11 +13018,8 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H550" t="s">
-        <v>8</v>
+      <c r="G550" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -14694,11 +13041,8 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H551" t="s">
-        <v>8</v>
+      <c r="G551" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="552">
@@ -14720,11 +13064,8 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H552" t="s">
-        <v>8</v>
+      <c r="G552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -14746,11 +13087,8 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H553" t="s">
-        <v>8</v>
+      <c r="G553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -14772,11 +13110,8 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H554" t="s">
-        <v>8</v>
+      <c r="G554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -14798,11 +13133,8 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H555" t="s">
-        <v>8</v>
+      <c r="G555" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="556">
@@ -14824,11 +13156,8 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H556" t="s">
-        <v>8</v>
+      <c r="G556" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="557">
@@ -14850,11 +13179,8 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H557" t="s">
-        <v>8</v>
+      <c r="G557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -14876,11 +13202,8 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H558" t="s">
-        <v>8</v>
+      <c r="G558" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="559">
@@ -14902,11 +13225,8 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H559" t="s">
-        <v>8</v>
+      <c r="G559" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="560">
@@ -14928,11 +13248,8 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H560" t="s">
-        <v>8</v>
+      <c r="G560" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -14954,11 +13271,8 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H561" t="s">
-        <v>8</v>
+      <c r="G561" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="562">
@@ -14980,11 +13294,8 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H562" t="s">
-        <v>8</v>
+      <c r="G562" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="563">
@@ -15006,11 +13317,8 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H563" t="s">
-        <v>8</v>
+      <c r="G563" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="564">
@@ -15032,11 +13340,8 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H564" t="s">
-        <v>8</v>
+      <c r="G564" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -15058,11 +13363,8 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H565" t="s">
-        <v>8</v>
+      <c r="G565" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="566">
@@ -15084,11 +13386,8 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H566" t="s">
-        <v>8</v>
+      <c r="G566" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -15110,11 +13409,8 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H567" t="s">
-        <v>8</v>
+      <c r="G567" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="568">
@@ -15136,11 +13432,8 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H568" t="s">
-        <v>8</v>
+      <c r="G568" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -15162,11 +13455,8 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H569" t="s">
-        <v>8</v>
+      <c r="G569" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="570">
@@ -15188,11 +13478,8 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H570" t="s">
-        <v>8</v>
+      <c r="G570" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -15214,11 +13501,8 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H571" t="s">
-        <v>8</v>
+      <c r="G571" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="572">
@@ -15240,11 +13524,8 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H572" t="s">
-        <v>8</v>
+      <c r="G572" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -15266,11 +13547,8 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H573" t="s">
-        <v>8</v>
+      <c r="G573" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="574">
@@ -15292,11 +13570,8 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H574" t="s">
-        <v>8</v>
+      <c r="G574" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -15318,11 +13593,8 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H575" t="s">
-        <v>8</v>
+      <c r="G575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -15344,11 +13616,8 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H576" t="s">
-        <v>8</v>
+      <c r="G576" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -15370,11 +13639,8 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H577" t="s">
-        <v>8</v>
+      <c r="G577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -15396,11 +13662,8 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="n">
-        <v>0.0175000000745058</v>
-      </c>
-      <c r="H578" t="s">
-        <v>8</v>
+      <c r="G578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579">
@@ -15422,11 +13685,8 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H579" t="s">
-        <v>8</v>
+      <c r="G579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580">
@@ -15448,11 +13708,8 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H580" t="s">
-        <v>8</v>
+      <c r="G580" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="581">
@@ -15474,11 +13731,8 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H581" t="s">
-        <v>8</v>
+      <c r="G581" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="582">
@@ -15500,11 +13754,8 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H582" t="s">
-        <v>8</v>
+      <c r="G582" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -15526,11 +13777,8 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H583" t="s">
-        <v>8</v>
+      <c r="G583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -15552,11 +13800,8 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H584" t="s">
-        <v>8</v>
+      <c r="G584" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="585">
@@ -15578,11 +13823,8 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H585" t="s">
-        <v>8</v>
+      <c r="G585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586">
@@ -15604,11 +13846,8 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H586" t="s">
-        <v>8</v>
+      <c r="G586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -15630,11 +13869,8 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H587" t="s">
-        <v>8</v>
+      <c r="G587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588">
@@ -15656,11 +13892,8 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H588" t="s">
-        <v>8</v>
+      <c r="G588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589">
@@ -15682,11 +13915,8 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H589" t="s">
-        <v>8</v>
+      <c r="G589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590">
@@ -15708,11 +13938,8 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="n">
-        <v>0.0171000007539988</v>
-      </c>
-      <c r="H590" t="s">
-        <v>8</v>
+      <c r="G590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591">
@@ -15734,11 +13961,8 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H591" t="s">
-        <v>8</v>
+      <c r="G591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592">
@@ -15760,11 +13984,8 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H592" t="s">
-        <v>8</v>
+      <c r="G592" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="593">
@@ -15786,11 +14007,8 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H593" t="s">
-        <v>8</v>
+      <c r="G593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594">
@@ -15812,11 +14030,8 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="n">
-        <v>0.0215000007301569</v>
-      </c>
-      <c r="H594" t="s">
-        <v>8</v>
+      <c r="G594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595">
@@ -15838,11 +14053,8 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="n">
-        <v>0.0203000009059906</v>
-      </c>
-      <c r="H595" t="s">
-        <v>8</v>
+      <c r="G595" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="596">
@@ -15864,11 +14076,8 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H596" t="s">
-        <v>8</v>
+      <c r="G596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597">
@@ -15890,11 +14099,8 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H597" t="s">
-        <v>8</v>
+      <c r="G597" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="598">
@@ -15916,11 +14122,8 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H598" t="s">
-        <v>8</v>
+      <c r="G598" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="599">
@@ -15942,11 +14145,8 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H599" t="s">
-        <v>8</v>
+      <c r="G599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600">
@@ -15968,11 +14168,8 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="n">
-        <v>0.0183000005781651</v>
-      </c>
-      <c r="H600" t="s">
-        <v>8</v>
+      <c r="G600" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="601">
@@ -15994,11 +14191,8 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H601" t="s">
-        <v>8</v>
+      <c r="G601" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="602">
@@ -16020,11 +14214,8 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H602" t="s">
-        <v>8</v>
+      <c r="G602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603">
@@ -16046,11 +14237,8 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H603" t="s">
-        <v>8</v>
+      <c r="G603" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="604">
@@ -16072,11 +14260,8 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="n">
-        <v>0.0196000002324581</v>
-      </c>
-      <c r="H604" t="s">
-        <v>8</v>
+      <c r="G604" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="605">
@@ -16098,11 +14283,8 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="n">
-        <v>0.0192000009119511</v>
-      </c>
-      <c r="H605" t="s">
-        <v>8</v>
+      <c r="G605" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="606">
@@ -16124,11 +14306,8 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H606" t="s">
-        <v>8</v>
+      <c r="G606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607">
@@ -16150,11 +14329,8 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H607" t="s">
-        <v>8</v>
+      <c r="G607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608">
@@ -16176,11 +14352,8 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H608" t="s">
-        <v>8</v>
+      <c r="G608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609">
@@ -16202,11 +14375,8 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="n">
-        <v>0.0181000009179115</v>
-      </c>
-      <c r="H609" t="s">
-        <v>8</v>
+      <c r="G609" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="610">
@@ -16228,11 +14398,8 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H610" t="s">
-        <v>8</v>
+      <c r="G610" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="611">
@@ -16254,11 +14421,8 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H611" t="s">
-        <v>8</v>
+      <c r="G611" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="612">
@@ -16280,11 +14444,8 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H612" t="s">
-        <v>8</v>
+      <c r="G612" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="613">
@@ -16306,11 +14467,8 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H613" t="s">
-        <v>8</v>
+      <c r="G613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614">
@@ -16332,11 +14490,8 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H614" t="s">
-        <v>8</v>
+      <c r="G614" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -16358,11 +14513,8 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H615" t="s">
-        <v>8</v>
+      <c r="G615" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="616">
@@ -16384,11 +14536,8 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H616" t="s">
-        <v>8</v>
+      <c r="G616" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -16410,11 +14559,8 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H617" t="s">
-        <v>8</v>
+      <c r="G617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618">
@@ -16436,11 +14582,8 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H618" t="s">
-        <v>8</v>
+      <c r="G618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619">
@@ -16462,11 +14605,8 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H619" t="s">
-        <v>8</v>
+      <c r="G619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620">
@@ -16488,11 +14628,8 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H620" t="s">
-        <v>8</v>
+      <c r="G620" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="621">
@@ -16514,11 +14651,8 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H621" t="s">
-        <v>8</v>
+      <c r="G621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622">
@@ -16540,11 +14674,8 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H622" t="s">
-        <v>8</v>
+      <c r="G622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623">
@@ -16566,11 +14697,8 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H623" t="s">
-        <v>8</v>
+      <c r="G623" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="624">
@@ -16592,11 +14720,8 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H624" t="s">
-        <v>8</v>
+      <c r="G624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625">
@@ -16618,11 +14743,8 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H625" t="s">
-        <v>8</v>
+      <c r="G625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -16644,11 +14766,8 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H626" t="s">
-        <v>8</v>
+      <c r="G626" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="627">
@@ -16670,11 +14789,8 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H627" t="s">
-        <v>8</v>
+      <c r="G627" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="628">
@@ -16696,11 +14812,8 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H628" t="s">
-        <v>8</v>
+      <c r="G628" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="629">
@@ -16722,11 +14835,8 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H629" t="s">
-        <v>8</v>
+      <c r="G629" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="630">
@@ -16748,11 +14858,8 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H630" t="s">
-        <v>8</v>
+      <c r="G630" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -16774,11 +14881,8 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H631" t="s">
-        <v>8</v>
+      <c r="G631" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="632">
@@ -16800,11 +14904,8 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H632" t="s">
-        <v>8</v>
+      <c r="G632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633">
@@ -16826,11 +14927,8 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="n">
-        <v>0.0172000005841255</v>
-      </c>
-      <c r="H633" t="s">
-        <v>8</v>
+      <c r="G633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -16852,11 +14950,8 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H634" t="s">
-        <v>8</v>
+      <c r="G634" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -16878,11 +14973,8 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H635" t="s">
-        <v>8</v>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -16904,11 +14996,8 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H636" t="s">
-        <v>8</v>
+      <c r="G636" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="637">
@@ -16930,11 +15019,8 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H637" t="s">
-        <v>8</v>
+      <c r="G637" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="638">
@@ -16956,11 +15042,8 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H638" t="s">
-        <v>8</v>
+      <c r="G638" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="639">
@@ -16982,11 +15065,8 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H639" t="s">
-        <v>8</v>
+      <c r="G639" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="640">
@@ -17008,11 +15088,8 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H640" t="s">
-        <v>8</v>
+      <c r="G640" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="641">
@@ -17034,11 +15111,8 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H641" t="s">
-        <v>8</v>
+      <c r="G641" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -17060,11 +15134,8 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H642" t="s">
-        <v>8</v>
+      <c r="G642" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -17086,11 +15157,8 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H643" t="s">
-        <v>8</v>
+      <c r="G643" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="644">
@@ -17112,11 +15180,8 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H644" t="s">
-        <v>8</v>
+      <c r="G644" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -17138,11 +15203,8 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H645" t="s">
-        <v>8</v>
+      <c r="G645" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -17164,11 +15226,8 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H646" t="s">
-        <v>8</v>
+      <c r="G646" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="647">
@@ -17190,11 +15249,8 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H647" t="s">
-        <v>8</v>
+      <c r="G647" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -17216,11 +15272,8 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H648" t="s">
-        <v>8</v>
+      <c r="G648" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -17242,11 +15295,8 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H649" t="s">
-        <v>8</v>
+      <c r="G649" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="650">
@@ -17268,11 +15318,8 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H650" t="s">
-        <v>8</v>
+      <c r="G650" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="651">
@@ -17294,11 +15341,8 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H651" t="s">
-        <v>8</v>
+      <c r="G651" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="652">
@@ -17320,11 +15364,8 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H652" t="s">
-        <v>8</v>
+      <c r="G652" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="653">
@@ -17346,11 +15387,8 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H653" t="s">
-        <v>8</v>
+      <c r="G653" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -17372,11 +15410,8 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H654" t="s">
-        <v>8</v>
+      <c r="G654" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="655">
@@ -17398,11 +15433,8 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H655" t="s">
-        <v>8</v>
+      <c r="G655" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="656">
@@ -17424,11 +15456,8 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H656" t="s">
-        <v>8</v>
+      <c r="G656" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="657">
@@ -17450,11 +15479,8 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H657" t="s">
-        <v>8</v>
+      <c r="G657" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="658">
@@ -17476,11 +15502,8 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H658" t="s">
-        <v>8</v>
+      <c r="G658" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -17502,11 +15525,8 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H659" t="s">
-        <v>8</v>
+      <c r="G659" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -17528,11 +15548,8 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H660" t="s">
-        <v>8</v>
+      <c r="G660" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -17554,11 +15571,8 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H661" t="s">
-        <v>8</v>
+      <c r="G661" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="662">
@@ -17580,11 +15594,8 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H662" t="s">
-        <v>8</v>
+      <c r="G662" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="663">
@@ -17606,11 +15617,8 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H663" t="s">
-        <v>8</v>
+      <c r="G663" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="664">
@@ -17632,11 +15640,8 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H664" t="s">
-        <v>8</v>
+      <c r="G664" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="665">
@@ -17658,11 +15663,8 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H665" t="s">
-        <v>8</v>
+      <c r="G665" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="666">
@@ -17684,11 +15686,8 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H666" t="s">
-        <v>8</v>
+      <c r="G666" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="667">
@@ -17710,11 +15709,8 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H667" t="s">
-        <v>8</v>
+      <c r="G667" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="668">
@@ -17736,11 +15732,8 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H668" t="s">
-        <v>8</v>
+      <c r="G668" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="669">
@@ -17762,11 +15755,8 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H669" t="s">
-        <v>8</v>
+      <c r="G669" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -17788,11 +15778,8 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H670" t="s">
-        <v>8</v>
+      <c r="G670" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -17814,11 +15801,8 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H671" t="s">
-        <v>8</v>
+      <c r="G671" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="672">
@@ -17840,11 +15824,8 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="n">
-        <v>0.0201999992132187</v>
-      </c>
-      <c r="H672" t="s">
-        <v>8</v>
+      <c r="G672" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="673">
@@ -17866,11 +15847,8 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="n">
-        <v>0.0206000003963709</v>
-      </c>
-      <c r="H673" t="s">
-        <v>8</v>
+      <c r="G673" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="674">
@@ -17892,11 +15870,8 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="n">
-        <v>0.0208000000566244</v>
-      </c>
-      <c r="H674" t="s">
-        <v>8</v>
+      <c r="G674" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="675">
@@ -17918,11 +15893,8 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="n">
-        <v>0.0211999993771315</v>
-      </c>
-      <c r="H675" t="s">
-        <v>8</v>
+      <c r="G675" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="676">
@@ -17944,11 +15916,8 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="n">
-        <v>0.02280000038445</v>
-      </c>
-      <c r="H676" t="s">
-        <v>8</v>
+      <c r="G676" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="677">
@@ -17970,11 +15939,29 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="n">
-        <v>0.0216000005602837</v>
-      </c>
-      <c r="H677" t="s">
-        <v>8</v>
+      <c r="G677" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B678" t="n">
+        <v>1623367</v>
+      </c>
+      <c r="C678" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="D678" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="F678"/>
+      <c r="G678" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -394,6 +397,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -414,8 +420,11 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -437,8 +446,11 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +472,11 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -483,8 +498,11 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -506,8 +524,11 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -529,8 +550,11 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -552,8 +576,11 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -575,8 +602,11 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -598,8 +628,11 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -621,8 +654,11 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +680,11 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -667,8 +706,11 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -690,8 +732,11 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -713,8 +758,11 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -736,8 +784,11 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -759,8 +810,11 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -782,8 +836,11 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,8 +862,11 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -828,8 +888,11 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -851,8 +914,11 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -874,8 +940,11 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -897,8 +966,11 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -920,8 +992,11 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -943,8 +1018,11 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -966,8 +1044,11 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -989,8 +1070,11 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" t="n">
+        <v>0.019845999777317</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1012,8 +1096,11 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1035,8 +1122,11 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1058,8 +1148,11 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
+      <c r="G30" t="n">
+        <v>0.01923399977386</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1081,8 +1174,11 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1104,8 +1200,11 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1127,8 +1226,11 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1150,8 +1252,11 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1173,8 +1278,11 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1196,8 +1304,11 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1219,8 +1330,11 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1242,8 +1356,11 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1265,8 +1382,11 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1288,8 +1408,11 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1311,8 +1434,11 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1334,8 +1460,11 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="G42" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1357,8 +1486,11 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1380,8 +1512,11 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,8 +1538,11 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -1426,8 +1564,11 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1449,8 +1590,11 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1472,8 +1616,11 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1495,8 +1642,11 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1518,8 +1668,11 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1541,8 +1694,11 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1564,8 +1720,11 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1587,8 +1746,11 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -1610,8 +1772,11 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1633,8 +1798,11 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1656,8 +1824,11 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1679,8 +1850,11 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -1702,8 +1876,11 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1725,8 +1902,11 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1748,8 +1928,11 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="s">
-        <v>7</v>
+      <c r="G60" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1771,8 +1954,11 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="s">
-        <v>7</v>
+      <c r="G61" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1794,8 +1980,11 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="s">
-        <v>7</v>
+      <c r="G62" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1817,8 +2006,11 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1840,8 +2032,11 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1863,8 +2058,11 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1886,8 +2084,11 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1909,8 +2110,11 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1932,8 +2136,11 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -1955,8 +2162,11 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1978,8 +2188,11 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -2001,8 +2214,11 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2024,8 +2240,11 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2047,8 +2266,11 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -2070,8 +2292,11 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -2093,8 +2318,11 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -2116,8 +2344,11 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2139,8 +2370,11 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -2162,8 +2396,11 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -2185,8 +2422,11 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2208,8 +2448,11 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
+      <c r="G80" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -2231,8 +2474,11 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2254,8 +2500,11 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2277,8 +2526,11 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2300,8 +2552,11 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2323,8 +2578,11 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2346,8 +2604,11 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -2369,8 +2630,11 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -2392,8 +2656,11 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2415,8 +2682,11 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -2438,8 +2708,11 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2461,8 +2734,11 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2484,8 +2760,11 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2507,8 +2786,11 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2530,8 +2812,11 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2553,8 +2838,11 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2576,8 +2864,11 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2599,8 +2890,11 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="s">
-        <v>7</v>
+      <c r="G97" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2622,8 +2916,11 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="s">
-        <v>7</v>
+      <c r="G98" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -2645,8 +2942,11 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -2668,8 +2968,11 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -2691,8 +2994,11 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2714,8 +3020,11 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2737,8 +3046,11 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -2760,8 +3072,11 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -2783,8 +3098,11 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2806,8 +3124,11 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="s">
-        <v>7</v>
+      <c r="G106" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -2829,8 +3150,11 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -2852,8 +3176,11 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -2875,8 +3202,11 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2898,8 +3228,11 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -2921,8 +3254,11 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -2944,8 +3280,11 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -2967,8 +3306,11 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2990,8 +3332,11 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3013,8 +3358,11 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -3036,8 +3384,11 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -3059,8 +3410,11 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -3082,8 +3436,11 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3105,8 +3462,11 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -3128,8 +3488,11 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -3151,8 +3514,11 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="G121" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3174,8 +3540,11 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -3197,8 +3566,11 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H123" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3220,8 +3592,11 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -3243,8 +3618,11 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H125" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3266,8 +3644,11 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H126" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -3289,8 +3670,11 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H127" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3312,8 +3696,11 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H128" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -3335,8 +3722,11 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H129" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -3358,8 +3748,11 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H130" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -3381,8 +3774,11 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H131" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132">
@@ -3404,8 +3800,11 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H132" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -3427,8 +3826,11 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H133" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134">
@@ -3450,8 +3852,11 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -3473,8 +3878,11 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="s">
-        <v>7</v>
+      <c r="G135" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136">
@@ -3496,8 +3904,11 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="s">
-        <v>7</v>
+      <c r="G136" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137">
@@ -3519,8 +3930,11 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="s">
-        <v>7</v>
+      <c r="G137" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -3542,8 +3956,11 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3565,8 +3982,11 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140">
@@ -3588,8 +4008,11 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141">
@@ -3611,8 +4034,11 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -3634,8 +4060,11 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,8 +4086,11 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
@@ -3680,8 +4112,11 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -3703,8 +4138,11 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146">
@@ -3726,8 +4164,11 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3749,8 +4190,11 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148">
@@ -3772,8 +4216,11 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3795,8 +4242,11 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
+      <c r="G149" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150">
@@ -3818,8 +4268,11 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -3841,8 +4294,11 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
@@ -3864,8 +4320,11 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="s">
-        <v>7</v>
+      <c r="G152" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3887,8 +4346,11 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="s">
-        <v>7</v>
+      <c r="G153" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,8 +4372,11 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3933,8 +4398,11 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156">
@@ -3956,8 +4424,11 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -3979,8 +4450,11 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158">
@@ -4002,8 +4476,11 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -4025,8 +4502,11 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
+      <c r="G159" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -4048,8 +4528,11 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="s">
-        <v>7</v>
+      <c r="G160" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161">
@@ -4071,8 +4554,11 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="s">
-        <v>7</v>
+      <c r="G161" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162">
@@ -4094,8 +4580,11 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="s">
-        <v>7</v>
+      <c r="G162" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -4117,8 +4606,11 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="s">
-        <v>7</v>
+      <c r="G163" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -4140,8 +4632,11 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="s">
-        <v>7</v>
+      <c r="G164" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -4163,8 +4658,11 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="s">
-        <v>7</v>
+      <c r="G165" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -4186,8 +4684,11 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -4209,8 +4710,11 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -4232,8 +4736,11 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169">
@@ -4255,8 +4762,11 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4278,8 +4788,11 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H170" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -4301,8 +4814,11 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="s">
-        <v>7</v>
+      <c r="G171" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4324,8 +4840,11 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="s">
-        <v>7</v>
+      <c r="G172" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H172" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4347,8 +4866,11 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H173" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4370,8 +4892,11 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
+      <c r="G174" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H174" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -4393,8 +4918,11 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
+      <c r="G175" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H175" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176">
@@ -4416,8 +4944,11 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="s">
-        <v>7</v>
+      <c r="G176" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H176" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -4439,8 +4970,11 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="s">
-        <v>7</v>
+      <c r="G177" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H177" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -4462,8 +4996,11 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H178" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4485,8 +5022,11 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
+      <c r="G179" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H179" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4508,8 +5048,11 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="s">
-        <v>7</v>
+      <c r="G180" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H180" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
@@ -4531,8 +5074,11 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="s">
-        <v>7</v>
+      <c r="G181" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H181" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182">
@@ -4554,8 +5100,11 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="s">
-        <v>7</v>
+      <c r="G182" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H182" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183">
@@ -4577,8 +5126,11 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="s">
-        <v>7</v>
+      <c r="G183" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H183" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
@@ -4600,8 +5152,11 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="s">
-        <v>7</v>
+      <c r="G184" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185">
@@ -4623,8 +5178,11 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="s">
-        <v>7</v>
+      <c r="G185" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H185" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186">
@@ -4646,8 +5204,11 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="s">
-        <v>7</v>
+      <c r="G186" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H186" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187">
@@ -4669,8 +5230,11 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="s">
-        <v>7</v>
+      <c r="G187" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H187" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4692,8 +5256,11 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="s">
-        <v>7</v>
+      <c r="G188" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H188" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189">
@@ -4715,8 +5282,11 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="s">
-        <v>7</v>
+      <c r="G189" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H189" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4738,8 +5308,11 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="s">
-        <v>7</v>
+      <c r="G190" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H190" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4761,8 +5334,11 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="s">
-        <v>7</v>
+      <c r="G191" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H191" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -4784,8 +5360,11 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="s">
-        <v>7</v>
+      <c r="G192" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H192" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4807,8 +5386,11 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="s">
-        <v>7</v>
+      <c r="G193" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H193" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194">
@@ -4830,8 +5412,11 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="s">
-        <v>7</v>
+      <c r="G194" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H194" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195">
@@ -4853,8 +5438,11 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="s">
-        <v>7</v>
+      <c r="G195" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H195" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -4876,8 +5464,11 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="s">
-        <v>7</v>
+      <c r="G196" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H196" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -4899,8 +5490,11 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="s">
-        <v>7</v>
+      <c r="G197" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -4922,8 +5516,11 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="s">
-        <v>7</v>
+      <c r="G198" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H198" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199">
@@ -4945,8 +5542,11 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="s">
-        <v>7</v>
+      <c r="G199" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H199" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -4968,8 +5568,11 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="s">
-        <v>7</v>
+      <c r="G200" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H200" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201">
@@ -4991,8 +5594,11 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="s">
-        <v>7</v>
+      <c r="G201" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H201" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -5014,8 +5620,11 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="s">
-        <v>7</v>
+      <c r="G202" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H202" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -5037,8 +5646,11 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="s">
-        <v>7</v>
+      <c r="G203" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -5060,8 +5672,11 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="s">
-        <v>7</v>
+      <c r="G204" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H204" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -5083,8 +5698,11 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="s">
-        <v>7</v>
+      <c r="G205" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H205" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -5106,8 +5724,11 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="s">
-        <v>7</v>
+      <c r="G206" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H206" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207">
@@ -5129,8 +5750,11 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="s">
-        <v>7</v>
+      <c r="G207" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H207" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -5152,8 +5776,11 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="s">
-        <v>7</v>
+      <c r="G208" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H208" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209">
@@ -5175,8 +5802,11 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="s">
-        <v>7</v>
+      <c r="G209" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H209" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -5198,8 +5828,11 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="s">
-        <v>7</v>
+      <c r="G210" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H210" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5221,8 +5854,11 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="s">
-        <v>7</v>
+      <c r="G211" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H211" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -5244,8 +5880,11 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="s">
-        <v>7</v>
+      <c r="G212" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H212" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213">
@@ -5267,8 +5906,11 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="s">
-        <v>7</v>
+      <c r="G213" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H213" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214">
@@ -5290,8 +5932,11 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="s">
-        <v>7</v>
+      <c r="G214" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H214" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5313,8 +5958,11 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="s">
-        <v>7</v>
+      <c r="G215" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H215" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5336,8 +5984,11 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="s">
-        <v>7</v>
+      <c r="G216" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H216" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -5359,8 +6010,11 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="s">
-        <v>7</v>
+      <c r="G217" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H217" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5382,8 +6036,11 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="s">
-        <v>7</v>
+      <c r="G218" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H218" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -5405,8 +6062,11 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="s">
-        <v>7</v>
+      <c r="G219" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H219" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -5428,8 +6088,11 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="s">
-        <v>7</v>
+      <c r="G220" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H220" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -5451,8 +6114,11 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="s">
-        <v>7</v>
+      <c r="G221" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H221" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222">
@@ -5474,8 +6140,11 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="s">
-        <v>7</v>
+      <c r="G222" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H222" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -5497,8 +6166,11 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="s">
-        <v>7</v>
+      <c r="G223" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H223" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224">
@@ -5520,8 +6192,11 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="s">
-        <v>7</v>
+      <c r="G224" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H224" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225">
@@ -5543,8 +6218,11 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="s">
-        <v>7</v>
+      <c r="G225" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H225" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -5566,8 +6244,11 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="s">
-        <v>7</v>
+      <c r="G226" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H226" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5589,8 +6270,11 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="s">
-        <v>7</v>
+      <c r="G227" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H227" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5612,8 +6296,11 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="s">
-        <v>7</v>
+      <c r="G228" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H228" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229">
@@ -5635,8 +6322,11 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="s">
-        <v>7</v>
+      <c r="G229" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H229" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5658,8 +6348,11 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="s">
-        <v>7</v>
+      <c r="G230" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H230" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5681,8 +6374,11 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="s">
-        <v>7</v>
+      <c r="G231" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H231" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5704,8 +6400,11 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="s">
-        <v>7</v>
+      <c r="G232" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H232" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5727,8 +6426,11 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="s">
-        <v>7</v>
+      <c r="G233" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H233" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234">
@@ -5750,8 +6452,11 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="s">
-        <v>7</v>
+      <c r="G234" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H234" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -5773,8 +6478,11 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="s">
-        <v>7</v>
+      <c r="G235" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H235" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -5796,8 +6504,11 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="s">
-        <v>7</v>
+      <c r="G236" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H236" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -5819,8 +6530,11 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="s">
-        <v>7</v>
+      <c r="G237" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H237" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -5842,8 +6556,11 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="s">
-        <v>7</v>
+      <c r="G238" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H238" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239">
@@ -5865,8 +6582,11 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="s">
-        <v>7</v>
+      <c r="G239" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H239" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5888,8 +6608,11 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="s">
-        <v>7</v>
+      <c r="G240" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H240" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -5911,8 +6634,11 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="s">
-        <v>7</v>
+      <c r="G241" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H241" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -5934,8 +6660,11 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="s">
-        <v>7</v>
+      <c r="G242" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H242" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5957,8 +6686,11 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="s">
-        <v>7</v>
+      <c r="G243" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H243" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -5980,8 +6712,11 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="s">
-        <v>7</v>
+      <c r="G244" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H244" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -6003,8 +6738,11 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="s">
-        <v>7</v>
+      <c r="G245" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H245" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6026,8 +6764,11 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="s">
-        <v>7</v>
+      <c r="G246" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H246" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -6049,8 +6790,11 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="s">
-        <v>7</v>
+      <c r="G247" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H247" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -6072,8 +6816,11 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="s">
-        <v>7</v>
+      <c r="G248" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H248" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -6095,8 +6842,11 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="s">
-        <v>7</v>
+      <c r="G249" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H249" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -6118,8 +6868,11 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="s">
-        <v>7</v>
+      <c r="G250" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H250" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251">
@@ -6141,8 +6894,11 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="s">
-        <v>7</v>
+      <c r="G251" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H251" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6164,8 +6920,11 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="s">
-        <v>7</v>
+      <c r="G252" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H252" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6187,8 +6946,11 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="s">
-        <v>7</v>
+      <c r="G253" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H253" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6210,8 +6972,11 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="s">
-        <v>7</v>
+      <c r="G254" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H254" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6233,8 +6998,11 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="s">
-        <v>7</v>
+      <c r="G255" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6256,8 +7024,11 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="s">
-        <v>7</v>
+      <c r="G256" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257">
@@ -6279,8 +7050,11 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="s">
-        <v>7</v>
+      <c r="G257" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6302,8 +7076,11 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="s">
-        <v>7</v>
+      <c r="G258" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259">
@@ -6325,8 +7102,11 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="s">
-        <v>7</v>
+      <c r="G259" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H259" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260">
@@ -6348,8 +7128,11 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="s">
-        <v>7</v>
+      <c r="G260" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H260" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261">
@@ -6371,8 +7154,11 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="s">
-        <v>7</v>
+      <c r="G261" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H261" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -6394,8 +7180,11 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="s">
-        <v>7</v>
+      <c r="G262" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H262" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263">
@@ -6417,8 +7206,11 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="s">
-        <v>7</v>
+      <c r="G263" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H263" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264">
@@ -6440,8 +7232,11 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="s">
-        <v>7</v>
+      <c r="G264" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H264" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265">
@@ -6463,8 +7258,11 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="s">
-        <v>7</v>
+      <c r="G265" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H265" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -6486,8 +7284,11 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="s">
-        <v>7</v>
+      <c r="G266" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H266" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6509,8 +7310,11 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="s">
-        <v>7</v>
+      <c r="G267" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H267" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -6532,8 +7336,11 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="s">
-        <v>7</v>
+      <c r="G268" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H268" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -6555,8 +7362,11 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="s">
-        <v>7</v>
+      <c r="G269" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H269" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -6578,8 +7388,11 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="s">
-        <v>7</v>
+      <c r="G270" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H270" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271">
@@ -6601,8 +7414,11 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="s">
-        <v>7</v>
+      <c r="G271" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H271" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -6624,8 +7440,11 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="s">
-        <v>7</v>
+      <c r="G272" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H272" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -6647,8 +7466,11 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
+      <c r="G273" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H273" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6670,8 +7492,11 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="s">
-        <v>7</v>
+      <c r="G274" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H274" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -6693,8 +7518,11 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="s">
-        <v>7</v>
+      <c r="G275" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H275" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6716,8 +7544,11 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="s">
-        <v>7</v>
+      <c r="G276" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H276" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6739,8 +7570,11 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="s">
-        <v>7</v>
+      <c r="G277" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H277" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6762,8 +7596,11 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="s">
-        <v>7</v>
+      <c r="G278" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H278" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6785,8 +7622,11 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="s">
-        <v>7</v>
+      <c r="G279" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H279" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -6808,8 +7648,11 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="s">
-        <v>7</v>
+      <c r="G280" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H280" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -6831,8 +7674,11 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="s">
-        <v>7</v>
+      <c r="G281" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H281" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6854,8 +7700,11 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="s">
-        <v>7</v>
+      <c r="G282" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H282" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -6877,8 +7726,11 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="s">
-        <v>7</v>
+      <c r="G283" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H283" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284">
@@ -6900,8 +7752,11 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="s">
-        <v>7</v>
+      <c r="G284" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H284" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -6923,8 +7778,11 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="s">
-        <v>7</v>
+      <c r="G285" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H285" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6946,8 +7804,11 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="s">
-        <v>7</v>
+      <c r="G286" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H286" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6969,8 +7830,11 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="s">
-        <v>7</v>
+      <c r="G287" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H287" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6992,8 +7856,11 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="s">
-        <v>7</v>
+      <c r="G288" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H288" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -7015,8 +7882,11 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="s">
-        <v>7</v>
+      <c r="G289" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H289" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -7038,8 +7908,11 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="s">
-        <v>7</v>
+      <c r="G290" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H290" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7061,8 +7934,11 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="s">
-        <v>7</v>
+      <c r="G291" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H291" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -7084,8 +7960,11 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="s">
-        <v>7</v>
+      <c r="G292" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H292" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -7107,8 +7986,11 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="s">
-        <v>7</v>
+      <c r="G293" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H293" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -7130,8 +8012,11 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="s">
-        <v>7</v>
+      <c r="G294" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H294" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295">
@@ -7153,8 +8038,11 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="s">
-        <v>7</v>
+      <c r="G295" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H295" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -7176,8 +8064,11 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="s">
-        <v>7</v>
+      <c r="G296" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H296" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -7199,8 +8090,11 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="s">
-        <v>7</v>
+      <c r="G297" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H297" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -7222,8 +8116,11 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="s">
-        <v>7</v>
+      <c r="G298" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -7245,8 +8142,11 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="s">
-        <v>7</v>
+      <c r="G299" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H299" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -7268,8 +8168,11 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="s">
-        <v>7</v>
+      <c r="G300" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H300" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -7291,8 +8194,11 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="s">
-        <v>7</v>
+      <c r="G301" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H301" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7314,8 +8220,11 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="s">
-        <v>7</v>
+      <c r="G302" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H302" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -7337,8 +8246,11 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="s">
-        <v>7</v>
+      <c r="G303" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H303" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7360,8 +8272,11 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="s">
-        <v>7</v>
+      <c r="G304" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H304" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305">
@@ -7383,8 +8298,11 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="s">
-        <v>7</v>
+      <c r="G305" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H305" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -7406,8 +8324,11 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="s">
-        <v>7</v>
+      <c r="G306" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H306" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307">
@@ -7429,8 +8350,11 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="s">
-        <v>7</v>
+      <c r="G307" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H307" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308">
@@ -7452,8 +8376,11 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="s">
-        <v>7</v>
+      <c r="G308" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H308" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309">
@@ -7475,8 +8402,11 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="s">
-        <v>7</v>
+      <c r="G309" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H309" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310">
@@ -7498,8 +8428,11 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="s">
-        <v>7</v>
+      <c r="G310" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H310" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -7521,8 +8454,11 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="s">
-        <v>7</v>
+      <c r="G311" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H311" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -7544,8 +8480,11 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="s">
-        <v>7</v>
+      <c r="G312" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H312" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -7567,8 +8506,11 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="s">
-        <v>7</v>
+      <c r="G313" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H313" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7590,8 +8532,11 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="s">
-        <v>7</v>
+      <c r="G314" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H314" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315">
@@ -7613,8 +8558,11 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="s">
-        <v>7</v>
+      <c r="G315" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H315" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -7636,8 +8584,11 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="s">
-        <v>7</v>
+      <c r="G316" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H316" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -7659,8 +8610,11 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="s">
-        <v>7</v>
+      <c r="G317" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H317" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7682,8 +8636,11 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="s">
-        <v>7</v>
+      <c r="G318" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H318" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319">
@@ -7705,8 +8662,11 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="s">
-        <v>7</v>
+      <c r="G319" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H319" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -7728,8 +8688,11 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="s">
-        <v>7</v>
+      <c r="G320" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H320" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -7751,8 +8714,11 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="s">
-        <v>7</v>
+      <c r="G321" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H321" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -7774,8 +8740,11 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="s">
-        <v>7</v>
+      <c r="G322" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H322" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -7797,8 +8766,11 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="s">
-        <v>7</v>
+      <c r="G323" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H323" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7820,8 +8792,11 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="s">
-        <v>7</v>
+      <c r="G324" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H324" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7843,8 +8818,11 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="s">
-        <v>7</v>
+      <c r="G325" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H325" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -7866,8 +8844,11 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="s">
-        <v>7</v>
+      <c r="G326" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H326" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327">
@@ -7889,8 +8870,11 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="s">
-        <v>7</v>
+      <c r="G327" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H327" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7912,8 +8896,11 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="s">
-        <v>7</v>
+      <c r="G328" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H328" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329">
@@ -7935,8 +8922,11 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="s">
-        <v>7</v>
+      <c r="G329" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H329" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7958,8 +8948,11 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="s">
-        <v>7</v>
+      <c r="G330" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H330" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -7981,8 +8974,11 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="s">
-        <v>7</v>
+      <c r="G331" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332">
@@ -8004,8 +9000,11 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="s">
-        <v>7</v>
+      <c r="G332" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H332" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8027,8 +9026,11 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="s">
-        <v>7</v>
+      <c r="G333" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H333" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -8050,8 +9052,11 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="s">
-        <v>7</v>
+      <c r="G334" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H334" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -8073,8 +9078,11 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="s">
-        <v>7</v>
+      <c r="G335" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H335" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -8096,8 +9104,11 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="s">
-        <v>7</v>
+      <c r="G336" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H336" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8119,8 +9130,11 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="s">
-        <v>7</v>
+      <c r="G337" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H337" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338">
@@ -8142,8 +9156,11 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="s">
-        <v>7</v>
+      <c r="G338" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H338" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339">
@@ -8165,8 +9182,11 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="s">
-        <v>7</v>
+      <c r="G339" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H339" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -8188,8 +9208,11 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="s">
-        <v>7</v>
+      <c r="G340" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H340" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -8211,8 +9234,11 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="s">
-        <v>7</v>
+      <c r="G341" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H341" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342">
@@ -8234,8 +9260,11 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="s">
-        <v>7</v>
+      <c r="G342" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H342" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343">
@@ -8257,8 +9286,11 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="s">
-        <v>7</v>
+      <c r="G343" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H343" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344">
@@ -8280,8 +9312,11 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="s">
-        <v>7</v>
+      <c r="G344" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H344" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -8303,8 +9338,11 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="s">
-        <v>7</v>
+      <c r="G345" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H345" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -8326,8 +9364,11 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="s">
-        <v>7</v>
+      <c r="G346" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H346" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -8349,8 +9390,11 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="s">
-        <v>7</v>
+      <c r="G347" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H347" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348">
@@ -8372,8 +9416,11 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="s">
-        <v>7</v>
+      <c r="G348" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H348" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349">
@@ -8395,8 +9442,11 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="s">
-        <v>7</v>
+      <c r="G349" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H349" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -8418,8 +9468,11 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="s">
-        <v>7</v>
+      <c r="G350" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H350" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351">
@@ -8441,8 +9494,11 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="s">
-        <v>7</v>
+      <c r="G351" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H351" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8464,8 +9520,11 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="s">
-        <v>7</v>
+      <c r="G352" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H352" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -8487,8 +9546,11 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="s">
-        <v>7</v>
+      <c r="G353" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H353" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354">
@@ -8510,8 +9572,11 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="s">
-        <v>7</v>
+      <c r="G354" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H354" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8533,8 +9598,11 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="s">
-        <v>7</v>
+      <c r="G355" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H355" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -8556,8 +9624,11 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="s">
-        <v>7</v>
+      <c r="G356" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H356" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8579,8 +9650,11 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="s">
-        <v>7</v>
+      <c r="G357" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H357" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -8602,8 +9676,11 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="s">
-        <v>7</v>
+      <c r="G358" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H358" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359">
@@ -8625,8 +9702,11 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="s">
-        <v>7</v>
+      <c r="G359" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H359" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8648,8 +9728,11 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="s">
-        <v>7</v>
+      <c r="G360" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H360" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361">
@@ -8671,8 +9754,11 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="s">
-        <v>7</v>
+      <c r="G361" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H361" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362">
@@ -8694,8 +9780,11 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="s">
-        <v>7</v>
+      <c r="G362" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H362" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -8717,8 +9806,11 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="s">
-        <v>7</v>
+      <c r="G363" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H363" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8740,8 +9832,11 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="s">
-        <v>7</v>
+      <c r="G364" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H364" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8763,8 +9858,11 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="s">
-        <v>7</v>
+      <c r="G365" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H365" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8786,8 +9884,11 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="s">
-        <v>7</v>
+      <c r="G366" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H366" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8809,8 +9910,11 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="s">
-        <v>7</v>
+      <c r="G367" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H367" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8832,8 +9936,11 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="s">
-        <v>7</v>
+      <c r="G368" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H368" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -8855,8 +9962,11 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="s">
-        <v>7</v>
+      <c r="G369" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H369" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8878,8 +9988,11 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="s">
-        <v>7</v>
+      <c r="G370" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H370" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8901,8 +10014,11 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="s">
-        <v>7</v>
+      <c r="G371" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H371" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8924,8 +10040,11 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="s">
-        <v>7</v>
+      <c r="G372" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H372" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -8947,8 +10066,11 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="s">
-        <v>7</v>
+      <c r="G373" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H373" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8970,8 +10092,11 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="s">
-        <v>7</v>
+      <c r="G374" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H374" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8993,8 +10118,11 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="s">
-        <v>7</v>
+      <c r="G375" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H375" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -9016,8 +10144,11 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="s">
-        <v>7</v>
+      <c r="G376" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H376" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -9039,8 +10170,11 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="s">
-        <v>7</v>
+      <c r="G377" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H377" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -9062,8 +10196,11 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="s">
-        <v>7</v>
+      <c r="G378" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H378" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -9085,8 +10222,11 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="s">
-        <v>7</v>
+      <c r="G379" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H379" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -9108,8 +10248,11 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="s">
-        <v>7</v>
+      <c r="G380" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H380" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -9131,8 +10274,11 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="s">
-        <v>7</v>
+      <c r="G381" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H381" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -9154,8 +10300,11 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="s">
-        <v>7</v>
+      <c r="G382" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H382" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -9177,8 +10326,11 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="s">
-        <v>7</v>
+      <c r="G383" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H383" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -9200,8 +10352,11 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="s">
-        <v>7</v>
+      <c r="G384" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H384" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -9223,8 +10378,11 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="s">
-        <v>7</v>
+      <c r="G385" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H385" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -9246,8 +10404,11 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="s">
-        <v>7</v>
+      <c r="G386" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H386" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -9269,8 +10430,11 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="s">
-        <v>7</v>
+      <c r="G387" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H387" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -9292,8 +10456,11 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="s">
-        <v>7</v>
+      <c r="G388" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H388" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -9315,8 +10482,11 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="s">
-        <v>7</v>
+      <c r="G389" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H389" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -9338,8 +10508,11 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="s">
-        <v>7</v>
+      <c r="G390" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H390" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -9361,8 +10534,11 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="s">
-        <v>7</v>
+      <c r="G391" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H391" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -9384,8 +10560,11 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="s">
-        <v>7</v>
+      <c r="G392" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H392" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -9407,8 +10586,11 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="s">
-        <v>7</v>
+      <c r="G393" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H393" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -9430,8 +10612,11 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="s">
-        <v>7</v>
+      <c r="G394" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H394" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -9453,8 +10638,11 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="s">
-        <v>7</v>
+      <c r="G395" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H395" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -9476,8 +10664,11 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="s">
-        <v>7</v>
+      <c r="G396" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H396" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -9499,8 +10690,11 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="s">
-        <v>7</v>
+      <c r="G397" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H397" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -9522,8 +10716,11 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="s">
-        <v>7</v>
+      <c r="G398" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H398" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -9545,8 +10742,11 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="s">
-        <v>7</v>
+      <c r="G399" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H399" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -9568,8 +10768,11 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="s">
-        <v>7</v>
+      <c r="G400" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H400" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -9591,8 +10794,11 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="s">
-        <v>7</v>
+      <c r="G401" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H401" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -9614,8 +10820,11 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="s">
-        <v>7</v>
+      <c r="G402" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H402" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9637,8 +10846,11 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="s">
-        <v>7</v>
+      <c r="G403" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H403" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9660,8 +10872,11 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="s">
-        <v>7</v>
+      <c r="G404" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H404" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -9683,8 +10898,11 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="s">
-        <v>7</v>
+      <c r="G405" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H405" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9706,8 +10924,11 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="s">
-        <v>7</v>
+      <c r="G406" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H406" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -9729,8 +10950,11 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="s">
-        <v>7</v>
+      <c r="G407" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H407" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9752,8 +10976,11 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="s">
-        <v>7</v>
+      <c r="G408" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H408" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -9775,8 +11002,11 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="s">
-        <v>7</v>
+      <c r="G409" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H409" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9798,8 +11028,11 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="s">
-        <v>7</v>
+      <c r="G410" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H410" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9821,8 +11054,11 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="s">
-        <v>7</v>
+      <c r="G411" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H411" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9844,8 +11080,11 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="s">
-        <v>7</v>
+      <c r="G412" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H412" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9867,8 +11106,11 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="s">
-        <v>7</v>
+      <c r="G413" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H413" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -9890,8 +11132,11 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="s">
-        <v>7</v>
+      <c r="G414" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H414" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9913,8 +11158,11 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="s">
-        <v>7</v>
+      <c r="G415" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H415" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9936,8 +11184,11 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="s">
-        <v>7</v>
+      <c r="G416" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H416" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -9959,8 +11210,11 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="s">
-        <v>7</v>
+      <c r="G417" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H417" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -9982,8 +11236,11 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="s">
-        <v>7</v>
+      <c r="G418" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H418" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -10005,8 +11262,11 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="s">
-        <v>7</v>
+      <c r="G419" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H419" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -10028,8 +11288,11 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="s">
-        <v>7</v>
+      <c r="G420" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H420" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -10051,8 +11314,11 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="s">
-        <v>7</v>
+      <c r="G421" t="n">
+        <v>0.018673000857234</v>
+      </c>
+      <c r="H421" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -10074,8 +11340,11 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="s">
-        <v>7</v>
+      <c r="G422" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H422" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -10097,8 +11366,11 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="s">
-        <v>7</v>
+      <c r="G423" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H423" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -10120,8 +11392,11 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="s">
-        <v>7</v>
+      <c r="G424" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H424" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -10143,8 +11418,11 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="s">
-        <v>7</v>
+      <c r="G425" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H425" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -10166,8 +11444,11 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="s">
-        <v>7</v>
+      <c r="G426" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H426" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -10189,8 +11470,11 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="s">
-        <v>7</v>
+      <c r="G427" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H427" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -10212,8 +11496,11 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="s">
-        <v>7</v>
+      <c r="G428" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H428" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -10235,8 +11522,11 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="s">
-        <v>7</v>
+      <c r="G429" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H429" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -10258,8 +11548,11 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="s">
-        <v>7</v>
+      <c r="G430" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H430" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -10281,8 +11574,11 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="s">
-        <v>7</v>
+      <c r="G431" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H431" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -10304,8 +11600,11 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="s">
-        <v>7</v>
+      <c r="G432" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H432" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -10327,8 +11626,11 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="s">
-        <v>7</v>
+      <c r="G433" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H433" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -10350,8 +11652,11 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="s">
-        <v>7</v>
+      <c r="G434" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H434" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -10373,8 +11678,11 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="s">
-        <v>7</v>
+      <c r="G435" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H435" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -10396,8 +11704,11 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="s">
-        <v>7</v>
+      <c r="G436" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H436" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -10419,8 +11730,11 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="s">
-        <v>7</v>
+      <c r="G437" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H437" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -10442,8 +11756,11 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="s">
-        <v>7</v>
+      <c r="G438" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H438" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -10465,8 +11782,11 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="s">
-        <v>7</v>
+      <c r="G439" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H439" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -10488,8 +11808,11 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="s">
-        <v>7</v>
+      <c r="G440" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H440" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -10511,8 +11834,11 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="s">
-        <v>7</v>
+      <c r="G441" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H441" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -10534,8 +11860,11 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="s">
-        <v>7</v>
+      <c r="G442" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H442" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -10557,8 +11886,11 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="s">
-        <v>7</v>
+      <c r="G443" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H443" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -10580,8 +11912,11 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="s">
-        <v>7</v>
+      <c r="G444" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H444" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -10603,8 +11938,11 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="s">
-        <v>7</v>
+      <c r="G445" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H445" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -10626,8 +11964,11 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="s">
-        <v>7</v>
+      <c r="G446" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H446" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -10649,8 +11990,11 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="s">
-        <v>7</v>
+      <c r="G447" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H447" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -10672,8 +12016,11 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="s">
-        <v>7</v>
+      <c r="G448" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H448" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -10695,8 +12042,11 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="s">
-        <v>7</v>
+      <c r="G449" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H449" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -10718,8 +12068,11 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="s">
-        <v>7</v>
+      <c r="G450" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H450" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -10741,8 +12094,11 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="s">
-        <v>7</v>
+      <c r="G451" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H451" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10764,8 +12120,11 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="s">
-        <v>7</v>
+      <c r="G452" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H452" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10787,8 +12146,11 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="s">
-        <v>7</v>
+      <c r="G453" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H453" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -10810,8 +12172,11 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="s">
-        <v>7</v>
+      <c r="G454" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H454" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10833,8 +12198,11 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="s">
-        <v>7</v>
+      <c r="G455" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H455" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10856,8 +12224,11 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="s">
-        <v>7</v>
+      <c r="G456" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H456" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10879,8 +12250,11 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="s">
-        <v>7</v>
+      <c r="G457" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H457" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -10902,8 +12276,11 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="s">
-        <v>7</v>
+      <c r="G458" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H458" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -10925,8 +12302,11 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="s">
-        <v>7</v>
+      <c r="G459" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H459" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -10948,8 +12328,11 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="s">
-        <v>7</v>
+      <c r="G460" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H460" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -10971,8 +12354,11 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="s">
-        <v>7</v>
+      <c r="G461" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H461" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10994,8 +12380,11 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="s">
-        <v>7</v>
+      <c r="G462" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H462" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -11017,8 +12406,11 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="s">
-        <v>7</v>
+      <c r="G463" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H463" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -11040,8 +12432,11 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="s">
-        <v>7</v>
+      <c r="G464" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H464" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -11063,8 +12458,11 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="s">
-        <v>7</v>
+      <c r="G465" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H465" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -11086,8 +12484,11 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="s">
-        <v>7</v>
+      <c r="G466" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H466" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -11109,8 +12510,11 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="s">
-        <v>7</v>
+      <c r="G467" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H467" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -11132,8 +12536,11 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="s">
-        <v>7</v>
+      <c r="G468" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H468" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -11155,8 +12562,11 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="s">
-        <v>7</v>
+      <c r="G469" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -11178,8 +12588,11 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="s">
-        <v>7</v>
+      <c r="G470" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H470" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -11201,8 +12614,11 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="s">
-        <v>7</v>
+      <c r="G471" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H471" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -11224,8 +12640,11 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="s">
-        <v>7</v>
+      <c r="G472" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H472" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -11247,8 +12666,11 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="s">
-        <v>7</v>
+      <c r="G473" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H473" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -11270,8 +12692,11 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="s">
-        <v>7</v>
+      <c r="G474" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H474" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -11293,8 +12718,11 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="s">
-        <v>7</v>
+      <c r="G475" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H475" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -11316,8 +12744,11 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="s">
-        <v>7</v>
+      <c r="G476" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H476" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -11339,8 +12770,11 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="s">
-        <v>7</v>
+      <c r="G477" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H477" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -11362,8 +12796,11 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="s">
-        <v>7</v>
+      <c r="G478" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H478" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -11385,8 +12822,11 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="s">
-        <v>7</v>
+      <c r="G479" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H479" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -11408,8 +12848,11 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="s">
-        <v>7</v>
+      <c r="G480" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H480" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -11431,8 +12874,11 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="s">
-        <v>7</v>
+      <c r="G481" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H481" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -11454,8 +12900,11 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="s">
-        <v>7</v>
+      <c r="G482" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H482" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -11477,8 +12926,11 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="s">
-        <v>7</v>
+      <c r="G483" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H483" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -11500,8 +12952,11 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="s">
-        <v>7</v>
+      <c r="G484" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H484" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -11523,8 +12978,11 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="s">
-        <v>7</v>
+      <c r="G485" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H485" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -11546,8 +13004,11 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="s">
-        <v>7</v>
+      <c r="G486" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H486" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -11569,8 +13030,11 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="s">
-        <v>7</v>
+      <c r="G487" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H487" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="488">
@@ -11592,8 +13056,11 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="s">
-        <v>7</v>
+      <c r="G488" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H488" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -11615,8 +13082,11 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="s">
-        <v>7</v>
+      <c r="G489" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H489" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -11638,8 +13108,11 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="s">
-        <v>7</v>
+      <c r="G490" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H490" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -11661,8 +13134,11 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="s">
-        <v>7</v>
+      <c r="G491" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H491" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -11684,8 +13160,11 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="s">
-        <v>7</v>
+      <c r="G492" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H492" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -11707,8 +13186,11 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="s">
-        <v>7</v>
+      <c r="G493" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H493" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -11730,8 +13212,11 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="s">
-        <v>7</v>
+      <c r="G494" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H494" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -11753,8 +13238,11 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="s">
-        <v>7</v>
+      <c r="G495" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H495" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="496">
@@ -11776,8 +13264,11 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="s">
-        <v>7</v>
+      <c r="G496" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H496" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -11799,8 +13290,11 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="s">
-        <v>7</v>
+      <c r="G497" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H497" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="498">
@@ -11822,8 +13316,11 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="s">
-        <v>7</v>
+      <c r="G498" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H498" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="499">
@@ -11845,8 +13342,11 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="s">
-        <v>7</v>
+      <c r="G499" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H499" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="500">
@@ -11868,8 +13368,11 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="s">
-        <v>7</v>
+      <c r="G500" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H500" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="501">
@@ -11891,8 +13394,11 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="s">
-        <v>7</v>
+      <c r="G501" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H501" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="502">
@@ -11914,8 +13420,11 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="s">
-        <v>7</v>
+      <c r="G502" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H502" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="503">
@@ -11937,8 +13446,11 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="s">
-        <v>7</v>
+      <c r="G503" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H503" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="504">
@@ -11960,8 +13472,11 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="s">
-        <v>7</v>
+      <c r="G504" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H504" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11983,8 +13498,11 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="s">
-        <v>7</v>
+      <c r="G505" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H505" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -12006,8 +13524,11 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="s">
-        <v>7</v>
+      <c r="G506" t="n">
+        <v>0.0154079999774694</v>
+      </c>
+      <c r="H506" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="507">
@@ -12029,8 +13550,11 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="s">
-        <v>7</v>
+      <c r="G507" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H507" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="508">
@@ -12052,8 +13576,11 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="s">
-        <v>7</v>
+      <c r="G508" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H508" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -12075,8 +13602,11 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="s">
-        <v>7</v>
+      <c r="G509" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H509" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -12098,8 +13628,11 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="s">
-        <v>7</v>
+      <c r="G510" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H510" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="511">
@@ -12121,8 +13654,11 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="s">
-        <v>7</v>
+      <c r="G511" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H511" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="512">
@@ -12144,8 +13680,11 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="s">
-        <v>7</v>
+      <c r="G512" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H512" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -12167,8 +13706,11 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="s">
-        <v>7</v>
+      <c r="G513" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H513" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -12190,8 +13732,11 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="s">
-        <v>7</v>
+      <c r="G514" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H514" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="515">
@@ -12213,8 +13758,11 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="s">
-        <v>7</v>
+      <c r="G515" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H515" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="516">
@@ -12236,8 +13784,11 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="s">
-        <v>7</v>
+      <c r="G516" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H516" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="517">
@@ -12259,8 +13810,11 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="s">
-        <v>7</v>
+      <c r="G517" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H517" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="518">
@@ -12282,8 +13836,11 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="s">
-        <v>7</v>
+      <c r="G518" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H518" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="519">
@@ -12305,8 +13862,11 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="s">
-        <v>7</v>
+      <c r="G519" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H519" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -12328,8 +13888,11 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="s">
-        <v>7</v>
+      <c r="G520" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H520" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="521">
@@ -12351,8 +13914,11 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="s">
-        <v>7</v>
+      <c r="G521" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H521" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="522">
@@ -12374,8 +13940,11 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="s">
-        <v>7</v>
+      <c r="G522" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H522" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="523">
@@ -12397,8 +13966,11 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="s">
-        <v>7</v>
+      <c r="G523" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H523" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="524">
@@ -12420,8 +13992,11 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="s">
-        <v>7</v>
+      <c r="G524" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H524" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="525">
@@ -12443,8 +14018,11 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="s">
-        <v>7</v>
+      <c r="G525" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H525" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -12466,8 +14044,11 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="s">
-        <v>7</v>
+      <c r="G526" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H526" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="527">
@@ -12489,8 +14070,11 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="s">
-        <v>7</v>
+      <c r="G527" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H527" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="528">
@@ -12512,8 +14096,11 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="s">
-        <v>7</v>
+      <c r="G528" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H528" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="529">
@@ -12535,8 +14122,11 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="s">
-        <v>7</v>
+      <c r="G529" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H529" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="530">
@@ -12558,8 +14148,11 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="s">
-        <v>7</v>
+      <c r="G530" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H530" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -12581,8 +14174,11 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="s">
-        <v>7</v>
+      <c r="G531" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H531" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -12604,8 +14200,11 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="s">
-        <v>7</v>
+      <c r="G532" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H532" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="533">
@@ -12627,8 +14226,11 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="s">
-        <v>7</v>
+      <c r="G533" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H533" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="534">
@@ -12650,8 +14252,11 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="s">
-        <v>7</v>
+      <c r="G534" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H534" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="535">
@@ -12673,8 +14278,11 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="s">
-        <v>7</v>
+      <c r="G535" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H535" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="536">
@@ -12696,8 +14304,11 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="s">
-        <v>7</v>
+      <c r="G536" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H536" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -12719,8 +14330,11 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="s">
-        <v>7</v>
+      <c r="G537" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H537" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="538">
@@ -12742,8 +14356,11 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="s">
-        <v>7</v>
+      <c r="G538" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H538" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="539">
@@ -12765,8 +14382,11 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="s">
-        <v>7</v>
+      <c r="G539" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H539" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="540">
@@ -12788,8 +14408,11 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="s">
-        <v>7</v>
+      <c r="G540" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H540" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="541">
@@ -12811,8 +14434,11 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="s">
-        <v>7</v>
+      <c r="G541" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H541" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="542">
@@ -12834,8 +14460,11 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="s">
-        <v>7</v>
+      <c r="G542" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H542" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="543">
@@ -12857,8 +14486,11 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="s">
-        <v>7</v>
+      <c r="G543" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H543" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="544">
@@ -12880,8 +14512,11 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="s">
-        <v>7</v>
+      <c r="G544" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H544" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="545">
@@ -12903,8 +14538,11 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="s">
-        <v>7</v>
+      <c r="G545" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H545" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="546">
@@ -12926,8 +14564,11 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="s">
-        <v>7</v>
+      <c r="G546" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H546" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="547">
@@ -12949,8 +14590,11 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="s">
-        <v>7</v>
+      <c r="G547" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H547" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="548">
@@ -12972,8 +14616,11 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="s">
-        <v>7</v>
+      <c r="G548" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H548" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -12995,8 +14642,11 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="s">
-        <v>7</v>
+      <c r="G549" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H549" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="550">
@@ -13018,8 +14668,11 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="s">
-        <v>7</v>
+      <c r="G550" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H550" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="551">
@@ -13041,8 +14694,11 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="s">
-        <v>7</v>
+      <c r="G551" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H551" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="552">
@@ -13064,8 +14720,11 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="s">
-        <v>7</v>
+      <c r="G552" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H552" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="553">
@@ -13087,8 +14746,11 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="s">
-        <v>7</v>
+      <c r="G553" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H553" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="554">
@@ -13110,8 +14772,11 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="s">
-        <v>7</v>
+      <c r="G554" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H554" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -13133,8 +14798,11 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="s">
-        <v>7</v>
+      <c r="G555" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H555" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -13156,8 +14824,11 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="s">
-        <v>7</v>
+      <c r="G556" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H556" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="557">
@@ -13179,8 +14850,11 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="s">
-        <v>7</v>
+      <c r="G557" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H557" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="558">
@@ -13202,8 +14876,11 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="s">
-        <v>7</v>
+      <c r="G558" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H558" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="559">
@@ -13225,8 +14902,11 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="s">
-        <v>7</v>
+      <c r="G559" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H559" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -13248,8 +14928,11 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="s">
-        <v>7</v>
+      <c r="G560" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H560" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="561">
@@ -13271,8 +14954,11 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="s">
-        <v>7</v>
+      <c r="G561" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H561" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="562">
@@ -13294,8 +14980,11 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="s">
-        <v>7</v>
+      <c r="G562" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H562" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="563">
@@ -13317,8 +15006,11 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="s">
-        <v>7</v>
+      <c r="G563" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H563" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="564">
@@ -13340,8 +15032,11 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="s">
-        <v>7</v>
+      <c r="G564" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H564" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="565">
@@ -13363,8 +15058,11 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="s">
-        <v>7</v>
+      <c r="G565" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H565" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -13386,8 +15084,11 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="s">
-        <v>7</v>
+      <c r="G566" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H566" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="567">
@@ -13409,8 +15110,11 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="s">
-        <v>7</v>
+      <c r="G567" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H567" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="568">
@@ -13432,8 +15136,11 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="s">
-        <v>7</v>
+      <c r="G568" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H568" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="569">
@@ -13455,8 +15162,11 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="s">
-        <v>7</v>
+      <c r="G569" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H569" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="570">
@@ -13478,8 +15188,11 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="s">
-        <v>7</v>
+      <c r="G570" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H570" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="571">
@@ -13501,8 +15214,11 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="s">
-        <v>7</v>
+      <c r="G571" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H571" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="572">
@@ -13524,8 +15240,11 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="s">
-        <v>7</v>
+      <c r="G572" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H572" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="573">
@@ -13547,8 +15266,11 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="s">
-        <v>7</v>
+      <c r="G573" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H573" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="574">
@@ -13570,8 +15292,11 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="s">
-        <v>7</v>
+      <c r="G574" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H574" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="575">
@@ -13593,8 +15318,11 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="s">
-        <v>7</v>
+      <c r="G575" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H575" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="576">
@@ -13616,8 +15344,11 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="s">
-        <v>7</v>
+      <c r="G576" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H576" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="577">
@@ -13639,8 +15370,11 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="s">
-        <v>7</v>
+      <c r="G577" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H577" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="578">
@@ -13662,8 +15396,11 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="s">
-        <v>7</v>
+      <c r="G578" t="n">
+        <v>0.0175000000745058</v>
+      </c>
+      <c r="H578" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="579">
@@ -13685,8 +15422,11 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="s">
-        <v>7</v>
+      <c r="G579" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H579" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="580">
@@ -13708,8 +15448,11 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="s">
-        <v>7</v>
+      <c r="G580" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H580" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="581">
@@ -13731,8 +15474,11 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="s">
-        <v>7</v>
+      <c r="G581" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H581" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="582">
@@ -13754,8 +15500,11 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="s">
-        <v>7</v>
+      <c r="G582" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H582" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="583">
@@ -13777,8 +15526,11 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="s">
-        <v>7</v>
+      <c r="G583" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H583" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="584">
@@ -13800,8 +15552,11 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="s">
-        <v>7</v>
+      <c r="G584" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H584" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="585">
@@ -13823,8 +15578,11 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="s">
-        <v>7</v>
+      <c r="G585" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H585" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="586">
@@ -13846,8 +15604,11 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="s">
-        <v>7</v>
+      <c r="G586" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H586" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="587">
@@ -13869,8 +15630,11 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="s">
-        <v>7</v>
+      <c r="G587" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H587" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="588">
@@ -13892,8 +15656,11 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="s">
-        <v>7</v>
+      <c r="G588" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H588" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="589">
@@ -13915,8 +15682,11 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="s">
-        <v>7</v>
+      <c r="G589" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H589" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="590">
@@ -13938,8 +15708,11 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="s">
-        <v>7</v>
+      <c r="G590" t="n">
+        <v>0.0171000007539988</v>
+      </c>
+      <c r="H590" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -13961,8 +15734,11 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="s">
-        <v>7</v>
+      <c r="G591" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H591" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="592">
@@ -13984,8 +15760,11 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="s">
-        <v>7</v>
+      <c r="G592" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H592" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="593">
@@ -14007,8 +15786,11 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="s">
-        <v>7</v>
+      <c r="G593" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H593" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="594">
@@ -14030,8 +15812,11 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="s">
-        <v>7</v>
+      <c r="G594" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="H594" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="595">
@@ -14053,8 +15838,11 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="s">
-        <v>7</v>
+      <c r="G595" t="n">
+        <v>0.0203000009059906</v>
+      </c>
+      <c r="H595" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="596">
@@ -14076,8 +15864,11 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="s">
-        <v>7</v>
+      <c r="G596" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H596" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -14099,8 +15890,11 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="s">
-        <v>7</v>
+      <c r="G597" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H597" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="598">
@@ -14122,8 +15916,11 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="s">
-        <v>7</v>
+      <c r="G598" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H598" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="599">
@@ -14145,8 +15942,11 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="s">
-        <v>7</v>
+      <c r="G599" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H599" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="600">
@@ -14168,8 +15968,11 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="s">
-        <v>7</v>
+      <c r="G600" t="n">
+        <v>0.0183000005781651</v>
+      </c>
+      <c r="H600" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="601">
@@ -14191,8 +15994,11 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="s">
-        <v>7</v>
+      <c r="G601" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H601" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="602">
@@ -14214,8 +16020,11 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="s">
-        <v>7</v>
+      <c r="G602" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H602" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="603">
@@ -14237,8 +16046,11 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="s">
-        <v>7</v>
+      <c r="G603" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H603" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="604">
@@ -14260,8 +16072,11 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="s">
-        <v>7</v>
+      <c r="G604" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="H604" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="605">
@@ -14283,8 +16098,11 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="s">
-        <v>7</v>
+      <c r="G605" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H605" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="606">
@@ -14306,8 +16124,11 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="s">
-        <v>7</v>
+      <c r="G606" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H606" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="607">
@@ -14329,8 +16150,11 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="s">
-        <v>7</v>
+      <c r="G607" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H607" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="608">
@@ -14352,8 +16176,11 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="s">
-        <v>7</v>
+      <c r="G608" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H608" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="609">
@@ -14375,8 +16202,11 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="s">
-        <v>7</v>
+      <c r="G609" t="n">
+        <v>0.0181000009179115</v>
+      </c>
+      <c r="H609" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="610">
@@ -14398,8 +16228,11 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="s">
-        <v>7</v>
+      <c r="G610" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H610" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="611">
@@ -14421,8 +16254,11 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="s">
-        <v>7</v>
+      <c r="G611" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H611" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="612">
@@ -14444,8 +16280,11 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="s">
-        <v>7</v>
+      <c r="G612" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H612" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="613">
@@ -14467,8 +16306,11 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="s">
-        <v>7</v>
+      <c r="G613" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H613" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="614">
@@ -14490,8 +16332,11 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="s">
-        <v>7</v>
+      <c r="G614" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H614" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="615">
@@ -14513,8 +16358,11 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="s">
-        <v>7</v>
+      <c r="G615" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H615" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="616">
@@ -14536,8 +16384,11 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="s">
-        <v>7</v>
+      <c r="G616" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H616" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="617">
@@ -14559,8 +16410,11 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="s">
-        <v>7</v>
+      <c r="G617" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H617" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="618">
@@ -14582,8 +16436,11 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="s">
-        <v>7</v>
+      <c r="G618" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H618" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="619">
@@ -14605,8 +16462,11 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="s">
-        <v>7</v>
+      <c r="G619" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H619" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="620">
@@ -14628,8 +16488,11 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="s">
-        <v>7</v>
+      <c r="G620" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H620" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="621">
@@ -14651,8 +16514,11 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="s">
-        <v>7</v>
+      <c r="G621" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H621" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="622">
@@ -14674,8 +16540,11 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="s">
-        <v>7</v>
+      <c r="G622" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H622" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="623">
@@ -14697,8 +16566,11 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="s">
-        <v>7</v>
+      <c r="G623" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H623" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="624">
@@ -14720,8 +16592,11 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="s">
-        <v>7</v>
+      <c r="G624" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H624" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="625">
@@ -14743,8 +16618,11 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="s">
-        <v>7</v>
+      <c r="G625" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H625" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="626">
@@ -14766,8 +16644,11 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="s">
-        <v>7</v>
+      <c r="G626" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H626" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="627">
@@ -14789,8 +16670,11 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="s">
-        <v>7</v>
+      <c r="G627" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H627" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="628">
@@ -14812,8 +16696,11 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="s">
-        <v>7</v>
+      <c r="G628" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H628" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="629">
@@ -14835,8 +16722,11 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="s">
-        <v>7</v>
+      <c r="G629" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H629" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="630">
@@ -14858,8 +16748,11 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="s">
-        <v>7</v>
+      <c r="G630" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H630" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="631">
@@ -14881,8 +16774,11 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="s">
-        <v>7</v>
+      <c r="G631" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H631" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="632">
@@ -14904,8 +16800,11 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="s">
-        <v>7</v>
+      <c r="G632" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H632" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="633">
@@ -14927,8 +16826,11 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="s">
-        <v>7</v>
+      <c r="G633" t="n">
+        <v>0.0172000005841255</v>
+      </c>
+      <c r="H633" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="634">
@@ -14950,8 +16852,11 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="s">
-        <v>7</v>
+      <c r="G634" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H634" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="635">
@@ -14973,8 +16878,11 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="s">
-        <v>7</v>
+      <c r="G635" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H635" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="636">
@@ -14996,8 +16904,11 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="s">
-        <v>7</v>
+      <c r="G636" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H636" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="637">
@@ -15019,8 +16930,11 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="s">
-        <v>7</v>
+      <c r="G637" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H637" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="638">
@@ -15042,8 +16956,11 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="s">
-        <v>7</v>
+      <c r="G638" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H638" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="639">
@@ -15065,8 +16982,11 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="s">
-        <v>7</v>
+      <c r="G639" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H639" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="640">
@@ -15088,8 +17008,11 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="s">
-        <v>7</v>
+      <c r="G640" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H640" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="641">
@@ -15111,8 +17034,11 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="s">
-        <v>7</v>
+      <c r="G641" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H641" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="642">
@@ -15134,8 +17060,11 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="s">
-        <v>7</v>
+      <c r="G642" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H642" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="643">
@@ -15157,8 +17086,11 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="s">
-        <v>7</v>
+      <c r="G643" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H643" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="644">
@@ -15180,8 +17112,11 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="s">
-        <v>7</v>
+      <c r="G644" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H644" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="645">
@@ -15203,8 +17138,11 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="s">
-        <v>7</v>
+      <c r="G645" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H645" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="646">
@@ -15226,8 +17164,11 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="s">
-        <v>7</v>
+      <c r="G646" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H646" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="647">
@@ -15249,8 +17190,11 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="s">
-        <v>7</v>
+      <c r="G647" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H647" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="648">
@@ -15272,8 +17216,11 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="s">
-        <v>7</v>
+      <c r="G648" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H648" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="649">
@@ -15295,8 +17242,11 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="s">
-        <v>7</v>
+      <c r="G649" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H649" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="650">
@@ -15318,8 +17268,11 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="s">
-        <v>7</v>
+      <c r="G650" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H650" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="651">
@@ -15341,8 +17294,11 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="s">
-        <v>7</v>
+      <c r="G651" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H651" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="652">
@@ -15364,8 +17320,11 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="s">
-        <v>7</v>
+      <c r="G652" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H652" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="653">
@@ -15387,8 +17346,11 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="s">
-        <v>7</v>
+      <c r="G653" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H653" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="654">
@@ -15410,8 +17372,11 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="s">
-        <v>7</v>
+      <c r="G654" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H654" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="655">
@@ -15433,8 +17398,11 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="s">
-        <v>7</v>
+      <c r="G655" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H655" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="656">
@@ -15456,8 +17424,11 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="s">
-        <v>7</v>
+      <c r="G656" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H656" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="657">
@@ -15479,8 +17450,11 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="s">
-        <v>7</v>
+      <c r="G657" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H657" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="658">
@@ -15502,8 +17476,11 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="s">
-        <v>7</v>
+      <c r="G658" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H658" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="659">
@@ -15525,8 +17502,11 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="s">
-        <v>7</v>
+      <c r="G659" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H659" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="660">
@@ -15548,8 +17528,11 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="s">
-        <v>7</v>
+      <c r="G660" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H660" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="661">
@@ -15571,8 +17554,11 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="s">
-        <v>7</v>
+      <c r="G661" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H661" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="662">
@@ -15594,8 +17580,11 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="s">
-        <v>7</v>
+      <c r="G662" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H662" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="663">
@@ -15617,8 +17606,11 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="s">
-        <v>7</v>
+      <c r="G663" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H663" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="664">
@@ -15640,8 +17632,11 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="s">
-        <v>7</v>
+      <c r="G664" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H664" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="665">
@@ -15663,8 +17658,11 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="s">
-        <v>7</v>
+      <c r="G665" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H665" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="666">
@@ -15686,8 +17684,11 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="s">
-        <v>7</v>
+      <c r="G666" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H666" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="667">
@@ -15709,8 +17710,11 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="s">
-        <v>7</v>
+      <c r="G667" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H667" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="668">
@@ -15732,8 +17736,11 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="s">
-        <v>7</v>
+      <c r="G668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H668" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="669">
@@ -15755,8 +17762,11 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="s">
-        <v>7</v>
+      <c r="G669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H669" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="670">
@@ -15778,8 +17788,11 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="s">
-        <v>7</v>
+      <c r="G670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H670" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="671">
@@ -15801,8 +17814,11 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="s">
-        <v>7</v>
+      <c r="G671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H671" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="672">
@@ -15824,8 +17840,11 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="s">
-        <v>7</v>
+      <c r="G672" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="H672" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="673">
@@ -15847,8 +17866,11 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="s">
-        <v>7</v>
+      <c r="G673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H673" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="674">
@@ -15870,8 +17892,11 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="s">
-        <v>7</v>
+      <c r="G674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="H674" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="675">
@@ -15893,8 +17918,11 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="s">
-        <v>7</v>
+      <c r="G675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="H675" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="676">
@@ -15916,8 +17944,11 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="s">
-        <v>7</v>
+      <c r="G676" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="H676" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="677">
@@ -15939,8 +17970,11 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="s">
-        <v>7</v>
+      <c r="G677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H677" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="678">
@@ -15959,9 +17993,40 @@
       <c r="E678" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="F678"/>
-      <c r="G678" t="s">
-        <v>7</v>
+      <c r="F678" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="G678" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="H678" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B679" t="n">
+        <v>19122727</v>
+      </c>
+      <c r="C679" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0.0219999998807907</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="G679" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="H679" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -18029,6 +18029,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B680" t="n">
+        <v>12436264</v>
+      </c>
+      <c r="C680" t="n">
+        <v>0.0245999991893768</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="E680" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="G680" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H680" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -397,9 +394,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -420,11 +414,8 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -446,11 +437,8 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +460,8 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +483,8 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -524,11 +506,8 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -550,11 +529,8 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -576,11 +552,8 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
+      <c r="G8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -602,11 +575,8 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -628,11 +598,8 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+      <c r="G10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -654,11 +621,8 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
+      <c r="G11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -680,11 +644,8 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -706,11 +667,8 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -732,11 +690,8 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H14" t="s">
-        <v>8</v>
+      <c r="G14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -758,11 +713,8 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -784,11 +736,8 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
+      <c r="G16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -810,11 +759,8 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+      <c r="G17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -836,11 +782,8 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -862,11 +805,8 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -888,11 +828,8 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+      <c r="G20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -914,11 +851,8 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H21" t="s">
-        <v>8</v>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -940,11 +874,8 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
+      <c r="G22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -966,11 +897,8 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
+      <c r="G23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -992,11 +920,8 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1018,11 +943,8 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
+      <c r="G25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1044,11 +966,8 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>8</v>
+      <c r="G26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1070,11 +989,8 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.019845999777317</v>
-      </c>
-      <c r="H27" t="s">
-        <v>8</v>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1096,11 +1012,8 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H28" t="s">
-        <v>8</v>
+      <c r="G28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1122,11 +1035,8 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>8</v>
+      <c r="G29" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1148,11 +1058,8 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.01923399977386</v>
-      </c>
-      <c r="H30" t="s">
-        <v>8</v>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1174,11 +1081,8 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+      <c r="G31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1200,11 +1104,8 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+      <c r="G32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1127,8 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1252,11 +1150,8 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="G34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1278,11 +1173,8 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1304,11 +1196,8 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H36" t="s">
-        <v>8</v>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1330,11 +1219,8 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H37" t="s">
-        <v>8</v>
+      <c r="G37" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1356,11 +1242,8 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H38" t="s">
-        <v>8</v>
+      <c r="G38" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1382,11 +1265,8 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H39" t="s">
-        <v>8</v>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1408,11 +1288,8 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
+      <c r="G40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1434,11 +1311,8 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
+      <c r="G41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1460,11 +1334,8 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1486,11 +1357,8 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H43" t="s">
-        <v>8</v>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1512,11 +1380,8 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H44" t="s">
-        <v>8</v>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1538,11 +1403,8 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H45" t="s">
-        <v>8</v>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1564,11 +1426,8 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H46" t="s">
-        <v>8</v>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1590,11 +1449,8 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H47" t="s">
-        <v>8</v>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1616,11 +1472,8 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H48" t="s">
-        <v>8</v>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1642,11 +1495,8 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H49" t="s">
-        <v>8</v>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1668,11 +1518,8 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H50" t="s">
-        <v>8</v>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1694,11 +1541,8 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H51" t="s">
-        <v>8</v>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1720,11 +1564,8 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H52" t="s">
-        <v>8</v>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1746,11 +1587,8 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H53" t="s">
-        <v>8</v>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,11 +1610,8 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H54" t="s">
-        <v>8</v>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1798,11 +1633,8 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H55" t="s">
-        <v>8</v>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1824,11 +1656,8 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H56" t="s">
-        <v>8</v>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1850,11 +1679,8 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H57" t="s">
-        <v>8</v>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1876,11 +1702,8 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H58" t="s">
-        <v>8</v>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1902,11 +1725,8 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H59" t="s">
-        <v>8</v>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1928,11 +1748,8 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H60" t="s">
-        <v>8</v>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1954,11 +1771,8 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1980,11 +1794,8 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H62" t="s">
-        <v>8</v>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2006,11 +1817,8 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H63" t="s">
-        <v>8</v>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2032,11 +1840,8 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H64" t="s">
-        <v>8</v>
+      <c r="G64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2058,11 +1863,8 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H65" t="s">
-        <v>8</v>
+      <c r="G65" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2084,11 +1886,8 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H66" t="s">
-        <v>8</v>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2110,11 +1909,8 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H67" t="s">
-        <v>8</v>
+      <c r="G67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2136,11 +1932,8 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H68" t="s">
-        <v>8</v>
+      <c r="G68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2162,11 +1955,8 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H69" t="s">
-        <v>8</v>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -2188,11 +1978,8 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H70" t="s">
-        <v>8</v>
+      <c r="G70" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2214,11 +2001,8 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H71" t="s">
-        <v>8</v>
+      <c r="G71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2240,11 +2024,8 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H72" t="s">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2266,11 +2047,8 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H73" t="s">
-        <v>8</v>
+      <c r="G73" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -2292,11 +2070,8 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="G74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2318,11 +2093,8 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H75" t="s">
-        <v>8</v>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2344,11 +2116,8 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="G76" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2370,11 +2139,8 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H77" t="s">
-        <v>8</v>
+      <c r="G77" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2396,11 +2162,8 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2422,11 +2185,8 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H79" t="s">
-        <v>8</v>
+      <c r="G79" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2448,11 +2208,8 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+      <c r="G80" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2474,11 +2231,8 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H81" t="s">
-        <v>8</v>
+      <c r="G81" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2500,11 +2254,8 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+      <c r="G82" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2526,11 +2277,8 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H83" t="s">
-        <v>8</v>
+      <c r="G83" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2552,11 +2300,8 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H84" t="s">
-        <v>8</v>
+      <c r="G84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2578,11 +2323,8 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H85" t="s">
-        <v>8</v>
+      <c r="G85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2604,11 +2346,8 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H86" t="s">
-        <v>8</v>
+      <c r="G86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -2630,11 +2369,8 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>8</v>
+      <c r="G87" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2656,11 +2392,8 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>8</v>
+      <c r="G88" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2682,11 +2415,8 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H89" t="s">
-        <v>8</v>
+      <c r="G89" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -2708,11 +2438,8 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="G90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2734,11 +2461,8 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H91" t="s">
-        <v>8</v>
+      <c r="G91" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2760,11 +2484,8 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="G92" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2786,11 +2507,8 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H93" t="s">
-        <v>8</v>
+      <c r="G93" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -2812,11 +2530,8 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H94" t="s">
-        <v>8</v>
+      <c r="G94" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2838,11 +2553,8 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="G95" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2864,11 +2576,8 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H96" t="s">
-        <v>8</v>
+      <c r="G96" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2890,11 +2599,8 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+      <c r="G97" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -2916,11 +2622,8 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H98" t="s">
-        <v>8</v>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2942,11 +2645,8 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="G99" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2668,8 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H100" t="s">
-        <v>8</v>
+      <c r="G100" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2994,11 +2691,8 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H101" t="s">
-        <v>8</v>
+      <c r="G101" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3020,11 +2714,8 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H102" t="s">
-        <v>8</v>
+      <c r="G102" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3046,11 +2737,8 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="G103" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3072,11 +2760,8 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H104" t="s">
-        <v>8</v>
+      <c r="G104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3098,11 +2783,8 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H105" t="s">
-        <v>8</v>
+      <c r="G105" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3124,11 +2806,8 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H106" t="s">
-        <v>8</v>
+      <c r="G106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3150,11 +2829,8 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H107" t="s">
-        <v>8</v>
+      <c r="G107" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3176,11 +2852,8 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+      <c r="G108" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3202,11 +2875,8 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H109" t="s">
-        <v>8</v>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3228,11 +2898,8 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H110" t="s">
-        <v>8</v>
+      <c r="G110" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -3254,11 +2921,8 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H111" t="s">
-        <v>8</v>
+      <c r="G111" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -3280,11 +2944,8 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H112" t="s">
-        <v>8</v>
+      <c r="G112" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3306,11 +2967,8 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+      <c r="G113" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3332,11 +2990,8 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H114" t="s">
-        <v>8</v>
+      <c r="G114" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3358,11 +3013,8 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H115" t="s">
-        <v>8</v>
+      <c r="G115" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3384,11 +3036,8 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+      <c r="G116" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3410,11 +3059,8 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H117" t="s">
-        <v>8</v>
+      <c r="G117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3436,11 +3082,8 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H118" t="s">
-        <v>8</v>
+      <c r="G118" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3462,11 +3105,8 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H119" t="s">
-        <v>8</v>
+      <c r="G119" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -3488,11 +3128,8 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H120" t="s">
-        <v>8</v>
+      <c r="G120" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -3514,11 +3151,8 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
+      <c r="G121" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -3540,11 +3174,8 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H122" t="s">
-        <v>8</v>
+      <c r="G122" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -3566,11 +3197,8 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H123" t="s">
-        <v>8</v>
+      <c r="G123" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3592,11 +3220,8 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H124" t="s">
-        <v>8</v>
+      <c r="G124" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -3618,11 +3243,8 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H125" t="s">
-        <v>8</v>
+      <c r="G125" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -3644,11 +3266,8 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H126" t="s">
-        <v>8</v>
+      <c r="G126" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -3670,11 +3289,8 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H127" t="s">
-        <v>8</v>
+      <c r="G127" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3696,11 +3312,8 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H128" t="s">
-        <v>8</v>
+      <c r="G128" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="129">
@@ -3722,11 +3335,8 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H129" t="s">
-        <v>8</v>
+      <c r="G129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -3748,11 +3358,8 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H130" t="s">
-        <v>8</v>
+      <c r="G130" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3774,11 +3381,8 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H131" t="s">
-        <v>8</v>
+      <c r="G131" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -3800,11 +3404,8 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H132" t="s">
-        <v>8</v>
+      <c r="G132" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -3826,11 +3427,8 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H133" t="s">
-        <v>8</v>
+      <c r="G133" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -3852,11 +3450,8 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H134" t="s">
-        <v>8</v>
+      <c r="G134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3878,11 +3473,8 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H135" t="s">
-        <v>8</v>
+      <c r="G135" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="136">
@@ -3904,11 +3496,8 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H136" t="s">
-        <v>8</v>
+      <c r="G136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -3930,11 +3519,8 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H137" t="s">
-        <v>8</v>
+      <c r="G137" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3956,11 +3542,8 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H138" t="s">
-        <v>8</v>
+      <c r="G138" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3982,11 +3565,8 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>8</v>
+      <c r="G139" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -4008,11 +3588,8 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H140" t="s">
-        <v>8</v>
+      <c r="G140" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -4034,11 +3611,8 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H141" t="s">
-        <v>8</v>
+      <c r="G141" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -4060,11 +3634,8 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H142" t="s">
-        <v>8</v>
+      <c r="G142" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="143">
@@ -4086,11 +3657,8 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H143" t="s">
-        <v>8</v>
+      <c r="G143" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4112,11 +3680,8 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H144" t="s">
-        <v>8</v>
+      <c r="G144" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -4138,11 +3703,8 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H145" t="s">
-        <v>8</v>
+      <c r="G145" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -4164,11 +3726,8 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H146" t="s">
-        <v>8</v>
+      <c r="G146" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -4190,11 +3749,8 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H147" t="s">
-        <v>8</v>
+      <c r="G147" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -4216,11 +3772,8 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H148" t="s">
-        <v>8</v>
+      <c r="G148" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -4242,11 +3795,8 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H149" t="s">
-        <v>8</v>
+      <c r="G149" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -4268,11 +3818,8 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H150" t="s">
-        <v>8</v>
+      <c r="G150" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -4294,11 +3841,8 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H151" t="s">
-        <v>8</v>
+      <c r="G151" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -4320,11 +3864,8 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H152" t="s">
-        <v>8</v>
+      <c r="G152" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -4346,11 +3887,8 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>8</v>
+      <c r="G153" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4372,11 +3910,8 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H154" t="s">
-        <v>8</v>
+      <c r="G154" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -4398,11 +3933,8 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H155" t="s">
-        <v>8</v>
+      <c r="G155" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -4424,11 +3956,8 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H156" t="s">
-        <v>8</v>
+      <c r="G156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -4450,11 +3979,8 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H157" t="s">
-        <v>8</v>
+      <c r="G157" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -4476,11 +4002,8 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H158" t="s">
-        <v>8</v>
+      <c r="G158" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -4502,11 +4025,8 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H159" t="s">
-        <v>8</v>
+      <c r="G159" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -4528,11 +4048,8 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H160" t="s">
-        <v>8</v>
+      <c r="G160" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -4554,11 +4071,8 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H161" t="s">
-        <v>8</v>
+      <c r="G161" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -4580,11 +4094,8 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H162" t="s">
-        <v>8</v>
+      <c r="G162" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -4606,11 +4117,8 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H163" t="s">
-        <v>8</v>
+      <c r="G163" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4632,11 +4140,8 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H164" t="s">
-        <v>8</v>
+      <c r="G164" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4658,11 +4163,8 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H165" t="s">
-        <v>8</v>
+      <c r="G165" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -4684,11 +4186,8 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H166" t="s">
-        <v>8</v>
+      <c r="G166" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -4710,11 +4209,8 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H167" t="s">
-        <v>8</v>
+      <c r="G167" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4736,11 +4232,8 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H168" t="s">
-        <v>8</v>
+      <c r="G168" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -4762,11 +4255,8 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H169" t="s">
-        <v>8</v>
+      <c r="G169" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4788,11 +4278,8 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H170" t="s">
-        <v>8</v>
+      <c r="G170" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4814,11 +4301,8 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H171" t="s">
-        <v>8</v>
+      <c r="G171" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4840,11 +4324,8 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H172" t="s">
-        <v>8</v>
+      <c r="G172" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -4866,11 +4347,8 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H173" t="s">
-        <v>8</v>
+      <c r="G173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4370,8 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H174" t="s">
-        <v>8</v>
+      <c r="G174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4918,11 +4393,8 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H175" t="s">
-        <v>8</v>
+      <c r="G175" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -4944,11 +4416,8 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H176" t="s">
-        <v>8</v>
+      <c r="G176" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -4970,11 +4439,8 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H177" t="s">
-        <v>8</v>
+      <c r="G177" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -4996,11 +4462,8 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H178" t="s">
-        <v>8</v>
+      <c r="G178" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -5022,11 +4485,8 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H179" t="s">
-        <v>8</v>
+      <c r="G179" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="180">
@@ -5048,11 +4508,8 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H180" t="s">
-        <v>8</v>
+      <c r="G180" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -5074,11 +4531,8 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H181" t="s">
-        <v>8</v>
+      <c r="G181" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182">
@@ -5100,11 +4554,8 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H182" t="s">
-        <v>8</v>
+      <c r="G182" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -5126,11 +4577,8 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H183" t="s">
-        <v>8</v>
+      <c r="G183" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -5152,11 +4600,8 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H184" t="s">
-        <v>8</v>
+      <c r="G184" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -5178,11 +4623,8 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H185" t="s">
-        <v>8</v>
+      <c r="G185" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5204,11 +4646,8 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H186" t="s">
-        <v>8</v>
+      <c r="G186" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -5230,11 +4669,8 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H187" t="s">
-        <v>8</v>
+      <c r="G187" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5256,11 +4692,8 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H188" t="s">
-        <v>8</v>
+      <c r="G188" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5282,11 +4715,8 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H189" t="s">
-        <v>8</v>
+      <c r="G189" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -5308,11 +4738,8 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H190" t="s">
-        <v>8</v>
+      <c r="G190" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -5334,11 +4761,8 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H191" t="s">
-        <v>8</v>
+      <c r="G191" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -5360,11 +4784,8 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H192" t="s">
-        <v>8</v>
+      <c r="G192" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -5386,11 +4807,8 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H193" t="s">
-        <v>8</v>
+      <c r="G193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -5412,11 +4830,8 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H194" t="s">
-        <v>8</v>
+      <c r="G194" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -5438,11 +4853,8 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H195" t="s">
-        <v>8</v>
+      <c r="G195" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -5464,11 +4876,8 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H196" t="s">
-        <v>8</v>
+      <c r="G196" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -5490,11 +4899,8 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H197" t="s">
-        <v>8</v>
+      <c r="G197" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -5516,11 +4922,8 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H198" t="s">
-        <v>8</v>
+      <c r="G198" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -5542,11 +4945,8 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H199" t="s">
-        <v>8</v>
+      <c r="G199" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -5568,11 +4968,8 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H200" t="s">
-        <v>8</v>
+      <c r="G200" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -5594,11 +4991,8 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H201" t="s">
-        <v>8</v>
+      <c r="G201" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5620,11 +5014,8 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H202" t="s">
-        <v>8</v>
+      <c r="G202" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -5646,11 +5037,8 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H203" t="s">
-        <v>8</v>
+      <c r="G203" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -5672,11 +5060,8 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H204" t="s">
-        <v>8</v>
+      <c r="G204" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -5698,11 +5083,8 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H205" t="s">
-        <v>8</v>
+      <c r="G205" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -5724,11 +5106,8 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H206" t="s">
-        <v>8</v>
+      <c r="G206" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -5750,11 +5129,8 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H207" t="s">
-        <v>8</v>
+      <c r="G207" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -5776,11 +5152,8 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H208" t="s">
-        <v>8</v>
+      <c r="G208" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -5802,11 +5175,8 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H209" t="s">
-        <v>8</v>
+      <c r="G209" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5828,11 +5198,8 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H210" t="s">
-        <v>8</v>
+      <c r="G210" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -5854,11 +5221,8 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H211" t="s">
-        <v>8</v>
+      <c r="G211" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -5880,11 +5244,8 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H212" t="s">
-        <v>8</v>
+      <c r="G212" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5906,11 +5267,8 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H213" t="s">
-        <v>8</v>
+      <c r="G213" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -5932,11 +5290,8 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H214" t="s">
-        <v>8</v>
+      <c r="G214" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -5958,11 +5313,8 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H215" t="s">
-        <v>8</v>
+      <c r="G215" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -5984,11 +5336,8 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H216" t="s">
-        <v>8</v>
+      <c r="G216" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -6010,11 +5359,8 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H217" t="s">
-        <v>8</v>
+      <c r="G217" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -6036,11 +5382,8 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H218" t="s">
-        <v>8</v>
+      <c r="G218" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -6062,11 +5405,8 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H219" t="s">
-        <v>8</v>
+      <c r="G219" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -6088,11 +5428,8 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H220" t="s">
-        <v>8</v>
+      <c r="G220" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -6114,11 +5451,8 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H221" t="s">
-        <v>8</v>
+      <c r="G221" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -6140,11 +5474,8 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H222" t="s">
-        <v>8</v>
+      <c r="G222" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -6166,11 +5497,8 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H223" t="s">
-        <v>8</v>
+      <c r="G223" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -6192,11 +5520,8 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H224" t="s">
-        <v>8</v>
+      <c r="G224" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -6218,11 +5543,8 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H225" t="s">
-        <v>8</v>
+      <c r="G225" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="226">
@@ -6244,11 +5566,8 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H226" t="s">
-        <v>8</v>
+      <c r="G226" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -6270,11 +5589,8 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H227" t="s">
-        <v>8</v>
+      <c r="G227" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -6296,11 +5612,8 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H228" t="s">
-        <v>8</v>
+      <c r="G228" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -6322,11 +5635,8 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H229" t="s">
-        <v>8</v>
+      <c r="G229" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -6348,11 +5658,8 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H230" t="s">
-        <v>8</v>
+      <c r="G230" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -6374,11 +5681,8 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H231" t="s">
-        <v>8</v>
+      <c r="G231" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -6400,11 +5704,8 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H232" t="s">
-        <v>8</v>
+      <c r="G232" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -6426,11 +5727,8 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H233" t="s">
-        <v>8</v>
+      <c r="G233" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -6452,11 +5750,8 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H234" t="s">
-        <v>8</v>
+      <c r="G234" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -6478,11 +5773,8 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H235" t="s">
-        <v>8</v>
+      <c r="G235" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -6504,11 +5796,8 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H236" t="s">
-        <v>8</v>
+      <c r="G236" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -6530,11 +5819,8 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H237" t="s">
-        <v>8</v>
+      <c r="G237" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -6556,11 +5842,8 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H238" t="s">
-        <v>8</v>
+      <c r="G238" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -6582,11 +5865,8 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H239" t="s">
-        <v>8</v>
+      <c r="G239" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -6608,11 +5888,8 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H240" t="s">
-        <v>8</v>
+      <c r="G240" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6634,11 +5911,8 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H241" t="s">
-        <v>8</v>
+      <c r="G241" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -6660,11 +5934,8 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H242" t="s">
-        <v>8</v>
+      <c r="G242" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="243">
@@ -6686,11 +5957,8 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H243" t="s">
-        <v>8</v>
+      <c r="G243" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -6712,11 +5980,8 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H244" t="s">
-        <v>8</v>
+      <c r="G244" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6738,11 +6003,8 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H245" t="s">
-        <v>8</v>
+      <c r="G245" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -6764,11 +6026,8 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H246" t="s">
-        <v>8</v>
+      <c r="G246" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -6790,11 +6049,8 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H247" t="s">
-        <v>8</v>
+      <c r="G247" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -6816,11 +6072,8 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H248" t="s">
-        <v>8</v>
+      <c r="G248" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6842,11 +6095,8 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H249" t="s">
-        <v>8</v>
+      <c r="G249" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -6868,11 +6118,8 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H250" t="s">
-        <v>8</v>
+      <c r="G250" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -6894,11 +6141,8 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H251" t="s">
-        <v>8</v>
+      <c r="G251" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6920,11 +6164,8 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H252" t="s">
-        <v>8</v>
+      <c r="G252" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6946,11 +6187,8 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H253" t="s">
-        <v>8</v>
+      <c r="G253" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -6972,11 +6210,8 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H254" t="s">
-        <v>8</v>
+      <c r="G254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -6998,11 +6233,8 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H255" t="s">
-        <v>8</v>
+      <c r="G255" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -7024,11 +6256,8 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H256" t="s">
-        <v>8</v>
+      <c r="G256" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -7050,11 +6279,8 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H257" t="s">
-        <v>8</v>
+      <c r="G257" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -7076,11 +6302,8 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H258" t="s">
-        <v>8</v>
+      <c r="G258" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -7102,11 +6325,8 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H259" t="s">
-        <v>8</v>
+      <c r="G259" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -7128,11 +6348,8 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H260" t="s">
-        <v>8</v>
+      <c r="G260" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -7154,11 +6371,8 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H261" t="s">
-        <v>8</v>
+      <c r="G261" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -7180,11 +6394,8 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H262" t="s">
-        <v>8</v>
+      <c r="G262" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -7206,11 +6417,8 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H263" t="s">
-        <v>8</v>
+      <c r="G263" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -7232,11 +6440,8 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H264" t="s">
-        <v>8</v>
+      <c r="G264" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -7258,11 +6463,8 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H265" t="s">
-        <v>8</v>
+      <c r="G265" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7284,11 +6486,8 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H266" t="s">
-        <v>8</v>
+      <c r="G266" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -7310,11 +6509,8 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H267" t="s">
-        <v>8</v>
+      <c r="G267" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7336,11 +6532,8 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H268" t="s">
-        <v>8</v>
+      <c r="G268" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -7362,11 +6555,8 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H269" t="s">
-        <v>8</v>
+      <c r="G269" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -7388,11 +6578,8 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H270" t="s">
-        <v>8</v>
+      <c r="G270" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -7414,11 +6601,8 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H271" t="s">
-        <v>8</v>
+      <c r="G271" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -7440,11 +6624,8 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H272" t="s">
-        <v>8</v>
+      <c r="G272" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -7466,11 +6647,8 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H273" t="s">
-        <v>8</v>
+      <c r="G273" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -7492,11 +6670,8 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H274" t="s">
-        <v>8</v>
+      <c r="G274" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -7518,11 +6693,8 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H275" t="s">
-        <v>8</v>
+      <c r="G275" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -7544,11 +6716,8 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H276" t="s">
-        <v>8</v>
+      <c r="G276" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7570,11 +6739,8 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H277" t="s">
-        <v>8</v>
+      <c r="G277" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -7596,11 +6762,8 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H278" t="s">
-        <v>8</v>
+      <c r="G278" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -7622,11 +6785,8 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H279" t="s">
-        <v>8</v>
+      <c r="G279" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -7648,11 +6808,8 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H280" t="s">
-        <v>8</v>
+      <c r="G280" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -7674,11 +6831,8 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H281" t="s">
-        <v>8</v>
+      <c r="G281" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -7700,11 +6854,8 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H282" t="s">
-        <v>8</v>
+      <c r="G282" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -7726,11 +6877,8 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H283" t="s">
-        <v>8</v>
+      <c r="G283" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -7752,11 +6900,8 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H284" t="s">
-        <v>8</v>
+      <c r="G284" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -7778,11 +6923,8 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H285" t="s">
-        <v>8</v>
+      <c r="G285" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7804,11 +6946,8 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H286" t="s">
-        <v>8</v>
+      <c r="G286" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -7830,11 +6969,8 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H287" t="s">
-        <v>8</v>
+      <c r="G287" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -7856,11 +6992,8 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H288" t="s">
-        <v>8</v>
+      <c r="G288" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -7882,11 +7015,8 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H289" t="s">
-        <v>8</v>
+      <c r="G289" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -7908,11 +7038,8 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H290" t="s">
-        <v>8</v>
+      <c r="G290" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -7934,11 +7061,8 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H291" t="s">
-        <v>8</v>
+      <c r="G291" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -7960,11 +7084,8 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H292" t="s">
-        <v>8</v>
+      <c r="G292" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -7986,11 +7107,8 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H293" t="s">
-        <v>8</v>
+      <c r="G293" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -8012,11 +7130,8 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H294" t="s">
-        <v>8</v>
+      <c r="G294" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -8038,11 +7153,8 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H295" t="s">
-        <v>8</v>
+      <c r="G295" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -8064,11 +7176,8 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H296" t="s">
-        <v>8</v>
+      <c r="G296" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -8090,11 +7199,8 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H297" t="s">
-        <v>8</v>
+      <c r="G297" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -8116,11 +7222,8 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H298" t="s">
-        <v>8</v>
+      <c r="G298" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -8142,11 +7245,8 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H299" t="s">
-        <v>8</v>
+      <c r="G299" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -8168,11 +7268,8 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H300" t="s">
-        <v>8</v>
+      <c r="G300" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -8194,11 +7291,8 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H301" t="s">
-        <v>8</v>
+      <c r="G301" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -8220,11 +7314,8 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H302" t="s">
-        <v>8</v>
+      <c r="G302" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -8246,11 +7337,8 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H303" t="s">
-        <v>8</v>
+      <c r="G303" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -8272,11 +7360,8 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H304" t="s">
-        <v>8</v>
+      <c r="G304" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -8298,11 +7383,8 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H305" t="s">
-        <v>8</v>
+      <c r="G305" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -8324,11 +7406,8 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H306" t="s">
-        <v>8</v>
+      <c r="G306" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -8350,11 +7429,8 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H307" t="s">
-        <v>8</v>
+      <c r="G307" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -8376,11 +7452,8 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H308" t="s">
-        <v>8</v>
+      <c r="G308" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -8402,11 +7475,8 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H309" t="s">
-        <v>8</v>
+      <c r="G309" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -8428,11 +7498,8 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H310" t="s">
-        <v>8</v>
+      <c r="G310" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -8454,11 +7521,8 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H311" t="s">
-        <v>8</v>
+      <c r="G311" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -8480,11 +7544,8 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H312" t="s">
-        <v>8</v>
+      <c r="G312" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -8506,11 +7567,8 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H313" t="s">
-        <v>8</v>
+      <c r="G313" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -8532,11 +7590,8 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H314" t="s">
-        <v>8</v>
+      <c r="G314" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -8558,11 +7613,8 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H315" t="s">
-        <v>8</v>
+      <c r="G315" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -8584,11 +7636,8 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H316" t="s">
-        <v>8</v>
+      <c r="G316" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -8610,11 +7659,8 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H317" t="s">
-        <v>8</v>
+      <c r="G317" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -8636,11 +7682,8 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H318" t="s">
-        <v>8</v>
+      <c r="G318" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -8662,11 +7705,8 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H319" t="s">
-        <v>8</v>
+      <c r="G319" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -8688,11 +7728,8 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H320" t="s">
-        <v>8</v>
+      <c r="G320" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -8714,11 +7751,8 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H321" t="s">
-        <v>8</v>
+      <c r="G321" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -8740,11 +7774,8 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H322" t="s">
-        <v>8</v>
+      <c r="G322" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -8766,11 +7797,8 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H323" t="s">
-        <v>8</v>
+      <c r="G323" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -8792,11 +7820,8 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H324" t="s">
-        <v>8</v>
+      <c r="G324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -8818,11 +7843,8 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H325" t="s">
-        <v>8</v>
+      <c r="G325" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -8844,11 +7866,8 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H326" t="s">
-        <v>8</v>
+      <c r="G326" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -8870,11 +7889,8 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H327" t="s">
-        <v>8</v>
+      <c r="G327" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -8896,11 +7912,8 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H328" t="s">
-        <v>8</v>
+      <c r="G328" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -8922,11 +7935,8 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H329" t="s">
-        <v>8</v>
+      <c r="G329" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8948,11 +7958,8 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H330" t="s">
-        <v>8</v>
+      <c r="G330" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -8974,11 +7981,8 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H331" t="s">
-        <v>8</v>
+      <c r="G331" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -9000,11 +8004,8 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H332" t="s">
-        <v>8</v>
+      <c r="G332" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9026,11 +8027,8 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H333" t="s">
-        <v>8</v>
+      <c r="G333" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -9052,11 +8050,8 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H334" t="s">
-        <v>8</v>
+      <c r="G334" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -9078,11 +8073,8 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H335" t="s">
-        <v>8</v>
+      <c r="G335" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -9104,11 +8096,8 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H336" t="s">
-        <v>8</v>
+      <c r="G336" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -9130,11 +8119,8 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H337" t="s">
-        <v>8</v>
+      <c r="G337" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -9156,11 +8142,8 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H338" t="s">
-        <v>8</v>
+      <c r="G338" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -9182,11 +8165,8 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H339" t="s">
-        <v>8</v>
+      <c r="G339" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9208,11 +8188,8 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H340" t="s">
-        <v>8</v>
+      <c r="G340" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -9234,11 +8211,8 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H341" t="s">
-        <v>8</v>
+      <c r="G341" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -9260,11 +8234,8 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H342" t="s">
-        <v>8</v>
+      <c r="G342" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -9286,11 +8257,8 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H343" t="s">
-        <v>8</v>
+      <c r="G343" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -9312,11 +8280,8 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H344" t="s">
-        <v>8</v>
+      <c r="G344" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -9338,11 +8303,8 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H345" t="s">
-        <v>8</v>
+      <c r="G345" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -9364,11 +8326,8 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H346" t="s">
-        <v>8</v>
+      <c r="G346" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -9390,11 +8349,8 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H347" t="s">
-        <v>8</v>
+      <c r="G347" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -9416,11 +8372,8 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H348" t="s">
-        <v>8</v>
+      <c r="G348" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -9442,11 +8395,8 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H349" t="s">
-        <v>8</v>
+      <c r="G349" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -9468,11 +8418,8 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H350" t="s">
-        <v>8</v>
+      <c r="G350" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -9494,11 +8441,8 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H351" t="s">
-        <v>8</v>
+      <c r="G351" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -9520,11 +8464,8 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H352" t="s">
-        <v>8</v>
+      <c r="G352" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -9546,11 +8487,8 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H353" t="s">
-        <v>8</v>
+      <c r="G353" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -9572,11 +8510,8 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H354" t="s">
-        <v>8</v>
+      <c r="G354" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -9598,11 +8533,8 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H355" t="s">
-        <v>8</v>
+      <c r="G355" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -9624,11 +8556,8 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H356" t="s">
-        <v>8</v>
+      <c r="G356" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -9650,11 +8579,8 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H357" t="s">
-        <v>8</v>
+      <c r="G357" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -9676,11 +8602,8 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H358" t="s">
-        <v>8</v>
+      <c r="G358" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -9702,11 +8625,8 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H359" t="s">
-        <v>8</v>
+      <c r="G359" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -9728,11 +8648,8 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H360" t="s">
-        <v>8</v>
+      <c r="G360" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -9754,11 +8671,8 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H361" t="s">
-        <v>8</v>
+      <c r="G361" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -9780,11 +8694,8 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H362" t="s">
-        <v>8</v>
+      <c r="G362" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -9806,11 +8717,8 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H363" t="s">
-        <v>8</v>
+      <c r="G363" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -9832,11 +8740,8 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H364" t="s">
-        <v>8</v>
+      <c r="G364" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -9858,11 +8763,8 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H365" t="s">
-        <v>8</v>
+      <c r="G365" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -9884,11 +8786,8 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H366" t="s">
-        <v>8</v>
+      <c r="G366" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -9910,11 +8809,8 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H367" t="s">
-        <v>8</v>
+      <c r="G367" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -9936,11 +8832,8 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H368" t="s">
-        <v>8</v>
+      <c r="G368" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="369">
@@ -9962,11 +8855,8 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H369" t="s">
-        <v>8</v>
+      <c r="G369" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -9988,11 +8878,8 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H370" t="s">
-        <v>8</v>
+      <c r="G370" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -10014,11 +8901,8 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H371" t="s">
-        <v>8</v>
+      <c r="G371" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -10040,11 +8924,8 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H372" t="s">
-        <v>8</v>
+      <c r="G372" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="373">
@@ -10066,11 +8947,8 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H373" t="s">
-        <v>8</v>
+      <c r="G373" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -10092,11 +8970,8 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H374" t="s">
-        <v>8</v>
+      <c r="G374" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -10118,11 +8993,8 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H375" t="s">
-        <v>8</v>
+      <c r="G375" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -10144,11 +9016,8 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H376" t="s">
-        <v>8</v>
+      <c r="G376" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="377">
@@ -10170,11 +9039,8 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H377" t="s">
-        <v>8</v>
+      <c r="G377" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="378">
@@ -10196,11 +9062,8 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H378" t="s">
-        <v>8</v>
+      <c r="G378" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="379">
@@ -10222,11 +9085,8 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H379" t="s">
-        <v>8</v>
+      <c r="G379" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="380">
@@ -10248,11 +9108,8 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H380" t="s">
-        <v>8</v>
+      <c r="G380" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="381">
@@ -10274,11 +9131,8 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H381" t="s">
-        <v>8</v>
+      <c r="G381" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -10300,11 +9154,8 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H382" t="s">
-        <v>8</v>
+      <c r="G382" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -10326,11 +9177,8 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H383" t="s">
-        <v>8</v>
+      <c r="G383" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -10352,11 +9200,8 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H384" t="s">
-        <v>8</v>
+      <c r="G384" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -10378,11 +9223,8 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H385" t="s">
-        <v>8</v>
+      <c r="G385" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -10404,11 +9246,8 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H386" t="s">
-        <v>8</v>
+      <c r="G386" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -10430,11 +9269,8 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H387" t="s">
-        <v>8</v>
+      <c r="G387" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -10456,11 +9292,8 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H388" t="s">
-        <v>8</v>
+      <c r="G388" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -10482,11 +9315,8 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H389" t="s">
-        <v>8</v>
+      <c r="G389" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -10508,11 +9338,8 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H390" t="s">
-        <v>8</v>
+      <c r="G390" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -10534,11 +9361,8 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H391" t="s">
-        <v>8</v>
+      <c r="G391" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -10560,11 +9384,8 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H392" t="s">
-        <v>8</v>
+      <c r="G392" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -10586,11 +9407,8 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H393" t="s">
-        <v>8</v>
+      <c r="G393" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="394">
@@ -10612,11 +9430,8 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H394" t="s">
-        <v>8</v>
+      <c r="G394" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="395">
@@ -10638,11 +9453,8 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H395" t="s">
-        <v>8</v>
+      <c r="G395" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="396">
@@ -10664,11 +9476,8 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H396" t="s">
-        <v>8</v>
+      <c r="G396" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -10690,11 +9499,8 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H397" t="s">
-        <v>8</v>
+      <c r="G397" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="398">
@@ -10716,11 +9522,8 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H398" t="s">
-        <v>8</v>
+      <c r="G398" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -10742,11 +9545,8 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H399" t="s">
-        <v>8</v>
+      <c r="G399" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -10768,11 +9568,8 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H400" t="s">
-        <v>8</v>
+      <c r="G400" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="401">
@@ -10794,11 +9591,8 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H401" t="s">
-        <v>8</v>
+      <c r="G401" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -10820,11 +9614,8 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H402" t="s">
-        <v>8</v>
+      <c r="G402" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -10846,11 +9637,8 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H403" t="s">
-        <v>8</v>
+      <c r="G403" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="404">
@@ -10872,11 +9660,8 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H404" t="s">
-        <v>8</v>
+      <c r="G404" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -10898,11 +9683,8 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H405" t="s">
-        <v>8</v>
+      <c r="G405" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -10924,11 +9706,8 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H406" t="s">
-        <v>8</v>
+      <c r="G406" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -10950,11 +9729,8 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H407" t="s">
-        <v>8</v>
+      <c r="G407" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -10976,11 +9752,8 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H408" t="s">
-        <v>8</v>
+      <c r="G408" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="409">
@@ -11002,11 +9775,8 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H409" t="s">
-        <v>8</v>
+      <c r="G409" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -11028,11 +9798,8 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H410" t="s">
-        <v>8</v>
+      <c r="G410" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11054,11 +9821,8 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H411" t="s">
-        <v>8</v>
+      <c r="G411" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -11080,11 +9844,8 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H412" t="s">
-        <v>8</v>
+      <c r="G412" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -11106,11 +9867,8 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H413" t="s">
-        <v>8</v>
+      <c r="G413" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="414">
@@ -11132,11 +9890,8 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H414" t="s">
-        <v>8</v>
+      <c r="G414" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -11158,11 +9913,8 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H415" t="s">
-        <v>8</v>
+      <c r="G415" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="416">
@@ -11184,11 +9936,8 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H416" t="s">
-        <v>8</v>
+      <c r="G416" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -11210,11 +9959,8 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H417" t="s">
-        <v>8</v>
+      <c r="G417" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="418">
@@ -11236,11 +9982,8 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H418" t="s">
-        <v>8</v>
+      <c r="G418" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -11262,11 +10005,8 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H419" t="s">
-        <v>8</v>
+      <c r="G419" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -11288,11 +10028,8 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H420" t="s">
-        <v>8</v>
+      <c r="G420" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="421">
@@ -11314,11 +10051,8 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="n">
-        <v>0.018673000857234</v>
-      </c>
-      <c r="H421" t="s">
-        <v>8</v>
+      <c r="G421" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="422">
@@ -11340,11 +10074,8 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H422" t="s">
-        <v>8</v>
+      <c r="G422" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -11366,11 +10097,8 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H423" t="s">
-        <v>8</v>
+      <c r="G423" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -11392,11 +10120,8 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H424" t="s">
-        <v>8</v>
+      <c r="G424" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -11418,11 +10143,8 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H425" t="s">
-        <v>8</v>
+      <c r="G425" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -11444,11 +10166,8 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H426" t="s">
-        <v>8</v>
+      <c r="G426" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -11470,11 +10189,8 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H427" t="s">
-        <v>8</v>
+      <c r="G427" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -11496,11 +10212,8 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H428" t="s">
-        <v>8</v>
+      <c r="G428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429">
@@ -11522,11 +10235,8 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H429" t="s">
-        <v>8</v>
+      <c r="G429" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -11548,11 +10258,8 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H430" t="s">
-        <v>8</v>
+      <c r="G430" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -11574,11 +10281,8 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H431" t="s">
-        <v>8</v>
+      <c r="G431" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -11600,11 +10304,8 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H432" t="s">
-        <v>8</v>
+      <c r="G432" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="433">
@@ -11626,11 +10327,8 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H433" t="s">
-        <v>8</v>
+      <c r="G433" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="434">
@@ -11652,11 +10350,8 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H434" t="s">
-        <v>8</v>
+      <c r="G434" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="435">
@@ -11678,11 +10373,8 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H435" t="s">
-        <v>8</v>
+      <c r="G435" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -11704,11 +10396,8 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H436" t="s">
-        <v>8</v>
+      <c r="G436" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -11730,11 +10419,8 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H437" t="s">
-        <v>8</v>
+      <c r="G437" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="438">
@@ -11756,11 +10442,8 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H438" t="s">
-        <v>8</v>
+      <c r="G438" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -11782,11 +10465,8 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H439" t="s">
-        <v>8</v>
+      <c r="G439" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -11808,11 +10488,8 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H440" t="s">
-        <v>8</v>
+      <c r="G440" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="441">
@@ -11834,11 +10511,8 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H441" t="s">
-        <v>8</v>
+      <c r="G441" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -11860,11 +10534,8 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H442" t="s">
-        <v>8</v>
+      <c r="G442" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -11886,11 +10557,8 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H443" t="s">
-        <v>8</v>
+      <c r="G443" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="444">
@@ -11912,11 +10580,8 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H444" t="s">
-        <v>8</v>
+      <c r="G444" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="445">
@@ -11938,11 +10603,8 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H445" t="s">
-        <v>8</v>
+      <c r="G445" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="446">
@@ -11964,11 +10626,8 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H446" t="s">
-        <v>8</v>
+      <c r="G446" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="447">
@@ -11990,11 +10649,8 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H447" t="s">
-        <v>8</v>
+      <c r="G447" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -12016,11 +10672,8 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H448" t="s">
-        <v>8</v>
+      <c r="G448" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -12042,11 +10695,8 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H449" t="s">
-        <v>8</v>
+      <c r="G449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -12068,11 +10718,8 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H450" t="s">
-        <v>8</v>
+      <c r="G450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451">
@@ -12094,11 +10741,8 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H451" t="s">
-        <v>8</v>
+      <c r="G451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -12120,11 +10764,8 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H452" t="s">
-        <v>8</v>
+      <c r="G452" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -12146,11 +10787,8 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H453" t="s">
-        <v>8</v>
+      <c r="G453" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -12172,11 +10810,8 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H454" t="s">
-        <v>8</v>
+      <c r="G454" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -12198,11 +10833,8 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H455" t="s">
-        <v>8</v>
+      <c r="G455" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -12224,11 +10856,8 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H456" t="s">
-        <v>8</v>
+      <c r="G456" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -12250,11 +10879,8 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H457" t="s">
-        <v>8</v>
+      <c r="G457" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -12276,11 +10902,8 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H458" t="s">
-        <v>8</v>
+      <c r="G458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -12302,11 +10925,8 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H459" t="s">
-        <v>8</v>
+      <c r="G459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -12328,11 +10948,8 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H460" t="s">
-        <v>8</v>
+      <c r="G460" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -12354,11 +10971,8 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H461" t="s">
-        <v>8</v>
+      <c r="G461" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -12380,11 +10994,8 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H462" t="s">
-        <v>8</v>
+      <c r="G462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -12406,11 +11017,8 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H463" t="s">
-        <v>8</v>
+      <c r="G463" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -12432,11 +11040,8 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H464" t="s">
-        <v>8</v>
+      <c r="G464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -12458,11 +11063,8 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H465" t="s">
-        <v>8</v>
+      <c r="G465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -12484,11 +11086,8 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H466" t="s">
-        <v>8</v>
+      <c r="G466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -12510,11 +11109,8 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H467" t="s">
-        <v>8</v>
+      <c r="G467" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="468">
@@ -12536,11 +11132,8 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H468" t="s">
-        <v>8</v>
+      <c r="G468" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -12562,11 +11155,8 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H469" t="s">
-        <v>8</v>
+      <c r="G469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -12588,11 +11178,8 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H470" t="s">
-        <v>8</v>
+      <c r="G470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471">
@@ -12614,11 +11201,8 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H471" t="s">
-        <v>8</v>
+      <c r="G471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -12640,11 +11224,8 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H472" t="s">
-        <v>8</v>
+      <c r="G472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -12666,11 +11247,8 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H473" t="s">
-        <v>8</v>
+      <c r="G473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474">
@@ -12692,11 +11270,8 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H474" t="s">
-        <v>8</v>
+      <c r="G474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -12718,11 +11293,8 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H475" t="s">
-        <v>8</v>
+      <c r="G475" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="476">
@@ -12744,11 +11316,8 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H476" t="s">
-        <v>8</v>
+      <c r="G476" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="477">
@@ -12770,11 +11339,8 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H477" t="s">
-        <v>8</v>
+      <c r="G477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478">
@@ -12796,11 +11362,8 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H478" t="s">
-        <v>8</v>
+      <c r="G478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -12822,11 +11385,8 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H479" t="s">
-        <v>8</v>
+      <c r="G479" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="480">
@@ -12848,11 +11408,8 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H480" t="s">
-        <v>8</v>
+      <c r="G480" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="481">
@@ -12874,11 +11431,8 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H481" t="s">
-        <v>8</v>
+      <c r="G481" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -12900,11 +11454,8 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H482" t="s">
-        <v>8</v>
+      <c r="G482" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -12926,11 +11477,8 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H483" t="s">
-        <v>8</v>
+      <c r="G483" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -12952,11 +11500,8 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H484" t="s">
-        <v>8</v>
+      <c r="G484" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="485">
@@ -12978,11 +11523,8 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H485" t="s">
-        <v>8</v>
+      <c r="G485" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="486">
@@ -13004,11 +11546,8 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H486" t="s">
-        <v>8</v>
+      <c r="G486" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -13030,11 +11569,8 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H487" t="s">
-        <v>8</v>
+      <c r="G487" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="488">
@@ -13056,11 +11592,8 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H488" t="s">
-        <v>8</v>
+      <c r="G488" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -13082,11 +11615,8 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H489" t="s">
-        <v>8</v>
+      <c r="G489" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="490">
@@ -13108,11 +11638,8 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H490" t="s">
-        <v>8</v>
+      <c r="G490" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -13134,11 +11661,8 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H491" t="s">
-        <v>8</v>
+      <c r="G491" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -13160,11 +11684,8 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H492" t="s">
-        <v>8</v>
+      <c r="G492" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="493">
@@ -13186,11 +11707,8 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H493" t="s">
-        <v>8</v>
+      <c r="G493" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="494">
@@ -13212,11 +11730,8 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H494" t="s">
-        <v>8</v>
+      <c r="G494" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="495">
@@ -13238,11 +11753,8 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H495" t="s">
-        <v>8</v>
+      <c r="G495" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="496">
@@ -13264,11 +11776,8 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H496" t="s">
-        <v>8</v>
+      <c r="G496" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -13290,11 +11799,8 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H497" t="s">
-        <v>8</v>
+      <c r="G497" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -13316,11 +11822,8 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H498" t="s">
-        <v>8</v>
+      <c r="G498" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -13342,11 +11845,8 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H499" t="s">
-        <v>8</v>
+      <c r="G499" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -13368,11 +11868,8 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H500" t="s">
-        <v>8</v>
+      <c r="G500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -13394,11 +11891,8 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H501" t="s">
-        <v>8</v>
+      <c r="G501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -13420,11 +11914,8 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H502" t="s">
-        <v>8</v>
+      <c r="G502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -13446,11 +11937,8 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H503" t="s">
-        <v>8</v>
+      <c r="G503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -13472,11 +11960,8 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H504" t="s">
-        <v>8</v>
+      <c r="G504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505">
@@ -13498,11 +11983,8 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H505" t="s">
-        <v>8</v>
+      <c r="G505" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -13524,11 +12006,8 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="n">
-        <v>0.0154079999774694</v>
-      </c>
-      <c r="H506" t="s">
-        <v>8</v>
+      <c r="G506" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="507">
@@ -13550,11 +12029,8 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H507" t="s">
-        <v>8</v>
+      <c r="G507" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -13576,11 +12052,8 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H508" t="s">
-        <v>8</v>
+      <c r="G508" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -13602,11 +12075,8 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H509" t="s">
-        <v>8</v>
+      <c r="G509" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="510">
@@ -13628,11 +12098,8 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H510" t="s">
-        <v>8</v>
+      <c r="G510" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="511">
@@ -13654,11 +12121,8 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H511" t="s">
-        <v>8</v>
+      <c r="G511" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -13680,11 +12144,8 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H512" t="s">
-        <v>8</v>
+      <c r="G512" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="513">
@@ -13706,11 +12167,8 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H513" t="s">
-        <v>8</v>
+      <c r="G513" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -13732,11 +12190,8 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>8</v>
+      <c r="G514" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -13758,11 +12213,8 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H515" t="s">
-        <v>8</v>
+      <c r="G515" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -13784,11 +12236,8 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H516" t="s">
-        <v>8</v>
+      <c r="G516" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="517">
@@ -13810,11 +12259,8 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H517" t="s">
-        <v>8</v>
+      <c r="G517" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -13836,11 +12282,8 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H518" t="s">
-        <v>8</v>
+      <c r="G518" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -13862,11 +12305,8 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H519" t="s">
-        <v>8</v>
+      <c r="G519" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -13888,11 +12328,8 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H520" t="s">
-        <v>8</v>
+      <c r="G520" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -13914,11 +12351,8 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H521" t="s">
-        <v>8</v>
+      <c r="G521" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="522">
@@ -13940,11 +12374,8 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H522" t="s">
-        <v>8</v>
+      <c r="G522" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -13966,11 +12397,8 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H523" t="s">
-        <v>8</v>
+      <c r="G523" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -13992,11 +12420,8 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H524" t="s">
-        <v>8</v>
+      <c r="G524" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="525">
@@ -14018,11 +12443,8 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H525" t="s">
-        <v>8</v>
+      <c r="G525" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -14044,11 +12466,8 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H526" t="s">
-        <v>8</v>
+      <c r="G526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527">
@@ -14070,11 +12489,8 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H527" t="s">
-        <v>8</v>
+      <c r="G527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528">
@@ -14096,11 +12512,8 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H528" t="s">
-        <v>8</v>
+      <c r="G528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529">
@@ -14122,11 +12535,8 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H529" t="s">
-        <v>8</v>
+      <c r="G529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -14148,11 +12558,8 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H530" t="s">
-        <v>8</v>
+      <c r="G530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -14174,11 +12581,8 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H531" t="s">
-        <v>8</v>
+      <c r="G531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532">
@@ -14200,11 +12604,8 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H532" t="s">
-        <v>8</v>
+      <c r="G532" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="533">
@@ -14226,11 +12627,8 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H533" t="s">
-        <v>8</v>
+      <c r="G533" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -14252,11 +12650,8 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H534" t="s">
-        <v>8</v>
+      <c r="G534" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="535">
@@ -14278,11 +12673,8 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H535" t="s">
-        <v>8</v>
+      <c r="G535" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -14304,11 +12696,8 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H536" t="s">
-        <v>8</v>
+      <c r="G536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537">
@@ -14330,11 +12719,8 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H537" t="s">
-        <v>8</v>
+      <c r="G537" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="538">
@@ -14356,11 +12742,8 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H538" t="s">
-        <v>8</v>
+      <c r="G538" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="539">
@@ -14382,11 +12765,8 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H539" t="s">
-        <v>8</v>
+      <c r="G539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540">
@@ -14408,11 +12788,8 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H540" t="s">
-        <v>8</v>
+      <c r="G540" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -14434,11 +12811,8 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H541" t="s">
-        <v>8</v>
+      <c r="G541" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="542">
@@ -14460,11 +12834,8 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H542" t="s">
-        <v>8</v>
+      <c r="G542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -14486,11 +12857,8 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H543" t="s">
-        <v>8</v>
+      <c r="G543" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -14512,11 +12880,8 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H544" t="s">
-        <v>8</v>
+      <c r="G544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545">
@@ -14538,11 +12903,8 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H545" t="s">
-        <v>8</v>
+      <c r="G545" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="546">
@@ -14564,11 +12926,8 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H546" t="s">
-        <v>8</v>
+      <c r="G546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547">
@@ -14590,11 +12949,8 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H547" t="s">
-        <v>8</v>
+      <c r="G547" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="548">
@@ -14616,11 +12972,8 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H548" t="s">
-        <v>8</v>
+      <c r="G548" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -14642,11 +12995,8 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H549" t="s">
-        <v>8</v>
+      <c r="G549" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -14668,11 +13018,8 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H550" t="s">
-        <v>8</v>
+      <c r="G550" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -14694,11 +13041,8 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H551" t="s">
-        <v>8</v>
+      <c r="G551" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="552">
@@ -14720,11 +13064,8 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H552" t="s">
-        <v>8</v>
+      <c r="G552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -14746,11 +13087,8 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H553" t="s">
-        <v>8</v>
+      <c r="G553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -14772,11 +13110,8 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H554" t="s">
-        <v>8</v>
+      <c r="G554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -14798,11 +13133,8 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H555" t="s">
-        <v>8</v>
+      <c r="G555" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="556">
@@ -14824,11 +13156,8 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H556" t="s">
-        <v>8</v>
+      <c r="G556" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="557">
@@ -14850,11 +13179,8 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H557" t="s">
-        <v>8</v>
+      <c r="G557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -14876,11 +13202,8 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H558" t="s">
-        <v>8</v>
+      <c r="G558" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="559">
@@ -14902,11 +13225,8 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H559" t="s">
-        <v>8</v>
+      <c r="G559" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="560">
@@ -14928,11 +13248,8 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H560" t="s">
-        <v>8</v>
+      <c r="G560" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -14954,11 +13271,8 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H561" t="s">
-        <v>8</v>
+      <c r="G561" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="562">
@@ -14980,11 +13294,8 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H562" t="s">
-        <v>8</v>
+      <c r="G562" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="563">
@@ -15006,11 +13317,8 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H563" t="s">
-        <v>8</v>
+      <c r="G563" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="564">
@@ -15032,11 +13340,8 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H564" t="s">
-        <v>8</v>
+      <c r="G564" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -15058,11 +13363,8 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H565" t="s">
-        <v>8</v>
+      <c r="G565" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="566">
@@ -15084,11 +13386,8 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H566" t="s">
-        <v>8</v>
+      <c r="G566" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -15110,11 +13409,8 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H567" t="s">
-        <v>8</v>
+      <c r="G567" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="568">
@@ -15136,11 +13432,8 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H568" t="s">
-        <v>8</v>
+      <c r="G568" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -15162,11 +13455,8 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H569" t="s">
-        <v>8</v>
+      <c r="G569" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="570">
@@ -15188,11 +13478,8 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H570" t="s">
-        <v>8</v>
+      <c r="G570" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -15214,11 +13501,8 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H571" t="s">
-        <v>8</v>
+      <c r="G571" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="572">
@@ -15240,11 +13524,8 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H572" t="s">
-        <v>8</v>
+      <c r="G572" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -15266,11 +13547,8 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H573" t="s">
-        <v>8</v>
+      <c r="G573" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="574">
@@ -15292,11 +13570,8 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H574" t="s">
-        <v>8</v>
+      <c r="G574" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -15318,11 +13593,8 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H575" t="s">
-        <v>8</v>
+      <c r="G575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -15344,11 +13616,8 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H576" t="s">
-        <v>8</v>
+      <c r="G576" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -15370,11 +13639,8 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H577" t="s">
-        <v>8</v>
+      <c r="G577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -15396,11 +13662,8 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="n">
-        <v>0.0175000000745058</v>
-      </c>
-      <c r="H578" t="s">
-        <v>8</v>
+      <c r="G578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579">
@@ -15422,11 +13685,8 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H579" t="s">
-        <v>8</v>
+      <c r="G579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580">
@@ -15448,11 +13708,8 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H580" t="s">
-        <v>8</v>
+      <c r="G580" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="581">
@@ -15474,11 +13731,8 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H581" t="s">
-        <v>8</v>
+      <c r="G581" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="582">
@@ -15500,11 +13754,8 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H582" t="s">
-        <v>8</v>
+      <c r="G582" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -15526,11 +13777,8 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H583" t="s">
-        <v>8</v>
+      <c r="G583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -15552,11 +13800,8 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H584" t="s">
-        <v>8</v>
+      <c r="G584" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="585">
@@ -15578,11 +13823,8 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H585" t="s">
-        <v>8</v>
+      <c r="G585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586">
@@ -15604,11 +13846,8 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H586" t="s">
-        <v>8</v>
+      <c r="G586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -15630,11 +13869,8 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H587" t="s">
-        <v>8</v>
+      <c r="G587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588">
@@ -15656,11 +13892,8 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H588" t="s">
-        <v>8</v>
+      <c r="G588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589">
@@ -15682,11 +13915,8 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H589" t="s">
-        <v>8</v>
+      <c r="G589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590">
@@ -15708,11 +13938,8 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="n">
-        <v>0.0171000007539988</v>
-      </c>
-      <c r="H590" t="s">
-        <v>8</v>
+      <c r="G590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591">
@@ -15734,11 +13961,8 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H591" t="s">
-        <v>8</v>
+      <c r="G591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592">
@@ -15760,11 +13984,8 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H592" t="s">
-        <v>8</v>
+      <c r="G592" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="593">
@@ -15786,11 +14007,8 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H593" t="s">
-        <v>8</v>
+      <c r="G593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594">
@@ -15812,11 +14030,8 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="n">
-        <v>0.0215000007301569</v>
-      </c>
-      <c r="H594" t="s">
-        <v>8</v>
+      <c r="G594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595">
@@ -15838,11 +14053,8 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="n">
-        <v>0.0203000009059906</v>
-      </c>
-      <c r="H595" t="s">
-        <v>8</v>
+      <c r="G595" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="596">
@@ -15864,11 +14076,8 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H596" t="s">
-        <v>8</v>
+      <c r="G596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597">
@@ -15890,11 +14099,8 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H597" t="s">
-        <v>8</v>
+      <c r="G597" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="598">
@@ -15916,11 +14122,8 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H598" t="s">
-        <v>8</v>
+      <c r="G598" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="599">
@@ -15942,11 +14145,8 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H599" t="s">
-        <v>8</v>
+      <c r="G599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600">
@@ -15968,11 +14168,8 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="n">
-        <v>0.0183000005781651</v>
-      </c>
-      <c r="H600" t="s">
-        <v>8</v>
+      <c r="G600" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="601">
@@ -15994,11 +14191,8 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H601" t="s">
-        <v>8</v>
+      <c r="G601" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="602">
@@ -16020,11 +14214,8 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H602" t="s">
-        <v>8</v>
+      <c r="G602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603">
@@ -16046,11 +14237,8 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H603" t="s">
-        <v>8</v>
+      <c r="G603" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="604">
@@ -16072,11 +14260,8 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="n">
-        <v>0.0196000002324581</v>
-      </c>
-      <c r="H604" t="s">
-        <v>8</v>
+      <c r="G604" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="605">
@@ -16098,11 +14283,8 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="n">
-        <v>0.0192000009119511</v>
-      </c>
-      <c r="H605" t="s">
-        <v>8</v>
+      <c r="G605" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="606">
@@ -16124,11 +14306,8 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H606" t="s">
-        <v>8</v>
+      <c r="G606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607">
@@ -16150,11 +14329,8 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H607" t="s">
-        <v>8</v>
+      <c r="G607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608">
@@ -16176,11 +14352,8 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H608" t="s">
-        <v>8</v>
+      <c r="G608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609">
@@ -16202,11 +14375,8 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="n">
-        <v>0.0181000009179115</v>
-      </c>
-      <c r="H609" t="s">
-        <v>8</v>
+      <c r="G609" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="610">
@@ -16228,11 +14398,8 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H610" t="s">
-        <v>8</v>
+      <c r="G610" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="611">
@@ -16254,11 +14421,8 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H611" t="s">
-        <v>8</v>
+      <c r="G611" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="612">
@@ -16280,11 +14444,8 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H612" t="s">
-        <v>8</v>
+      <c r="G612" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="613">
@@ -16306,11 +14467,8 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H613" t="s">
-        <v>8</v>
+      <c r="G613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614">
@@ -16332,11 +14490,8 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H614" t="s">
-        <v>8</v>
+      <c r="G614" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -16358,11 +14513,8 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H615" t="s">
-        <v>8</v>
+      <c r="G615" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="616">
@@ -16384,11 +14536,8 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H616" t="s">
-        <v>8</v>
+      <c r="G616" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -16410,11 +14559,8 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H617" t="s">
-        <v>8</v>
+      <c r="G617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618">
@@ -16436,11 +14582,8 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H618" t="s">
-        <v>8</v>
+      <c r="G618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619">
@@ -16462,11 +14605,8 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H619" t="s">
-        <v>8</v>
+      <c r="G619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620">
@@ -16488,11 +14628,8 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H620" t="s">
-        <v>8</v>
+      <c r="G620" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="621">
@@ -16514,11 +14651,8 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H621" t="s">
-        <v>8</v>
+      <c r="G621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622">
@@ -16540,11 +14674,8 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H622" t="s">
-        <v>8</v>
+      <c r="G622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623">
@@ -16566,11 +14697,8 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H623" t="s">
-        <v>8</v>
+      <c r="G623" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="624">
@@ -16592,11 +14720,8 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H624" t="s">
-        <v>8</v>
+      <c r="G624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625">
@@ -16618,11 +14743,8 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H625" t="s">
-        <v>8</v>
+      <c r="G625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -16644,11 +14766,8 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H626" t="s">
-        <v>8</v>
+      <c r="G626" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="627">
@@ -16670,11 +14789,8 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H627" t="s">
-        <v>8</v>
+      <c r="G627" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="628">
@@ -16696,11 +14812,8 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H628" t="s">
-        <v>8</v>
+      <c r="G628" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="629">
@@ -16722,11 +14835,8 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H629" t="s">
-        <v>8</v>
+      <c r="G629" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="630">
@@ -16748,11 +14858,8 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H630" t="s">
-        <v>8</v>
+      <c r="G630" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -16774,11 +14881,8 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H631" t="s">
-        <v>8</v>
+      <c r="G631" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="632">
@@ -16800,11 +14904,8 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H632" t="s">
-        <v>8</v>
+      <c r="G632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633">
@@ -16826,11 +14927,8 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="n">
-        <v>0.0172000005841255</v>
-      </c>
-      <c r="H633" t="s">
-        <v>8</v>
+      <c r="G633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -16852,11 +14950,8 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H634" t="s">
-        <v>8</v>
+      <c r="G634" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -16878,11 +14973,8 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H635" t="s">
-        <v>8</v>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -16904,11 +14996,8 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H636" t="s">
-        <v>8</v>
+      <c r="G636" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="637">
@@ -16930,11 +15019,8 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H637" t="s">
-        <v>8</v>
+      <c r="G637" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="638">
@@ -16956,11 +15042,8 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H638" t="s">
-        <v>8</v>
+      <c r="G638" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="639">
@@ -16982,11 +15065,8 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H639" t="s">
-        <v>8</v>
+      <c r="G639" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="640">
@@ -17008,11 +15088,8 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H640" t="s">
-        <v>8</v>
+      <c r="G640" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="641">
@@ -17034,11 +15111,8 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H641" t="s">
-        <v>8</v>
+      <c r="G641" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -17060,11 +15134,8 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H642" t="s">
-        <v>8</v>
+      <c r="G642" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -17086,11 +15157,8 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H643" t="s">
-        <v>8</v>
+      <c r="G643" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="644">
@@ -17112,11 +15180,8 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H644" t="s">
-        <v>8</v>
+      <c r="G644" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -17138,11 +15203,8 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H645" t="s">
-        <v>8</v>
+      <c r="G645" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -17164,11 +15226,8 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H646" t="s">
-        <v>8</v>
+      <c r="G646" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="647">
@@ -17190,11 +15249,8 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H647" t="s">
-        <v>8</v>
+      <c r="G647" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -17216,11 +15272,8 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H648" t="s">
-        <v>8</v>
+      <c r="G648" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -17242,11 +15295,8 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H649" t="s">
-        <v>8</v>
+      <c r="G649" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="650">
@@ -17268,11 +15318,8 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H650" t="s">
-        <v>8</v>
+      <c r="G650" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="651">
@@ -17294,11 +15341,8 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H651" t="s">
-        <v>8</v>
+      <c r="G651" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="652">
@@ -17320,11 +15364,8 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H652" t="s">
-        <v>8</v>
+      <c r="G652" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="653">
@@ -17346,11 +15387,8 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H653" t="s">
-        <v>8</v>
+      <c r="G653" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -17372,11 +15410,8 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H654" t="s">
-        <v>8</v>
+      <c r="G654" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="655">
@@ -17398,11 +15433,8 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H655" t="s">
-        <v>8</v>
+      <c r="G655" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="656">
@@ -17424,11 +15456,8 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H656" t="s">
-        <v>8</v>
+      <c r="G656" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="657">
@@ -17450,11 +15479,8 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H657" t="s">
-        <v>8</v>
+      <c r="G657" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="658">
@@ -17476,11 +15502,8 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H658" t="s">
-        <v>8</v>
+      <c r="G658" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -17502,11 +15525,8 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H659" t="s">
-        <v>8</v>
+      <c r="G659" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -17528,11 +15548,8 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H660" t="s">
-        <v>8</v>
+      <c r="G660" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -17554,11 +15571,8 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H661" t="s">
-        <v>8</v>
+      <c r="G661" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="662">
@@ -17580,11 +15594,8 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H662" t="s">
-        <v>8</v>
+      <c r="G662" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="663">
@@ -17606,11 +15617,8 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H663" t="s">
-        <v>8</v>
+      <c r="G663" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="664">
@@ -17632,11 +15640,8 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H664" t="s">
-        <v>8</v>
+      <c r="G664" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="665">
@@ -17658,11 +15663,8 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H665" t="s">
-        <v>8</v>
+      <c r="G665" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="666">
@@ -17684,11 +15686,8 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H666" t="s">
-        <v>8</v>
+      <c r="G666" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="667">
@@ -17710,11 +15709,8 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H667" t="s">
-        <v>8</v>
+      <c r="G667" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="668">
@@ -17736,11 +15732,8 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H668" t="s">
-        <v>8</v>
+      <c r="G668" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="669">
@@ -17762,11 +15755,8 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H669" t="s">
-        <v>8</v>
+      <c r="G669" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -17788,11 +15778,8 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H670" t="s">
-        <v>8</v>
+      <c r="G670" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -17814,11 +15801,8 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H671" t="s">
-        <v>8</v>
+      <c r="G671" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="672">
@@ -17840,11 +15824,8 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="n">
-        <v>0.0201999992132187</v>
-      </c>
-      <c r="H672" t="s">
-        <v>8</v>
+      <c r="G672" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="673">
@@ -17866,11 +15847,8 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="n">
-        <v>0.0206000003963709</v>
-      </c>
-      <c r="H673" t="s">
-        <v>8</v>
+      <c r="G673" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="674">
@@ -17892,11 +15870,8 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="n">
-        <v>0.0208000000566244</v>
-      </c>
-      <c r="H674" t="s">
-        <v>8</v>
+      <c r="G674" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="675">
@@ -17918,11 +15893,8 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="n">
-        <v>0.0211999993771315</v>
-      </c>
-      <c r="H675" t="s">
-        <v>8</v>
+      <c r="G675" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="676">
@@ -17944,11 +15916,8 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="n">
-        <v>0.02280000038445</v>
-      </c>
-      <c r="H676" t="s">
-        <v>8</v>
+      <c r="G676" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="677">
@@ -17970,11 +15939,8 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="n">
-        <v>0.0216000005602837</v>
-      </c>
-      <c r="H677" t="s">
-        <v>8</v>
+      <c r="G677" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="678">
@@ -17996,11 +15962,8 @@
       <c r="F678" t="n">
         <v>0.0221999995410442</v>
       </c>
-      <c r="G678" t="n">
-        <v>0.0221999995410442</v>
-      </c>
-      <c r="H678" t="s">
-        <v>8</v>
+      <c r="G678" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="679">
@@ -18022,11 +15985,8 @@
       <c r="F679" t="n">
         <v>0.0233999993652105</v>
       </c>
-      <c r="G679" t="n">
-        <v>0.0233999993652105</v>
-      </c>
-      <c r="H679" t="s">
-        <v>8</v>
+      <c r="G679" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="680">
@@ -18048,11 +16008,29 @@
       <c r="F680" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G680" t="n">
+      <c r="G680" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B681" t="n">
+        <v>6497665</v>
+      </c>
+      <c r="C681" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="H680" t="s">
-        <v>8</v>
+      <c r="D681" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="F681"/>
+      <c r="G681" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -394,6 +397,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -414,8 +420,11 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -437,8 +446,11 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +472,11 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -483,8 +498,11 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -506,8 +524,11 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -529,8 +550,11 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -552,8 +576,11 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -575,8 +602,11 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -598,8 +628,11 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -621,8 +654,11 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +680,11 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -667,8 +706,11 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -690,8 +732,11 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -713,8 +758,11 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -736,8 +784,11 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -759,8 +810,11 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -782,8 +836,11 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,8 +862,11 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -828,8 +888,11 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -851,8 +914,11 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -874,8 +940,11 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -897,8 +966,11 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -920,8 +992,11 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -943,8 +1018,11 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -966,8 +1044,11 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -989,8 +1070,11 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" t="n">
+        <v>0.019845999777317</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1012,8 +1096,11 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1035,8 +1122,11 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1058,8 +1148,11 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
+      <c r="G30" t="n">
+        <v>0.01923399977386</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1081,8 +1174,11 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1104,8 +1200,11 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1127,8 +1226,11 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1150,8 +1252,11 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1173,8 +1278,11 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1196,8 +1304,11 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1219,8 +1330,11 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1242,8 +1356,11 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1265,8 +1382,11 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1288,8 +1408,11 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1311,8 +1434,11 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1334,8 +1460,11 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="G42" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1357,8 +1486,11 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1380,8 +1512,11 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,8 +1538,11 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -1426,8 +1564,11 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1449,8 +1590,11 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1472,8 +1616,11 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1495,8 +1642,11 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1518,8 +1668,11 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1541,8 +1694,11 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1564,8 +1720,11 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1587,8 +1746,11 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -1610,8 +1772,11 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1633,8 +1798,11 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1656,8 +1824,11 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1679,8 +1850,11 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -1702,8 +1876,11 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1725,8 +1902,11 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1748,8 +1928,11 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="s">
-        <v>7</v>
+      <c r="G60" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1771,8 +1954,11 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="s">
-        <v>7</v>
+      <c r="G61" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1794,8 +1980,11 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="s">
-        <v>7</v>
+      <c r="G62" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1817,8 +2006,11 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1840,8 +2032,11 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1863,8 +2058,11 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1886,8 +2084,11 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1909,8 +2110,11 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1932,8 +2136,11 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -1955,8 +2162,11 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1978,8 +2188,11 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -2001,8 +2214,11 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2024,8 +2240,11 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2047,8 +2266,11 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -2070,8 +2292,11 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -2093,8 +2318,11 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -2116,8 +2344,11 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2139,8 +2370,11 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -2162,8 +2396,11 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -2185,8 +2422,11 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2208,8 +2448,11 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
+      <c r="G80" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -2231,8 +2474,11 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2254,8 +2500,11 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2277,8 +2526,11 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2300,8 +2552,11 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2323,8 +2578,11 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2346,8 +2604,11 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -2369,8 +2630,11 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -2392,8 +2656,11 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2415,8 +2682,11 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -2438,8 +2708,11 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2461,8 +2734,11 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2484,8 +2760,11 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2507,8 +2786,11 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2530,8 +2812,11 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2553,8 +2838,11 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2576,8 +2864,11 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2599,8 +2890,11 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="s">
-        <v>7</v>
+      <c r="G97" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2622,8 +2916,11 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="s">
-        <v>7</v>
+      <c r="G98" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -2645,8 +2942,11 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -2668,8 +2968,11 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -2691,8 +2994,11 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2714,8 +3020,11 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2737,8 +3046,11 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -2760,8 +3072,11 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -2783,8 +3098,11 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2806,8 +3124,11 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="s">
-        <v>7</v>
+      <c r="G106" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -2829,8 +3150,11 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -2852,8 +3176,11 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -2875,8 +3202,11 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2898,8 +3228,11 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -2921,8 +3254,11 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -2944,8 +3280,11 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -2967,8 +3306,11 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2990,8 +3332,11 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3013,8 +3358,11 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -3036,8 +3384,11 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -3059,8 +3410,11 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -3082,8 +3436,11 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3105,8 +3462,11 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -3128,8 +3488,11 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -3151,8 +3514,11 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="G121" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3174,8 +3540,11 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -3197,8 +3566,11 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H123" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3220,8 +3592,11 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -3243,8 +3618,11 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H125" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3266,8 +3644,11 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H126" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -3289,8 +3670,11 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H127" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3312,8 +3696,11 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H128" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -3335,8 +3722,11 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H129" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -3358,8 +3748,11 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H130" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -3381,8 +3774,11 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H131" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132">
@@ -3404,8 +3800,11 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H132" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -3427,8 +3826,11 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H133" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134">
@@ -3450,8 +3852,11 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -3473,8 +3878,11 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="s">
-        <v>7</v>
+      <c r="G135" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136">
@@ -3496,8 +3904,11 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="s">
-        <v>7</v>
+      <c r="G136" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137">
@@ -3519,8 +3930,11 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="s">
-        <v>7</v>
+      <c r="G137" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -3542,8 +3956,11 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3565,8 +3982,11 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140">
@@ -3588,8 +4008,11 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141">
@@ -3611,8 +4034,11 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -3634,8 +4060,11 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,8 +4086,11 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
@@ -3680,8 +4112,11 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -3703,8 +4138,11 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146">
@@ -3726,8 +4164,11 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3749,8 +4190,11 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148">
@@ -3772,8 +4216,11 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3795,8 +4242,11 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
+      <c r="G149" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150">
@@ -3818,8 +4268,11 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -3841,8 +4294,11 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
@@ -3864,8 +4320,11 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="s">
-        <v>7</v>
+      <c r="G152" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3887,8 +4346,11 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="s">
-        <v>7</v>
+      <c r="G153" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,8 +4372,11 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3933,8 +4398,11 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156">
@@ -3956,8 +4424,11 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -3979,8 +4450,11 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158">
@@ -4002,8 +4476,11 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -4025,8 +4502,11 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
+      <c r="G159" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -4048,8 +4528,11 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="s">
-        <v>7</v>
+      <c r="G160" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161">
@@ -4071,8 +4554,11 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="s">
-        <v>7</v>
+      <c r="G161" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162">
@@ -4094,8 +4580,11 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="s">
-        <v>7</v>
+      <c r="G162" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -4117,8 +4606,11 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="s">
-        <v>7</v>
+      <c r="G163" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -4140,8 +4632,11 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="s">
-        <v>7</v>
+      <c r="G164" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -4163,8 +4658,11 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="s">
-        <v>7</v>
+      <c r="G165" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -4186,8 +4684,11 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -4209,8 +4710,11 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -4232,8 +4736,11 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169">
@@ -4255,8 +4762,11 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4278,8 +4788,11 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H170" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -4301,8 +4814,11 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="s">
-        <v>7</v>
+      <c r="G171" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4324,8 +4840,11 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="s">
-        <v>7</v>
+      <c r="G172" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H172" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4347,8 +4866,11 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H173" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4370,8 +4892,11 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
+      <c r="G174" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H174" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -4393,8 +4918,11 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
+      <c r="G175" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H175" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176">
@@ -4416,8 +4944,11 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="s">
-        <v>7</v>
+      <c r="G176" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H176" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -4439,8 +4970,11 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="s">
-        <v>7</v>
+      <c r="G177" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H177" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -4462,8 +4996,11 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H178" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4485,8 +5022,11 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
+      <c r="G179" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H179" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4508,8 +5048,11 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="s">
-        <v>7</v>
+      <c r="G180" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H180" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
@@ -4531,8 +5074,11 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="s">
-        <v>7</v>
+      <c r="G181" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H181" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182">
@@ -4554,8 +5100,11 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="s">
-        <v>7</v>
+      <c r="G182" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H182" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183">
@@ -4577,8 +5126,11 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="s">
-        <v>7</v>
+      <c r="G183" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H183" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
@@ -4600,8 +5152,11 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="s">
-        <v>7</v>
+      <c r="G184" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185">
@@ -4623,8 +5178,11 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="s">
-        <v>7</v>
+      <c r="G185" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H185" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186">
@@ -4646,8 +5204,11 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="s">
-        <v>7</v>
+      <c r="G186" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H186" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187">
@@ -4669,8 +5230,11 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="s">
-        <v>7</v>
+      <c r="G187" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H187" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4692,8 +5256,11 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="s">
-        <v>7</v>
+      <c r="G188" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H188" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189">
@@ -4715,8 +5282,11 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="s">
-        <v>7</v>
+      <c r="G189" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H189" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4738,8 +5308,11 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="s">
-        <v>7</v>
+      <c r="G190" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H190" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4761,8 +5334,11 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="s">
-        <v>7</v>
+      <c r="G191" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H191" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -4784,8 +5360,11 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="s">
-        <v>7</v>
+      <c r="G192" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H192" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4807,8 +5386,11 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="s">
-        <v>7</v>
+      <c r="G193" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H193" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194">
@@ -4830,8 +5412,11 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="s">
-        <v>7</v>
+      <c r="G194" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H194" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195">
@@ -4853,8 +5438,11 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="s">
-        <v>7</v>
+      <c r="G195" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H195" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -4876,8 +5464,11 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="s">
-        <v>7</v>
+      <c r="G196" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H196" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -4899,8 +5490,11 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="s">
-        <v>7</v>
+      <c r="G197" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -4922,8 +5516,11 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="s">
-        <v>7</v>
+      <c r="G198" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H198" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199">
@@ -4945,8 +5542,11 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="s">
-        <v>7</v>
+      <c r="G199" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H199" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -4968,8 +5568,11 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="s">
-        <v>7</v>
+      <c r="G200" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H200" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201">
@@ -4991,8 +5594,11 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="s">
-        <v>7</v>
+      <c r="G201" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H201" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -5014,8 +5620,11 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="s">
-        <v>7</v>
+      <c r="G202" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H202" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -5037,8 +5646,11 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="s">
-        <v>7</v>
+      <c r="G203" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -5060,8 +5672,11 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="s">
-        <v>7</v>
+      <c r="G204" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H204" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -5083,8 +5698,11 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="s">
-        <v>7</v>
+      <c r="G205" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H205" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -5106,8 +5724,11 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="s">
-        <v>7</v>
+      <c r="G206" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H206" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207">
@@ -5129,8 +5750,11 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="s">
-        <v>7</v>
+      <c r="G207" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H207" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -5152,8 +5776,11 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="s">
-        <v>7</v>
+      <c r="G208" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H208" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209">
@@ -5175,8 +5802,11 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="s">
-        <v>7</v>
+      <c r="G209" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H209" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -5198,8 +5828,11 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="s">
-        <v>7</v>
+      <c r="G210" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H210" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5221,8 +5854,11 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="s">
-        <v>7</v>
+      <c r="G211" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H211" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -5244,8 +5880,11 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="s">
-        <v>7</v>
+      <c r="G212" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H212" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213">
@@ -5267,8 +5906,11 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="s">
-        <v>7</v>
+      <c r="G213" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H213" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214">
@@ -5290,8 +5932,11 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="s">
-        <v>7</v>
+      <c r="G214" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H214" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5313,8 +5958,11 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="s">
-        <v>7</v>
+      <c r="G215" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H215" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5336,8 +5984,11 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="s">
-        <v>7</v>
+      <c r="G216" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H216" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -5359,8 +6010,11 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="s">
-        <v>7</v>
+      <c r="G217" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H217" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5382,8 +6036,11 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="s">
-        <v>7</v>
+      <c r="G218" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H218" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -5405,8 +6062,11 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="s">
-        <v>7</v>
+      <c r="G219" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H219" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -5428,8 +6088,11 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="s">
-        <v>7</v>
+      <c r="G220" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H220" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -5451,8 +6114,11 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="s">
-        <v>7</v>
+      <c r="G221" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H221" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222">
@@ -5474,8 +6140,11 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="s">
-        <v>7</v>
+      <c r="G222" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H222" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -5497,8 +6166,11 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="s">
-        <v>7</v>
+      <c r="G223" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H223" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224">
@@ -5520,8 +6192,11 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="s">
-        <v>7</v>
+      <c r="G224" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H224" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225">
@@ -5543,8 +6218,11 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="s">
-        <v>7</v>
+      <c r="G225" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H225" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -5566,8 +6244,11 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="s">
-        <v>7</v>
+      <c r="G226" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H226" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5589,8 +6270,11 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="s">
-        <v>7</v>
+      <c r="G227" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H227" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5612,8 +6296,11 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="s">
-        <v>7</v>
+      <c r="G228" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H228" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229">
@@ -5635,8 +6322,11 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="s">
-        <v>7</v>
+      <c r="G229" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H229" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5658,8 +6348,11 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="s">
-        <v>7</v>
+      <c r="G230" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H230" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5681,8 +6374,11 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="s">
-        <v>7</v>
+      <c r="G231" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H231" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5704,8 +6400,11 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="s">
-        <v>7</v>
+      <c r="G232" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H232" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5727,8 +6426,11 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="s">
-        <v>7</v>
+      <c r="G233" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H233" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234">
@@ -5750,8 +6452,11 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="s">
-        <v>7</v>
+      <c r="G234" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H234" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -5773,8 +6478,11 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="s">
-        <v>7</v>
+      <c r="G235" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H235" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -5796,8 +6504,11 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="s">
-        <v>7</v>
+      <c r="G236" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H236" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -5819,8 +6530,11 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="s">
-        <v>7</v>
+      <c r="G237" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H237" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -5842,8 +6556,11 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="s">
-        <v>7</v>
+      <c r="G238" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H238" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239">
@@ -5865,8 +6582,11 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="s">
-        <v>7</v>
+      <c r="G239" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H239" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5888,8 +6608,11 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="s">
-        <v>7</v>
+      <c r="G240" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H240" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -5911,8 +6634,11 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="s">
-        <v>7</v>
+      <c r="G241" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H241" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -5934,8 +6660,11 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="s">
-        <v>7</v>
+      <c r="G242" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H242" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5957,8 +6686,11 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="s">
-        <v>7</v>
+      <c r="G243" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H243" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -5980,8 +6712,11 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="s">
-        <v>7</v>
+      <c r="G244" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H244" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -6003,8 +6738,11 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="s">
-        <v>7</v>
+      <c r="G245" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H245" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6026,8 +6764,11 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="s">
-        <v>7</v>
+      <c r="G246" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H246" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -6049,8 +6790,11 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="s">
-        <v>7</v>
+      <c r="G247" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H247" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -6072,8 +6816,11 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="s">
-        <v>7</v>
+      <c r="G248" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H248" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -6095,8 +6842,11 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="s">
-        <v>7</v>
+      <c r="G249" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H249" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -6118,8 +6868,11 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="s">
-        <v>7</v>
+      <c r="G250" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H250" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251">
@@ -6141,8 +6894,11 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="s">
-        <v>7</v>
+      <c r="G251" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H251" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6164,8 +6920,11 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="s">
-        <v>7</v>
+      <c r="G252" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H252" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6187,8 +6946,11 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="s">
-        <v>7</v>
+      <c r="G253" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H253" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6210,8 +6972,11 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="s">
-        <v>7</v>
+      <c r="G254" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H254" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6233,8 +6998,11 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="s">
-        <v>7</v>
+      <c r="G255" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6256,8 +7024,11 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="s">
-        <v>7</v>
+      <c r="G256" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257">
@@ -6279,8 +7050,11 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="s">
-        <v>7</v>
+      <c r="G257" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6302,8 +7076,11 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="s">
-        <v>7</v>
+      <c r="G258" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259">
@@ -6325,8 +7102,11 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="s">
-        <v>7</v>
+      <c r="G259" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H259" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260">
@@ -6348,8 +7128,11 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="s">
-        <v>7</v>
+      <c r="G260" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H260" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261">
@@ -6371,8 +7154,11 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="s">
-        <v>7</v>
+      <c r="G261" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H261" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -6394,8 +7180,11 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="s">
-        <v>7</v>
+      <c r="G262" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H262" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263">
@@ -6417,8 +7206,11 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="s">
-        <v>7</v>
+      <c r="G263" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H263" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264">
@@ -6440,8 +7232,11 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="s">
-        <v>7</v>
+      <c r="G264" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H264" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265">
@@ -6463,8 +7258,11 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="s">
-        <v>7</v>
+      <c r="G265" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H265" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -6486,8 +7284,11 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="s">
-        <v>7</v>
+      <c r="G266" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H266" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6509,8 +7310,11 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="s">
-        <v>7</v>
+      <c r="G267" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H267" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -6532,8 +7336,11 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="s">
-        <v>7</v>
+      <c r="G268" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H268" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -6555,8 +7362,11 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="s">
-        <v>7</v>
+      <c r="G269" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H269" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -6578,8 +7388,11 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="s">
-        <v>7</v>
+      <c r="G270" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H270" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271">
@@ -6601,8 +7414,11 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="s">
-        <v>7</v>
+      <c r="G271" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H271" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -6624,8 +7440,11 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="s">
-        <v>7</v>
+      <c r="G272" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H272" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -6647,8 +7466,11 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
+      <c r="G273" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H273" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6670,8 +7492,11 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="s">
-        <v>7</v>
+      <c r="G274" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H274" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -6693,8 +7518,11 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="s">
-        <v>7</v>
+      <c r="G275" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H275" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6716,8 +7544,11 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="s">
-        <v>7</v>
+      <c r="G276" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H276" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6739,8 +7570,11 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="s">
-        <v>7</v>
+      <c r="G277" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H277" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6762,8 +7596,11 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="s">
-        <v>7</v>
+      <c r="G278" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H278" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6785,8 +7622,11 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="s">
-        <v>7</v>
+      <c r="G279" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H279" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -6808,8 +7648,11 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="s">
-        <v>7</v>
+      <c r="G280" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H280" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -6831,8 +7674,11 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="s">
-        <v>7</v>
+      <c r="G281" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H281" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6854,8 +7700,11 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="s">
-        <v>7</v>
+      <c r="G282" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H282" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -6877,8 +7726,11 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="s">
-        <v>7</v>
+      <c r="G283" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H283" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284">
@@ -6900,8 +7752,11 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="s">
-        <v>7</v>
+      <c r="G284" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H284" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -6923,8 +7778,11 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="s">
-        <v>7</v>
+      <c r="G285" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H285" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6946,8 +7804,11 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="s">
-        <v>7</v>
+      <c r="G286" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H286" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6969,8 +7830,11 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="s">
-        <v>7</v>
+      <c r="G287" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H287" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6992,8 +7856,11 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="s">
-        <v>7</v>
+      <c r="G288" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H288" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -7015,8 +7882,11 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="s">
-        <v>7</v>
+      <c r="G289" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H289" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -7038,8 +7908,11 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="s">
-        <v>7</v>
+      <c r="G290" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H290" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7061,8 +7934,11 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="s">
-        <v>7</v>
+      <c r="G291" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H291" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -7084,8 +7960,11 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="s">
-        <v>7</v>
+      <c r="G292" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H292" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -7107,8 +7986,11 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="s">
-        <v>7</v>
+      <c r="G293" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H293" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -7130,8 +8012,11 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="s">
-        <v>7</v>
+      <c r="G294" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H294" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295">
@@ -7153,8 +8038,11 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="s">
-        <v>7</v>
+      <c r="G295" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H295" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -7176,8 +8064,11 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="s">
-        <v>7</v>
+      <c r="G296" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H296" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -7199,8 +8090,11 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="s">
-        <v>7</v>
+      <c r="G297" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H297" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -7222,8 +8116,11 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="s">
-        <v>7</v>
+      <c r="G298" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -7245,8 +8142,11 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="s">
-        <v>7</v>
+      <c r="G299" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H299" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -7268,8 +8168,11 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="s">
-        <v>7</v>
+      <c r="G300" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H300" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -7291,8 +8194,11 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="s">
-        <v>7</v>
+      <c r="G301" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H301" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7314,8 +8220,11 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="s">
-        <v>7</v>
+      <c r="G302" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H302" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -7337,8 +8246,11 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="s">
-        <v>7</v>
+      <c r="G303" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H303" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7360,8 +8272,11 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="s">
-        <v>7</v>
+      <c r="G304" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H304" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305">
@@ -7383,8 +8298,11 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="s">
-        <v>7</v>
+      <c r="G305" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H305" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -7406,8 +8324,11 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="s">
-        <v>7</v>
+      <c r="G306" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H306" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307">
@@ -7429,8 +8350,11 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="s">
-        <v>7</v>
+      <c r="G307" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H307" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308">
@@ -7452,8 +8376,11 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="s">
-        <v>7</v>
+      <c r="G308" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H308" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309">
@@ -7475,8 +8402,11 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="s">
-        <v>7</v>
+      <c r="G309" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H309" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310">
@@ -7498,8 +8428,11 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="s">
-        <v>7</v>
+      <c r="G310" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H310" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -7521,8 +8454,11 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="s">
-        <v>7</v>
+      <c r="G311" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H311" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -7544,8 +8480,11 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="s">
-        <v>7</v>
+      <c r="G312" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H312" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -7567,8 +8506,11 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="s">
-        <v>7</v>
+      <c r="G313" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H313" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7590,8 +8532,11 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="s">
-        <v>7</v>
+      <c r="G314" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H314" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315">
@@ -7613,8 +8558,11 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="s">
-        <v>7</v>
+      <c r="G315" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H315" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -7636,8 +8584,11 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="s">
-        <v>7</v>
+      <c r="G316" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H316" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -7659,8 +8610,11 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="s">
-        <v>7</v>
+      <c r="G317" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H317" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7682,8 +8636,11 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="s">
-        <v>7</v>
+      <c r="G318" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H318" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319">
@@ -7705,8 +8662,11 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="s">
-        <v>7</v>
+      <c r="G319" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H319" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -7728,8 +8688,11 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="s">
-        <v>7</v>
+      <c r="G320" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H320" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -7751,8 +8714,11 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="s">
-        <v>7</v>
+      <c r="G321" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H321" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -7774,8 +8740,11 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="s">
-        <v>7</v>
+      <c r="G322" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H322" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -7797,8 +8766,11 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="s">
-        <v>7</v>
+      <c r="G323" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H323" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7820,8 +8792,11 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="s">
-        <v>7</v>
+      <c r="G324" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H324" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7843,8 +8818,11 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="s">
-        <v>7</v>
+      <c r="G325" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H325" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -7866,8 +8844,11 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="s">
-        <v>7</v>
+      <c r="G326" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H326" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327">
@@ -7889,8 +8870,11 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="s">
-        <v>7</v>
+      <c r="G327" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H327" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7912,8 +8896,11 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="s">
-        <v>7</v>
+      <c r="G328" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H328" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329">
@@ -7935,8 +8922,11 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="s">
-        <v>7</v>
+      <c r="G329" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H329" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7958,8 +8948,11 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="s">
-        <v>7</v>
+      <c r="G330" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H330" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -7981,8 +8974,11 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="s">
-        <v>7</v>
+      <c r="G331" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332">
@@ -8004,8 +9000,11 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="s">
-        <v>7</v>
+      <c r="G332" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H332" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8027,8 +9026,11 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="s">
-        <v>7</v>
+      <c r="G333" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H333" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -8050,8 +9052,11 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="s">
-        <v>7</v>
+      <c r="G334" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H334" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -8073,8 +9078,11 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="s">
-        <v>7</v>
+      <c r="G335" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H335" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -8096,8 +9104,11 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="s">
-        <v>7</v>
+      <c r="G336" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H336" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8119,8 +9130,11 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="s">
-        <v>7</v>
+      <c r="G337" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H337" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338">
@@ -8142,8 +9156,11 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="s">
-        <v>7</v>
+      <c r="G338" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H338" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339">
@@ -8165,8 +9182,11 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="s">
-        <v>7</v>
+      <c r="G339" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H339" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -8188,8 +9208,11 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="s">
-        <v>7</v>
+      <c r="G340" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H340" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -8211,8 +9234,11 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="s">
-        <v>7</v>
+      <c r="G341" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H341" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342">
@@ -8234,8 +9260,11 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="s">
-        <v>7</v>
+      <c r="G342" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H342" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343">
@@ -8257,8 +9286,11 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="s">
-        <v>7</v>
+      <c r="G343" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H343" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344">
@@ -8280,8 +9312,11 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="s">
-        <v>7</v>
+      <c r="G344" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H344" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -8303,8 +9338,11 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="s">
-        <v>7</v>
+      <c r="G345" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H345" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -8326,8 +9364,11 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="s">
-        <v>7</v>
+      <c r="G346" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H346" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -8349,8 +9390,11 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="s">
-        <v>7</v>
+      <c r="G347" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H347" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348">
@@ -8372,8 +9416,11 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="s">
-        <v>7</v>
+      <c r="G348" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H348" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349">
@@ -8395,8 +9442,11 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="s">
-        <v>7</v>
+      <c r="G349" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H349" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -8418,8 +9468,11 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="s">
-        <v>7</v>
+      <c r="G350" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H350" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351">
@@ -8441,8 +9494,11 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="s">
-        <v>7</v>
+      <c r="G351" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H351" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8464,8 +9520,11 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="s">
-        <v>7</v>
+      <c r="G352" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H352" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -8487,8 +9546,11 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="s">
-        <v>7</v>
+      <c r="G353" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H353" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354">
@@ -8510,8 +9572,11 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="s">
-        <v>7</v>
+      <c r="G354" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H354" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8533,8 +9598,11 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="s">
-        <v>7</v>
+      <c r="G355" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H355" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -8556,8 +9624,11 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="s">
-        <v>7</v>
+      <c r="G356" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H356" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8579,8 +9650,11 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="s">
-        <v>7</v>
+      <c r="G357" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H357" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -8602,8 +9676,11 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="s">
-        <v>7</v>
+      <c r="G358" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H358" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359">
@@ -8625,8 +9702,11 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="s">
-        <v>7</v>
+      <c r="G359" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H359" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8648,8 +9728,11 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="s">
-        <v>7</v>
+      <c r="G360" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H360" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361">
@@ -8671,8 +9754,11 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="s">
-        <v>7</v>
+      <c r="G361" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H361" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362">
@@ -8694,8 +9780,11 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="s">
-        <v>7</v>
+      <c r="G362" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H362" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -8717,8 +9806,11 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="s">
-        <v>7</v>
+      <c r="G363" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H363" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8740,8 +9832,11 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="s">
-        <v>7</v>
+      <c r="G364" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H364" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8763,8 +9858,11 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="s">
-        <v>7</v>
+      <c r="G365" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H365" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8786,8 +9884,11 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="s">
-        <v>7</v>
+      <c r="G366" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H366" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8809,8 +9910,11 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="s">
-        <v>7</v>
+      <c r="G367" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H367" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8832,8 +9936,11 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="s">
-        <v>7</v>
+      <c r="G368" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H368" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -8855,8 +9962,11 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="s">
-        <v>7</v>
+      <c r="G369" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H369" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8878,8 +9988,11 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="s">
-        <v>7</v>
+      <c r="G370" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H370" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8901,8 +10014,11 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="s">
-        <v>7</v>
+      <c r="G371" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H371" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8924,8 +10040,11 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="s">
-        <v>7</v>
+      <c r="G372" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H372" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -8947,8 +10066,11 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="s">
-        <v>7</v>
+      <c r="G373" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H373" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8970,8 +10092,11 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="s">
-        <v>7</v>
+      <c r="G374" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H374" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8993,8 +10118,11 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="s">
-        <v>7</v>
+      <c r="G375" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H375" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -9016,8 +10144,11 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="s">
-        <v>7</v>
+      <c r="G376" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H376" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -9039,8 +10170,11 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="s">
-        <v>7</v>
+      <c r="G377" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H377" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -9062,8 +10196,11 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="s">
-        <v>7</v>
+      <c r="G378" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H378" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -9085,8 +10222,11 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="s">
-        <v>7</v>
+      <c r="G379" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H379" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -9108,8 +10248,11 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="s">
-        <v>7</v>
+      <c r="G380" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H380" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -9131,8 +10274,11 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="s">
-        <v>7</v>
+      <c r="G381" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H381" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -9154,8 +10300,11 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="s">
-        <v>7</v>
+      <c r="G382" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H382" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -9177,8 +10326,11 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="s">
-        <v>7</v>
+      <c r="G383" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H383" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -9200,8 +10352,11 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="s">
-        <v>7</v>
+      <c r="G384" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H384" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -9223,8 +10378,11 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="s">
-        <v>7</v>
+      <c r="G385" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H385" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -9246,8 +10404,11 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="s">
-        <v>7</v>
+      <c r="G386" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H386" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -9269,8 +10430,11 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="s">
-        <v>7</v>
+      <c r="G387" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H387" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -9292,8 +10456,11 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="s">
-        <v>7</v>
+      <c r="G388" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H388" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -9315,8 +10482,11 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="s">
-        <v>7</v>
+      <c r="G389" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H389" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -9338,8 +10508,11 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="s">
-        <v>7</v>
+      <c r="G390" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H390" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -9361,8 +10534,11 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="s">
-        <v>7</v>
+      <c r="G391" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H391" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -9384,8 +10560,11 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="s">
-        <v>7</v>
+      <c r="G392" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H392" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -9407,8 +10586,11 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="s">
-        <v>7</v>
+      <c r="G393" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H393" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -9430,8 +10612,11 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="s">
-        <v>7</v>
+      <c r="G394" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H394" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -9453,8 +10638,11 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="s">
-        <v>7</v>
+      <c r="G395" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H395" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -9476,8 +10664,11 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="s">
-        <v>7</v>
+      <c r="G396" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H396" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -9499,8 +10690,11 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="s">
-        <v>7</v>
+      <c r="G397" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H397" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -9522,8 +10716,11 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="s">
-        <v>7</v>
+      <c r="G398" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H398" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -9545,8 +10742,11 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="s">
-        <v>7</v>
+      <c r="G399" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H399" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -9568,8 +10768,11 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="s">
-        <v>7</v>
+      <c r="G400" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H400" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -9591,8 +10794,11 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="s">
-        <v>7</v>
+      <c r="G401" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H401" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -9614,8 +10820,11 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="s">
-        <v>7</v>
+      <c r="G402" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H402" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9637,8 +10846,11 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="s">
-        <v>7</v>
+      <c r="G403" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H403" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9660,8 +10872,11 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="s">
-        <v>7</v>
+      <c r="G404" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H404" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -9683,8 +10898,11 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="s">
-        <v>7</v>
+      <c r="G405" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H405" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9706,8 +10924,11 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="s">
-        <v>7</v>
+      <c r="G406" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H406" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -9729,8 +10950,11 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="s">
-        <v>7</v>
+      <c r="G407" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H407" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9752,8 +10976,11 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="s">
-        <v>7</v>
+      <c r="G408" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H408" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -9775,8 +11002,11 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="s">
-        <v>7</v>
+      <c r="G409" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H409" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9798,8 +11028,11 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="s">
-        <v>7</v>
+      <c r="G410" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H410" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9821,8 +11054,11 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="s">
-        <v>7</v>
+      <c r="G411" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H411" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9844,8 +11080,11 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="s">
-        <v>7</v>
+      <c r="G412" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H412" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9867,8 +11106,11 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="s">
-        <v>7</v>
+      <c r="G413" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H413" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -9890,8 +11132,11 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="s">
-        <v>7</v>
+      <c r="G414" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H414" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9913,8 +11158,11 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="s">
-        <v>7</v>
+      <c r="G415" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H415" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9936,8 +11184,11 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="s">
-        <v>7</v>
+      <c r="G416" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H416" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -9959,8 +11210,11 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="s">
-        <v>7</v>
+      <c r="G417" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H417" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -9982,8 +11236,11 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="s">
-        <v>7</v>
+      <c r="G418" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H418" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -10005,8 +11262,11 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="s">
-        <v>7</v>
+      <c r="G419" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H419" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -10028,8 +11288,11 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="s">
-        <v>7</v>
+      <c r="G420" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H420" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -10051,8 +11314,11 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="s">
-        <v>7</v>
+      <c r="G421" t="n">
+        <v>0.018673000857234</v>
+      </c>
+      <c r="H421" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -10074,8 +11340,11 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="s">
-        <v>7</v>
+      <c r="G422" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H422" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -10097,8 +11366,11 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="s">
-        <v>7</v>
+      <c r="G423" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H423" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -10120,8 +11392,11 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="s">
-        <v>7</v>
+      <c r="G424" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H424" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -10143,8 +11418,11 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="s">
-        <v>7</v>
+      <c r="G425" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H425" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -10166,8 +11444,11 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="s">
-        <v>7</v>
+      <c r="G426" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H426" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -10189,8 +11470,11 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="s">
-        <v>7</v>
+      <c r="G427" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H427" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -10212,8 +11496,11 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="s">
-        <v>7</v>
+      <c r="G428" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H428" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -10235,8 +11522,11 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="s">
-        <v>7</v>
+      <c r="G429" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H429" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -10258,8 +11548,11 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="s">
-        <v>7</v>
+      <c r="G430" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H430" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -10281,8 +11574,11 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="s">
-        <v>7</v>
+      <c r="G431" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H431" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -10304,8 +11600,11 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="s">
-        <v>7</v>
+      <c r="G432" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H432" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -10327,8 +11626,11 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="s">
-        <v>7</v>
+      <c r="G433" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H433" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -10350,8 +11652,11 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="s">
-        <v>7</v>
+      <c r="G434" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H434" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -10373,8 +11678,11 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="s">
-        <v>7</v>
+      <c r="G435" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H435" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -10396,8 +11704,11 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="s">
-        <v>7</v>
+      <c r="G436" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H436" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -10419,8 +11730,11 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="s">
-        <v>7</v>
+      <c r="G437" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H437" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -10442,8 +11756,11 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="s">
-        <v>7</v>
+      <c r="G438" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H438" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -10465,8 +11782,11 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="s">
-        <v>7</v>
+      <c r="G439" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H439" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -10488,8 +11808,11 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="s">
-        <v>7</v>
+      <c r="G440" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H440" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -10511,8 +11834,11 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="s">
-        <v>7</v>
+      <c r="G441" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H441" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -10534,8 +11860,11 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="s">
-        <v>7</v>
+      <c r="G442" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H442" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -10557,8 +11886,11 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="s">
-        <v>7</v>
+      <c r="G443" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H443" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -10580,8 +11912,11 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="s">
-        <v>7</v>
+      <c r="G444" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H444" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -10603,8 +11938,11 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="s">
-        <v>7</v>
+      <c r="G445" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H445" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -10626,8 +11964,11 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="s">
-        <v>7</v>
+      <c r="G446" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H446" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -10649,8 +11990,11 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="s">
-        <v>7</v>
+      <c r="G447" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H447" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -10672,8 +12016,11 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="s">
-        <v>7</v>
+      <c r="G448" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H448" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -10695,8 +12042,11 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="s">
-        <v>7</v>
+      <c r="G449" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H449" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -10718,8 +12068,11 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="s">
-        <v>7</v>
+      <c r="G450" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H450" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -10741,8 +12094,11 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="s">
-        <v>7</v>
+      <c r="G451" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H451" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10764,8 +12120,11 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="s">
-        <v>7</v>
+      <c r="G452" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H452" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10787,8 +12146,11 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="s">
-        <v>7</v>
+      <c r="G453" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H453" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -10810,8 +12172,11 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="s">
-        <v>7</v>
+      <c r="G454" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H454" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10833,8 +12198,11 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="s">
-        <v>7</v>
+      <c r="G455" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H455" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10856,8 +12224,11 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="s">
-        <v>7</v>
+      <c r="G456" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H456" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10879,8 +12250,11 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="s">
-        <v>7</v>
+      <c r="G457" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H457" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -10902,8 +12276,11 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="s">
-        <v>7</v>
+      <c r="G458" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H458" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -10925,8 +12302,11 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="s">
-        <v>7</v>
+      <c r="G459" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H459" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -10948,8 +12328,11 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="s">
-        <v>7</v>
+      <c r="G460" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H460" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -10971,8 +12354,11 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="s">
-        <v>7</v>
+      <c r="G461" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H461" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10994,8 +12380,11 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="s">
-        <v>7</v>
+      <c r="G462" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H462" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -11017,8 +12406,11 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="s">
-        <v>7</v>
+      <c r="G463" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H463" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -11040,8 +12432,11 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="s">
-        <v>7</v>
+      <c r="G464" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H464" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -11063,8 +12458,11 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="s">
-        <v>7</v>
+      <c r="G465" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H465" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -11086,8 +12484,11 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="s">
-        <v>7</v>
+      <c r="G466" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H466" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -11109,8 +12510,11 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="s">
-        <v>7</v>
+      <c r="G467" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H467" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -11132,8 +12536,11 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="s">
-        <v>7</v>
+      <c r="G468" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H468" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -11155,8 +12562,11 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="s">
-        <v>7</v>
+      <c r="G469" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -11178,8 +12588,11 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="s">
-        <v>7</v>
+      <c r="G470" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H470" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -11201,8 +12614,11 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="s">
-        <v>7</v>
+      <c r="G471" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H471" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -11224,8 +12640,11 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="s">
-        <v>7</v>
+      <c r="G472" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H472" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -11247,8 +12666,11 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="s">
-        <v>7</v>
+      <c r="G473" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H473" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -11270,8 +12692,11 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="s">
-        <v>7</v>
+      <c r="G474" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H474" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -11293,8 +12718,11 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="s">
-        <v>7</v>
+      <c r="G475" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H475" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -11316,8 +12744,11 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="s">
-        <v>7</v>
+      <c r="G476" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H476" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -11339,8 +12770,11 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="s">
-        <v>7</v>
+      <c r="G477" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H477" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -11362,8 +12796,11 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="s">
-        <v>7</v>
+      <c r="G478" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H478" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -11385,8 +12822,11 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="s">
-        <v>7</v>
+      <c r="G479" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H479" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -11408,8 +12848,11 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="s">
-        <v>7</v>
+      <c r="G480" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H480" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -11431,8 +12874,11 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="s">
-        <v>7</v>
+      <c r="G481" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H481" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -11454,8 +12900,11 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="s">
-        <v>7</v>
+      <c r="G482" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H482" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -11477,8 +12926,11 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="s">
-        <v>7</v>
+      <c r="G483" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H483" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -11500,8 +12952,11 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="s">
-        <v>7</v>
+      <c r="G484" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H484" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -11523,8 +12978,11 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="s">
-        <v>7</v>
+      <c r="G485" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H485" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -11546,8 +13004,11 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="s">
-        <v>7</v>
+      <c r="G486" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H486" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -11569,8 +13030,11 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="s">
-        <v>7</v>
+      <c r="G487" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H487" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="488">
@@ -11592,8 +13056,11 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="s">
-        <v>7</v>
+      <c r="G488" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H488" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -11615,8 +13082,11 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="s">
-        <v>7</v>
+      <c r="G489" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H489" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -11638,8 +13108,11 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="s">
-        <v>7</v>
+      <c r="G490" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H490" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -11661,8 +13134,11 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="s">
-        <v>7</v>
+      <c r="G491" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H491" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -11684,8 +13160,11 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="s">
-        <v>7</v>
+      <c r="G492" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H492" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -11707,8 +13186,11 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="s">
-        <v>7</v>
+      <c r="G493" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H493" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -11730,8 +13212,11 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="s">
-        <v>7</v>
+      <c r="G494" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H494" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -11753,8 +13238,11 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="s">
-        <v>7</v>
+      <c r="G495" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H495" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="496">
@@ -11776,8 +13264,11 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="s">
-        <v>7</v>
+      <c r="G496" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H496" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -11799,8 +13290,11 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="s">
-        <v>7</v>
+      <c r="G497" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H497" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="498">
@@ -11822,8 +13316,11 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="s">
-        <v>7</v>
+      <c r="G498" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H498" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="499">
@@ -11845,8 +13342,11 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="s">
-        <v>7</v>
+      <c r="G499" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H499" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="500">
@@ -11868,8 +13368,11 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="s">
-        <v>7</v>
+      <c r="G500" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H500" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="501">
@@ -11891,8 +13394,11 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="s">
-        <v>7</v>
+      <c r="G501" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H501" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="502">
@@ -11914,8 +13420,11 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="s">
-        <v>7</v>
+      <c r="G502" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H502" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="503">
@@ -11937,8 +13446,11 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="s">
-        <v>7</v>
+      <c r="G503" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H503" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="504">
@@ -11960,8 +13472,11 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="s">
-        <v>7</v>
+      <c r="G504" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H504" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11983,8 +13498,11 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="s">
-        <v>7</v>
+      <c r="G505" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H505" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -12006,8 +13524,11 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="s">
-        <v>7</v>
+      <c r="G506" t="n">
+        <v>0.0154079999774694</v>
+      </c>
+      <c r="H506" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="507">
@@ -12029,8 +13550,11 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="s">
-        <v>7</v>
+      <c r="G507" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H507" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="508">
@@ -12052,8 +13576,11 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="s">
-        <v>7</v>
+      <c r="G508" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H508" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -12075,8 +13602,11 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="s">
-        <v>7</v>
+      <c r="G509" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H509" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -12098,8 +13628,11 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="s">
-        <v>7</v>
+      <c r="G510" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H510" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="511">
@@ -12121,8 +13654,11 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="s">
-        <v>7</v>
+      <c r="G511" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H511" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="512">
@@ -12144,8 +13680,11 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="s">
-        <v>7</v>
+      <c r="G512" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H512" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -12167,8 +13706,11 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="s">
-        <v>7</v>
+      <c r="G513" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H513" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -12190,8 +13732,11 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="s">
-        <v>7</v>
+      <c r="G514" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H514" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="515">
@@ -12213,8 +13758,11 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="s">
-        <v>7</v>
+      <c r="G515" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H515" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="516">
@@ -12236,8 +13784,11 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="s">
-        <v>7</v>
+      <c r="G516" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H516" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="517">
@@ -12259,8 +13810,11 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="s">
-        <v>7</v>
+      <c r="G517" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H517" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="518">
@@ -12282,8 +13836,11 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="s">
-        <v>7</v>
+      <c r="G518" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H518" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="519">
@@ -12305,8 +13862,11 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="s">
-        <v>7</v>
+      <c r="G519" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H519" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -12328,8 +13888,11 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="s">
-        <v>7</v>
+      <c r="G520" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H520" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="521">
@@ -12351,8 +13914,11 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="s">
-        <v>7</v>
+      <c r="G521" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H521" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="522">
@@ -12374,8 +13940,11 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="s">
-        <v>7</v>
+      <c r="G522" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H522" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="523">
@@ -12397,8 +13966,11 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="s">
-        <v>7</v>
+      <c r="G523" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H523" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="524">
@@ -12420,8 +13992,11 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="s">
-        <v>7</v>
+      <c r="G524" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H524" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="525">
@@ -12443,8 +14018,11 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="s">
-        <v>7</v>
+      <c r="G525" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H525" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -12466,8 +14044,11 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="s">
-        <v>7</v>
+      <c r="G526" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H526" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="527">
@@ -12489,8 +14070,11 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="s">
-        <v>7</v>
+      <c r="G527" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H527" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="528">
@@ -12512,8 +14096,11 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="s">
-        <v>7</v>
+      <c r="G528" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H528" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="529">
@@ -12535,8 +14122,11 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="s">
-        <v>7</v>
+      <c r="G529" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H529" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="530">
@@ -12558,8 +14148,11 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="s">
-        <v>7</v>
+      <c r="G530" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H530" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -12581,8 +14174,11 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="s">
-        <v>7</v>
+      <c r="G531" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H531" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -12604,8 +14200,11 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="s">
-        <v>7</v>
+      <c r="G532" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H532" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="533">
@@ -12627,8 +14226,11 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="s">
-        <v>7</v>
+      <c r="G533" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H533" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="534">
@@ -12650,8 +14252,11 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="s">
-        <v>7</v>
+      <c r="G534" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H534" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="535">
@@ -12673,8 +14278,11 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="s">
-        <v>7</v>
+      <c r="G535" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H535" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="536">
@@ -12696,8 +14304,11 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="s">
-        <v>7</v>
+      <c r="G536" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H536" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -12719,8 +14330,11 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="s">
-        <v>7</v>
+      <c r="G537" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H537" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="538">
@@ -12742,8 +14356,11 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="s">
-        <v>7</v>
+      <c r="G538" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H538" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="539">
@@ -12765,8 +14382,11 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="s">
-        <v>7</v>
+      <c r="G539" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H539" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="540">
@@ -12788,8 +14408,11 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="s">
-        <v>7</v>
+      <c r="G540" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H540" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="541">
@@ -12811,8 +14434,11 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="s">
-        <v>7</v>
+      <c r="G541" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H541" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="542">
@@ -12834,8 +14460,11 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="s">
-        <v>7</v>
+      <c r="G542" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H542" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="543">
@@ -12857,8 +14486,11 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="s">
-        <v>7</v>
+      <c r="G543" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H543" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="544">
@@ -12880,8 +14512,11 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="s">
-        <v>7</v>
+      <c r="G544" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H544" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="545">
@@ -12903,8 +14538,11 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="s">
-        <v>7</v>
+      <c r="G545" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H545" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="546">
@@ -12926,8 +14564,11 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="s">
-        <v>7</v>
+      <c r="G546" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H546" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="547">
@@ -12949,8 +14590,11 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="s">
-        <v>7</v>
+      <c r="G547" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H547" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="548">
@@ -12972,8 +14616,11 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="s">
-        <v>7</v>
+      <c r="G548" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H548" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -12995,8 +14642,11 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="s">
-        <v>7</v>
+      <c r="G549" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H549" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="550">
@@ -13018,8 +14668,11 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="s">
-        <v>7</v>
+      <c r="G550" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H550" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="551">
@@ -13041,8 +14694,11 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="s">
-        <v>7</v>
+      <c r="G551" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H551" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="552">
@@ -13064,8 +14720,11 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="s">
-        <v>7</v>
+      <c r="G552" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H552" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="553">
@@ -13087,8 +14746,11 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="s">
-        <v>7</v>
+      <c r="G553" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H553" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="554">
@@ -13110,8 +14772,11 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="s">
-        <v>7</v>
+      <c r="G554" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H554" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -13133,8 +14798,11 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="s">
-        <v>7</v>
+      <c r="G555" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H555" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -13156,8 +14824,11 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="s">
-        <v>7</v>
+      <c r="G556" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H556" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="557">
@@ -13179,8 +14850,11 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="s">
-        <v>7</v>
+      <c r="G557" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H557" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="558">
@@ -13202,8 +14876,11 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="s">
-        <v>7</v>
+      <c r="G558" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H558" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="559">
@@ -13225,8 +14902,11 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="s">
-        <v>7</v>
+      <c r="G559" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H559" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -13248,8 +14928,11 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="s">
-        <v>7</v>
+      <c r="G560" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H560" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="561">
@@ -13271,8 +14954,11 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="s">
-        <v>7</v>
+      <c r="G561" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H561" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="562">
@@ -13294,8 +14980,11 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="s">
-        <v>7</v>
+      <c r="G562" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H562" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="563">
@@ -13317,8 +15006,11 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="s">
-        <v>7</v>
+      <c r="G563" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H563" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="564">
@@ -13340,8 +15032,11 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="s">
-        <v>7</v>
+      <c r="G564" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H564" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="565">
@@ -13363,8 +15058,11 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="s">
-        <v>7</v>
+      <c r="G565" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H565" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -13386,8 +15084,11 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="s">
-        <v>7</v>
+      <c r="G566" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H566" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="567">
@@ -13409,8 +15110,11 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="s">
-        <v>7</v>
+      <c r="G567" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H567" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="568">
@@ -13432,8 +15136,11 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="s">
-        <v>7</v>
+      <c r="G568" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H568" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="569">
@@ -13455,8 +15162,11 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="s">
-        <v>7</v>
+      <c r="G569" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H569" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="570">
@@ -13478,8 +15188,11 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="s">
-        <v>7</v>
+      <c r="G570" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H570" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="571">
@@ -13501,8 +15214,11 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="s">
-        <v>7</v>
+      <c r="G571" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H571" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="572">
@@ -13524,8 +15240,11 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="s">
-        <v>7</v>
+      <c r="G572" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H572" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="573">
@@ -13547,8 +15266,11 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="s">
-        <v>7</v>
+      <c r="G573" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H573" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="574">
@@ -13570,8 +15292,11 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="s">
-        <v>7</v>
+      <c r="G574" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H574" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="575">
@@ -13593,8 +15318,11 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="s">
-        <v>7</v>
+      <c r="G575" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H575" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="576">
@@ -13616,8 +15344,11 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="s">
-        <v>7</v>
+      <c r="G576" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H576" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="577">
@@ -13639,8 +15370,11 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="s">
-        <v>7</v>
+      <c r="G577" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H577" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="578">
@@ -13662,8 +15396,11 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="s">
-        <v>7</v>
+      <c r="G578" t="n">
+        <v>0.0175000000745058</v>
+      </c>
+      <c r="H578" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="579">
@@ -13685,8 +15422,11 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="s">
-        <v>7</v>
+      <c r="G579" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H579" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="580">
@@ -13708,8 +15448,11 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="s">
-        <v>7</v>
+      <c r="G580" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H580" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="581">
@@ -13731,8 +15474,11 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="s">
-        <v>7</v>
+      <c r="G581" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H581" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="582">
@@ -13754,8 +15500,11 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="s">
-        <v>7</v>
+      <c r="G582" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H582" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="583">
@@ -13777,8 +15526,11 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="s">
-        <v>7</v>
+      <c r="G583" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H583" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="584">
@@ -13800,8 +15552,11 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="s">
-        <v>7</v>
+      <c r="G584" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H584" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="585">
@@ -13823,8 +15578,11 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="s">
-        <v>7</v>
+      <c r="G585" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H585" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="586">
@@ -13846,8 +15604,11 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="s">
-        <v>7</v>
+      <c r="G586" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H586" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="587">
@@ -13869,8 +15630,11 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="s">
-        <v>7</v>
+      <c r="G587" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H587" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="588">
@@ -13892,8 +15656,11 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="s">
-        <v>7</v>
+      <c r="G588" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H588" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="589">
@@ -13915,8 +15682,11 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="s">
-        <v>7</v>
+      <c r="G589" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H589" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="590">
@@ -13938,8 +15708,11 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="s">
-        <v>7</v>
+      <c r="G590" t="n">
+        <v>0.0171000007539988</v>
+      </c>
+      <c r="H590" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -13961,8 +15734,11 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="s">
-        <v>7</v>
+      <c r="G591" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H591" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="592">
@@ -13984,8 +15760,11 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="s">
-        <v>7</v>
+      <c r="G592" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H592" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="593">
@@ -14007,8 +15786,11 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="s">
-        <v>7</v>
+      <c r="G593" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H593" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="594">
@@ -14030,8 +15812,11 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="s">
-        <v>7</v>
+      <c r="G594" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="H594" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="595">
@@ -14053,8 +15838,11 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="s">
-        <v>7</v>
+      <c r="G595" t="n">
+        <v>0.0203000009059906</v>
+      </c>
+      <c r="H595" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="596">
@@ -14076,8 +15864,11 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="s">
-        <v>7</v>
+      <c r="G596" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H596" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -14099,8 +15890,11 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="s">
-        <v>7</v>
+      <c r="G597" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H597" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="598">
@@ -14122,8 +15916,11 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="s">
-        <v>7</v>
+      <c r="G598" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H598" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="599">
@@ -14145,8 +15942,11 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="s">
-        <v>7</v>
+      <c r="G599" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H599" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="600">
@@ -14168,8 +15968,11 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="s">
-        <v>7</v>
+      <c r="G600" t="n">
+        <v>0.0183000005781651</v>
+      </c>
+      <c r="H600" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="601">
@@ -14191,8 +15994,11 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="s">
-        <v>7</v>
+      <c r="G601" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H601" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="602">
@@ -14214,8 +16020,11 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="s">
-        <v>7</v>
+      <c r="G602" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H602" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="603">
@@ -14237,8 +16046,11 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="s">
-        <v>7</v>
+      <c r="G603" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H603" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="604">
@@ -14260,8 +16072,11 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="s">
-        <v>7</v>
+      <c r="G604" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="H604" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="605">
@@ -14283,8 +16098,11 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="s">
-        <v>7</v>
+      <c r="G605" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H605" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="606">
@@ -14306,8 +16124,11 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="s">
-        <v>7</v>
+      <c r="G606" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H606" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="607">
@@ -14329,8 +16150,11 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="s">
-        <v>7</v>
+      <c r="G607" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H607" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="608">
@@ -14352,8 +16176,11 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="s">
-        <v>7</v>
+      <c r="G608" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H608" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="609">
@@ -14375,8 +16202,11 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="s">
-        <v>7</v>
+      <c r="G609" t="n">
+        <v>0.0181000009179115</v>
+      </c>
+      <c r="H609" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="610">
@@ -14398,8 +16228,11 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="s">
-        <v>7</v>
+      <c r="G610" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H610" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="611">
@@ -14421,8 +16254,11 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="s">
-        <v>7</v>
+      <c r="G611" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H611" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="612">
@@ -14444,8 +16280,11 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="s">
-        <v>7</v>
+      <c r="G612" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H612" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="613">
@@ -14467,8 +16306,11 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="s">
-        <v>7</v>
+      <c r="G613" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H613" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="614">
@@ -14490,8 +16332,11 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="s">
-        <v>7</v>
+      <c r="G614" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H614" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="615">
@@ -14513,8 +16358,11 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="s">
-        <v>7</v>
+      <c r="G615" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H615" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="616">
@@ -14536,8 +16384,11 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="s">
-        <v>7</v>
+      <c r="G616" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H616" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="617">
@@ -14559,8 +16410,11 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="s">
-        <v>7</v>
+      <c r="G617" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H617" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="618">
@@ -14582,8 +16436,11 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="s">
-        <v>7</v>
+      <c r="G618" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H618" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="619">
@@ -14605,8 +16462,11 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="s">
-        <v>7</v>
+      <c r="G619" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H619" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="620">
@@ -14628,8 +16488,11 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="s">
-        <v>7</v>
+      <c r="G620" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H620" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="621">
@@ -14651,8 +16514,11 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="s">
-        <v>7</v>
+      <c r="G621" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H621" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="622">
@@ -14674,8 +16540,11 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="s">
-        <v>7</v>
+      <c r="G622" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H622" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="623">
@@ -14697,8 +16566,11 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="s">
-        <v>7</v>
+      <c r="G623" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H623" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="624">
@@ -14720,8 +16592,11 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="s">
-        <v>7</v>
+      <c r="G624" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H624" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="625">
@@ -14743,8 +16618,11 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="s">
-        <v>7</v>
+      <c r="G625" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H625" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="626">
@@ -14766,8 +16644,11 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="s">
-        <v>7</v>
+      <c r="G626" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H626" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="627">
@@ -14789,8 +16670,11 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="s">
-        <v>7</v>
+      <c r="G627" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H627" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="628">
@@ -14812,8 +16696,11 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="s">
-        <v>7</v>
+      <c r="G628" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H628" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="629">
@@ -14835,8 +16722,11 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="s">
-        <v>7</v>
+      <c r="G629" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H629" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="630">
@@ -14858,8 +16748,11 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="s">
-        <v>7</v>
+      <c r="G630" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H630" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="631">
@@ -14881,8 +16774,11 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="s">
-        <v>7</v>
+      <c r="G631" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H631" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="632">
@@ -14904,8 +16800,11 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="s">
-        <v>7</v>
+      <c r="G632" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H632" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="633">
@@ -14927,8 +16826,11 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="s">
-        <v>7</v>
+      <c r="G633" t="n">
+        <v>0.0172000005841255</v>
+      </c>
+      <c r="H633" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="634">
@@ -14950,8 +16852,11 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="s">
-        <v>7</v>
+      <c r="G634" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H634" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="635">
@@ -14973,8 +16878,11 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="s">
-        <v>7</v>
+      <c r="G635" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H635" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="636">
@@ -14996,8 +16904,11 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="s">
-        <v>7</v>
+      <c r="G636" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H636" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="637">
@@ -15019,8 +16930,11 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="s">
-        <v>7</v>
+      <c r="G637" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H637" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="638">
@@ -15042,8 +16956,11 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="s">
-        <v>7</v>
+      <c r="G638" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H638" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="639">
@@ -15065,8 +16982,11 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="s">
-        <v>7</v>
+      <c r="G639" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H639" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="640">
@@ -15088,8 +17008,11 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="s">
-        <v>7</v>
+      <c r="G640" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H640" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="641">
@@ -15111,8 +17034,11 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="s">
-        <v>7</v>
+      <c r="G641" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H641" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="642">
@@ -15134,8 +17060,11 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="s">
-        <v>7</v>
+      <c r="G642" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H642" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="643">
@@ -15157,8 +17086,11 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="s">
-        <v>7</v>
+      <c r="G643" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H643" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="644">
@@ -15180,8 +17112,11 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="s">
-        <v>7</v>
+      <c r="G644" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H644" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="645">
@@ -15203,8 +17138,11 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="s">
-        <v>7</v>
+      <c r="G645" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H645" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="646">
@@ -15226,8 +17164,11 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="s">
-        <v>7</v>
+      <c r="G646" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H646" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="647">
@@ -15249,8 +17190,11 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="s">
-        <v>7</v>
+      <c r="G647" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H647" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="648">
@@ -15272,8 +17216,11 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="s">
-        <v>7</v>
+      <c r="G648" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H648" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="649">
@@ -15295,8 +17242,11 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="s">
-        <v>7</v>
+      <c r="G649" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H649" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="650">
@@ -15318,8 +17268,11 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="s">
-        <v>7</v>
+      <c r="G650" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H650" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="651">
@@ -15341,8 +17294,11 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="s">
-        <v>7</v>
+      <c r="G651" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H651" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="652">
@@ -15364,8 +17320,11 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="s">
-        <v>7</v>
+      <c r="G652" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H652" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="653">
@@ -15387,8 +17346,11 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="s">
-        <v>7</v>
+      <c r="G653" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H653" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="654">
@@ -15410,8 +17372,11 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="s">
-        <v>7</v>
+      <c r="G654" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H654" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="655">
@@ -15433,8 +17398,11 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="s">
-        <v>7</v>
+      <c r="G655" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H655" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="656">
@@ -15456,8 +17424,11 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="s">
-        <v>7</v>
+      <c r="G656" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H656" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="657">
@@ -15479,8 +17450,11 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="s">
-        <v>7</v>
+      <c r="G657" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H657" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="658">
@@ -15502,8 +17476,11 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="s">
-        <v>7</v>
+      <c r="G658" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H658" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="659">
@@ -15525,8 +17502,11 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="s">
-        <v>7</v>
+      <c r="G659" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H659" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="660">
@@ -15548,8 +17528,11 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="s">
-        <v>7</v>
+      <c r="G660" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H660" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="661">
@@ -15571,8 +17554,11 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="s">
-        <v>7</v>
+      <c r="G661" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H661" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="662">
@@ -15594,8 +17580,11 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="s">
-        <v>7</v>
+      <c r="G662" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H662" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="663">
@@ -15617,8 +17606,11 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="s">
-        <v>7</v>
+      <c r="G663" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H663" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="664">
@@ -15640,8 +17632,11 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="s">
-        <v>7</v>
+      <c r="G664" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H664" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="665">
@@ -15663,8 +17658,11 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="s">
-        <v>7</v>
+      <c r="G665" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H665" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="666">
@@ -15686,8 +17684,11 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="s">
-        <v>7</v>
+      <c r="G666" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H666" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="667">
@@ -15709,8 +17710,11 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="s">
-        <v>7</v>
+      <c r="G667" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H667" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="668">
@@ -15732,8 +17736,11 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="s">
-        <v>7</v>
+      <c r="G668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H668" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="669">
@@ -15755,8 +17762,11 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="s">
-        <v>7</v>
+      <c r="G669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H669" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="670">
@@ -15778,8 +17788,11 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="s">
-        <v>7</v>
+      <c r="G670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H670" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="671">
@@ -15801,8 +17814,11 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="s">
-        <v>7</v>
+      <c r="G671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H671" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="672">
@@ -15824,8 +17840,11 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="s">
-        <v>7</v>
+      <c r="G672" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="H672" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="673">
@@ -15847,8 +17866,11 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="s">
-        <v>7</v>
+      <c r="G673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H673" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="674">
@@ -15870,8 +17892,11 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="s">
-        <v>7</v>
+      <c r="G674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="H674" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="675">
@@ -15893,8 +17918,11 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="s">
-        <v>7</v>
+      <c r="G675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="H675" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="676">
@@ -15916,8 +17944,11 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="s">
-        <v>7</v>
+      <c r="G676" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="H676" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="677">
@@ -15939,8 +17970,11 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="s">
-        <v>7</v>
+      <c r="G677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H677" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="678">
@@ -15962,8 +17996,11 @@
       <c r="F678" t="n">
         <v>0.0221999995410442</v>
       </c>
-      <c r="G678" t="s">
-        <v>7</v>
+      <c r="G678" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="H678" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="679">
@@ -15985,8 +18022,11 @@
       <c r="F679" t="n">
         <v>0.0233999993652105</v>
       </c>
-      <c r="G679" t="s">
-        <v>7</v>
+      <c r="G679" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="H679" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="680">
@@ -16008,8 +18048,11 @@
       <c r="F680" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G680" t="s">
-        <v>7</v>
+      <c r="G680" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H680" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="681">
@@ -16028,9 +18071,40 @@
       <c r="E681" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="F681"/>
-      <c r="G681" t="s">
-        <v>7</v>
+      <c r="F681" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="H681" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B682" t="n">
+        <v>4444866</v>
+      </c>
+      <c r="C682" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="G682" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H682" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -397,9 +394,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -420,11 +414,8 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -446,11 +437,8 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +460,8 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +483,8 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -524,11 +506,8 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -550,11 +529,8 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -576,11 +552,8 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
+      <c r="G8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -602,11 +575,8 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -628,11 +598,8 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+      <c r="G10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -654,11 +621,8 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
+      <c r="G11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -680,11 +644,8 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -706,11 +667,8 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -732,11 +690,8 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H14" t="s">
-        <v>8</v>
+      <c r="G14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -758,11 +713,8 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -784,11 +736,8 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
+      <c r="G16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -810,11 +759,8 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+      <c r="G17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -836,11 +782,8 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -862,11 +805,8 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -888,11 +828,8 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+      <c r="G20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -914,11 +851,8 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H21" t="s">
-        <v>8</v>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -940,11 +874,8 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
+      <c r="G22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -966,11 +897,8 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
+      <c r="G23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -992,11 +920,8 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1018,11 +943,8 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
+      <c r="G25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1044,11 +966,8 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>8</v>
+      <c r="G26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1070,11 +989,8 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.019845999777317</v>
-      </c>
-      <c r="H27" t="s">
-        <v>8</v>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1096,11 +1012,8 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H28" t="s">
-        <v>8</v>
+      <c r="G28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1122,11 +1035,8 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>8</v>
+      <c r="G29" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1148,11 +1058,8 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.01923399977386</v>
-      </c>
-      <c r="H30" t="s">
-        <v>8</v>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1174,11 +1081,8 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+      <c r="G31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1200,11 +1104,8 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+      <c r="G32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1127,8 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1252,11 +1150,8 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="G34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1278,11 +1173,8 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1304,11 +1196,8 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H36" t="s">
-        <v>8</v>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1330,11 +1219,8 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H37" t="s">
-        <v>8</v>
+      <c r="G37" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1356,11 +1242,8 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H38" t="s">
-        <v>8</v>
+      <c r="G38" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1382,11 +1265,8 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H39" t="s">
-        <v>8</v>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1408,11 +1288,8 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
+      <c r="G40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1434,11 +1311,8 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
+      <c r="G41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1460,11 +1334,8 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1486,11 +1357,8 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H43" t="s">
-        <v>8</v>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1512,11 +1380,8 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H44" t="s">
-        <v>8</v>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1538,11 +1403,8 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H45" t="s">
-        <v>8</v>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1564,11 +1426,8 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H46" t="s">
-        <v>8</v>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1590,11 +1449,8 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H47" t="s">
-        <v>8</v>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1616,11 +1472,8 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H48" t="s">
-        <v>8</v>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1642,11 +1495,8 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H49" t="s">
-        <v>8</v>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1668,11 +1518,8 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H50" t="s">
-        <v>8</v>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1694,11 +1541,8 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H51" t="s">
-        <v>8</v>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1720,11 +1564,8 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H52" t="s">
-        <v>8</v>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1746,11 +1587,8 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H53" t="s">
-        <v>8</v>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,11 +1610,8 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H54" t="s">
-        <v>8</v>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1798,11 +1633,8 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H55" t="s">
-        <v>8</v>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1824,11 +1656,8 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H56" t="s">
-        <v>8</v>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1850,11 +1679,8 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H57" t="s">
-        <v>8</v>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1876,11 +1702,8 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H58" t="s">
-        <v>8</v>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1902,11 +1725,8 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H59" t="s">
-        <v>8</v>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1928,11 +1748,8 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H60" t="s">
-        <v>8</v>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1954,11 +1771,8 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1980,11 +1794,8 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H62" t="s">
-        <v>8</v>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2006,11 +1817,8 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H63" t="s">
-        <v>8</v>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2032,11 +1840,8 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H64" t="s">
-        <v>8</v>
+      <c r="G64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2058,11 +1863,8 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H65" t="s">
-        <v>8</v>
+      <c r="G65" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2084,11 +1886,8 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H66" t="s">
-        <v>8</v>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2110,11 +1909,8 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H67" t="s">
-        <v>8</v>
+      <c r="G67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2136,11 +1932,8 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H68" t="s">
-        <v>8</v>
+      <c r="G68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2162,11 +1955,8 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H69" t="s">
-        <v>8</v>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -2188,11 +1978,8 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H70" t="s">
-        <v>8</v>
+      <c r="G70" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2214,11 +2001,8 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H71" t="s">
-        <v>8</v>
+      <c r="G71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2240,11 +2024,8 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H72" t="s">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2266,11 +2047,8 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H73" t="s">
-        <v>8</v>
+      <c r="G73" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -2292,11 +2070,8 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="G74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2318,11 +2093,8 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H75" t="s">
-        <v>8</v>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2344,11 +2116,8 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="G76" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2370,11 +2139,8 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H77" t="s">
-        <v>8</v>
+      <c r="G77" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2396,11 +2162,8 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2422,11 +2185,8 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H79" t="s">
-        <v>8</v>
+      <c r="G79" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2448,11 +2208,8 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+      <c r="G80" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2474,11 +2231,8 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H81" t="s">
-        <v>8</v>
+      <c r="G81" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2500,11 +2254,8 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+      <c r="G82" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2526,11 +2277,8 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H83" t="s">
-        <v>8</v>
+      <c r="G83" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2552,11 +2300,8 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H84" t="s">
-        <v>8</v>
+      <c r="G84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2578,11 +2323,8 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H85" t="s">
-        <v>8</v>
+      <c r="G85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2604,11 +2346,8 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H86" t="s">
-        <v>8</v>
+      <c r="G86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -2630,11 +2369,8 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>8</v>
+      <c r="G87" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2656,11 +2392,8 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>8</v>
+      <c r="G88" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2682,11 +2415,8 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H89" t="s">
-        <v>8</v>
+      <c r="G89" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -2708,11 +2438,8 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="G90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2734,11 +2461,8 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H91" t="s">
-        <v>8</v>
+      <c r="G91" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2760,11 +2484,8 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="G92" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2786,11 +2507,8 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H93" t="s">
-        <v>8</v>
+      <c r="G93" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -2812,11 +2530,8 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H94" t="s">
-        <v>8</v>
+      <c r="G94" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2838,11 +2553,8 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="G95" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2864,11 +2576,8 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H96" t="s">
-        <v>8</v>
+      <c r="G96" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2890,11 +2599,8 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+      <c r="G97" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -2916,11 +2622,8 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H98" t="s">
-        <v>8</v>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2942,11 +2645,8 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="G99" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2668,8 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H100" t="s">
-        <v>8</v>
+      <c r="G100" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2994,11 +2691,8 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H101" t="s">
-        <v>8</v>
+      <c r="G101" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3020,11 +2714,8 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H102" t="s">
-        <v>8</v>
+      <c r="G102" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3046,11 +2737,8 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="G103" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3072,11 +2760,8 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H104" t="s">
-        <v>8</v>
+      <c r="G104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3098,11 +2783,8 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H105" t="s">
-        <v>8</v>
+      <c r="G105" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3124,11 +2806,8 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H106" t="s">
-        <v>8</v>
+      <c r="G106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3150,11 +2829,8 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H107" t="s">
-        <v>8</v>
+      <c r="G107" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3176,11 +2852,8 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+      <c r="G108" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3202,11 +2875,8 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H109" t="s">
-        <v>8</v>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3228,11 +2898,8 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H110" t="s">
-        <v>8</v>
+      <c r="G110" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -3254,11 +2921,8 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H111" t="s">
-        <v>8</v>
+      <c r="G111" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -3280,11 +2944,8 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H112" t="s">
-        <v>8</v>
+      <c r="G112" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3306,11 +2967,8 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+      <c r="G113" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3332,11 +2990,8 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H114" t="s">
-        <v>8</v>
+      <c r="G114" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3358,11 +3013,8 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H115" t="s">
-        <v>8</v>
+      <c r="G115" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3384,11 +3036,8 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+      <c r="G116" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3410,11 +3059,8 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H117" t="s">
-        <v>8</v>
+      <c r="G117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3436,11 +3082,8 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H118" t="s">
-        <v>8</v>
+      <c r="G118" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3462,11 +3105,8 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H119" t="s">
-        <v>8</v>
+      <c r="G119" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -3488,11 +3128,8 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H120" t="s">
-        <v>8</v>
+      <c r="G120" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -3514,11 +3151,8 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
+      <c r="G121" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -3540,11 +3174,8 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H122" t="s">
-        <v>8</v>
+      <c r="G122" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -3566,11 +3197,8 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H123" t="s">
-        <v>8</v>
+      <c r="G123" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3592,11 +3220,8 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H124" t="s">
-        <v>8</v>
+      <c r="G124" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -3618,11 +3243,8 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H125" t="s">
-        <v>8</v>
+      <c r="G125" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -3644,11 +3266,8 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H126" t="s">
-        <v>8</v>
+      <c r="G126" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -3670,11 +3289,8 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H127" t="s">
-        <v>8</v>
+      <c r="G127" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3696,11 +3312,8 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H128" t="s">
-        <v>8</v>
+      <c r="G128" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="129">
@@ -3722,11 +3335,8 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H129" t="s">
-        <v>8</v>
+      <c r="G129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -3748,11 +3358,8 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H130" t="s">
-        <v>8</v>
+      <c r="G130" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3774,11 +3381,8 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H131" t="s">
-        <v>8</v>
+      <c r="G131" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -3800,11 +3404,8 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H132" t="s">
-        <v>8</v>
+      <c r="G132" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -3826,11 +3427,8 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H133" t="s">
-        <v>8</v>
+      <c r="G133" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -3852,11 +3450,8 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H134" t="s">
-        <v>8</v>
+      <c r="G134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3878,11 +3473,8 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H135" t="s">
-        <v>8</v>
+      <c r="G135" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="136">
@@ -3904,11 +3496,8 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H136" t="s">
-        <v>8</v>
+      <c r="G136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -3930,11 +3519,8 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H137" t="s">
-        <v>8</v>
+      <c r="G137" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3956,11 +3542,8 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H138" t="s">
-        <v>8</v>
+      <c r="G138" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3982,11 +3565,8 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>8</v>
+      <c r="G139" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -4008,11 +3588,8 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H140" t="s">
-        <v>8</v>
+      <c r="G140" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -4034,11 +3611,8 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H141" t="s">
-        <v>8</v>
+      <c r="G141" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -4060,11 +3634,8 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H142" t="s">
-        <v>8</v>
+      <c r="G142" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="143">
@@ -4086,11 +3657,8 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H143" t="s">
-        <v>8</v>
+      <c r="G143" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4112,11 +3680,8 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H144" t="s">
-        <v>8</v>
+      <c r="G144" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -4138,11 +3703,8 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H145" t="s">
-        <v>8</v>
+      <c r="G145" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -4164,11 +3726,8 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H146" t="s">
-        <v>8</v>
+      <c r="G146" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -4190,11 +3749,8 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H147" t="s">
-        <v>8</v>
+      <c r="G147" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -4216,11 +3772,8 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H148" t="s">
-        <v>8</v>
+      <c r="G148" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -4242,11 +3795,8 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H149" t="s">
-        <v>8</v>
+      <c r="G149" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -4268,11 +3818,8 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H150" t="s">
-        <v>8</v>
+      <c r="G150" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -4294,11 +3841,8 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H151" t="s">
-        <v>8</v>
+      <c r="G151" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -4320,11 +3864,8 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H152" t="s">
-        <v>8</v>
+      <c r="G152" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -4346,11 +3887,8 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>8</v>
+      <c r="G153" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4372,11 +3910,8 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H154" t="s">
-        <v>8</v>
+      <c r="G154" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -4398,11 +3933,8 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H155" t="s">
-        <v>8</v>
+      <c r="G155" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -4424,11 +3956,8 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H156" t="s">
-        <v>8</v>
+      <c r="G156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -4450,11 +3979,8 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H157" t="s">
-        <v>8</v>
+      <c r="G157" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -4476,11 +4002,8 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H158" t="s">
-        <v>8</v>
+      <c r="G158" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -4502,11 +4025,8 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H159" t="s">
-        <v>8</v>
+      <c r="G159" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -4528,11 +4048,8 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H160" t="s">
-        <v>8</v>
+      <c r="G160" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -4554,11 +4071,8 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H161" t="s">
-        <v>8</v>
+      <c r="G161" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -4580,11 +4094,8 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H162" t="s">
-        <v>8</v>
+      <c r="G162" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -4606,11 +4117,8 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H163" t="s">
-        <v>8</v>
+      <c r="G163" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4632,11 +4140,8 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H164" t="s">
-        <v>8</v>
+      <c r="G164" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4658,11 +4163,8 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H165" t="s">
-        <v>8</v>
+      <c r="G165" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -4684,11 +4186,8 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H166" t="s">
-        <v>8</v>
+      <c r="G166" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -4710,11 +4209,8 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H167" t="s">
-        <v>8</v>
+      <c r="G167" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4736,11 +4232,8 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H168" t="s">
-        <v>8</v>
+      <c r="G168" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -4762,11 +4255,8 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H169" t="s">
-        <v>8</v>
+      <c r="G169" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4788,11 +4278,8 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H170" t="s">
-        <v>8</v>
+      <c r="G170" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4814,11 +4301,8 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H171" t="s">
-        <v>8</v>
+      <c r="G171" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4840,11 +4324,8 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H172" t="s">
-        <v>8</v>
+      <c r="G172" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -4866,11 +4347,8 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H173" t="s">
-        <v>8</v>
+      <c r="G173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4370,8 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H174" t="s">
-        <v>8</v>
+      <c r="G174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4918,11 +4393,8 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H175" t="s">
-        <v>8</v>
+      <c r="G175" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -4944,11 +4416,8 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H176" t="s">
-        <v>8</v>
+      <c r="G176" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -4970,11 +4439,8 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H177" t="s">
-        <v>8</v>
+      <c r="G177" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -4996,11 +4462,8 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H178" t="s">
-        <v>8</v>
+      <c r="G178" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -5022,11 +4485,8 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H179" t="s">
-        <v>8</v>
+      <c r="G179" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="180">
@@ -5048,11 +4508,8 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H180" t="s">
-        <v>8</v>
+      <c r="G180" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -5074,11 +4531,8 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H181" t="s">
-        <v>8</v>
+      <c r="G181" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182">
@@ -5100,11 +4554,8 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H182" t="s">
-        <v>8</v>
+      <c r="G182" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -5126,11 +4577,8 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H183" t="s">
-        <v>8</v>
+      <c r="G183" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -5152,11 +4600,8 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H184" t="s">
-        <v>8</v>
+      <c r="G184" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -5178,11 +4623,8 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H185" t="s">
-        <v>8</v>
+      <c r="G185" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5204,11 +4646,8 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H186" t="s">
-        <v>8</v>
+      <c r="G186" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -5230,11 +4669,8 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H187" t="s">
-        <v>8</v>
+      <c r="G187" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5256,11 +4692,8 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H188" t="s">
-        <v>8</v>
+      <c r="G188" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5282,11 +4715,8 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H189" t="s">
-        <v>8</v>
+      <c r="G189" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -5308,11 +4738,8 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H190" t="s">
-        <v>8</v>
+      <c r="G190" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -5334,11 +4761,8 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H191" t="s">
-        <v>8</v>
+      <c r="G191" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -5360,11 +4784,8 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H192" t="s">
-        <v>8</v>
+      <c r="G192" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -5386,11 +4807,8 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H193" t="s">
-        <v>8</v>
+      <c r="G193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -5412,11 +4830,8 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H194" t="s">
-        <v>8</v>
+      <c r="G194" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -5438,11 +4853,8 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H195" t="s">
-        <v>8</v>
+      <c r="G195" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -5464,11 +4876,8 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H196" t="s">
-        <v>8</v>
+      <c r="G196" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -5490,11 +4899,8 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H197" t="s">
-        <v>8</v>
+      <c r="G197" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -5516,11 +4922,8 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H198" t="s">
-        <v>8</v>
+      <c r="G198" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -5542,11 +4945,8 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H199" t="s">
-        <v>8</v>
+      <c r="G199" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -5568,11 +4968,8 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H200" t="s">
-        <v>8</v>
+      <c r="G200" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -5594,11 +4991,8 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H201" t="s">
-        <v>8</v>
+      <c r="G201" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5620,11 +5014,8 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H202" t="s">
-        <v>8</v>
+      <c r="G202" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -5646,11 +5037,8 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H203" t="s">
-        <v>8</v>
+      <c r="G203" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -5672,11 +5060,8 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H204" t="s">
-        <v>8</v>
+      <c r="G204" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -5698,11 +5083,8 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H205" t="s">
-        <v>8</v>
+      <c r="G205" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -5724,11 +5106,8 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H206" t="s">
-        <v>8</v>
+      <c r="G206" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -5750,11 +5129,8 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H207" t="s">
-        <v>8</v>
+      <c r="G207" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -5776,11 +5152,8 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H208" t="s">
-        <v>8</v>
+      <c r="G208" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -5802,11 +5175,8 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H209" t="s">
-        <v>8</v>
+      <c r="G209" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5828,11 +5198,8 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H210" t="s">
-        <v>8</v>
+      <c r="G210" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -5854,11 +5221,8 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H211" t="s">
-        <v>8</v>
+      <c r="G211" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -5880,11 +5244,8 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H212" t="s">
-        <v>8</v>
+      <c r="G212" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5906,11 +5267,8 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H213" t="s">
-        <v>8</v>
+      <c r="G213" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -5932,11 +5290,8 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H214" t="s">
-        <v>8</v>
+      <c r="G214" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -5958,11 +5313,8 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H215" t="s">
-        <v>8</v>
+      <c r="G215" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -5984,11 +5336,8 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H216" t="s">
-        <v>8</v>
+      <c r="G216" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -6010,11 +5359,8 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H217" t="s">
-        <v>8</v>
+      <c r="G217" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -6036,11 +5382,8 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H218" t="s">
-        <v>8</v>
+      <c r="G218" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -6062,11 +5405,8 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H219" t="s">
-        <v>8</v>
+      <c r="G219" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -6088,11 +5428,8 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H220" t="s">
-        <v>8</v>
+      <c r="G220" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -6114,11 +5451,8 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H221" t="s">
-        <v>8</v>
+      <c r="G221" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -6140,11 +5474,8 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H222" t="s">
-        <v>8</v>
+      <c r="G222" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -6166,11 +5497,8 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H223" t="s">
-        <v>8</v>
+      <c r="G223" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -6192,11 +5520,8 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H224" t="s">
-        <v>8</v>
+      <c r="G224" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -6218,11 +5543,8 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H225" t="s">
-        <v>8</v>
+      <c r="G225" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="226">
@@ -6244,11 +5566,8 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H226" t="s">
-        <v>8</v>
+      <c r="G226" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -6270,11 +5589,8 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H227" t="s">
-        <v>8</v>
+      <c r="G227" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -6296,11 +5612,8 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H228" t="s">
-        <v>8</v>
+      <c r="G228" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -6322,11 +5635,8 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H229" t="s">
-        <v>8</v>
+      <c r="G229" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -6348,11 +5658,8 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H230" t="s">
-        <v>8</v>
+      <c r="G230" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -6374,11 +5681,8 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H231" t="s">
-        <v>8</v>
+      <c r="G231" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -6400,11 +5704,8 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H232" t="s">
-        <v>8</v>
+      <c r="G232" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -6426,11 +5727,8 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H233" t="s">
-        <v>8</v>
+      <c r="G233" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -6452,11 +5750,8 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H234" t="s">
-        <v>8</v>
+      <c r="G234" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -6478,11 +5773,8 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H235" t="s">
-        <v>8</v>
+      <c r="G235" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -6504,11 +5796,8 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H236" t="s">
-        <v>8</v>
+      <c r="G236" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -6530,11 +5819,8 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H237" t="s">
-        <v>8</v>
+      <c r="G237" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -6556,11 +5842,8 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H238" t="s">
-        <v>8</v>
+      <c r="G238" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -6582,11 +5865,8 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H239" t="s">
-        <v>8</v>
+      <c r="G239" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -6608,11 +5888,8 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H240" t="s">
-        <v>8</v>
+      <c r="G240" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6634,11 +5911,8 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H241" t="s">
-        <v>8</v>
+      <c r="G241" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -6660,11 +5934,8 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H242" t="s">
-        <v>8</v>
+      <c r="G242" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="243">
@@ -6686,11 +5957,8 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H243" t="s">
-        <v>8</v>
+      <c r="G243" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -6712,11 +5980,8 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H244" t="s">
-        <v>8</v>
+      <c r="G244" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6738,11 +6003,8 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H245" t="s">
-        <v>8</v>
+      <c r="G245" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -6764,11 +6026,8 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H246" t="s">
-        <v>8</v>
+      <c r="G246" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -6790,11 +6049,8 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H247" t="s">
-        <v>8</v>
+      <c r="G247" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -6816,11 +6072,8 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H248" t="s">
-        <v>8</v>
+      <c r="G248" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6842,11 +6095,8 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H249" t="s">
-        <v>8</v>
+      <c r="G249" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -6868,11 +6118,8 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H250" t="s">
-        <v>8</v>
+      <c r="G250" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -6894,11 +6141,8 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H251" t="s">
-        <v>8</v>
+      <c r="G251" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6920,11 +6164,8 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H252" t="s">
-        <v>8</v>
+      <c r="G252" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6946,11 +6187,8 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H253" t="s">
-        <v>8</v>
+      <c r="G253" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -6972,11 +6210,8 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H254" t="s">
-        <v>8</v>
+      <c r="G254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -6998,11 +6233,8 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H255" t="s">
-        <v>8</v>
+      <c r="G255" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -7024,11 +6256,8 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H256" t="s">
-        <v>8</v>
+      <c r="G256" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -7050,11 +6279,8 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H257" t="s">
-        <v>8</v>
+      <c r="G257" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -7076,11 +6302,8 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H258" t="s">
-        <v>8</v>
+      <c r="G258" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -7102,11 +6325,8 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H259" t="s">
-        <v>8</v>
+      <c r="G259" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -7128,11 +6348,8 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H260" t="s">
-        <v>8</v>
+      <c r="G260" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -7154,11 +6371,8 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H261" t="s">
-        <v>8</v>
+      <c r="G261" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -7180,11 +6394,8 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H262" t="s">
-        <v>8</v>
+      <c r="G262" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -7206,11 +6417,8 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H263" t="s">
-        <v>8</v>
+      <c r="G263" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -7232,11 +6440,8 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H264" t="s">
-        <v>8</v>
+      <c r="G264" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -7258,11 +6463,8 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H265" t="s">
-        <v>8</v>
+      <c r="G265" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7284,11 +6486,8 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H266" t="s">
-        <v>8</v>
+      <c r="G266" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -7310,11 +6509,8 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H267" t="s">
-        <v>8</v>
+      <c r="G267" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7336,11 +6532,8 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H268" t="s">
-        <v>8</v>
+      <c r="G268" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -7362,11 +6555,8 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H269" t="s">
-        <v>8</v>
+      <c r="G269" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -7388,11 +6578,8 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H270" t="s">
-        <v>8</v>
+      <c r="G270" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -7414,11 +6601,8 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H271" t="s">
-        <v>8</v>
+      <c r="G271" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -7440,11 +6624,8 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H272" t="s">
-        <v>8</v>
+      <c r="G272" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -7466,11 +6647,8 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H273" t="s">
-        <v>8</v>
+      <c r="G273" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -7492,11 +6670,8 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H274" t="s">
-        <v>8</v>
+      <c r="G274" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -7518,11 +6693,8 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H275" t="s">
-        <v>8</v>
+      <c r="G275" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -7544,11 +6716,8 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H276" t="s">
-        <v>8</v>
+      <c r="G276" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7570,11 +6739,8 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H277" t="s">
-        <v>8</v>
+      <c r="G277" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -7596,11 +6762,8 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H278" t="s">
-        <v>8</v>
+      <c r="G278" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -7622,11 +6785,8 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H279" t="s">
-        <v>8</v>
+      <c r="G279" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -7648,11 +6808,8 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H280" t="s">
-        <v>8</v>
+      <c r="G280" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -7674,11 +6831,8 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H281" t="s">
-        <v>8</v>
+      <c r="G281" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -7700,11 +6854,8 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H282" t="s">
-        <v>8</v>
+      <c r="G282" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -7726,11 +6877,8 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H283" t="s">
-        <v>8</v>
+      <c r="G283" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -7752,11 +6900,8 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H284" t="s">
-        <v>8</v>
+      <c r="G284" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -7778,11 +6923,8 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H285" t="s">
-        <v>8</v>
+      <c r="G285" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7804,11 +6946,8 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H286" t="s">
-        <v>8</v>
+      <c r="G286" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -7830,11 +6969,8 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H287" t="s">
-        <v>8</v>
+      <c r="G287" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -7856,11 +6992,8 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H288" t="s">
-        <v>8</v>
+      <c r="G288" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -7882,11 +7015,8 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H289" t="s">
-        <v>8</v>
+      <c r="G289" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -7908,11 +7038,8 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H290" t="s">
-        <v>8</v>
+      <c r="G290" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -7934,11 +7061,8 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H291" t="s">
-        <v>8</v>
+      <c r="G291" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -7960,11 +7084,8 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H292" t="s">
-        <v>8</v>
+      <c r="G292" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -7986,11 +7107,8 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H293" t="s">
-        <v>8</v>
+      <c r="G293" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -8012,11 +7130,8 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H294" t="s">
-        <v>8</v>
+      <c r="G294" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -8038,11 +7153,8 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H295" t="s">
-        <v>8</v>
+      <c r="G295" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -8064,11 +7176,8 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H296" t="s">
-        <v>8</v>
+      <c r="G296" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -8090,11 +7199,8 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H297" t="s">
-        <v>8</v>
+      <c r="G297" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -8116,11 +7222,8 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H298" t="s">
-        <v>8</v>
+      <c r="G298" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -8142,11 +7245,8 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H299" t="s">
-        <v>8</v>
+      <c r="G299" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -8168,11 +7268,8 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H300" t="s">
-        <v>8</v>
+      <c r="G300" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -8194,11 +7291,8 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H301" t="s">
-        <v>8</v>
+      <c r="G301" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -8220,11 +7314,8 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H302" t="s">
-        <v>8</v>
+      <c r="G302" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -8246,11 +7337,8 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H303" t="s">
-        <v>8</v>
+      <c r="G303" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -8272,11 +7360,8 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H304" t="s">
-        <v>8</v>
+      <c r="G304" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -8298,11 +7383,8 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H305" t="s">
-        <v>8</v>
+      <c r="G305" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -8324,11 +7406,8 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H306" t="s">
-        <v>8</v>
+      <c r="G306" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -8350,11 +7429,8 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H307" t="s">
-        <v>8</v>
+      <c r="G307" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -8376,11 +7452,8 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H308" t="s">
-        <v>8</v>
+      <c r="G308" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -8402,11 +7475,8 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H309" t="s">
-        <v>8</v>
+      <c r="G309" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -8428,11 +7498,8 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H310" t="s">
-        <v>8</v>
+      <c r="G310" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -8454,11 +7521,8 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H311" t="s">
-        <v>8</v>
+      <c r="G311" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -8480,11 +7544,8 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H312" t="s">
-        <v>8</v>
+      <c r="G312" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -8506,11 +7567,8 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H313" t="s">
-        <v>8</v>
+      <c r="G313" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -8532,11 +7590,8 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H314" t="s">
-        <v>8</v>
+      <c r="G314" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -8558,11 +7613,8 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H315" t="s">
-        <v>8</v>
+      <c r="G315" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -8584,11 +7636,8 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H316" t="s">
-        <v>8</v>
+      <c r="G316" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -8610,11 +7659,8 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H317" t="s">
-        <v>8</v>
+      <c r="G317" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -8636,11 +7682,8 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H318" t="s">
-        <v>8</v>
+      <c r="G318" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -8662,11 +7705,8 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H319" t="s">
-        <v>8</v>
+      <c r="G319" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -8688,11 +7728,8 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H320" t="s">
-        <v>8</v>
+      <c r="G320" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -8714,11 +7751,8 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H321" t="s">
-        <v>8</v>
+      <c r="G321" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -8740,11 +7774,8 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H322" t="s">
-        <v>8</v>
+      <c r="G322" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -8766,11 +7797,8 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H323" t="s">
-        <v>8</v>
+      <c r="G323" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -8792,11 +7820,8 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H324" t="s">
-        <v>8</v>
+      <c r="G324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -8818,11 +7843,8 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H325" t="s">
-        <v>8</v>
+      <c r="G325" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -8844,11 +7866,8 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H326" t="s">
-        <v>8</v>
+      <c r="G326" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -8870,11 +7889,8 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H327" t="s">
-        <v>8</v>
+      <c r="G327" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -8896,11 +7912,8 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H328" t="s">
-        <v>8</v>
+      <c r="G328" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -8922,11 +7935,8 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H329" t="s">
-        <v>8</v>
+      <c r="G329" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8948,11 +7958,8 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H330" t="s">
-        <v>8</v>
+      <c r="G330" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -8974,11 +7981,8 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H331" t="s">
-        <v>8</v>
+      <c r="G331" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -9000,11 +8004,8 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H332" t="s">
-        <v>8</v>
+      <c r="G332" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9026,11 +8027,8 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H333" t="s">
-        <v>8</v>
+      <c r="G333" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -9052,11 +8050,8 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H334" t="s">
-        <v>8</v>
+      <c r="G334" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -9078,11 +8073,8 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H335" t="s">
-        <v>8</v>
+      <c r="G335" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -9104,11 +8096,8 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H336" t="s">
-        <v>8</v>
+      <c r="G336" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -9130,11 +8119,8 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H337" t="s">
-        <v>8</v>
+      <c r="G337" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -9156,11 +8142,8 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H338" t="s">
-        <v>8</v>
+      <c r="G338" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -9182,11 +8165,8 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H339" t="s">
-        <v>8</v>
+      <c r="G339" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9208,11 +8188,8 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H340" t="s">
-        <v>8</v>
+      <c r="G340" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -9234,11 +8211,8 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H341" t="s">
-        <v>8</v>
+      <c r="G341" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -9260,11 +8234,8 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H342" t="s">
-        <v>8</v>
+      <c r="G342" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -9286,11 +8257,8 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H343" t="s">
-        <v>8</v>
+      <c r="G343" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -9312,11 +8280,8 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H344" t="s">
-        <v>8</v>
+      <c r="G344" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -9338,11 +8303,8 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H345" t="s">
-        <v>8</v>
+      <c r="G345" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -9364,11 +8326,8 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H346" t="s">
-        <v>8</v>
+      <c r="G346" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -9390,11 +8349,8 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H347" t="s">
-        <v>8</v>
+      <c r="G347" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -9416,11 +8372,8 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H348" t="s">
-        <v>8</v>
+      <c r="G348" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -9442,11 +8395,8 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H349" t="s">
-        <v>8</v>
+      <c r="G349" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -9468,11 +8418,8 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H350" t="s">
-        <v>8</v>
+      <c r="G350" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -9494,11 +8441,8 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H351" t="s">
-        <v>8</v>
+      <c r="G351" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -9520,11 +8464,8 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H352" t="s">
-        <v>8</v>
+      <c r="G352" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -9546,11 +8487,8 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H353" t="s">
-        <v>8</v>
+      <c r="G353" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -9572,11 +8510,8 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H354" t="s">
-        <v>8</v>
+      <c r="G354" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -9598,11 +8533,8 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H355" t="s">
-        <v>8</v>
+      <c r="G355" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -9624,11 +8556,8 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H356" t="s">
-        <v>8</v>
+      <c r="G356" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -9650,11 +8579,8 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H357" t="s">
-        <v>8</v>
+      <c r="G357" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -9676,11 +8602,8 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H358" t="s">
-        <v>8</v>
+      <c r="G358" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -9702,11 +8625,8 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H359" t="s">
-        <v>8</v>
+      <c r="G359" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -9728,11 +8648,8 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H360" t="s">
-        <v>8</v>
+      <c r="G360" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -9754,11 +8671,8 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H361" t="s">
-        <v>8</v>
+      <c r="G361" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -9780,11 +8694,8 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H362" t="s">
-        <v>8</v>
+      <c r="G362" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -9806,11 +8717,8 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H363" t="s">
-        <v>8</v>
+      <c r="G363" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -9832,11 +8740,8 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H364" t="s">
-        <v>8</v>
+      <c r="G364" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -9858,11 +8763,8 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H365" t="s">
-        <v>8</v>
+      <c r="G365" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -9884,11 +8786,8 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H366" t="s">
-        <v>8</v>
+      <c r="G366" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -9910,11 +8809,8 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H367" t="s">
-        <v>8</v>
+      <c r="G367" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -9936,11 +8832,8 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H368" t="s">
-        <v>8</v>
+      <c r="G368" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="369">
@@ -9962,11 +8855,8 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H369" t="s">
-        <v>8</v>
+      <c r="G369" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -9988,11 +8878,8 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H370" t="s">
-        <v>8</v>
+      <c r="G370" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -10014,11 +8901,8 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H371" t="s">
-        <v>8</v>
+      <c r="G371" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -10040,11 +8924,8 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H372" t="s">
-        <v>8</v>
+      <c r="G372" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="373">
@@ -10066,11 +8947,8 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H373" t="s">
-        <v>8</v>
+      <c r="G373" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -10092,11 +8970,8 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H374" t="s">
-        <v>8</v>
+      <c r="G374" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -10118,11 +8993,8 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H375" t="s">
-        <v>8</v>
+      <c r="G375" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -10144,11 +9016,8 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H376" t="s">
-        <v>8</v>
+      <c r="G376" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="377">
@@ -10170,11 +9039,8 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H377" t="s">
-        <v>8</v>
+      <c r="G377" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="378">
@@ -10196,11 +9062,8 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H378" t="s">
-        <v>8</v>
+      <c r="G378" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="379">
@@ -10222,11 +9085,8 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H379" t="s">
-        <v>8</v>
+      <c r="G379" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="380">
@@ -10248,11 +9108,8 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H380" t="s">
-        <v>8</v>
+      <c r="G380" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="381">
@@ -10274,11 +9131,8 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H381" t="s">
-        <v>8</v>
+      <c r="G381" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -10300,11 +9154,8 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H382" t="s">
-        <v>8</v>
+      <c r="G382" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -10326,11 +9177,8 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H383" t="s">
-        <v>8</v>
+      <c r="G383" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -10352,11 +9200,8 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H384" t="s">
-        <v>8</v>
+      <c r="G384" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -10378,11 +9223,8 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H385" t="s">
-        <v>8</v>
+      <c r="G385" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -10404,11 +9246,8 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H386" t="s">
-        <v>8</v>
+      <c r="G386" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -10430,11 +9269,8 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H387" t="s">
-        <v>8</v>
+      <c r="G387" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -10456,11 +9292,8 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H388" t="s">
-        <v>8</v>
+      <c r="G388" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -10482,11 +9315,8 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H389" t="s">
-        <v>8</v>
+      <c r="G389" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -10508,11 +9338,8 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H390" t="s">
-        <v>8</v>
+      <c r="G390" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -10534,11 +9361,8 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H391" t="s">
-        <v>8</v>
+      <c r="G391" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -10560,11 +9384,8 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H392" t="s">
-        <v>8</v>
+      <c r="G392" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -10586,11 +9407,8 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H393" t="s">
-        <v>8</v>
+      <c r="G393" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="394">
@@ -10612,11 +9430,8 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H394" t="s">
-        <v>8</v>
+      <c r="G394" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="395">
@@ -10638,11 +9453,8 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H395" t="s">
-        <v>8</v>
+      <c r="G395" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="396">
@@ -10664,11 +9476,8 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H396" t="s">
-        <v>8</v>
+      <c r="G396" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -10690,11 +9499,8 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H397" t="s">
-        <v>8</v>
+      <c r="G397" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="398">
@@ -10716,11 +9522,8 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H398" t="s">
-        <v>8</v>
+      <c r="G398" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -10742,11 +9545,8 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H399" t="s">
-        <v>8</v>
+      <c r="G399" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -10768,11 +9568,8 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H400" t="s">
-        <v>8</v>
+      <c r="G400" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="401">
@@ -10794,11 +9591,8 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H401" t="s">
-        <v>8</v>
+      <c r="G401" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -10820,11 +9614,8 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H402" t="s">
-        <v>8</v>
+      <c r="G402" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -10846,11 +9637,8 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H403" t="s">
-        <v>8</v>
+      <c r="G403" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="404">
@@ -10872,11 +9660,8 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H404" t="s">
-        <v>8</v>
+      <c r="G404" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -10898,11 +9683,8 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H405" t="s">
-        <v>8</v>
+      <c r="G405" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -10924,11 +9706,8 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H406" t="s">
-        <v>8</v>
+      <c r="G406" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -10950,11 +9729,8 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H407" t="s">
-        <v>8</v>
+      <c r="G407" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -10976,11 +9752,8 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H408" t="s">
-        <v>8</v>
+      <c r="G408" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="409">
@@ -11002,11 +9775,8 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H409" t="s">
-        <v>8</v>
+      <c r="G409" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -11028,11 +9798,8 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H410" t="s">
-        <v>8</v>
+      <c r="G410" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11054,11 +9821,8 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H411" t="s">
-        <v>8</v>
+      <c r="G411" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -11080,11 +9844,8 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H412" t="s">
-        <v>8</v>
+      <c r="G412" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -11106,11 +9867,8 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H413" t="s">
-        <v>8</v>
+      <c r="G413" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="414">
@@ -11132,11 +9890,8 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H414" t="s">
-        <v>8</v>
+      <c r="G414" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -11158,11 +9913,8 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H415" t="s">
-        <v>8</v>
+      <c r="G415" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="416">
@@ -11184,11 +9936,8 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H416" t="s">
-        <v>8</v>
+      <c r="G416" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -11210,11 +9959,8 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H417" t="s">
-        <v>8</v>
+      <c r="G417" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="418">
@@ -11236,11 +9982,8 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H418" t="s">
-        <v>8</v>
+      <c r="G418" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -11262,11 +10005,8 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H419" t="s">
-        <v>8</v>
+      <c r="G419" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -11288,11 +10028,8 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H420" t="s">
-        <v>8</v>
+      <c r="G420" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="421">
@@ -11314,11 +10051,8 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="n">
-        <v>0.018673000857234</v>
-      </c>
-      <c r="H421" t="s">
-        <v>8</v>
+      <c r="G421" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="422">
@@ -11340,11 +10074,8 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H422" t="s">
-        <v>8</v>
+      <c r="G422" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -11366,11 +10097,8 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H423" t="s">
-        <v>8</v>
+      <c r="G423" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -11392,11 +10120,8 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H424" t="s">
-        <v>8</v>
+      <c r="G424" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -11418,11 +10143,8 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H425" t="s">
-        <v>8</v>
+      <c r="G425" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -11444,11 +10166,8 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H426" t="s">
-        <v>8</v>
+      <c r="G426" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -11470,11 +10189,8 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H427" t="s">
-        <v>8</v>
+      <c r="G427" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -11496,11 +10212,8 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H428" t="s">
-        <v>8</v>
+      <c r="G428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429">
@@ -11522,11 +10235,8 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H429" t="s">
-        <v>8</v>
+      <c r="G429" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -11548,11 +10258,8 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H430" t="s">
-        <v>8</v>
+      <c r="G430" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -11574,11 +10281,8 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H431" t="s">
-        <v>8</v>
+      <c r="G431" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -11600,11 +10304,8 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H432" t="s">
-        <v>8</v>
+      <c r="G432" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="433">
@@ -11626,11 +10327,8 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H433" t="s">
-        <v>8</v>
+      <c r="G433" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="434">
@@ -11652,11 +10350,8 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H434" t="s">
-        <v>8</v>
+      <c r="G434" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="435">
@@ -11678,11 +10373,8 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H435" t="s">
-        <v>8</v>
+      <c r="G435" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -11704,11 +10396,8 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H436" t="s">
-        <v>8</v>
+      <c r="G436" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -11730,11 +10419,8 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H437" t="s">
-        <v>8</v>
+      <c r="G437" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="438">
@@ -11756,11 +10442,8 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H438" t="s">
-        <v>8</v>
+      <c r="G438" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -11782,11 +10465,8 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H439" t="s">
-        <v>8</v>
+      <c r="G439" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -11808,11 +10488,8 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H440" t="s">
-        <v>8</v>
+      <c r="G440" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="441">
@@ -11834,11 +10511,8 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H441" t="s">
-        <v>8</v>
+      <c r="G441" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -11860,11 +10534,8 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H442" t="s">
-        <v>8</v>
+      <c r="G442" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -11886,11 +10557,8 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H443" t="s">
-        <v>8</v>
+      <c r="G443" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="444">
@@ -11912,11 +10580,8 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H444" t="s">
-        <v>8</v>
+      <c r="G444" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="445">
@@ -11938,11 +10603,8 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H445" t="s">
-        <v>8</v>
+      <c r="G445" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="446">
@@ -11964,11 +10626,8 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H446" t="s">
-        <v>8</v>
+      <c r="G446" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="447">
@@ -11990,11 +10649,8 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H447" t="s">
-        <v>8</v>
+      <c r="G447" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -12016,11 +10672,8 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H448" t="s">
-        <v>8</v>
+      <c r="G448" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -12042,11 +10695,8 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H449" t="s">
-        <v>8</v>
+      <c r="G449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -12068,11 +10718,8 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H450" t="s">
-        <v>8</v>
+      <c r="G450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451">
@@ -12094,11 +10741,8 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H451" t="s">
-        <v>8</v>
+      <c r="G451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -12120,11 +10764,8 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H452" t="s">
-        <v>8</v>
+      <c r="G452" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -12146,11 +10787,8 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H453" t="s">
-        <v>8</v>
+      <c r="G453" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -12172,11 +10810,8 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H454" t="s">
-        <v>8</v>
+      <c r="G454" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -12198,11 +10833,8 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H455" t="s">
-        <v>8</v>
+      <c r="G455" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -12224,11 +10856,8 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H456" t="s">
-        <v>8</v>
+      <c r="G456" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -12250,11 +10879,8 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H457" t="s">
-        <v>8</v>
+      <c r="G457" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -12276,11 +10902,8 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H458" t="s">
-        <v>8</v>
+      <c r="G458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -12302,11 +10925,8 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H459" t="s">
-        <v>8</v>
+      <c r="G459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -12328,11 +10948,8 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H460" t="s">
-        <v>8</v>
+      <c r="G460" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -12354,11 +10971,8 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H461" t="s">
-        <v>8</v>
+      <c r="G461" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -12380,11 +10994,8 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H462" t="s">
-        <v>8</v>
+      <c r="G462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -12406,11 +11017,8 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H463" t="s">
-        <v>8</v>
+      <c r="G463" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -12432,11 +11040,8 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H464" t="s">
-        <v>8</v>
+      <c r="G464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -12458,11 +11063,8 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H465" t="s">
-        <v>8</v>
+      <c r="G465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -12484,11 +11086,8 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H466" t="s">
-        <v>8</v>
+      <c r="G466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -12510,11 +11109,8 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H467" t="s">
-        <v>8</v>
+      <c r="G467" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="468">
@@ -12536,11 +11132,8 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H468" t="s">
-        <v>8</v>
+      <c r="G468" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -12562,11 +11155,8 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H469" t="s">
-        <v>8</v>
+      <c r="G469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -12588,11 +11178,8 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H470" t="s">
-        <v>8</v>
+      <c r="G470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471">
@@ -12614,11 +11201,8 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H471" t="s">
-        <v>8</v>
+      <c r="G471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -12640,11 +11224,8 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H472" t="s">
-        <v>8</v>
+      <c r="G472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -12666,11 +11247,8 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H473" t="s">
-        <v>8</v>
+      <c r="G473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474">
@@ -12692,11 +11270,8 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H474" t="s">
-        <v>8</v>
+      <c r="G474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -12718,11 +11293,8 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H475" t="s">
-        <v>8</v>
+      <c r="G475" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="476">
@@ -12744,11 +11316,8 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H476" t="s">
-        <v>8</v>
+      <c r="G476" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="477">
@@ -12770,11 +11339,8 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H477" t="s">
-        <v>8</v>
+      <c r="G477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478">
@@ -12796,11 +11362,8 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H478" t="s">
-        <v>8</v>
+      <c r="G478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -12822,11 +11385,8 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H479" t="s">
-        <v>8</v>
+      <c r="G479" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="480">
@@ -12848,11 +11408,8 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H480" t="s">
-        <v>8</v>
+      <c r="G480" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="481">
@@ -12874,11 +11431,8 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H481" t="s">
-        <v>8</v>
+      <c r="G481" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -12900,11 +11454,8 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H482" t="s">
-        <v>8</v>
+      <c r="G482" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -12926,11 +11477,8 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H483" t="s">
-        <v>8</v>
+      <c r="G483" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -12952,11 +11500,8 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H484" t="s">
-        <v>8</v>
+      <c r="G484" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="485">
@@ -12978,11 +11523,8 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H485" t="s">
-        <v>8</v>
+      <c r="G485" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="486">
@@ -13004,11 +11546,8 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H486" t="s">
-        <v>8</v>
+      <c r="G486" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -13030,11 +11569,8 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H487" t="s">
-        <v>8</v>
+      <c r="G487" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="488">
@@ -13056,11 +11592,8 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H488" t="s">
-        <v>8</v>
+      <c r="G488" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -13082,11 +11615,8 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H489" t="s">
-        <v>8</v>
+      <c r="G489" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="490">
@@ -13108,11 +11638,8 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H490" t="s">
-        <v>8</v>
+      <c r="G490" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -13134,11 +11661,8 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H491" t="s">
-        <v>8</v>
+      <c r="G491" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -13160,11 +11684,8 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H492" t="s">
-        <v>8</v>
+      <c r="G492" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="493">
@@ -13186,11 +11707,8 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H493" t="s">
-        <v>8</v>
+      <c r="G493" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="494">
@@ -13212,11 +11730,8 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H494" t="s">
-        <v>8</v>
+      <c r="G494" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="495">
@@ -13238,11 +11753,8 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H495" t="s">
-        <v>8</v>
+      <c r="G495" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="496">
@@ -13264,11 +11776,8 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H496" t="s">
-        <v>8</v>
+      <c r="G496" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -13290,11 +11799,8 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H497" t="s">
-        <v>8</v>
+      <c r="G497" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -13316,11 +11822,8 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H498" t="s">
-        <v>8</v>
+      <c r="G498" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -13342,11 +11845,8 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H499" t="s">
-        <v>8</v>
+      <c r="G499" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -13368,11 +11868,8 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H500" t="s">
-        <v>8</v>
+      <c r="G500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -13394,11 +11891,8 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H501" t="s">
-        <v>8</v>
+      <c r="G501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -13420,11 +11914,8 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H502" t="s">
-        <v>8</v>
+      <c r="G502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -13446,11 +11937,8 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H503" t="s">
-        <v>8</v>
+      <c r="G503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -13472,11 +11960,8 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H504" t="s">
-        <v>8</v>
+      <c r="G504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505">
@@ -13498,11 +11983,8 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H505" t="s">
-        <v>8</v>
+      <c r="G505" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -13524,11 +12006,8 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="n">
-        <v>0.0154079999774694</v>
-      </c>
-      <c r="H506" t="s">
-        <v>8</v>
+      <c r="G506" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="507">
@@ -13550,11 +12029,8 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H507" t="s">
-        <v>8</v>
+      <c r="G507" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -13576,11 +12052,8 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H508" t="s">
-        <v>8</v>
+      <c r="G508" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -13602,11 +12075,8 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H509" t="s">
-        <v>8</v>
+      <c r="G509" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="510">
@@ -13628,11 +12098,8 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H510" t="s">
-        <v>8</v>
+      <c r="G510" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="511">
@@ -13654,11 +12121,8 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H511" t="s">
-        <v>8</v>
+      <c r="G511" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -13680,11 +12144,8 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H512" t="s">
-        <v>8</v>
+      <c r="G512" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="513">
@@ -13706,11 +12167,8 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H513" t="s">
-        <v>8</v>
+      <c r="G513" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -13732,11 +12190,8 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>8</v>
+      <c r="G514" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -13758,11 +12213,8 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H515" t="s">
-        <v>8</v>
+      <c r="G515" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -13784,11 +12236,8 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H516" t="s">
-        <v>8</v>
+      <c r="G516" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="517">
@@ -13810,11 +12259,8 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H517" t="s">
-        <v>8</v>
+      <c r="G517" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -13836,11 +12282,8 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H518" t="s">
-        <v>8</v>
+      <c r="G518" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -13862,11 +12305,8 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H519" t="s">
-        <v>8</v>
+      <c r="G519" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -13888,11 +12328,8 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H520" t="s">
-        <v>8</v>
+      <c r="G520" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -13914,11 +12351,8 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H521" t="s">
-        <v>8</v>
+      <c r="G521" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="522">
@@ -13940,11 +12374,8 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H522" t="s">
-        <v>8</v>
+      <c r="G522" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -13966,11 +12397,8 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H523" t="s">
-        <v>8</v>
+      <c r="G523" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -13992,11 +12420,8 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H524" t="s">
-        <v>8</v>
+      <c r="G524" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="525">
@@ -14018,11 +12443,8 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H525" t="s">
-        <v>8</v>
+      <c r="G525" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -14044,11 +12466,8 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H526" t="s">
-        <v>8</v>
+      <c r="G526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527">
@@ -14070,11 +12489,8 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H527" t="s">
-        <v>8</v>
+      <c r="G527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528">
@@ -14096,11 +12512,8 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H528" t="s">
-        <v>8</v>
+      <c r="G528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529">
@@ -14122,11 +12535,8 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H529" t="s">
-        <v>8</v>
+      <c r="G529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -14148,11 +12558,8 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H530" t="s">
-        <v>8</v>
+      <c r="G530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -14174,11 +12581,8 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H531" t="s">
-        <v>8</v>
+      <c r="G531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532">
@@ -14200,11 +12604,8 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H532" t="s">
-        <v>8</v>
+      <c r="G532" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="533">
@@ -14226,11 +12627,8 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H533" t="s">
-        <v>8</v>
+      <c r="G533" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -14252,11 +12650,8 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H534" t="s">
-        <v>8</v>
+      <c r="G534" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="535">
@@ -14278,11 +12673,8 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H535" t="s">
-        <v>8</v>
+      <c r="G535" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -14304,11 +12696,8 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H536" t="s">
-        <v>8</v>
+      <c r="G536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537">
@@ -14330,11 +12719,8 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H537" t="s">
-        <v>8</v>
+      <c r="G537" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="538">
@@ -14356,11 +12742,8 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H538" t="s">
-        <v>8</v>
+      <c r="G538" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="539">
@@ -14382,11 +12765,8 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H539" t="s">
-        <v>8</v>
+      <c r="G539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540">
@@ -14408,11 +12788,8 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H540" t="s">
-        <v>8</v>
+      <c r="G540" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -14434,11 +12811,8 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H541" t="s">
-        <v>8</v>
+      <c r="G541" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="542">
@@ -14460,11 +12834,8 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H542" t="s">
-        <v>8</v>
+      <c r="G542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -14486,11 +12857,8 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H543" t="s">
-        <v>8</v>
+      <c r="G543" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -14512,11 +12880,8 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H544" t="s">
-        <v>8</v>
+      <c r="G544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545">
@@ -14538,11 +12903,8 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H545" t="s">
-        <v>8</v>
+      <c r="G545" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="546">
@@ -14564,11 +12926,8 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H546" t="s">
-        <v>8</v>
+      <c r="G546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547">
@@ -14590,11 +12949,8 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H547" t="s">
-        <v>8</v>
+      <c r="G547" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="548">
@@ -14616,11 +12972,8 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H548" t="s">
-        <v>8</v>
+      <c r="G548" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -14642,11 +12995,8 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H549" t="s">
-        <v>8</v>
+      <c r="G549" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -14668,11 +13018,8 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H550" t="s">
-        <v>8</v>
+      <c r="G550" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -14694,11 +13041,8 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H551" t="s">
-        <v>8</v>
+      <c r="G551" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="552">
@@ -14720,11 +13064,8 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H552" t="s">
-        <v>8</v>
+      <c r="G552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -14746,11 +13087,8 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H553" t="s">
-        <v>8</v>
+      <c r="G553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -14772,11 +13110,8 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H554" t="s">
-        <v>8</v>
+      <c r="G554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -14798,11 +13133,8 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H555" t="s">
-        <v>8</v>
+      <c r="G555" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="556">
@@ -14824,11 +13156,8 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H556" t="s">
-        <v>8</v>
+      <c r="G556" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="557">
@@ -14850,11 +13179,8 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H557" t="s">
-        <v>8</v>
+      <c r="G557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -14876,11 +13202,8 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H558" t="s">
-        <v>8</v>
+      <c r="G558" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="559">
@@ -14902,11 +13225,8 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H559" t="s">
-        <v>8</v>
+      <c r="G559" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="560">
@@ -14928,11 +13248,8 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H560" t="s">
-        <v>8</v>
+      <c r="G560" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -14954,11 +13271,8 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H561" t="s">
-        <v>8</v>
+      <c r="G561" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="562">
@@ -14980,11 +13294,8 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H562" t="s">
-        <v>8</v>
+      <c r="G562" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="563">
@@ -15006,11 +13317,8 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H563" t="s">
-        <v>8</v>
+      <c r="G563" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="564">
@@ -15032,11 +13340,8 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H564" t="s">
-        <v>8</v>
+      <c r="G564" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -15058,11 +13363,8 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H565" t="s">
-        <v>8</v>
+      <c r="G565" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="566">
@@ -15084,11 +13386,8 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H566" t="s">
-        <v>8</v>
+      <c r="G566" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -15110,11 +13409,8 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H567" t="s">
-        <v>8</v>
+      <c r="G567" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="568">
@@ -15136,11 +13432,8 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H568" t="s">
-        <v>8</v>
+      <c r="G568" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -15162,11 +13455,8 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H569" t="s">
-        <v>8</v>
+      <c r="G569" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="570">
@@ -15188,11 +13478,8 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H570" t="s">
-        <v>8</v>
+      <c r="G570" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -15214,11 +13501,8 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H571" t="s">
-        <v>8</v>
+      <c r="G571" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="572">
@@ -15240,11 +13524,8 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H572" t="s">
-        <v>8</v>
+      <c r="G572" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -15266,11 +13547,8 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H573" t="s">
-        <v>8</v>
+      <c r="G573" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="574">
@@ -15292,11 +13570,8 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H574" t="s">
-        <v>8</v>
+      <c r="G574" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -15318,11 +13593,8 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H575" t="s">
-        <v>8</v>
+      <c r="G575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -15344,11 +13616,8 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H576" t="s">
-        <v>8</v>
+      <c r="G576" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -15370,11 +13639,8 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H577" t="s">
-        <v>8</v>
+      <c r="G577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -15396,11 +13662,8 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="n">
-        <v>0.0175000000745058</v>
-      </c>
-      <c r="H578" t="s">
-        <v>8</v>
+      <c r="G578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579">
@@ -15422,11 +13685,8 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H579" t="s">
-        <v>8</v>
+      <c r="G579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580">
@@ -15448,11 +13708,8 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H580" t="s">
-        <v>8</v>
+      <c r="G580" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="581">
@@ -15474,11 +13731,8 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H581" t="s">
-        <v>8</v>
+      <c r="G581" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="582">
@@ -15500,11 +13754,8 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H582" t="s">
-        <v>8</v>
+      <c r="G582" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -15526,11 +13777,8 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H583" t="s">
-        <v>8</v>
+      <c r="G583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -15552,11 +13800,8 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H584" t="s">
-        <v>8</v>
+      <c r="G584" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="585">
@@ -15578,11 +13823,8 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H585" t="s">
-        <v>8</v>
+      <c r="G585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586">
@@ -15604,11 +13846,8 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H586" t="s">
-        <v>8</v>
+      <c r="G586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -15630,11 +13869,8 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H587" t="s">
-        <v>8</v>
+      <c r="G587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588">
@@ -15656,11 +13892,8 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H588" t="s">
-        <v>8</v>
+      <c r="G588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589">
@@ -15682,11 +13915,8 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H589" t="s">
-        <v>8</v>
+      <c r="G589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590">
@@ -15708,11 +13938,8 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="n">
-        <v>0.0171000007539988</v>
-      </c>
-      <c r="H590" t="s">
-        <v>8</v>
+      <c r="G590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591">
@@ -15734,11 +13961,8 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H591" t="s">
-        <v>8</v>
+      <c r="G591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592">
@@ -15760,11 +13984,8 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H592" t="s">
-        <v>8</v>
+      <c r="G592" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="593">
@@ -15786,11 +14007,8 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H593" t="s">
-        <v>8</v>
+      <c r="G593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594">
@@ -15812,11 +14030,8 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="n">
-        <v>0.0215000007301569</v>
-      </c>
-      <c r="H594" t="s">
-        <v>8</v>
+      <c r="G594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595">
@@ -15838,11 +14053,8 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="n">
-        <v>0.0203000009059906</v>
-      </c>
-      <c r="H595" t="s">
-        <v>8</v>
+      <c r="G595" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="596">
@@ -15864,11 +14076,8 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H596" t="s">
-        <v>8</v>
+      <c r="G596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597">
@@ -15890,11 +14099,8 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H597" t="s">
-        <v>8</v>
+      <c r="G597" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="598">
@@ -15916,11 +14122,8 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H598" t="s">
-        <v>8</v>
+      <c r="G598" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="599">
@@ -15942,11 +14145,8 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H599" t="s">
-        <v>8</v>
+      <c r="G599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600">
@@ -15968,11 +14168,8 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="n">
-        <v>0.0183000005781651</v>
-      </c>
-      <c r="H600" t="s">
-        <v>8</v>
+      <c r="G600" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="601">
@@ -15994,11 +14191,8 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H601" t="s">
-        <v>8</v>
+      <c r="G601" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="602">
@@ -16020,11 +14214,8 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H602" t="s">
-        <v>8</v>
+      <c r="G602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603">
@@ -16046,11 +14237,8 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H603" t="s">
-        <v>8</v>
+      <c r="G603" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="604">
@@ -16072,11 +14260,8 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="n">
-        <v>0.0196000002324581</v>
-      </c>
-      <c r="H604" t="s">
-        <v>8</v>
+      <c r="G604" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="605">
@@ -16098,11 +14283,8 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="n">
-        <v>0.0192000009119511</v>
-      </c>
-      <c r="H605" t="s">
-        <v>8</v>
+      <c r="G605" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="606">
@@ -16124,11 +14306,8 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H606" t="s">
-        <v>8</v>
+      <c r="G606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607">
@@ -16150,11 +14329,8 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H607" t="s">
-        <v>8</v>
+      <c r="G607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608">
@@ -16176,11 +14352,8 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H608" t="s">
-        <v>8</v>
+      <c r="G608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609">
@@ -16202,11 +14375,8 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="n">
-        <v>0.0181000009179115</v>
-      </c>
-      <c r="H609" t="s">
-        <v>8</v>
+      <c r="G609" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="610">
@@ -16228,11 +14398,8 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H610" t="s">
-        <v>8</v>
+      <c r="G610" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="611">
@@ -16254,11 +14421,8 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H611" t="s">
-        <v>8</v>
+      <c r="G611" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="612">
@@ -16280,11 +14444,8 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H612" t="s">
-        <v>8</v>
+      <c r="G612" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="613">
@@ -16306,11 +14467,8 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H613" t="s">
-        <v>8</v>
+      <c r="G613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614">
@@ -16332,11 +14490,8 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H614" t="s">
-        <v>8</v>
+      <c r="G614" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -16358,11 +14513,8 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H615" t="s">
-        <v>8</v>
+      <c r="G615" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="616">
@@ -16384,11 +14536,8 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H616" t="s">
-        <v>8</v>
+      <c r="G616" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -16410,11 +14559,8 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H617" t="s">
-        <v>8</v>
+      <c r="G617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618">
@@ -16436,11 +14582,8 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H618" t="s">
-        <v>8</v>
+      <c r="G618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619">
@@ -16462,11 +14605,8 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H619" t="s">
-        <v>8</v>
+      <c r="G619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620">
@@ -16488,11 +14628,8 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H620" t="s">
-        <v>8</v>
+      <c r="G620" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="621">
@@ -16514,11 +14651,8 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H621" t="s">
-        <v>8</v>
+      <c r="G621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622">
@@ -16540,11 +14674,8 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H622" t="s">
-        <v>8</v>
+      <c r="G622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623">
@@ -16566,11 +14697,8 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H623" t="s">
-        <v>8</v>
+      <c r="G623" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="624">
@@ -16592,11 +14720,8 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H624" t="s">
-        <v>8</v>
+      <c r="G624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625">
@@ -16618,11 +14743,8 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H625" t="s">
-        <v>8</v>
+      <c r="G625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -16644,11 +14766,8 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H626" t="s">
-        <v>8</v>
+      <c r="G626" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="627">
@@ -16670,11 +14789,8 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H627" t="s">
-        <v>8</v>
+      <c r="G627" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="628">
@@ -16696,11 +14812,8 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H628" t="s">
-        <v>8</v>
+      <c r="G628" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="629">
@@ -16722,11 +14835,8 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H629" t="s">
-        <v>8</v>
+      <c r="G629" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="630">
@@ -16748,11 +14858,8 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H630" t="s">
-        <v>8</v>
+      <c r="G630" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -16774,11 +14881,8 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H631" t="s">
-        <v>8</v>
+      <c r="G631" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="632">
@@ -16800,11 +14904,8 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H632" t="s">
-        <v>8</v>
+      <c r="G632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633">
@@ -16826,11 +14927,8 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="n">
-        <v>0.0172000005841255</v>
-      </c>
-      <c r="H633" t="s">
-        <v>8</v>
+      <c r="G633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -16852,11 +14950,8 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H634" t="s">
-        <v>8</v>
+      <c r="G634" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -16878,11 +14973,8 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H635" t="s">
-        <v>8</v>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -16904,11 +14996,8 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H636" t="s">
-        <v>8</v>
+      <c r="G636" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="637">
@@ -16930,11 +15019,8 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H637" t="s">
-        <v>8</v>
+      <c r="G637" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="638">
@@ -16956,11 +15042,8 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H638" t="s">
-        <v>8</v>
+      <c r="G638" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="639">
@@ -16982,11 +15065,8 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H639" t="s">
-        <v>8</v>
+      <c r="G639" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="640">
@@ -17008,11 +15088,8 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H640" t="s">
-        <v>8</v>
+      <c r="G640" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="641">
@@ -17034,11 +15111,8 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H641" t="s">
-        <v>8</v>
+      <c r="G641" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -17060,11 +15134,8 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H642" t="s">
-        <v>8</v>
+      <c r="G642" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -17086,11 +15157,8 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H643" t="s">
-        <v>8</v>
+      <c r="G643" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="644">
@@ -17112,11 +15180,8 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H644" t="s">
-        <v>8</v>
+      <c r="G644" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -17138,11 +15203,8 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H645" t="s">
-        <v>8</v>
+      <c r="G645" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -17164,11 +15226,8 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H646" t="s">
-        <v>8</v>
+      <c r="G646" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="647">
@@ -17190,11 +15249,8 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H647" t="s">
-        <v>8</v>
+      <c r="G647" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -17216,11 +15272,8 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H648" t="s">
-        <v>8</v>
+      <c r="G648" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -17242,11 +15295,8 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H649" t="s">
-        <v>8</v>
+      <c r="G649" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="650">
@@ -17268,11 +15318,8 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H650" t="s">
-        <v>8</v>
+      <c r="G650" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="651">
@@ -17294,11 +15341,8 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H651" t="s">
-        <v>8</v>
+      <c r="G651" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="652">
@@ -17320,11 +15364,8 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H652" t="s">
-        <v>8</v>
+      <c r="G652" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="653">
@@ -17346,11 +15387,8 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H653" t="s">
-        <v>8</v>
+      <c r="G653" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -17372,11 +15410,8 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H654" t="s">
-        <v>8</v>
+      <c r="G654" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="655">
@@ -17398,11 +15433,8 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H655" t="s">
-        <v>8</v>
+      <c r="G655" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="656">
@@ -17424,11 +15456,8 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H656" t="s">
-        <v>8</v>
+      <c r="G656" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="657">
@@ -17450,11 +15479,8 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H657" t="s">
-        <v>8</v>
+      <c r="G657" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="658">
@@ -17476,11 +15502,8 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H658" t="s">
-        <v>8</v>
+      <c r="G658" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -17502,11 +15525,8 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H659" t="s">
-        <v>8</v>
+      <c r="G659" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -17528,11 +15548,8 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H660" t="s">
-        <v>8</v>
+      <c r="G660" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -17554,11 +15571,8 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H661" t="s">
-        <v>8</v>
+      <c r="G661" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="662">
@@ -17580,11 +15594,8 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H662" t="s">
-        <v>8</v>
+      <c r="G662" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="663">
@@ -17606,11 +15617,8 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H663" t="s">
-        <v>8</v>
+      <c r="G663" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="664">
@@ -17632,11 +15640,8 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H664" t="s">
-        <v>8</v>
+      <c r="G664" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="665">
@@ -17658,11 +15663,8 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H665" t="s">
-        <v>8</v>
+      <c r="G665" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="666">
@@ -17684,11 +15686,8 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H666" t="s">
-        <v>8</v>
+      <c r="G666" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="667">
@@ -17710,11 +15709,8 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H667" t="s">
-        <v>8</v>
+      <c r="G667" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="668">
@@ -17736,11 +15732,8 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H668" t="s">
-        <v>8</v>
+      <c r="G668" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="669">
@@ -17762,11 +15755,8 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H669" t="s">
-        <v>8</v>
+      <c r="G669" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -17788,11 +15778,8 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H670" t="s">
-        <v>8</v>
+      <c r="G670" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -17814,11 +15801,8 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H671" t="s">
-        <v>8</v>
+      <c r="G671" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="672">
@@ -17840,11 +15824,8 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="n">
-        <v>0.0201999992132187</v>
-      </c>
-      <c r="H672" t="s">
-        <v>8</v>
+      <c r="G672" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="673">
@@ -17866,11 +15847,8 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="n">
-        <v>0.0206000003963709</v>
-      </c>
-      <c r="H673" t="s">
-        <v>8</v>
+      <c r="G673" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="674">
@@ -17892,11 +15870,8 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="n">
-        <v>0.0208000000566244</v>
-      </c>
-      <c r="H674" t="s">
-        <v>8</v>
+      <c r="G674" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="675">
@@ -17918,11 +15893,8 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="n">
-        <v>0.0211999993771315</v>
-      </c>
-      <c r="H675" t="s">
-        <v>8</v>
+      <c r="G675" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="676">
@@ -17944,11 +15916,8 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="n">
-        <v>0.02280000038445</v>
-      </c>
-      <c r="H676" t="s">
-        <v>8</v>
+      <c r="G676" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="677">
@@ -17970,11 +15939,8 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="n">
-        <v>0.0216000005602837</v>
-      </c>
-      <c r="H677" t="s">
-        <v>8</v>
+      <c r="G677" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="678">
@@ -17996,11 +15962,8 @@
       <c r="F678" t="n">
         <v>0.0221999995410442</v>
       </c>
-      <c r="G678" t="n">
-        <v>0.0221999995410442</v>
-      </c>
-      <c r="H678" t="s">
-        <v>8</v>
+      <c r="G678" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="679">
@@ -18022,11 +15985,8 @@
       <c r="F679" t="n">
         <v>0.0233999993652105</v>
       </c>
-      <c r="G679" t="n">
-        <v>0.0233999993652105</v>
-      </c>
-      <c r="H679" t="s">
-        <v>8</v>
+      <c r="G679" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="680">
@@ -18048,11 +16008,8 @@
       <c r="F680" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G680" t="n">
-        <v>0.0243999995291233</v>
-      </c>
-      <c r="H680" t="s">
-        <v>8</v>
+      <c r="G680" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="681">
@@ -18074,11 +16031,8 @@
       <c r="F681" t="n">
         <v>0.0240000002086163</v>
       </c>
-      <c r="G681" t="n">
-        <v>0.0240000002086163</v>
-      </c>
-      <c r="H681" t="s">
-        <v>8</v>
+      <c r="G681" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="682">
@@ -18100,11 +16054,29 @@
       <c r="F682" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G682" t="n">
+      <c r="G682" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B683" t="n">
+        <v>5508835</v>
+      </c>
+      <c r="C683" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0.0241999998688698</v>
+      </c>
+      <c r="E683" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="H682" t="s">
-        <v>8</v>
+      <c r="F683"/>
+      <c r="G683" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -16074,8 +16074,31 @@
       <c r="E683" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="F683"/>
+      <c r="F683" t="n">
+        <v>0.0253999996930361</v>
+      </c>
       <c r="G683" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B684" t="n">
+        <v>3426919</v>
+      </c>
+      <c r="C684" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="D684" t="n">
+        <v>0.0248000007122755</v>
+      </c>
+      <c r="E684" t="n">
+        <v>0.0252000000327826</v>
+      </c>
+      <c r="F684"/>
+      <c r="G684" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -16097,8 +16097,31 @@
       <c r="E684" t="n">
         <v>0.0252000000327826</v>
       </c>
-      <c r="F684"/>
+      <c r="F684" t="n">
+        <v>0.0252000000327826</v>
+      </c>
       <c r="G684" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B685" t="n">
+        <v>9232889</v>
+      </c>
+      <c r="C685" t="n">
+        <v>0.0252000000327826</v>
+      </c>
+      <c r="D685" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="E685" t="n">
+        <v>0.0252000000327826</v>
+      </c>
+      <c r="F685"/>
+      <c r="G685" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -16120,8 +16120,31 @@
       <c r="E685" t="n">
         <v>0.0252000000327826</v>
       </c>
-      <c r="F685"/>
+      <c r="F685" t="n">
+        <v>0.0248000007122755</v>
+      </c>
       <c r="G685" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B686" t="n">
+        <v>10833631</v>
+      </c>
+      <c r="C686" t="n">
+        <v>0.025000000372529</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="E686" t="n">
+        <v>0.025000000372529</v>
+      </c>
+      <c r="F686"/>
+      <c r="G686" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -16143,8 +16143,31 @@
       <c r="E686" t="n">
         <v>0.025000000372529</v>
       </c>
-      <c r="F686"/>
+      <c r="F686" t="n">
+        <v>0.0238000005483627</v>
+      </c>
       <c r="G686" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B687" t="n">
+        <v>2404755</v>
+      </c>
+      <c r="C687" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="E687" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="F687"/>
+      <c r="G687" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -394,6 +397,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -414,8 +420,11 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -437,8 +446,11 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +472,11 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -483,8 +498,11 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -506,8 +524,11 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -529,8 +550,11 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -552,8 +576,11 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -575,8 +602,11 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -598,8 +628,11 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -621,8 +654,11 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +680,11 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -667,8 +706,11 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -690,8 +732,11 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -713,8 +758,11 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -736,8 +784,11 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -759,8 +810,11 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -782,8 +836,11 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,8 +862,11 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -828,8 +888,11 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -851,8 +914,11 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -874,8 +940,11 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -897,8 +966,11 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -920,8 +992,11 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -943,8 +1018,11 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -966,8 +1044,11 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -989,8 +1070,11 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" t="n">
+        <v>0.019845999777317</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1012,8 +1096,11 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1035,8 +1122,11 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1058,8 +1148,11 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
+      <c r="G30" t="n">
+        <v>0.01923399977386</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1081,8 +1174,11 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1104,8 +1200,11 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1127,8 +1226,11 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1150,8 +1252,11 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1173,8 +1278,11 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1196,8 +1304,11 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1219,8 +1330,11 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1242,8 +1356,11 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1265,8 +1382,11 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1288,8 +1408,11 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1311,8 +1434,11 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1334,8 +1460,11 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="G42" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1357,8 +1486,11 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1380,8 +1512,11 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,8 +1538,11 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -1426,8 +1564,11 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1449,8 +1590,11 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1472,8 +1616,11 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1495,8 +1642,11 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1518,8 +1668,11 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1541,8 +1694,11 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1564,8 +1720,11 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1587,8 +1746,11 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -1610,8 +1772,11 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1633,8 +1798,11 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1656,8 +1824,11 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1679,8 +1850,11 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -1702,8 +1876,11 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1725,8 +1902,11 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1748,8 +1928,11 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="s">
-        <v>7</v>
+      <c r="G60" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1771,8 +1954,11 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="s">
-        <v>7</v>
+      <c r="G61" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1794,8 +1980,11 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="s">
-        <v>7</v>
+      <c r="G62" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1817,8 +2006,11 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1840,8 +2032,11 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1863,8 +2058,11 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1886,8 +2084,11 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1909,8 +2110,11 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1932,8 +2136,11 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -1955,8 +2162,11 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1978,8 +2188,11 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -2001,8 +2214,11 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2024,8 +2240,11 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2047,8 +2266,11 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -2070,8 +2292,11 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -2093,8 +2318,11 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -2116,8 +2344,11 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2139,8 +2370,11 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -2162,8 +2396,11 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -2185,8 +2422,11 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2208,8 +2448,11 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
+      <c r="G80" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -2231,8 +2474,11 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2254,8 +2500,11 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2277,8 +2526,11 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2300,8 +2552,11 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2323,8 +2578,11 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2346,8 +2604,11 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -2369,8 +2630,11 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -2392,8 +2656,11 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2415,8 +2682,11 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -2438,8 +2708,11 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2461,8 +2734,11 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2484,8 +2760,11 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2507,8 +2786,11 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2530,8 +2812,11 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2553,8 +2838,11 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2576,8 +2864,11 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2599,8 +2890,11 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="s">
-        <v>7</v>
+      <c r="G97" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2622,8 +2916,11 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="s">
-        <v>7</v>
+      <c r="G98" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -2645,8 +2942,11 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -2668,8 +2968,11 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -2691,8 +2994,11 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2714,8 +3020,11 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2737,8 +3046,11 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -2760,8 +3072,11 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -2783,8 +3098,11 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2806,8 +3124,11 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="s">
-        <v>7</v>
+      <c r="G106" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -2829,8 +3150,11 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -2852,8 +3176,11 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -2875,8 +3202,11 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2898,8 +3228,11 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -2921,8 +3254,11 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -2944,8 +3280,11 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -2967,8 +3306,11 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2990,8 +3332,11 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3013,8 +3358,11 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -3036,8 +3384,11 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -3059,8 +3410,11 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -3082,8 +3436,11 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3105,8 +3462,11 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -3128,8 +3488,11 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -3151,8 +3514,11 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="G121" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3174,8 +3540,11 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -3197,8 +3566,11 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H123" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3220,8 +3592,11 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -3243,8 +3618,11 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H125" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3266,8 +3644,11 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H126" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -3289,8 +3670,11 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H127" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3312,8 +3696,11 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H128" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -3335,8 +3722,11 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H129" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -3358,8 +3748,11 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H130" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -3381,8 +3774,11 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H131" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132">
@@ -3404,8 +3800,11 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H132" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -3427,8 +3826,11 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H133" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134">
@@ -3450,8 +3852,11 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -3473,8 +3878,11 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="s">
-        <v>7</v>
+      <c r="G135" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136">
@@ -3496,8 +3904,11 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="s">
-        <v>7</v>
+      <c r="G136" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137">
@@ -3519,8 +3930,11 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="s">
-        <v>7</v>
+      <c r="G137" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -3542,8 +3956,11 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3565,8 +3982,11 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140">
@@ -3588,8 +4008,11 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141">
@@ -3611,8 +4034,11 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -3634,8 +4060,11 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,8 +4086,11 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
@@ -3680,8 +4112,11 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -3703,8 +4138,11 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146">
@@ -3726,8 +4164,11 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3749,8 +4190,11 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148">
@@ -3772,8 +4216,11 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3795,8 +4242,11 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
+      <c r="G149" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150">
@@ -3818,8 +4268,11 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -3841,8 +4294,11 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
@@ -3864,8 +4320,11 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="s">
-        <v>7</v>
+      <c r="G152" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3887,8 +4346,11 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="s">
-        <v>7</v>
+      <c r="G153" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,8 +4372,11 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3933,8 +4398,11 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156">
@@ -3956,8 +4424,11 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -3979,8 +4450,11 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158">
@@ -4002,8 +4476,11 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -4025,8 +4502,11 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
+      <c r="G159" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -4048,8 +4528,11 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="s">
-        <v>7</v>
+      <c r="G160" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161">
@@ -4071,8 +4554,11 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="s">
-        <v>7</v>
+      <c r="G161" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162">
@@ -4094,8 +4580,11 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="s">
-        <v>7</v>
+      <c r="G162" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -4117,8 +4606,11 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="s">
-        <v>7</v>
+      <c r="G163" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -4140,8 +4632,11 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="s">
-        <v>7</v>
+      <c r="G164" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -4163,8 +4658,11 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="s">
-        <v>7</v>
+      <c r="G165" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -4186,8 +4684,11 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -4209,8 +4710,11 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -4232,8 +4736,11 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169">
@@ -4255,8 +4762,11 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4278,8 +4788,11 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H170" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -4301,8 +4814,11 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="s">
-        <v>7</v>
+      <c r="G171" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4324,8 +4840,11 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="s">
-        <v>7</v>
+      <c r="G172" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H172" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4347,8 +4866,11 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H173" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4370,8 +4892,11 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
+      <c r="G174" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H174" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -4393,8 +4918,11 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
+      <c r="G175" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H175" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176">
@@ -4416,8 +4944,11 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="s">
-        <v>7</v>
+      <c r="G176" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H176" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -4439,8 +4970,11 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="s">
-        <v>7</v>
+      <c r="G177" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H177" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -4462,8 +4996,11 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H178" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4485,8 +5022,11 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
+      <c r="G179" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H179" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4508,8 +5048,11 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="s">
-        <v>7</v>
+      <c r="G180" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H180" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
@@ -4531,8 +5074,11 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="s">
-        <v>7</v>
+      <c r="G181" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H181" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182">
@@ -4554,8 +5100,11 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="s">
-        <v>7</v>
+      <c r="G182" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H182" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183">
@@ -4577,8 +5126,11 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="s">
-        <v>7</v>
+      <c r="G183" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H183" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
@@ -4600,8 +5152,11 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="s">
-        <v>7</v>
+      <c r="G184" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185">
@@ -4623,8 +5178,11 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="s">
-        <v>7</v>
+      <c r="G185" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H185" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186">
@@ -4646,8 +5204,11 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="s">
-        <v>7</v>
+      <c r="G186" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H186" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187">
@@ -4669,8 +5230,11 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="s">
-        <v>7</v>
+      <c r="G187" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H187" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4692,8 +5256,11 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="s">
-        <v>7</v>
+      <c r="G188" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H188" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189">
@@ -4715,8 +5282,11 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="s">
-        <v>7</v>
+      <c r="G189" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H189" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4738,8 +5308,11 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="s">
-        <v>7</v>
+      <c r="G190" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H190" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4761,8 +5334,11 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="s">
-        <v>7</v>
+      <c r="G191" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H191" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -4784,8 +5360,11 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="s">
-        <v>7</v>
+      <c r="G192" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H192" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4807,8 +5386,11 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="s">
-        <v>7</v>
+      <c r="G193" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H193" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194">
@@ -4830,8 +5412,11 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="s">
-        <v>7</v>
+      <c r="G194" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H194" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195">
@@ -4853,8 +5438,11 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="s">
-        <v>7</v>
+      <c r="G195" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H195" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -4876,8 +5464,11 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="s">
-        <v>7</v>
+      <c r="G196" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H196" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -4899,8 +5490,11 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="s">
-        <v>7</v>
+      <c r="G197" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -4922,8 +5516,11 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="s">
-        <v>7</v>
+      <c r="G198" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H198" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199">
@@ -4945,8 +5542,11 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="s">
-        <v>7</v>
+      <c r="G199" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H199" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -4968,8 +5568,11 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="s">
-        <v>7</v>
+      <c r="G200" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H200" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201">
@@ -4991,8 +5594,11 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="s">
-        <v>7</v>
+      <c r="G201" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H201" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -5014,8 +5620,11 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="s">
-        <v>7</v>
+      <c r="G202" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H202" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -5037,8 +5646,11 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="s">
-        <v>7</v>
+      <c r="G203" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -5060,8 +5672,11 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="s">
-        <v>7</v>
+      <c r="G204" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H204" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -5083,8 +5698,11 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="s">
-        <v>7</v>
+      <c r="G205" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H205" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -5106,8 +5724,11 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="s">
-        <v>7</v>
+      <c r="G206" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H206" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207">
@@ -5129,8 +5750,11 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="s">
-        <v>7</v>
+      <c r="G207" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H207" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -5152,8 +5776,11 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="s">
-        <v>7</v>
+      <c r="G208" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H208" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209">
@@ -5175,8 +5802,11 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="s">
-        <v>7</v>
+      <c r="G209" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H209" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -5198,8 +5828,11 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="s">
-        <v>7</v>
+      <c r="G210" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H210" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5221,8 +5854,11 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="s">
-        <v>7</v>
+      <c r="G211" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H211" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -5244,8 +5880,11 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="s">
-        <v>7</v>
+      <c r="G212" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H212" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213">
@@ -5267,8 +5906,11 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="s">
-        <v>7</v>
+      <c r="G213" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H213" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214">
@@ -5290,8 +5932,11 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="s">
-        <v>7</v>
+      <c r="G214" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H214" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5313,8 +5958,11 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="s">
-        <v>7</v>
+      <c r="G215" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H215" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5336,8 +5984,11 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="s">
-        <v>7</v>
+      <c r="G216" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H216" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -5359,8 +6010,11 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="s">
-        <v>7</v>
+      <c r="G217" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H217" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5382,8 +6036,11 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="s">
-        <v>7</v>
+      <c r="G218" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H218" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -5405,8 +6062,11 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="s">
-        <v>7</v>
+      <c r="G219" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H219" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -5428,8 +6088,11 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="s">
-        <v>7</v>
+      <c r="G220" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H220" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -5451,8 +6114,11 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="s">
-        <v>7</v>
+      <c r="G221" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H221" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222">
@@ -5474,8 +6140,11 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="s">
-        <v>7</v>
+      <c r="G222" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H222" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -5497,8 +6166,11 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="s">
-        <v>7</v>
+      <c r="G223" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H223" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224">
@@ -5520,8 +6192,11 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="s">
-        <v>7</v>
+      <c r="G224" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H224" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225">
@@ -5543,8 +6218,11 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="s">
-        <v>7</v>
+      <c r="G225" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H225" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -5566,8 +6244,11 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="s">
-        <v>7</v>
+      <c r="G226" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H226" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5589,8 +6270,11 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="s">
-        <v>7</v>
+      <c r="G227" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H227" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5612,8 +6296,11 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="s">
-        <v>7</v>
+      <c r="G228" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H228" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229">
@@ -5635,8 +6322,11 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="s">
-        <v>7</v>
+      <c r="G229" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H229" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5658,8 +6348,11 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="s">
-        <v>7</v>
+      <c r="G230" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H230" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5681,8 +6374,11 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="s">
-        <v>7</v>
+      <c r="G231" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H231" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5704,8 +6400,11 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="s">
-        <v>7</v>
+      <c r="G232" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H232" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5727,8 +6426,11 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="s">
-        <v>7</v>
+      <c r="G233" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H233" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234">
@@ -5750,8 +6452,11 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="s">
-        <v>7</v>
+      <c r="G234" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H234" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -5773,8 +6478,11 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="s">
-        <v>7</v>
+      <c r="G235" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H235" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -5796,8 +6504,11 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="s">
-        <v>7</v>
+      <c r="G236" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H236" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -5819,8 +6530,11 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="s">
-        <v>7</v>
+      <c r="G237" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H237" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -5842,8 +6556,11 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="s">
-        <v>7</v>
+      <c r="G238" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H238" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239">
@@ -5865,8 +6582,11 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="s">
-        <v>7</v>
+      <c r="G239" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H239" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5888,8 +6608,11 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="s">
-        <v>7</v>
+      <c r="G240" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H240" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -5911,8 +6634,11 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="s">
-        <v>7</v>
+      <c r="G241" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H241" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -5934,8 +6660,11 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="s">
-        <v>7</v>
+      <c r="G242" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H242" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5957,8 +6686,11 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="s">
-        <v>7</v>
+      <c r="G243" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H243" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -5980,8 +6712,11 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="s">
-        <v>7</v>
+      <c r="G244" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H244" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -6003,8 +6738,11 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="s">
-        <v>7</v>
+      <c r="G245" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H245" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6026,8 +6764,11 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="s">
-        <v>7</v>
+      <c r="G246" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H246" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -6049,8 +6790,11 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="s">
-        <v>7</v>
+      <c r="G247" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H247" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -6072,8 +6816,11 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="s">
-        <v>7</v>
+      <c r="G248" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H248" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -6095,8 +6842,11 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="s">
-        <v>7</v>
+      <c r="G249" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H249" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -6118,8 +6868,11 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="s">
-        <v>7</v>
+      <c r="G250" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H250" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251">
@@ -6141,8 +6894,11 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="s">
-        <v>7</v>
+      <c r="G251" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H251" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6164,8 +6920,11 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="s">
-        <v>7</v>
+      <c r="G252" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H252" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6187,8 +6946,11 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="s">
-        <v>7</v>
+      <c r="G253" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H253" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6210,8 +6972,11 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="s">
-        <v>7</v>
+      <c r="G254" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H254" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6233,8 +6998,11 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="s">
-        <v>7</v>
+      <c r="G255" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6256,8 +7024,11 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="s">
-        <v>7</v>
+      <c r="G256" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257">
@@ -6279,8 +7050,11 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="s">
-        <v>7</v>
+      <c r="G257" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6302,8 +7076,11 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="s">
-        <v>7</v>
+      <c r="G258" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259">
@@ -6325,8 +7102,11 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="s">
-        <v>7</v>
+      <c r="G259" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H259" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260">
@@ -6348,8 +7128,11 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="s">
-        <v>7</v>
+      <c r="G260" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H260" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261">
@@ -6371,8 +7154,11 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="s">
-        <v>7</v>
+      <c r="G261" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H261" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -6394,8 +7180,11 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="s">
-        <v>7</v>
+      <c r="G262" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H262" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263">
@@ -6417,8 +7206,11 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="s">
-        <v>7</v>
+      <c r="G263" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H263" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264">
@@ -6440,8 +7232,11 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="s">
-        <v>7</v>
+      <c r="G264" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H264" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265">
@@ -6463,8 +7258,11 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="s">
-        <v>7</v>
+      <c r="G265" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H265" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -6486,8 +7284,11 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="s">
-        <v>7</v>
+      <c r="G266" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H266" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6509,8 +7310,11 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="s">
-        <v>7</v>
+      <c r="G267" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H267" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -6532,8 +7336,11 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="s">
-        <v>7</v>
+      <c r="G268" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H268" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -6555,8 +7362,11 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="s">
-        <v>7</v>
+      <c r="G269" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H269" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -6578,8 +7388,11 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="s">
-        <v>7</v>
+      <c r="G270" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H270" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271">
@@ -6601,8 +7414,11 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="s">
-        <v>7</v>
+      <c r="G271" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H271" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -6624,8 +7440,11 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="s">
-        <v>7</v>
+      <c r="G272" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H272" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -6647,8 +7466,11 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
+      <c r="G273" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H273" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6670,8 +7492,11 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="s">
-        <v>7</v>
+      <c r="G274" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H274" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -6693,8 +7518,11 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="s">
-        <v>7</v>
+      <c r="G275" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H275" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6716,8 +7544,11 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="s">
-        <v>7</v>
+      <c r="G276" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H276" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6739,8 +7570,11 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="s">
-        <v>7</v>
+      <c r="G277" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H277" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6762,8 +7596,11 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="s">
-        <v>7</v>
+      <c r="G278" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H278" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6785,8 +7622,11 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="s">
-        <v>7</v>
+      <c r="G279" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H279" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -6808,8 +7648,11 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="s">
-        <v>7</v>
+      <c r="G280" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H280" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -6831,8 +7674,11 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="s">
-        <v>7</v>
+      <c r="G281" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H281" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6854,8 +7700,11 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="s">
-        <v>7</v>
+      <c r="G282" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H282" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -6877,8 +7726,11 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="s">
-        <v>7</v>
+      <c r="G283" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H283" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284">
@@ -6900,8 +7752,11 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="s">
-        <v>7</v>
+      <c r="G284" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H284" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -6923,8 +7778,11 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="s">
-        <v>7</v>
+      <c r="G285" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H285" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6946,8 +7804,11 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="s">
-        <v>7</v>
+      <c r="G286" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H286" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6969,8 +7830,11 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="s">
-        <v>7</v>
+      <c r="G287" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H287" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6992,8 +7856,11 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="s">
-        <v>7</v>
+      <c r="G288" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H288" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -7015,8 +7882,11 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="s">
-        <v>7</v>
+      <c r="G289" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H289" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -7038,8 +7908,11 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="s">
-        <v>7</v>
+      <c r="G290" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H290" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7061,8 +7934,11 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="s">
-        <v>7</v>
+      <c r="G291" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H291" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -7084,8 +7960,11 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="s">
-        <v>7</v>
+      <c r="G292" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H292" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -7107,8 +7986,11 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="s">
-        <v>7</v>
+      <c r="G293" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H293" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -7130,8 +8012,11 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="s">
-        <v>7</v>
+      <c r="G294" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H294" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295">
@@ -7153,8 +8038,11 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="s">
-        <v>7</v>
+      <c r="G295" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H295" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -7176,8 +8064,11 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="s">
-        <v>7</v>
+      <c r="G296" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H296" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -7199,8 +8090,11 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="s">
-        <v>7</v>
+      <c r="G297" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H297" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -7222,8 +8116,11 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="s">
-        <v>7</v>
+      <c r="G298" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -7245,8 +8142,11 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="s">
-        <v>7</v>
+      <c r="G299" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H299" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -7268,8 +8168,11 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="s">
-        <v>7</v>
+      <c r="G300" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H300" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -7291,8 +8194,11 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="s">
-        <v>7</v>
+      <c r="G301" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H301" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7314,8 +8220,11 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="s">
-        <v>7</v>
+      <c r="G302" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H302" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -7337,8 +8246,11 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="s">
-        <v>7</v>
+      <c r="G303" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H303" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7360,8 +8272,11 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="s">
-        <v>7</v>
+      <c r="G304" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H304" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305">
@@ -7383,8 +8298,11 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="s">
-        <v>7</v>
+      <c r="G305" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H305" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -7406,8 +8324,11 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="s">
-        <v>7</v>
+      <c r="G306" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H306" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307">
@@ -7429,8 +8350,11 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="s">
-        <v>7</v>
+      <c r="G307" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H307" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308">
@@ -7452,8 +8376,11 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="s">
-        <v>7</v>
+      <c r="G308" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H308" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309">
@@ -7475,8 +8402,11 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="s">
-        <v>7</v>
+      <c r="G309" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H309" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310">
@@ -7498,8 +8428,11 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="s">
-        <v>7</v>
+      <c r="G310" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H310" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -7521,8 +8454,11 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="s">
-        <v>7</v>
+      <c r="G311" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H311" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -7544,8 +8480,11 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="s">
-        <v>7</v>
+      <c r="G312" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H312" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -7567,8 +8506,11 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="s">
-        <v>7</v>
+      <c r="G313" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H313" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7590,8 +8532,11 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="s">
-        <v>7</v>
+      <c r="G314" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H314" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315">
@@ -7613,8 +8558,11 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="s">
-        <v>7</v>
+      <c r="G315" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H315" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -7636,8 +8584,11 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="s">
-        <v>7</v>
+      <c r="G316" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H316" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -7659,8 +8610,11 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="s">
-        <v>7</v>
+      <c r="G317" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H317" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7682,8 +8636,11 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="s">
-        <v>7</v>
+      <c r="G318" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H318" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319">
@@ -7705,8 +8662,11 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="s">
-        <v>7</v>
+      <c r="G319" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H319" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -7728,8 +8688,11 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="s">
-        <v>7</v>
+      <c r="G320" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H320" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -7751,8 +8714,11 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="s">
-        <v>7</v>
+      <c r="G321" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H321" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -7774,8 +8740,11 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="s">
-        <v>7</v>
+      <c r="G322" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H322" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -7797,8 +8766,11 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="s">
-        <v>7</v>
+      <c r="G323" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H323" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7820,8 +8792,11 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="s">
-        <v>7</v>
+      <c r="G324" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H324" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7843,8 +8818,11 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="s">
-        <v>7</v>
+      <c r="G325" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H325" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -7866,8 +8844,11 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="s">
-        <v>7</v>
+      <c r="G326" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H326" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327">
@@ -7889,8 +8870,11 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="s">
-        <v>7</v>
+      <c r="G327" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H327" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7912,8 +8896,11 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="s">
-        <v>7</v>
+      <c r="G328" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H328" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329">
@@ -7935,8 +8922,11 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="s">
-        <v>7</v>
+      <c r="G329" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H329" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7958,8 +8948,11 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="s">
-        <v>7</v>
+      <c r="G330" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H330" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -7981,8 +8974,11 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="s">
-        <v>7</v>
+      <c r="G331" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332">
@@ -8004,8 +9000,11 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="s">
-        <v>7</v>
+      <c r="G332" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H332" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8027,8 +9026,11 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="s">
-        <v>7</v>
+      <c r="G333" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H333" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -8050,8 +9052,11 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="s">
-        <v>7</v>
+      <c r="G334" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H334" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -8073,8 +9078,11 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="s">
-        <v>7</v>
+      <c r="G335" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H335" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -8096,8 +9104,11 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="s">
-        <v>7</v>
+      <c r="G336" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H336" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8119,8 +9130,11 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="s">
-        <v>7</v>
+      <c r="G337" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H337" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338">
@@ -8142,8 +9156,11 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="s">
-        <v>7</v>
+      <c r="G338" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H338" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339">
@@ -8165,8 +9182,11 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="s">
-        <v>7</v>
+      <c r="G339" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H339" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -8188,8 +9208,11 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="s">
-        <v>7</v>
+      <c r="G340" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H340" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -8211,8 +9234,11 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="s">
-        <v>7</v>
+      <c r="G341" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H341" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342">
@@ -8234,8 +9260,11 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="s">
-        <v>7</v>
+      <c r="G342" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H342" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343">
@@ -8257,8 +9286,11 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="s">
-        <v>7</v>
+      <c r="G343" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H343" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344">
@@ -8280,8 +9312,11 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="s">
-        <v>7</v>
+      <c r="G344" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H344" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -8303,8 +9338,11 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="s">
-        <v>7</v>
+      <c r="G345" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H345" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -8326,8 +9364,11 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="s">
-        <v>7</v>
+      <c r="G346" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H346" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -8349,8 +9390,11 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="s">
-        <v>7</v>
+      <c r="G347" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H347" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348">
@@ -8372,8 +9416,11 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="s">
-        <v>7</v>
+      <c r="G348" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H348" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349">
@@ -8395,8 +9442,11 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="s">
-        <v>7</v>
+      <c r="G349" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H349" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -8418,8 +9468,11 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="s">
-        <v>7</v>
+      <c r="G350" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H350" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351">
@@ -8441,8 +9494,11 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="s">
-        <v>7</v>
+      <c r="G351" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H351" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8464,8 +9520,11 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="s">
-        <v>7</v>
+      <c r="G352" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H352" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -8487,8 +9546,11 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="s">
-        <v>7</v>
+      <c r="G353" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H353" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354">
@@ -8510,8 +9572,11 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="s">
-        <v>7</v>
+      <c r="G354" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H354" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8533,8 +9598,11 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="s">
-        <v>7</v>
+      <c r="G355" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H355" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -8556,8 +9624,11 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="s">
-        <v>7</v>
+      <c r="G356" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H356" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8579,8 +9650,11 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="s">
-        <v>7</v>
+      <c r="G357" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H357" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -8602,8 +9676,11 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="s">
-        <v>7</v>
+      <c r="G358" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H358" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359">
@@ -8625,8 +9702,11 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="s">
-        <v>7</v>
+      <c r="G359" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H359" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8648,8 +9728,11 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="s">
-        <v>7</v>
+      <c r="G360" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H360" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361">
@@ -8671,8 +9754,11 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="s">
-        <v>7</v>
+      <c r="G361" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H361" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362">
@@ -8694,8 +9780,11 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="s">
-        <v>7</v>
+      <c r="G362" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H362" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -8717,8 +9806,11 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="s">
-        <v>7</v>
+      <c r="G363" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H363" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8740,8 +9832,11 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="s">
-        <v>7</v>
+      <c r="G364" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H364" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8763,8 +9858,11 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="s">
-        <v>7</v>
+      <c r="G365" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H365" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8786,8 +9884,11 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="s">
-        <v>7</v>
+      <c r="G366" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H366" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8809,8 +9910,11 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="s">
-        <v>7</v>
+      <c r="G367" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H367" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8832,8 +9936,11 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="s">
-        <v>7</v>
+      <c r="G368" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H368" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -8855,8 +9962,11 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="s">
-        <v>7</v>
+      <c r="G369" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H369" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8878,8 +9988,11 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="s">
-        <v>7</v>
+      <c r="G370" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H370" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8901,8 +10014,11 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="s">
-        <v>7</v>
+      <c r="G371" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H371" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8924,8 +10040,11 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="s">
-        <v>7</v>
+      <c r="G372" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H372" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -8947,8 +10066,11 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="s">
-        <v>7</v>
+      <c r="G373" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H373" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8970,8 +10092,11 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="s">
-        <v>7</v>
+      <c r="G374" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H374" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8993,8 +10118,11 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="s">
-        <v>7</v>
+      <c r="G375" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H375" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -9016,8 +10144,11 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="s">
-        <v>7</v>
+      <c r="G376" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H376" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -9039,8 +10170,11 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="s">
-        <v>7</v>
+      <c r="G377" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H377" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -9062,8 +10196,11 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="s">
-        <v>7</v>
+      <c r="G378" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H378" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -9085,8 +10222,11 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="s">
-        <v>7</v>
+      <c r="G379" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H379" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -9108,8 +10248,11 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="s">
-        <v>7</v>
+      <c r="G380" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H380" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -9131,8 +10274,11 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="s">
-        <v>7</v>
+      <c r="G381" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H381" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -9154,8 +10300,11 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="s">
-        <v>7</v>
+      <c r="G382" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H382" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -9177,8 +10326,11 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="s">
-        <v>7</v>
+      <c r="G383" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H383" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -9200,8 +10352,11 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="s">
-        <v>7</v>
+      <c r="G384" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H384" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -9223,8 +10378,11 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="s">
-        <v>7</v>
+      <c r="G385" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H385" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -9246,8 +10404,11 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="s">
-        <v>7</v>
+      <c r="G386" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H386" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -9269,8 +10430,11 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="s">
-        <v>7</v>
+      <c r="G387" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H387" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -9292,8 +10456,11 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="s">
-        <v>7</v>
+      <c r="G388" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H388" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -9315,8 +10482,11 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="s">
-        <v>7</v>
+      <c r="G389" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H389" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -9338,8 +10508,11 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="s">
-        <v>7</v>
+      <c r="G390" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H390" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -9361,8 +10534,11 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="s">
-        <v>7</v>
+      <c r="G391" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H391" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -9384,8 +10560,11 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="s">
-        <v>7</v>
+      <c r="G392" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H392" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -9407,8 +10586,11 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="s">
-        <v>7</v>
+      <c r="G393" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H393" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -9430,8 +10612,11 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="s">
-        <v>7</v>
+      <c r="G394" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H394" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -9453,8 +10638,11 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="s">
-        <v>7</v>
+      <c r="G395" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H395" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -9476,8 +10664,11 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="s">
-        <v>7</v>
+      <c r="G396" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H396" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -9499,8 +10690,11 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="s">
-        <v>7</v>
+      <c r="G397" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H397" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -9522,8 +10716,11 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="s">
-        <v>7</v>
+      <c r="G398" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H398" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -9545,8 +10742,11 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="s">
-        <v>7</v>
+      <c r="G399" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H399" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -9568,8 +10768,11 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="s">
-        <v>7</v>
+      <c r="G400" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H400" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -9591,8 +10794,11 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="s">
-        <v>7</v>
+      <c r="G401" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H401" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -9614,8 +10820,11 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="s">
-        <v>7</v>
+      <c r="G402" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H402" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9637,8 +10846,11 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="s">
-        <v>7</v>
+      <c r="G403" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H403" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9660,8 +10872,11 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="s">
-        <v>7</v>
+      <c r="G404" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H404" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -9683,8 +10898,11 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="s">
-        <v>7</v>
+      <c r="G405" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H405" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9706,8 +10924,11 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="s">
-        <v>7</v>
+      <c r="G406" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H406" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -9729,8 +10950,11 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="s">
-        <v>7</v>
+      <c r="G407" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H407" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9752,8 +10976,11 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="s">
-        <v>7</v>
+      <c r="G408" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H408" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -9775,8 +11002,11 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="s">
-        <v>7</v>
+      <c r="G409" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H409" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9798,8 +11028,11 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="s">
-        <v>7</v>
+      <c r="G410" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H410" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9821,8 +11054,11 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="s">
-        <v>7</v>
+      <c r="G411" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H411" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9844,8 +11080,11 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="s">
-        <v>7</v>
+      <c r="G412" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H412" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9867,8 +11106,11 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="s">
-        <v>7</v>
+      <c r="G413" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H413" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -9890,8 +11132,11 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="s">
-        <v>7</v>
+      <c r="G414" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H414" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9913,8 +11158,11 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="s">
-        <v>7</v>
+      <c r="G415" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H415" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9936,8 +11184,11 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="s">
-        <v>7</v>
+      <c r="G416" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H416" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -9959,8 +11210,11 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="s">
-        <v>7</v>
+      <c r="G417" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H417" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -9982,8 +11236,11 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="s">
-        <v>7</v>
+      <c r="G418" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H418" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -10005,8 +11262,11 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="s">
-        <v>7</v>
+      <c r="G419" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H419" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -10028,8 +11288,11 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="s">
-        <v>7</v>
+      <c r="G420" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H420" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -10051,8 +11314,11 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="s">
-        <v>7</v>
+      <c r="G421" t="n">
+        <v>0.018673000857234</v>
+      </c>
+      <c r="H421" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -10074,8 +11340,11 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="s">
-        <v>7</v>
+      <c r="G422" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H422" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -10097,8 +11366,11 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="s">
-        <v>7</v>
+      <c r="G423" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H423" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -10120,8 +11392,11 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="s">
-        <v>7</v>
+      <c r="G424" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H424" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -10143,8 +11418,11 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="s">
-        <v>7</v>
+      <c r="G425" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H425" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -10166,8 +11444,11 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="s">
-        <v>7</v>
+      <c r="G426" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H426" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -10189,8 +11470,11 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="s">
-        <v>7</v>
+      <c r="G427" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H427" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -10212,8 +11496,11 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="s">
-        <v>7</v>
+      <c r="G428" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H428" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -10235,8 +11522,11 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="s">
-        <v>7</v>
+      <c r="G429" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H429" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -10258,8 +11548,11 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="s">
-        <v>7</v>
+      <c r="G430" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H430" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -10281,8 +11574,11 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="s">
-        <v>7</v>
+      <c r="G431" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H431" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -10304,8 +11600,11 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="s">
-        <v>7</v>
+      <c r="G432" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H432" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -10327,8 +11626,11 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="s">
-        <v>7</v>
+      <c r="G433" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H433" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -10350,8 +11652,11 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="s">
-        <v>7</v>
+      <c r="G434" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H434" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -10373,8 +11678,11 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="s">
-        <v>7</v>
+      <c r="G435" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H435" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -10396,8 +11704,11 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="s">
-        <v>7</v>
+      <c r="G436" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H436" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -10419,8 +11730,11 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="s">
-        <v>7</v>
+      <c r="G437" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H437" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -10442,8 +11756,11 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="s">
-        <v>7</v>
+      <c r="G438" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H438" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -10465,8 +11782,11 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="s">
-        <v>7</v>
+      <c r="G439" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H439" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -10488,8 +11808,11 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="s">
-        <v>7</v>
+      <c r="G440" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H440" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -10511,8 +11834,11 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="s">
-        <v>7</v>
+      <c r="G441" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H441" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -10534,8 +11860,11 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="s">
-        <v>7</v>
+      <c r="G442" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H442" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -10557,8 +11886,11 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="s">
-        <v>7</v>
+      <c r="G443" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H443" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -10580,8 +11912,11 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="s">
-        <v>7</v>
+      <c r="G444" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H444" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -10603,8 +11938,11 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="s">
-        <v>7</v>
+      <c r="G445" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H445" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -10626,8 +11964,11 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="s">
-        <v>7</v>
+      <c r="G446" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H446" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -10649,8 +11990,11 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="s">
-        <v>7</v>
+      <c r="G447" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H447" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -10672,8 +12016,11 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="s">
-        <v>7</v>
+      <c r="G448" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H448" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -10695,8 +12042,11 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="s">
-        <v>7</v>
+      <c r="G449" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H449" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -10718,8 +12068,11 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="s">
-        <v>7</v>
+      <c r="G450" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H450" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -10741,8 +12094,11 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="s">
-        <v>7</v>
+      <c r="G451" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H451" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10764,8 +12120,11 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="s">
-        <v>7</v>
+      <c r="G452" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H452" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10787,8 +12146,11 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="s">
-        <v>7</v>
+      <c r="G453" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H453" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -10810,8 +12172,11 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="s">
-        <v>7</v>
+      <c r="G454" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H454" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10833,8 +12198,11 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="s">
-        <v>7</v>
+      <c r="G455" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H455" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10856,8 +12224,11 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="s">
-        <v>7</v>
+      <c r="G456" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H456" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10879,8 +12250,11 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="s">
-        <v>7</v>
+      <c r="G457" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H457" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -10902,8 +12276,11 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="s">
-        <v>7</v>
+      <c r="G458" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H458" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -10925,8 +12302,11 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="s">
-        <v>7</v>
+      <c r="G459" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H459" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -10948,8 +12328,11 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="s">
-        <v>7</v>
+      <c r="G460" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H460" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -10971,8 +12354,11 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="s">
-        <v>7</v>
+      <c r="G461" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H461" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10994,8 +12380,11 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="s">
-        <v>7</v>
+      <c r="G462" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H462" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -11017,8 +12406,11 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="s">
-        <v>7</v>
+      <c r="G463" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H463" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -11040,8 +12432,11 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="s">
-        <v>7</v>
+      <c r="G464" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H464" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -11063,8 +12458,11 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="s">
-        <v>7</v>
+      <c r="G465" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H465" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -11086,8 +12484,11 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="s">
-        <v>7</v>
+      <c r="G466" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H466" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -11109,8 +12510,11 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="s">
-        <v>7</v>
+      <c r="G467" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H467" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -11132,8 +12536,11 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="s">
-        <v>7</v>
+      <c r="G468" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H468" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -11155,8 +12562,11 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="s">
-        <v>7</v>
+      <c r="G469" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -11178,8 +12588,11 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="s">
-        <v>7</v>
+      <c r="G470" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H470" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -11201,8 +12614,11 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="s">
-        <v>7</v>
+      <c r="G471" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H471" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -11224,8 +12640,11 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="s">
-        <v>7</v>
+      <c r="G472" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H472" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -11247,8 +12666,11 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="s">
-        <v>7</v>
+      <c r="G473" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H473" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -11270,8 +12692,11 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="s">
-        <v>7</v>
+      <c r="G474" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H474" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -11293,8 +12718,11 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="s">
-        <v>7</v>
+      <c r="G475" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H475" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -11316,8 +12744,11 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="s">
-        <v>7</v>
+      <c r="G476" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H476" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -11339,8 +12770,11 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="s">
-        <v>7</v>
+      <c r="G477" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H477" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -11362,8 +12796,11 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="s">
-        <v>7</v>
+      <c r="G478" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H478" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -11385,8 +12822,11 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="s">
-        <v>7</v>
+      <c r="G479" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H479" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -11408,8 +12848,11 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="s">
-        <v>7</v>
+      <c r="G480" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H480" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -11431,8 +12874,11 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="s">
-        <v>7</v>
+      <c r="G481" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H481" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -11454,8 +12900,11 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="s">
-        <v>7</v>
+      <c r="G482" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H482" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -11477,8 +12926,11 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="s">
-        <v>7</v>
+      <c r="G483" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H483" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -11500,8 +12952,11 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="s">
-        <v>7</v>
+      <c r="G484" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H484" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -11523,8 +12978,11 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="s">
-        <v>7</v>
+      <c r="G485" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H485" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -11546,8 +13004,11 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="s">
-        <v>7</v>
+      <c r="G486" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H486" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -11569,8 +13030,11 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="s">
-        <v>7</v>
+      <c r="G487" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H487" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="488">
@@ -11592,8 +13056,11 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="s">
-        <v>7</v>
+      <c r="G488" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H488" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -11615,8 +13082,11 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="s">
-        <v>7</v>
+      <c r="G489" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H489" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -11638,8 +13108,11 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="s">
-        <v>7</v>
+      <c r="G490" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H490" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -11661,8 +13134,11 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="s">
-        <v>7</v>
+      <c r="G491" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H491" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -11684,8 +13160,11 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="s">
-        <v>7</v>
+      <c r="G492" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H492" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -11707,8 +13186,11 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="s">
-        <v>7</v>
+      <c r="G493" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H493" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -11730,8 +13212,11 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="s">
-        <v>7</v>
+      <c r="G494" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H494" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -11753,8 +13238,11 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="s">
-        <v>7</v>
+      <c r="G495" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H495" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="496">
@@ -11776,8 +13264,11 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="s">
-        <v>7</v>
+      <c r="G496" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H496" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -11799,8 +13290,11 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="s">
-        <v>7</v>
+      <c r="G497" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H497" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="498">
@@ -11822,8 +13316,11 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="s">
-        <v>7</v>
+      <c r="G498" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H498" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="499">
@@ -11845,8 +13342,11 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="s">
-        <v>7</v>
+      <c r="G499" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H499" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="500">
@@ -11868,8 +13368,11 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="s">
-        <v>7</v>
+      <c r="G500" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H500" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="501">
@@ -11891,8 +13394,11 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="s">
-        <v>7</v>
+      <c r="G501" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H501" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="502">
@@ -11914,8 +13420,11 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="s">
-        <v>7</v>
+      <c r="G502" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H502" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="503">
@@ -11937,8 +13446,11 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="s">
-        <v>7</v>
+      <c r="G503" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H503" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="504">
@@ -11960,8 +13472,11 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="s">
-        <v>7</v>
+      <c r="G504" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H504" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11983,8 +13498,11 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="s">
-        <v>7</v>
+      <c r="G505" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H505" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -12006,8 +13524,11 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="s">
-        <v>7</v>
+      <c r="G506" t="n">
+        <v>0.0154079999774694</v>
+      </c>
+      <c r="H506" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="507">
@@ -12029,8 +13550,11 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="s">
-        <v>7</v>
+      <c r="G507" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H507" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="508">
@@ -12052,8 +13576,11 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="s">
-        <v>7</v>
+      <c r="G508" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H508" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -12075,8 +13602,11 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="s">
-        <v>7</v>
+      <c r="G509" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H509" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -12098,8 +13628,11 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="s">
-        <v>7</v>
+      <c r="G510" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H510" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="511">
@@ -12121,8 +13654,11 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="s">
-        <v>7</v>
+      <c r="G511" t="n">
+        <v>0.0153059996664524</v>
+      </c>
+      <c r="H511" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="512">
@@ -12144,8 +13680,11 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="s">
-        <v>7</v>
+      <c r="G512" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H512" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -12167,8 +13706,11 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="s">
-        <v>7</v>
+      <c r="G513" t="n">
+        <v>0.0151019999757409</v>
+      </c>
+      <c r="H513" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -12190,8 +13732,11 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="s">
-        <v>7</v>
+      <c r="G514" t="n">
+        <v>0.0152040002867579</v>
+      </c>
+      <c r="H514" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="515">
@@ -12213,8 +13758,11 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="s">
-        <v>7</v>
+      <c r="G515" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H515" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="516">
@@ -12236,8 +13784,11 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="s">
-        <v>7</v>
+      <c r="G516" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H516" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="517">
@@ -12259,8 +13810,11 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="s">
-        <v>7</v>
+      <c r="G517" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H517" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="518">
@@ -12282,8 +13836,11 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="s">
-        <v>7</v>
+      <c r="G518" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H518" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="519">
@@ -12305,8 +13862,11 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="s">
-        <v>7</v>
+      <c r="G519" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H519" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -12328,8 +13888,11 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="s">
-        <v>7</v>
+      <c r="G520" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H520" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="521">
@@ -12351,8 +13914,11 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="s">
-        <v>7</v>
+      <c r="G521" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H521" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="522">
@@ -12374,8 +13940,11 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="s">
-        <v>7</v>
+      <c r="G522" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H522" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="523">
@@ -12397,8 +13966,11 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="s">
-        <v>7</v>
+      <c r="G523" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H523" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="524">
@@ -12420,8 +13992,11 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="s">
-        <v>7</v>
+      <c r="G524" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H524" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="525">
@@ -12443,8 +14018,11 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="s">
-        <v>7</v>
+      <c r="G525" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H525" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -12466,8 +14044,11 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="s">
-        <v>7</v>
+      <c r="G526" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H526" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="527">
@@ -12489,8 +14070,11 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="s">
-        <v>7</v>
+      <c r="G527" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H527" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="528">
@@ -12512,8 +14096,11 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="s">
-        <v>7</v>
+      <c r="G528" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H528" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="529">
@@ -12535,8 +14122,11 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="s">
-        <v>7</v>
+      <c r="G529" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H529" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="530">
@@ -12558,8 +14148,11 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="s">
-        <v>7</v>
+      <c r="G530" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H530" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -12581,8 +14174,11 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="s">
-        <v>7</v>
+      <c r="G531" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H531" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -12604,8 +14200,11 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="s">
-        <v>7</v>
+      <c r="G532" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H532" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="533">
@@ -12627,8 +14226,11 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="s">
-        <v>7</v>
+      <c r="G533" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H533" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="534">
@@ -12650,8 +14252,11 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="s">
-        <v>7</v>
+      <c r="G534" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H534" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="535">
@@ -12673,8 +14278,11 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="s">
-        <v>7</v>
+      <c r="G535" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H535" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="536">
@@ -12696,8 +14304,11 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="s">
-        <v>7</v>
+      <c r="G536" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H536" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -12719,8 +14330,11 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="s">
-        <v>7</v>
+      <c r="G537" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H537" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="538">
@@ -12742,8 +14356,11 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="s">
-        <v>7</v>
+      <c r="G538" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H538" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="539">
@@ -12765,8 +14382,11 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="s">
-        <v>7</v>
+      <c r="G539" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H539" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="540">
@@ -12788,8 +14408,11 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="s">
-        <v>7</v>
+      <c r="G540" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H540" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="541">
@@ -12811,8 +14434,11 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="s">
-        <v>7</v>
+      <c r="G541" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H541" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="542">
@@ -12834,8 +14460,11 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="s">
-        <v>7</v>
+      <c r="G542" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H542" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="543">
@@ -12857,8 +14486,11 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="s">
-        <v>7</v>
+      <c r="G543" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H543" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="544">
@@ -12880,8 +14512,11 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="s">
-        <v>7</v>
+      <c r="G544" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H544" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="545">
@@ -12903,8 +14538,11 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="s">
-        <v>7</v>
+      <c r="G545" t="n">
+        <v>0.0155100002884865</v>
+      </c>
+      <c r="H545" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="546">
@@ -12926,8 +14564,11 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="s">
-        <v>7</v>
+      <c r="G546" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H546" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="547">
@@ -12949,8 +14590,11 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="s">
-        <v>7</v>
+      <c r="G547" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H547" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="548">
@@ -12972,8 +14616,11 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="s">
-        <v>7</v>
+      <c r="G548" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H548" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -12995,8 +14642,11 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="s">
-        <v>7</v>
+      <c r="G549" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H549" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="550">
@@ -13018,8 +14668,11 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="s">
-        <v>7</v>
+      <c r="G550" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H550" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="551">
@@ -13041,8 +14694,11 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="s">
-        <v>7</v>
+      <c r="G551" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H551" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="552">
@@ -13064,8 +14720,11 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="s">
-        <v>7</v>
+      <c r="G552" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H552" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="553">
@@ -13087,8 +14746,11 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="s">
-        <v>7</v>
+      <c r="G553" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H553" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="554">
@@ -13110,8 +14772,11 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="s">
-        <v>7</v>
+      <c r="G554" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H554" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -13133,8 +14798,11 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="s">
-        <v>7</v>
+      <c r="G555" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H555" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -13156,8 +14824,11 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="s">
-        <v>7</v>
+      <c r="G556" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H556" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="557">
@@ -13179,8 +14850,11 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="s">
-        <v>7</v>
+      <c r="G557" t="n">
+        <v>0.0164279993623495</v>
+      </c>
+      <c r="H557" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="558">
@@ -13202,8 +14876,11 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="s">
-        <v>7</v>
+      <c r="G558" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H558" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="559">
@@ -13225,8 +14902,11 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="s">
-        <v>7</v>
+      <c r="G559" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H559" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -13248,8 +14928,11 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="s">
-        <v>7</v>
+      <c r="G560" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H560" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="561">
@@ -13271,8 +14954,11 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="s">
-        <v>7</v>
+      <c r="G561" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H561" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="562">
@@ -13294,8 +14980,11 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="s">
-        <v>7</v>
+      <c r="G562" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H562" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="563">
@@ -13317,8 +15006,11 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="s">
-        <v>7</v>
+      <c r="G563" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H563" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="564">
@@ -13340,8 +15032,11 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="s">
-        <v>7</v>
+      <c r="G564" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H564" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="565">
@@ -13363,8 +15058,11 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="s">
-        <v>7</v>
+      <c r="G565" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H565" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -13386,8 +15084,11 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="s">
-        <v>7</v>
+      <c r="G566" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H566" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="567">
@@ -13409,8 +15110,11 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="s">
-        <v>7</v>
+      <c r="G567" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H567" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="568">
@@ -13432,8 +15136,11 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="s">
-        <v>7</v>
+      <c r="G568" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H568" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="569">
@@ -13455,8 +15162,11 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="s">
-        <v>7</v>
+      <c r="G569" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H569" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="570">
@@ -13478,8 +15188,11 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="s">
-        <v>7</v>
+      <c r="G570" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H570" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="571">
@@ -13501,8 +15214,11 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="s">
-        <v>7</v>
+      <c r="G571" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H571" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="572">
@@ -13524,8 +15240,11 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="s">
-        <v>7</v>
+      <c r="G572" t="n">
+        <v>0.0174480006098747</v>
+      </c>
+      <c r="H572" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="573">
@@ -13547,8 +15266,11 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="s">
-        <v>7</v>
+      <c r="G573" t="n">
+        <v>0.0175509992986917</v>
+      </c>
+      <c r="H573" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="574">
@@ -13570,8 +15292,11 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="s">
-        <v>7</v>
+      <c r="G574" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H574" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="575">
@@ -13593,8 +15318,11 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="s">
-        <v>7</v>
+      <c r="G575" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H575" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="576">
@@ -13616,8 +15344,11 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="s">
-        <v>7</v>
+      <c r="G576" t="n">
+        <v>0.0177549999207258</v>
+      </c>
+      <c r="H576" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="577">
@@ -13639,8 +15370,11 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="s">
-        <v>7</v>
+      <c r="G577" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H577" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="578">
@@ -13662,8 +15396,11 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="s">
-        <v>7</v>
+      <c r="G578" t="n">
+        <v>0.0175000000745058</v>
+      </c>
+      <c r="H578" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="579">
@@ -13685,8 +15422,11 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="s">
-        <v>7</v>
+      <c r="G579" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H579" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="580">
@@ -13708,8 +15448,11 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="s">
-        <v>7</v>
+      <c r="G580" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H580" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="581">
@@ -13731,8 +15474,11 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="s">
-        <v>7</v>
+      <c r="G581" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H581" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="582">
@@ -13754,8 +15500,11 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="s">
-        <v>7</v>
+      <c r="G582" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H582" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="583">
@@ -13777,8 +15526,11 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="s">
-        <v>7</v>
+      <c r="G583" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H583" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="584">
@@ -13800,8 +15552,11 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="s">
-        <v>7</v>
+      <c r="G584" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H584" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="585">
@@ -13823,8 +15578,11 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="s">
-        <v>7</v>
+      <c r="G585" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H585" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="586">
@@ -13846,8 +15604,11 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="s">
-        <v>7</v>
+      <c r="G586" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H586" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="587">
@@ -13869,8 +15630,11 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="s">
-        <v>7</v>
+      <c r="G587" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H587" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="588">
@@ -13892,8 +15656,11 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="s">
-        <v>7</v>
+      <c r="G588" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H588" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="589">
@@ -13915,8 +15682,11 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="s">
-        <v>7</v>
+      <c r="G589" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H589" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="590">
@@ -13938,8 +15708,11 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="s">
-        <v>7</v>
+      <c r="G590" t="n">
+        <v>0.0171000007539988</v>
+      </c>
+      <c r="H590" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -13961,8 +15734,11 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="s">
-        <v>7</v>
+      <c r="G591" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H591" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="592">
@@ -13984,8 +15760,11 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="s">
-        <v>7</v>
+      <c r="G592" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H592" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="593">
@@ -14007,8 +15786,11 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="s">
-        <v>7</v>
+      <c r="G593" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H593" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="594">
@@ -14030,8 +15812,11 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="s">
-        <v>7</v>
+      <c r="G594" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="H594" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="595">
@@ -14053,8 +15838,11 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="s">
-        <v>7</v>
+      <c r="G595" t="n">
+        <v>0.0203000009059906</v>
+      </c>
+      <c r="H595" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="596">
@@ -14076,8 +15864,11 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="s">
-        <v>7</v>
+      <c r="G596" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H596" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -14099,8 +15890,11 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="s">
-        <v>7</v>
+      <c r="G597" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H597" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="598">
@@ -14122,8 +15916,11 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="s">
-        <v>7</v>
+      <c r="G598" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H598" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="599">
@@ -14145,8 +15942,11 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="s">
-        <v>7</v>
+      <c r="G599" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H599" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="600">
@@ -14168,8 +15968,11 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="s">
-        <v>7</v>
+      <c r="G600" t="n">
+        <v>0.0183000005781651</v>
+      </c>
+      <c r="H600" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="601">
@@ -14191,8 +15994,11 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="s">
-        <v>7</v>
+      <c r="G601" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H601" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="602">
@@ -14214,8 +16020,11 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="s">
-        <v>7</v>
+      <c r="G602" t="n">
+        <v>0.0185000002384186</v>
+      </c>
+      <c r="H602" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="603">
@@ -14237,8 +16046,11 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="s">
-        <v>7</v>
+      <c r="G603" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H603" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="604">
@@ -14260,8 +16072,11 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="s">
-        <v>7</v>
+      <c r="G604" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="H604" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="605">
@@ -14283,8 +16098,11 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="s">
-        <v>7</v>
+      <c r="G605" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H605" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="606">
@@ -14306,8 +16124,11 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="s">
-        <v>7</v>
+      <c r="G606" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H606" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="607">
@@ -14329,8 +16150,11 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="s">
-        <v>7</v>
+      <c r="G607" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H607" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="608">
@@ -14352,8 +16176,11 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="s">
-        <v>7</v>
+      <c r="G608" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="H608" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="609">
@@ -14375,8 +16202,11 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="s">
-        <v>7</v>
+      <c r="G609" t="n">
+        <v>0.0181000009179115</v>
+      </c>
+      <c r="H609" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="610">
@@ -14398,8 +16228,11 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="s">
-        <v>7</v>
+      <c r="G610" t="n">
+        <v>0.0173000004142523</v>
+      </c>
+      <c r="H610" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="611">
@@ -14421,8 +16254,11 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="s">
-        <v>7</v>
+      <c r="G611" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H611" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="612">
@@ -14444,8 +16280,11 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="s">
-        <v>7</v>
+      <c r="G612" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H612" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="613">
@@ -14467,8 +16306,11 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="s">
-        <v>7</v>
+      <c r="G613" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="H613" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="614">
@@ -14490,8 +16332,11 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="s">
-        <v>7</v>
+      <c r="G614" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H614" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="615">
@@ -14513,8 +16358,11 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="s">
-        <v>7</v>
+      <c r="G615" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H615" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="616">
@@ -14536,8 +16384,11 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="s">
-        <v>7</v>
+      <c r="G616" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H616" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="617">
@@ -14559,8 +16410,11 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="s">
-        <v>7</v>
+      <c r="G617" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H617" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="618">
@@ -14582,8 +16436,11 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="s">
-        <v>7</v>
+      <c r="G618" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H618" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="619">
@@ -14605,8 +16462,11 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="s">
-        <v>7</v>
+      <c r="G619" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H619" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="620">
@@ -14628,8 +16488,11 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="s">
-        <v>7</v>
+      <c r="G620" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H620" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="621">
@@ -14651,8 +16514,11 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="s">
-        <v>7</v>
+      <c r="G621" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H621" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="622">
@@ -14674,8 +16540,11 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="s">
-        <v>7</v>
+      <c r="G622" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H622" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="623">
@@ -14697,8 +16566,11 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="s">
-        <v>7</v>
+      <c r="G623" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H623" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="624">
@@ -14720,8 +16592,11 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="s">
-        <v>7</v>
+      <c r="G624" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H624" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="625">
@@ -14743,8 +16618,11 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="s">
-        <v>7</v>
+      <c r="G625" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H625" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="626">
@@ -14766,8 +16644,11 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="s">
-        <v>7</v>
+      <c r="G626" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="H626" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="627">
@@ -14789,8 +16670,11 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="s">
-        <v>7</v>
+      <c r="G627" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H627" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="628">
@@ -14812,8 +16696,11 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="s">
-        <v>7</v>
+      <c r="G628" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H628" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="629">
@@ -14835,8 +16722,11 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="s">
-        <v>7</v>
+      <c r="G629" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H629" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="630">
@@ -14858,8 +16748,11 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="s">
-        <v>7</v>
+      <c r="G630" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H630" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="631">
@@ -14881,8 +16774,11 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="s">
-        <v>7</v>
+      <c r="G631" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H631" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="632">
@@ -14904,8 +16800,11 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="s">
-        <v>7</v>
+      <c r="G632" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H632" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="633">
@@ -14927,8 +16826,11 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="s">
-        <v>7</v>
+      <c r="G633" t="n">
+        <v>0.0172000005841255</v>
+      </c>
+      <c r="H633" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="634">
@@ -14950,8 +16852,11 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="s">
-        <v>7</v>
+      <c r="G634" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="H634" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="635">
@@ -14973,8 +16878,11 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="s">
-        <v>7</v>
+      <c r="G635" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H635" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="636">
@@ -14996,8 +16904,11 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="s">
-        <v>7</v>
+      <c r="G636" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H636" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="637">
@@ -15019,8 +16930,11 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="s">
-        <v>7</v>
+      <c r="G637" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="H637" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="638">
@@ -15042,8 +16956,11 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="s">
-        <v>7</v>
+      <c r="G638" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H638" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="639">
@@ -15065,8 +16982,11 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="s">
-        <v>7</v>
+      <c r="G639" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H639" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="640">
@@ -15088,8 +17008,11 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="s">
-        <v>7</v>
+      <c r="G640" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H640" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="641">
@@ -15111,8 +17034,11 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="s">
-        <v>7</v>
+      <c r="G641" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H641" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="642">
@@ -15134,8 +17060,11 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="s">
-        <v>7</v>
+      <c r="G642" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H642" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="643">
@@ -15157,8 +17086,11 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="s">
-        <v>7</v>
+      <c r="G643" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H643" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="644">
@@ -15180,8 +17112,11 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="s">
-        <v>7</v>
+      <c r="G644" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H644" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="645">
@@ -15203,8 +17138,11 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="s">
-        <v>7</v>
+      <c r="G645" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H645" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="646">
@@ -15226,8 +17164,11 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="s">
-        <v>7</v>
+      <c r="G646" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H646" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="647">
@@ -15249,8 +17190,11 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="s">
-        <v>7</v>
+      <c r="G647" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H647" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="648">
@@ -15272,8 +17216,11 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="s">
-        <v>7</v>
+      <c r="G648" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H648" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="649">
@@ -15295,8 +17242,11 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="s">
-        <v>7</v>
+      <c r="G649" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H649" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="650">
@@ -15318,8 +17268,11 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="s">
-        <v>7</v>
+      <c r="G650" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H650" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="651">
@@ -15341,8 +17294,11 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="s">
-        <v>7</v>
+      <c r="G651" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H651" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="652">
@@ -15364,8 +17320,11 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="s">
-        <v>7</v>
+      <c r="G652" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H652" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="653">
@@ -15387,8 +17346,11 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="s">
-        <v>7</v>
+      <c r="G653" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H653" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="654">
@@ -15410,8 +17372,11 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="s">
-        <v>7</v>
+      <c r="G654" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H654" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="655">
@@ -15433,8 +17398,11 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="s">
-        <v>7</v>
+      <c r="G655" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H655" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="656">
@@ -15456,8 +17424,11 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="s">
-        <v>7</v>
+      <c r="G656" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H656" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="657">
@@ -15479,8 +17450,11 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="s">
-        <v>7</v>
+      <c r="G657" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H657" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="658">
@@ -15502,8 +17476,11 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="s">
-        <v>7</v>
+      <c r="G658" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H658" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="659">
@@ -15525,8 +17502,11 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="s">
-        <v>7</v>
+      <c r="G659" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H659" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="660">
@@ -15548,8 +17528,11 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="s">
-        <v>7</v>
+      <c r="G660" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H660" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="661">
@@ -15571,8 +17554,11 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="s">
-        <v>7</v>
+      <c r="G661" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H661" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="662">
@@ -15594,8 +17580,11 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="s">
-        <v>7</v>
+      <c r="G662" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H662" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="663">
@@ -15617,8 +17606,11 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="s">
-        <v>7</v>
+      <c r="G663" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H663" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="664">
@@ -15640,8 +17632,11 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="s">
-        <v>7</v>
+      <c r="G664" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H664" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="665">
@@ -15663,8 +17658,11 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="s">
-        <v>7</v>
+      <c r="G665" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H665" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="666">
@@ -15686,8 +17684,11 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="s">
-        <v>7</v>
+      <c r="G666" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H666" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="667">
@@ -15709,8 +17710,11 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="s">
-        <v>7</v>
+      <c r="G667" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H667" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="668">
@@ -15732,8 +17736,11 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="s">
-        <v>7</v>
+      <c r="G668" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H668" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="669">
@@ -15755,8 +17762,11 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="s">
-        <v>7</v>
+      <c r="G669" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H669" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="670">
@@ -15778,8 +17788,11 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="s">
-        <v>7</v>
+      <c r="G670" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="H670" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="671">
@@ -15801,8 +17814,11 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="s">
-        <v>7</v>
+      <c r="G671" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="H671" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="672">
@@ -15824,8 +17840,11 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="s">
-        <v>7</v>
+      <c r="G672" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="H672" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="673">
@@ -15847,8 +17866,11 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="s">
-        <v>7</v>
+      <c r="G673" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H673" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="674">
@@ -15870,8 +17892,11 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="s">
-        <v>7</v>
+      <c r="G674" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="H674" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="675">
@@ -15893,8 +17918,11 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="s">
-        <v>7</v>
+      <c r="G675" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="H675" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="676">
@@ -15916,8 +17944,11 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="s">
-        <v>7</v>
+      <c r="G676" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="H676" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="677">
@@ -15939,8 +17970,11 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="s">
-        <v>7</v>
+      <c r="G677" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H677" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="678">
@@ -15962,8 +17996,11 @@
       <c r="F678" t="n">
         <v>0.0221999995410442</v>
       </c>
-      <c r="G678" t="s">
-        <v>7</v>
+      <c r="G678" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="H678" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="679">
@@ -15985,8 +18022,11 @@
       <c r="F679" t="n">
         <v>0.0233999993652105</v>
       </c>
-      <c r="G679" t="s">
-        <v>7</v>
+      <c r="G679" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="H679" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="680">
@@ -16008,8 +18048,11 @@
       <c r="F680" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G680" t="s">
-        <v>7</v>
+      <c r="G680" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H680" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="681">
@@ -16031,8 +18074,11 @@
       <c r="F681" t="n">
         <v>0.0240000002086163</v>
       </c>
-      <c r="G681" t="s">
-        <v>7</v>
+      <c r="G681" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="H681" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="682">
@@ -16054,8 +18100,11 @@
       <c r="F682" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G682" t="s">
-        <v>7</v>
+      <c r="G682" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H682" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="683">
@@ -16077,8 +18126,11 @@
       <c r="F683" t="n">
         <v>0.0253999996930361</v>
       </c>
-      <c r="G683" t="s">
-        <v>7</v>
+      <c r="G683" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="H683" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="684">
@@ -16100,8 +18152,11 @@
       <c r="F684" t="n">
         <v>0.0252000000327826</v>
       </c>
-      <c r="G684" t="s">
-        <v>7</v>
+      <c r="G684" t="n">
+        <v>0.0252000000327826</v>
+      </c>
+      <c r="H684" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="685">
@@ -16123,8 +18178,11 @@
       <c r="F685" t="n">
         <v>0.0248000007122755</v>
       </c>
-      <c r="G685" t="s">
-        <v>7</v>
+      <c r="G685" t="n">
+        <v>0.0248000007122755</v>
+      </c>
+      <c r="H685" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="686">
@@ -16146,8 +18204,11 @@
       <c r="F686" t="n">
         <v>0.0238000005483627</v>
       </c>
-      <c r="G686" t="s">
-        <v>7</v>
+      <c r="G686" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="H686" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="687">
@@ -16166,9 +18227,14 @@
       <c r="E687" t="n">
         <v>0.0236000008881092</v>
       </c>
-      <c r="F687"/>
-      <c r="G687" t="s">
-        <v>7</v>
+      <c r="F687" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="G687" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="H687" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -397,9 +394,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -420,11 +414,8 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -446,11 +437,8 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +460,8 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +483,8 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -524,11 +506,8 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -550,11 +529,8 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -576,11 +552,8 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
+      <c r="G8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -602,11 +575,8 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -628,11 +598,8 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+      <c r="G10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -654,11 +621,8 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
+      <c r="G11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -680,11 +644,8 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -706,11 +667,8 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -732,11 +690,8 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H14" t="s">
-        <v>8</v>
+      <c r="G14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -758,11 +713,8 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -784,11 +736,8 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
+      <c r="G16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -810,11 +759,8 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+      <c r="G17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -836,11 +782,8 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -862,11 +805,8 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -888,11 +828,8 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+      <c r="G20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -914,11 +851,8 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H21" t="s">
-        <v>8</v>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -940,11 +874,8 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
+      <c r="G22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -966,11 +897,8 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
+      <c r="G23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -992,11 +920,8 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1018,11 +943,8 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
+      <c r="G25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1044,11 +966,8 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0203060004860163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>8</v>
+      <c r="G26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1070,11 +989,8 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.019845999777317</v>
-      </c>
-      <c r="H27" t="s">
-        <v>8</v>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1096,11 +1012,8 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H28" t="s">
-        <v>8</v>
+      <c r="G28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1122,11 +1035,8 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>8</v>
+      <c r="G29" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1148,11 +1058,8 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.01923399977386</v>
-      </c>
-      <c r="H30" t="s">
-        <v>8</v>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1174,11 +1081,8 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+      <c r="G31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1200,11 +1104,8 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+      <c r="G32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1127,8 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1252,11 +1150,8 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="G34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1278,11 +1173,8 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1304,11 +1196,8 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H36" t="s">
-        <v>8</v>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1330,11 +1219,8 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H37" t="s">
-        <v>8</v>
+      <c r="G37" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1356,11 +1242,8 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H38" t="s">
-        <v>8</v>
+      <c r="G38" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1382,11 +1265,8 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H39" t="s">
-        <v>8</v>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1408,11 +1288,8 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
+      <c r="G40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1434,11 +1311,8 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
+      <c r="G41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1460,11 +1334,8 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1486,11 +1357,8 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.0191319994628429</v>
-      </c>
-      <c r="H43" t="s">
-        <v>8</v>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1512,11 +1380,8 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H44" t="s">
-        <v>8</v>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1538,11 +1403,8 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H45" t="s">
-        <v>8</v>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1564,11 +1426,8 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H46" t="s">
-        <v>8</v>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1590,11 +1449,8 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H47" t="s">
-        <v>8</v>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1616,11 +1472,8 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H48" t="s">
-        <v>8</v>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1642,11 +1495,8 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H49" t="s">
-        <v>8</v>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1668,11 +1518,8 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H50" t="s">
-        <v>8</v>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1694,11 +1541,8 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H51" t="s">
-        <v>8</v>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1720,11 +1564,8 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H52" t="s">
-        <v>8</v>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1746,11 +1587,8 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H53" t="s">
-        <v>8</v>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,11 +1610,8 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H54" t="s">
-        <v>8</v>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1798,11 +1633,8 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H55" t="s">
-        <v>8</v>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1824,11 +1656,8 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H56" t="s">
-        <v>8</v>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -1850,11 +1679,8 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H57" t="s">
-        <v>8</v>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1876,11 +1702,8 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H58" t="s">
-        <v>8</v>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1902,11 +1725,8 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H59" t="s">
-        <v>8</v>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1928,11 +1748,8 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H60" t="s">
-        <v>8</v>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1954,11 +1771,8 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1980,11 +1794,8 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H62" t="s">
-        <v>8</v>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2006,11 +1817,8 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H63" t="s">
-        <v>8</v>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2032,11 +1840,8 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H64" t="s">
-        <v>8</v>
+      <c r="G64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2058,11 +1863,8 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H65" t="s">
-        <v>8</v>
+      <c r="G65" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2084,11 +1886,8 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H66" t="s">
-        <v>8</v>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2110,11 +1909,8 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H67" t="s">
-        <v>8</v>
+      <c r="G67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2136,11 +1932,8 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H68" t="s">
-        <v>8</v>
+      <c r="G68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2162,11 +1955,8 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H69" t="s">
-        <v>8</v>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -2188,11 +1978,8 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H70" t="s">
-        <v>8</v>
+      <c r="G70" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2214,11 +2001,8 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H71" t="s">
-        <v>8</v>
+      <c r="G71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2240,11 +2024,8 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H72" t="s">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2266,11 +2047,8 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H73" t="s">
-        <v>8</v>
+      <c r="G73" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -2292,11 +2070,8 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="G74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2318,11 +2093,8 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H75" t="s">
-        <v>8</v>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2344,11 +2116,8 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="G76" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2370,11 +2139,8 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H77" t="s">
-        <v>8</v>
+      <c r="G77" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2396,11 +2162,8 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2422,11 +2185,8 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H79" t="s">
-        <v>8</v>
+      <c r="G79" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2448,11 +2208,8 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+      <c r="G80" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2474,11 +2231,8 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H81" t="s">
-        <v>8</v>
+      <c r="G81" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2500,11 +2254,8 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+      <c r="G82" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2526,11 +2277,8 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H83" t="s">
-        <v>8</v>
+      <c r="G83" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2552,11 +2300,8 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H84" t="s">
-        <v>8</v>
+      <c r="G84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2578,11 +2323,8 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H85" t="s">
-        <v>8</v>
+      <c r="G85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2604,11 +2346,8 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H86" t="s">
-        <v>8</v>
+      <c r="G86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -2630,11 +2369,8 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>8</v>
+      <c r="G87" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2656,11 +2392,8 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>8</v>
+      <c r="G88" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2682,11 +2415,8 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H89" t="s">
-        <v>8</v>
+      <c r="G89" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -2708,11 +2438,8 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="G90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2734,11 +2461,8 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H91" t="s">
-        <v>8</v>
+      <c r="G91" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2760,11 +2484,8 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.0202040001749992</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="G92" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2786,11 +2507,8 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H93" t="s">
-        <v>8</v>
+      <c r="G93" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -2812,11 +2530,8 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H94" t="s">
-        <v>8</v>
+      <c r="G94" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2838,11 +2553,8 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="G95" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2864,11 +2576,8 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H96" t="s">
-        <v>8</v>
+      <c r="G96" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2890,11 +2599,8 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+      <c r="G97" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -2916,11 +2622,8 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H98" t="s">
-        <v>8</v>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2942,11 +2645,8 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="G99" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2668,8 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H100" t="s">
-        <v>8</v>
+      <c r="G100" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2994,11 +2691,8 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H101" t="s">
-        <v>8</v>
+      <c r="G101" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3020,11 +2714,8 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H102" t="s">
-        <v>8</v>
+      <c r="G102" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3046,11 +2737,8 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="G103" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3072,11 +2760,8 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H104" t="s">
-        <v>8</v>
+      <c r="G104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3098,11 +2783,8 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H105" t="s">
-        <v>8</v>
+      <c r="G105" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3124,11 +2806,8 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H106" t="s">
-        <v>8</v>
+      <c r="G106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3150,11 +2829,8 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H107" t="s">
-        <v>8</v>
+      <c r="G107" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3176,11 +2852,8 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+      <c r="G108" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3202,11 +2875,8 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H109" t="s">
-        <v>8</v>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3228,11 +2898,8 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H110" t="s">
-        <v>8</v>
+      <c r="G110" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -3254,11 +2921,8 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H111" t="s">
-        <v>8</v>
+      <c r="G111" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -3280,11 +2944,8 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H112" t="s">
-        <v>8</v>
+      <c r="G112" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3306,11 +2967,8 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+      <c r="G113" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3332,11 +2990,8 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H114" t="s">
-        <v>8</v>
+      <c r="G114" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3358,11 +3013,8 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H115" t="s">
-        <v>8</v>
+      <c r="G115" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3384,11 +3036,8 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+      <c r="G116" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3410,11 +3059,8 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H117" t="s">
-        <v>8</v>
+      <c r="G117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3436,11 +3082,8 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H118" t="s">
-        <v>8</v>
+      <c r="G118" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3462,11 +3105,8 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H119" t="s">
-        <v>8</v>
+      <c r="G119" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -3488,11 +3128,8 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H120" t="s">
-        <v>8</v>
+      <c r="G120" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -3514,11 +3151,8 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
+      <c r="G121" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -3540,11 +3174,8 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H122" t="s">
-        <v>8</v>
+      <c r="G122" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -3566,11 +3197,8 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H123" t="s">
-        <v>8</v>
+      <c r="G123" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3592,11 +3220,8 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H124" t="s">
-        <v>8</v>
+      <c r="G124" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -3618,11 +3243,8 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H125" t="s">
-        <v>8</v>
+      <c r="G125" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -3644,11 +3266,8 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H126" t="s">
-        <v>8</v>
+      <c r="G126" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -3670,11 +3289,8 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H127" t="s">
-        <v>8</v>
+      <c r="G127" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3696,11 +3312,8 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H128" t="s">
-        <v>8</v>
+      <c r="G128" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="129">
@@ -3722,11 +3335,8 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H129" t="s">
-        <v>8</v>
+      <c r="G129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -3748,11 +3358,8 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H130" t="s">
-        <v>8</v>
+      <c r="G130" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3774,11 +3381,8 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H131" t="s">
-        <v>8</v>
+      <c r="G131" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -3800,11 +3404,8 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H132" t="s">
-        <v>8</v>
+      <c r="G132" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -3826,11 +3427,8 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H133" t="s">
-        <v>8</v>
+      <c r="G133" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -3852,11 +3450,8 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H134" t="s">
-        <v>8</v>
+      <c r="G134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3878,11 +3473,8 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H135" t="s">
-        <v>8</v>
+      <c r="G135" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="136">
@@ -3904,11 +3496,8 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H136" t="s">
-        <v>8</v>
+      <c r="G136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -3930,11 +3519,8 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H137" t="s">
-        <v>8</v>
+      <c r="G137" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3956,11 +3542,8 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H138" t="s">
-        <v>8</v>
+      <c r="G138" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3982,11 +3565,8 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>8</v>
+      <c r="G139" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -4008,11 +3588,8 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H140" t="s">
-        <v>8</v>
+      <c r="G140" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -4034,11 +3611,8 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H141" t="s">
-        <v>8</v>
+      <c r="G141" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -4060,11 +3634,8 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H142" t="s">
-        <v>8</v>
+      <c r="G142" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="143">
@@ -4086,11 +3657,8 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H143" t="s">
-        <v>8</v>
+      <c r="G143" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4112,11 +3680,8 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H144" t="s">
-        <v>8</v>
+      <c r="G144" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -4138,11 +3703,8 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H145" t="s">
-        <v>8</v>
+      <c r="G145" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -4164,11 +3726,8 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H146" t="s">
-        <v>8</v>
+      <c r="G146" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -4190,11 +3749,8 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H147" t="s">
-        <v>8</v>
+      <c r="G147" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -4216,11 +3772,8 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H148" t="s">
-        <v>8</v>
+      <c r="G148" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -4242,11 +3795,8 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H149" t="s">
-        <v>8</v>
+      <c r="G149" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -4268,11 +3818,8 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H150" t="s">
-        <v>8</v>
+      <c r="G150" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -4294,11 +3841,8 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H151" t="s">
-        <v>8</v>
+      <c r="G151" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -4320,11 +3864,8 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H152" t="s">
-        <v>8</v>
+      <c r="G152" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -4346,11 +3887,8 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>8</v>
+      <c r="G153" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4372,11 +3910,8 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H154" t="s">
-        <v>8</v>
+      <c r="G154" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -4398,11 +3933,8 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H155" t="s">
-        <v>8</v>
+      <c r="G155" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -4424,11 +3956,8 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H156" t="s">
-        <v>8</v>
+      <c r="G156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -4450,11 +3979,8 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H157" t="s">
-        <v>8</v>
+      <c r="G157" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -4476,11 +4002,8 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H158" t="s">
-        <v>8</v>
+      <c r="G158" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -4502,11 +4025,8 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H159" t="s">
-        <v>8</v>
+      <c r="G159" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -4528,11 +4048,8 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H160" t="s">
-        <v>8</v>
+      <c r="G160" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -4554,11 +4071,8 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H161" t="s">
-        <v>8</v>
+      <c r="G161" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -4580,11 +4094,8 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H162" t="s">
-        <v>8</v>
+      <c r="G162" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -4606,11 +4117,8 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H163" t="s">
-        <v>8</v>
+      <c r="G163" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4632,11 +4140,8 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H164" t="s">
-        <v>8</v>
+      <c r="G164" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4658,11 +4163,8 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H165" t="s">
-        <v>8</v>
+      <c r="G165" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -4684,11 +4186,8 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H166" t="s">
-        <v>8</v>
+      <c r="G166" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -4710,11 +4209,8 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H167" t="s">
-        <v>8</v>
+      <c r="G167" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4736,11 +4232,8 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H168" t="s">
-        <v>8</v>
+      <c r="G168" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -4762,11 +4255,8 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H169" t="s">
-        <v>8</v>
+      <c r="G169" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4788,11 +4278,8 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H170" t="s">
-        <v>8</v>
+      <c r="G170" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4814,11 +4301,8 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H171" t="s">
-        <v>8</v>
+      <c r="G171" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4840,11 +4324,8 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H172" t="s">
-        <v>8</v>
+      <c r="G172" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -4866,11 +4347,8 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H173" t="s">
-        <v>8</v>
+      <c r="G173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4370,8 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H174" t="s">
-        <v>8</v>
+      <c r="G174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4918,11 +4393,8 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H175" t="s">
-        <v>8</v>
+      <c r="G175" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -4944,11 +4416,8 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H176" t="s">
-        <v>8</v>
+      <c r="G176" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -4970,11 +4439,8 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H177" t="s">
-        <v>8</v>
+      <c r="G177" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -4996,11 +4462,8 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H178" t="s">
-        <v>8</v>
+      <c r="G178" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -5022,11 +4485,8 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H179" t="s">
-        <v>8</v>
+      <c r="G179" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="180">
@@ -5048,11 +4508,8 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H180" t="s">
-        <v>8</v>
+      <c r="G180" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -5074,11 +4531,8 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H181" t="s">
-        <v>8</v>
+      <c r="G181" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182">
@@ -5100,11 +4554,8 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H182" t="s">
-        <v>8</v>
+      <c r="G182" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -5126,11 +4577,8 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H183" t="s">
-        <v>8</v>
+      <c r="G183" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -5152,11 +4600,8 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H184" t="s">
-        <v>8</v>
+      <c r="G184" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -5178,11 +4623,8 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H185" t="s">
-        <v>8</v>
+      <c r="G185" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5204,11 +4646,8 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H186" t="s">
-        <v>8</v>
+      <c r="G186" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -5230,11 +4669,8 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H187" t="s">
-        <v>8</v>
+      <c r="G187" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5256,11 +4692,8 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H188" t="s">
-        <v>8</v>
+      <c r="G188" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5282,11 +4715,8 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H189" t="s">
-        <v>8</v>
+      <c r="G189" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -5308,11 +4738,8 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H190" t="s">
-        <v>8</v>
+      <c r="G190" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -5334,11 +4761,8 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H191" t="s">
-        <v>8</v>
+      <c r="G191" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -5360,11 +4784,8 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H192" t="s">
-        <v>8</v>
+      <c r="G192" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -5386,11 +4807,8 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H193" t="s">
-        <v>8</v>
+      <c r="G193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -5412,11 +4830,8 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H194" t="s">
-        <v>8</v>
+      <c r="G194" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -5438,11 +4853,8 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H195" t="s">
-        <v>8</v>
+      <c r="G195" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -5464,11 +4876,8 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H196" t="s">
-        <v>8</v>
+      <c r="G196" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -5490,11 +4899,8 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H197" t="s">
-        <v>8</v>
+      <c r="G197" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -5516,11 +4922,8 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H198" t="s">
-        <v>8</v>
+      <c r="G198" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -5542,11 +4945,8 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H199" t="s">
-        <v>8</v>
+      <c r="G199" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -5568,11 +4968,8 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H200" t="s">
-        <v>8</v>
+      <c r="G200" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -5594,11 +4991,8 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H201" t="s">
-        <v>8</v>
+      <c r="G201" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5620,11 +5014,8 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="n">
-        <v>0.0187749993056059</v>
-      </c>
-      <c r="H202" t="s">
-        <v>8</v>
+      <c r="G202" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -5646,11 +5037,8 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H203" t="s">
-        <v>8</v>
+      <c r="G203" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -5672,11 +5060,8 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H204" t="s">
-        <v>8</v>
+      <c r="G204" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -5698,11 +5083,8 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H205" t="s">
-        <v>8</v>
+      <c r="G205" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -5724,11 +5106,8 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H206" t="s">
-        <v>8</v>
+      <c r="G206" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -5750,11 +5129,8 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H207" t="s">
-        <v>8</v>
+      <c r="G207" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -5776,11 +5152,8 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H208" t="s">
-        <v>8</v>
+      <c r="G208" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -5802,11 +5175,8 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H209" t="s">
-        <v>8</v>
+      <c r="G209" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5828,11 +5198,8 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H210" t="s">
-        <v>8</v>
+      <c r="G210" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -5854,11 +5221,8 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H211" t="s">
-        <v>8</v>
+      <c r="G211" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -5880,11 +5244,8 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H212" t="s">
-        <v>8</v>
+      <c r="G212" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5906,11 +5267,8 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H213" t="s">
-        <v>8</v>
+      <c r="G213" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -5932,11 +5290,8 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H214" t="s">
-        <v>8</v>
+      <c r="G214" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -5958,11 +5313,8 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H215" t="s">
-        <v>8</v>
+      <c r="G215" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -5984,11 +5336,8 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H216" t="s">
-        <v>8</v>
+      <c r="G216" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -6010,11 +5359,8 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H217" t="s">
-        <v>8</v>
+      <c r="G217" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -6036,11 +5382,8 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H218" t="s">
-        <v>8</v>
+      <c r="G218" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -6062,11 +5405,8 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H219" t="s">
-        <v>8</v>
+      <c r="G219" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -6088,11 +5428,8 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H220" t="s">
-        <v>8</v>
+      <c r="G220" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -6114,11 +5451,8 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H221" t="s">
-        <v>8</v>
+      <c r="G221" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -6140,11 +5474,8 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H222" t="s">
-        <v>8</v>
+      <c r="G222" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -6166,11 +5497,8 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H223" t="s">
-        <v>8</v>
+      <c r="G223" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -6192,11 +5520,8 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H224" t="s">
-        <v>8</v>
+      <c r="G224" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -6218,11 +5543,8 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H225" t="s">
-        <v>8</v>
+      <c r="G225" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="226">
@@ -6244,11 +5566,8 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H226" t="s">
-        <v>8</v>
+      <c r="G226" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -6270,11 +5589,8 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H227" t="s">
-        <v>8</v>
+      <c r="G227" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -6296,11 +5612,8 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H228" t="s">
-        <v>8</v>
+      <c r="G228" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -6322,11 +5635,8 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H229" t="s">
-        <v>8</v>
+      <c r="G229" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230">
@@ -6348,11 +5658,8 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H230" t="s">
-        <v>8</v>
+      <c r="G230" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -6374,11 +5681,8 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H231" t="s">
-        <v>8</v>
+      <c r="G231" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -6400,11 +5704,8 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H232" t="s">
-        <v>8</v>
+      <c r="G232" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -6426,11 +5727,8 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H233" t="s">
-        <v>8</v>
+      <c r="G233" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -6452,11 +5750,8 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H234" t="s">
-        <v>8</v>
+      <c r="G234" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -6478,11 +5773,8 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H235" t="s">
-        <v>8</v>
+      <c r="G235" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -6504,11 +5796,8 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H236" t="s">
-        <v>8</v>
+      <c r="G236" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -6530,11 +5819,8 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H237" t="s">
-        <v>8</v>
+      <c r="G237" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238">
@@ -6556,11 +5842,8 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H238" t="s">
-        <v>8</v>
+      <c r="G238" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -6582,11 +5865,8 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H239" t="s">
-        <v>8</v>
+      <c r="G239" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -6608,11 +5888,8 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H240" t="s">
-        <v>8</v>
+      <c r="G240" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6634,11 +5911,8 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H241" t="s">
-        <v>8</v>
+      <c r="G241" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -6660,11 +5934,8 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H242" t="s">
-        <v>8</v>
+      <c r="G242" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="243">
@@ -6686,11 +5957,8 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H243" t="s">
-        <v>8</v>
+      <c r="G243" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -6712,11 +5980,8 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H244" t="s">
-        <v>8</v>
+      <c r="G244" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6738,11 +6003,8 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H245" t="s">
-        <v>8</v>
+      <c r="G245" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -6764,11 +6026,8 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H246" t="s">
-        <v>8</v>
+      <c r="G246" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -6790,11 +6049,8 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H247" t="s">
-        <v>8</v>
+      <c r="G247" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -6816,11 +6072,8 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H248" t="s">
-        <v>8</v>
+      <c r="G248" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6842,11 +6095,8 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H249" t="s">
-        <v>8</v>
+      <c r="G249" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -6868,11 +6118,8 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H250" t="s">
-        <v>8</v>
+      <c r="G250" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -6894,11 +6141,8 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H251" t="s">
-        <v>8</v>
+      <c r="G251" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6920,11 +6164,8 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H252" t="s">
-        <v>8</v>
+      <c r="G252" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6946,11 +6187,8 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H253" t="s">
-        <v>8</v>
+      <c r="G253" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -6972,11 +6210,8 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H254" t="s">
-        <v>8</v>
+      <c r="G254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -6998,11 +6233,8 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H255" t="s">
-        <v>8</v>
+      <c r="G255" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -7024,11 +6256,8 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H256" t="s">
-        <v>8</v>
+      <c r="G256" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -7050,11 +6279,8 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H257" t="s">
-        <v>8</v>
+      <c r="G257" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -7076,11 +6302,8 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H258" t="s">
-        <v>8</v>
+      <c r="G258" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -7102,11 +6325,8 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H259" t="s">
-        <v>8</v>
+      <c r="G259" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -7128,11 +6348,8 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H260" t="s">
-        <v>8</v>
+      <c r="G260" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -7154,11 +6371,8 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H261" t="s">
-        <v>8</v>
+      <c r="G261" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -7180,11 +6394,8 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H262" t="s">
-        <v>8</v>
+      <c r="G262" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -7206,11 +6417,8 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H263" t="s">
-        <v>8</v>
+      <c r="G263" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -7232,11 +6440,8 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H264" t="s">
-        <v>8</v>
+      <c r="G264" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -7258,11 +6463,8 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H265" t="s">
-        <v>8</v>
+      <c r="G265" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7284,11 +6486,8 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H266" t="s">
-        <v>8</v>
+      <c r="G266" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -7310,11 +6509,8 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H267" t="s">
-        <v>8</v>
+      <c r="G267" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7336,11 +6532,8 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H268" t="s">
-        <v>8</v>
+      <c r="G268" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -7362,11 +6555,8 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H269" t="s">
-        <v>8</v>
+      <c r="G269" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -7388,11 +6578,8 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H270" t="s">
-        <v>8</v>
+      <c r="G270" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -7414,11 +6601,8 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H271" t="s">
-        <v>8</v>
+      <c r="G271" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -7440,11 +6624,8 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H272" t="s">
-        <v>8</v>
+      <c r="G272" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -7466,11 +6647,8 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H273" t="s">
-        <v>8</v>
+      <c r="G273" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -7492,11 +6670,8 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H274" t="s">
-        <v>8</v>
+      <c r="G274" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -7518,11 +6693,8 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H275" t="s">
-        <v>8</v>
+      <c r="G275" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -7544,11 +6716,8 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H276" t="s">
-        <v>8</v>
+      <c r="G276" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7570,11 +6739,8 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H277" t="s">
-        <v>8</v>
+      <c r="G277" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -7596,11 +6762,8 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H278" t="s">
-        <v>8</v>
+      <c r="G278" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -7622,11 +6785,8 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H279" t="s">
-        <v>8</v>
+      <c r="G279" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -7648,11 +6808,8 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H280" t="s">
-        <v>8</v>
+      <c r="G280" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -7674,11 +6831,8 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H281" t="s">
-        <v>8</v>
+      <c r="G281" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -7700,11 +6854,8 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H282" t="s">
-        <v>8</v>
+      <c r="G282" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -7726,11 +6877,8 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H283" t="s">
-        <v>8</v>
+      <c r="G283" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -7752,11 +6900,8 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H284" t="s">
-        <v>8</v>
+      <c r="G284" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -7778,11 +6923,8 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H285" t="s">
-        <v>8</v>
+      <c r="G285" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7804,11 +6946,8 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H286" t="s">
-        <v>8</v>
+      <c r="G286" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -7830,11 +6969,8 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H287" t="s">
-        <v>8</v>
+      <c r="G287" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -7856,11 +6992,8 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H288" t="s">
-        <v>8</v>
+      <c r="G288" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -7882,11 +7015,8 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H289" t="s">
-        <v>8</v>
+      <c r="G289" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -7908,11 +7038,8 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H290" t="s">
-        <v>8</v>
+      <c r="G290" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -7934,11 +7061,8 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H291" t="s">
-        <v>8</v>
+      <c r="G291" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -7960,11 +7084,8 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H292" t="s">
-        <v>8</v>
+      <c r="G292" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -7986,11 +7107,8 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H293" t="s">
-        <v>8</v>
+      <c r="G293" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -8012,11 +7130,8 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H294" t="s">
-        <v>8</v>
+      <c r="G294" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -8038,11 +7153,8 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H295" t="s">
-        <v>8</v>
+      <c r="G295" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -8064,11 +7176,8 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H296" t="s">
-        <v>8</v>
+      <c r="G296" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -8090,11 +7199,8 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H297" t="s">
-        <v>8</v>
+      <c r="G297" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -8116,11 +7222,8 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H298" t="s">
-        <v>8</v>
+      <c r="G298" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -8142,11 +7245,8 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H299" t="s">
-        <v>8</v>
+      <c r="G299" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -8168,11 +7268,8 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H300" t="s">
-        <v>8</v>
+      <c r="G300" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -8194,11 +7291,8 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H301" t="s">
-        <v>8</v>
+      <c r="G301" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -8220,11 +7314,8 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H302" t="s">
-        <v>8</v>
+      <c r="G302" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -8246,11 +7337,8 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H303" t="s">
-        <v>8</v>
+      <c r="G303" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -8272,11 +7360,8 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H304" t="s">
-        <v>8</v>
+      <c r="G304" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -8298,11 +7383,8 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H305" t="s">
-        <v>8</v>
+      <c r="G305" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -8324,11 +7406,8 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H306" t="s">
-        <v>8</v>
+      <c r="G306" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -8350,11 +7429,8 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H307" t="s">
-        <v>8</v>
+      <c r="G307" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -8376,11 +7452,8 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H308" t="s">
-        <v>8</v>
+      <c r="G308" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -8402,11 +7475,8 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H309" t="s">
-        <v>8</v>
+      <c r="G309" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -8428,11 +7498,8 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H310" t="s">
-        <v>8</v>
+      <c r="G310" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -8454,11 +7521,8 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H311" t="s">
-        <v>8</v>
+      <c r="G311" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -8480,11 +7544,8 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H312" t="s">
-        <v>8</v>
+      <c r="G312" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -8506,11 +7567,8 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H313" t="s">
-        <v>8</v>
+      <c r="G313" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -8532,11 +7590,8 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H314" t="s">
-        <v>8</v>
+      <c r="G314" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -8558,11 +7613,8 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H315" t="s">
-        <v>8</v>
+      <c r="G315" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -8584,11 +7636,8 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H316" t="s">
-        <v>8</v>
+      <c r="G316" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -8610,11 +7659,8 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H317" t="s">
-        <v>8</v>
+      <c r="G317" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -8636,11 +7682,8 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H318" t="s">
-        <v>8</v>
+      <c r="G318" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -8662,11 +7705,8 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H319" t="s">
-        <v>8</v>
+      <c r="G319" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -8688,11 +7728,8 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H320" t="s">
-        <v>8</v>
+      <c r="G320" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -8714,11 +7751,8 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H321" t="s">
-        <v>8</v>
+      <c r="G321" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -8740,11 +7774,8 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H322" t="s">
-        <v>8</v>
+      <c r="G322" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -8766,11 +7797,8 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H323" t="s">
-        <v>8</v>
+      <c r="G323" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -8792,11 +7820,8 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H324" t="s">
-        <v>8</v>
+      <c r="G324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -8818,11 +7843,8 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H325" t="s">
-        <v>8</v>
+      <c r="G325" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -8844,11 +7866,8 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H326" t="s">
-        <v>8</v>
+      <c r="G326" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -8870,11 +7889,8 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H327" t="s">
-        <v>8</v>
+      <c r="G327" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -8896,11 +7912,8 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H328" t="s">
-        <v>8</v>
+      <c r="G328" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -8922,11 +7935,8 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H329" t="s">
-        <v>8</v>
+      <c r="G329" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8948,11 +7958,8 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H330" t="s">
-        <v>8</v>
+      <c r="G330" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -8974,11 +7981,8 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H331" t="s">
-        <v>8</v>
+      <c r="G331" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -9000,11 +8004,8 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H332" t="s">
-        <v>8</v>
+      <c r="G332" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9026,11 +8027,8 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H333" t="s">
-        <v>8</v>
+      <c r="G333" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -9052,11 +8050,8 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H334" t="s">
-        <v>8</v>
+      <c r="G334" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -9078,11 +8073,8 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="n">
-        <v>0.0204080007970333</v>
-      </c>
-      <c r="H335" t="s">
-        <v>8</v>
+      <c r="G335" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -9104,11 +8096,8 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H336" t="s">
-        <v>8</v>
+      <c r="G336" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -9130,11 +8119,8 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H337" t="s">
-        <v>8</v>
+      <c r="G337" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -9156,11 +8142,8 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H338" t="s">
-        <v>8</v>
+      <c r="G338" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -9182,11 +8165,8 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H339" t="s">
-        <v>8</v>
+      <c r="G339" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9208,11 +8188,8 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H340" t="s">
-        <v>8</v>
+      <c r="G340" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -9234,11 +8211,8 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H341" t="s">
-        <v>8</v>
+      <c r="G341" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -9260,11 +8234,8 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H342" t="s">
-        <v>8</v>
+      <c r="G342" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -9286,11 +8257,8 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="n">
-        <v>0.019590999931097</v>
-      </c>
-      <c r="H343" t="s">
-        <v>8</v>
+      <c r="G343" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -9312,11 +8280,8 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H344" t="s">
-        <v>8</v>
+      <c r="G344" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -9338,11 +8303,8 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H345" t="s">
-        <v>8</v>
+      <c r="G345" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -9364,11 +8326,8 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H346" t="s">
-        <v>8</v>
+      <c r="G346" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -9390,11 +8349,8 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H347" t="s">
-        <v>8</v>
+      <c r="G347" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -9416,11 +8372,8 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H348" t="s">
-        <v>8</v>
+      <c r="G348" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -9442,11 +8395,8 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H349" t="s">
-        <v>8</v>
+      <c r="G349" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -9468,11 +8418,8 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H350" t="s">
-        <v>8</v>
+      <c r="G350" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -9494,11 +8441,8 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H351" t="s">
-        <v>8</v>
+      <c r="G351" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -9520,11 +8464,8 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H352" t="s">
-        <v>8</v>
+      <c r="G352" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -9546,11 +8487,8 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H353" t="s">
-        <v>8</v>
+      <c r="G353" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -9572,11 +8510,8 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H354" t="s">
-        <v>8</v>
+      <c r="G354" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -9598,11 +8533,8 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H355" t="s">
-        <v>8</v>
+      <c r="G355" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -9624,11 +8556,8 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H356" t="s">
-        <v>8</v>
+      <c r="G356" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -9650,11 +8579,8 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H357" t="s">
-        <v>8</v>
+      <c r="G357" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -9676,11 +8602,8 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H358" t="s">
-        <v>8</v>
+      <c r="G358" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -9702,11 +8625,8 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H359" t="s">
-        <v>8</v>
+      <c r="G359" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -9728,11 +8648,8 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="n">
-        <v>0.0201019998639822</v>
-      </c>
-      <c r="H360" t="s">
-        <v>8</v>
+      <c r="G360" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -9754,11 +8671,8 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H361" t="s">
-        <v>8</v>
+      <c r="G361" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -9780,11 +8694,8 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H362" t="s">
-        <v>8</v>
+      <c r="G362" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -9806,11 +8717,8 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H363" t="s">
-        <v>8</v>
+      <c r="G363" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -9832,11 +8740,8 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H364" t="s">
-        <v>8</v>
+      <c r="G364" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -9858,11 +8763,8 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H365" t="s">
-        <v>8</v>
+      <c r="G365" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -9884,11 +8786,8 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="n">
-        <v>0.0197950005531311</v>
-      </c>
-      <c r="H366" t="s">
-        <v>8</v>
+      <c r="G366" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -9910,11 +8809,8 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H367" t="s">
-        <v>8</v>
+      <c r="G367" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -9936,11 +8832,8 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H368" t="s">
-        <v>8</v>
+      <c r="G368" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="369">
@@ -9962,11 +8855,8 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H369" t="s">
-        <v>8</v>
+      <c r="G369" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -9988,11 +8878,8 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H370" t="s">
-        <v>8</v>
+      <c r="G370" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -10014,11 +8901,8 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="n">
-        <v>0.0192850008606911</v>
-      </c>
-      <c r="H371" t="s">
-        <v>8</v>
+      <c r="G371" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -10040,11 +8924,8 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H372" t="s">
-        <v>8</v>
+      <c r="G372" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="373">
@@ -10066,11 +8947,8 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H373" t="s">
-        <v>8</v>
+      <c r="G373" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -10092,11 +8970,8 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H374" t="s">
-        <v>8</v>
+      <c r="G374" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -10118,11 +8993,8 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H375" t="s">
-        <v>8</v>
+      <c r="G375" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -10144,11 +9016,8 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H376" t="s">
-        <v>8</v>
+      <c r="G376" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="377">
@@ -10170,11 +9039,8 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H377" t="s">
-        <v>8</v>
+      <c r="G377" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="378">
@@ -10196,11 +9062,8 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H378" t="s">
-        <v>8</v>
+      <c r="G378" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="379">
@@ -10222,11 +9085,8 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H379" t="s">
-        <v>8</v>
+      <c r="G379" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="380">
@@ -10248,11 +9108,8 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="n">
-        <v>0.019386999309063</v>
-      </c>
-      <c r="H380" t="s">
-        <v>8</v>
+      <c r="G380" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="381">
@@ -10274,11 +9131,8 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H381" t="s">
-        <v>8</v>
+      <c r="G381" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -10300,11 +9154,8 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H382" t="s">
-        <v>8</v>
+      <c r="G382" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -10326,11 +9177,8 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H383" t="s">
-        <v>8</v>
+      <c r="G383" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -10352,11 +9200,8 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="n">
-        <v>0.0198970008641481</v>
-      </c>
-      <c r="H384" t="s">
-        <v>8</v>
+      <c r="G384" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -10378,11 +9223,8 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="n">
-        <v>0.0196930002421141</v>
-      </c>
-      <c r="H385" t="s">
-        <v>8</v>
+      <c r="G385" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -10404,11 +9246,8 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="n">
-        <v>0.019183000549674</v>
-      </c>
-      <c r="H386" t="s">
-        <v>8</v>
+      <c r="G386" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -10430,11 +9269,8 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H387" t="s">
-        <v>8</v>
+      <c r="G387" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -10456,11 +9292,8 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H388" t="s">
-        <v>8</v>
+      <c r="G388" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="389">
@@ -10482,11 +9315,8 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H389" t="s">
-        <v>8</v>
+      <c r="G389" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="390">
@@ -10508,11 +9338,8 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H390" t="s">
-        <v>8</v>
+      <c r="G390" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="391">
@@ -10534,11 +9361,8 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H391" t="s">
-        <v>8</v>
+      <c r="G391" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -10560,11 +9384,8 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H392" t="s">
-        <v>8</v>
+      <c r="G392" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -10586,11 +9407,8 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H393" t="s">
-        <v>8</v>
+      <c r="G393" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="394">
@@ -10612,11 +9430,8 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H394" t="s">
-        <v>8</v>
+      <c r="G394" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="395">
@@ -10638,11 +9453,8 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H395" t="s">
-        <v>8</v>
+      <c r="G395" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="396">
@@ -10664,11 +9476,8 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H396" t="s">
-        <v>8</v>
+      <c r="G396" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -10690,11 +9499,8 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H397" t="s">
-        <v>8</v>
+      <c r="G397" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="398">
@@ -10716,11 +9522,8 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H398" t="s">
-        <v>8</v>
+      <c r="G398" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -10742,11 +9545,8 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H399" t="s">
-        <v>8</v>
+      <c r="G399" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -10768,11 +9568,8 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H400" t="s">
-        <v>8</v>
+      <c r="G400" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="401">
@@ -10794,11 +9591,8 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H401" t="s">
-        <v>8</v>
+      <c r="G401" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -10820,11 +9614,8 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="n">
-        <v>0.01948899962008</v>
-      </c>
-      <c r="H402" t="s">
-        <v>8</v>
+      <c r="G402" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -10846,11 +9637,8 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H403" t="s">
-        <v>8</v>
+      <c r="G403" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="404">
@@ -10872,11 +9660,8 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H404" t="s">
-        <v>8</v>
+      <c r="G404" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -10898,11 +9683,8 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H405" t="s">
-        <v>8</v>
+      <c r="G405" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -10924,11 +9706,8 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H406" t="s">
-        <v>8</v>
+      <c r="G406" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -10950,11 +9729,8 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H407" t="s">
-        <v>8</v>
+      <c r="G407" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -10976,11 +9752,8 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H408" t="s">
-        <v>8</v>
+      <c r="G408" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="409">
@@ -11002,11 +9775,8 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H409" t="s">
-        <v>8</v>
+      <c r="G409" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -11028,11 +9798,8 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H410" t="s">
-        <v>8</v>
+      <c r="G410" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11054,11 +9821,8 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="n">
-        <v>0.019081000238657</v>
-      </c>
-      <c r="H411" t="s">
-        <v>8</v>
+      <c r="G411" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -11080,11 +9844,8 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H412" t="s">
-        <v>8</v>
+      <c r="G412" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -11106,11 +9867,8 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H413" t="s">
-        <v>8</v>
+      <c r="G413" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="414">
@@ -11132,11 +9890,8 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H414" t="s">
-        <v>8</v>
+      <c r="G414" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -11158,11 +9913,8 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H415" t="s">
-        <v>8</v>
+      <c r="G415" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="416">
@@ -11184,11 +9936,8 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H416" t="s">
-        <v>8</v>
+      <c r="G416" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -11210,11 +9959,8 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="n">
-        <v>0.01897899992764</v>
-      </c>
-      <c r="H417" t="s">
-        <v>8</v>
+      <c r="G417" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="418">
@@ -11236,11 +9982,8 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H418" t="s">
-        <v>8</v>
+      <c r="G418" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -11262,11 +10005,8 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H419" t="s">
-        <v>8</v>
+      <c r="G419" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -11288,11 +10028,8 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="n">
-        <v>0.0188769996166229</v>
-      </c>
-      <c r="H420" t="s">
-        <v>8</v>
+      <c r="G420" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="421">
@@ -11314,11 +10051,8 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="n">
-        <v>0.018673000857234</v>
-      </c>
-      <c r="H421" t="s">
-        <v>8</v>
+      <c r="G421" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="422">
@@ -11340,11 +10074,8 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H422" t="s">
-        <v>8</v>
+      <c r="G422" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -11366,11 +10097,8 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H423" t="s">
-        <v>8</v>
+      <c r="G423" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -11392,11 +10120,8 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H424" t="s">
-        <v>8</v>
+      <c r="G424" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -11418,11 +10143,8 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H425" t="s">
-        <v>8</v>
+      <c r="G425" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -11444,11 +10166,8 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H426" t="s">
-        <v>8</v>
+      <c r="G426" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -11470,11 +10189,8 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H427" t="s">
-        <v>8</v>
+      <c r="G427" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -11496,11 +10212,8 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H428" t="s">
-        <v>8</v>
+      <c r="G428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429">
@@ -11522,11 +10235,8 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H429" t="s">
-        <v>8</v>
+      <c r="G429" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -11548,11 +10258,8 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H430" t="s">
-        <v>8</v>
+      <c r="G430" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -11574,11 +10281,8 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H431" t="s">
-        <v>8</v>
+      <c r="G431" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -11600,11 +10304,8 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="n">
-        <v>0.018571000546217</v>
-      </c>
-      <c r="H432" t="s">
-        <v>8</v>
+      <c r="G432" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="433">
@@ -11626,11 +10327,8 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H433" t="s">
-        <v>8</v>
+      <c r="G433" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="434">
@@ -11652,11 +10350,8 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H434" t="s">
-        <v>8</v>
+      <c r="G434" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="435">
@@ -11678,11 +10373,8 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="n">
-        <v>0.0183669999241829</v>
-      </c>
-      <c r="H435" t="s">
-        <v>8</v>
+      <c r="G435" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -11704,11 +10396,8 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H436" t="s">
-        <v>8</v>
+      <c r="G436" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -11730,11 +10419,8 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="n">
-        <v>0.0182649996131659</v>
-      </c>
-      <c r="H437" t="s">
-        <v>8</v>
+      <c r="G437" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="438">
@@ -11756,11 +10442,8 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H438" t="s">
-        <v>8</v>
+      <c r="G438" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -11782,11 +10465,8 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H439" t="s">
-        <v>8</v>
+      <c r="G439" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -11808,11 +10488,8 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H440" t="s">
-        <v>8</v>
+      <c r="G440" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="441">
@@ -11834,11 +10511,8 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H441" t="s">
-        <v>8</v>
+      <c r="G441" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -11860,11 +10534,8 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H442" t="s">
-        <v>8</v>
+      <c r="G442" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -11886,11 +10557,8 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H443" t="s">
-        <v>8</v>
+      <c r="G443" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="444">
@@ -11912,11 +10580,8 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H444" t="s">
-        <v>8</v>
+      <c r="G444" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="445">
@@ -11938,11 +10603,8 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H445" t="s">
-        <v>8</v>
+      <c r="G445" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="446">
@@ -11964,11 +10626,8 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H446" t="s">
-        <v>8</v>
+      <c r="G446" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="447">
@@ -11990,11 +10649,8 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H447" t="s">
-        <v>8</v>
+      <c r="G447" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -12016,11 +10672,8 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H448" t="s">
-        <v>8</v>
+      <c r="G448" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -12042,11 +10695,8 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H449" t="s">
-        <v>8</v>
+      <c r="G449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -12068,11 +10718,8 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H450" t="s">
-        <v>8</v>
+      <c r="G450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451">
@@ -12094,11 +10741,8 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H451" t="s">
-        <v>8</v>
+      <c r="G451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -12120,11 +10764,8 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H452" t="s">
-        <v>8</v>
+      <c r="G452" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -12146,11 +10787,8 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H453" t="s">
-        <v>8</v>
+      <c r="G453" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -12172,11 +10810,8 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H454" t="s">
-        <v>8</v>
+      <c r="G454" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -12198,11 +10833,8 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H455" t="s">
-        <v>8</v>
+      <c r="G455" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -12224,11 +10856,8 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H456" t="s">
-        <v>8</v>
+      <c r="G456" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -12250,11 +10879,8 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H457" t="s">
-        <v>8</v>
+      <c r="G457" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -12276,11 +10902,8 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H458" t="s">
-        <v>8</v>
+      <c r="G458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -12302,11 +10925,8 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H459" t="s">
-        <v>8</v>
+      <c r="G459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -12328,11 +10948,8 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H460" t="s">
-        <v>8</v>
+      <c r="G460" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -12354,11 +10971,8 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H461" t="s">
-        <v>8</v>
+      <c r="G461" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -12380,11 +10994,8 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H462" t="s">
-        <v>8</v>
+      <c r="G462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463">
@@ -12406,11 +11017,8 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H463" t="s">
-        <v>8</v>
+      <c r="G463" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -12432,11 +11040,8 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H464" t="s">
-        <v>8</v>
+      <c r="G464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465">
@@ -12458,11 +11063,8 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H465" t="s">
-        <v>8</v>
+      <c r="G465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -12484,11 +11086,8 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H466" t="s">
-        <v>8</v>
+      <c r="G466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -12510,11 +11109,8 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H467" t="s">
-        <v>8</v>
+      <c r="G467" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="468">
@@ -12536,11 +11132,8 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H468" t="s">
-        <v>8</v>
+      <c r="G468" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -12562,11 +11155,8 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H469" t="s">
-        <v>8</v>
+      <c r="G469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -12588,11 +11178,8 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H470" t="s">
-        <v>8</v>
+      <c r="G470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471">
@@ -12614,11 +11201,8 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H471" t="s">
-        <v>8</v>
+      <c r="G471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -12640,11 +11224,8 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H472" t="s">
-        <v>8</v>
+      <c r="G472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -12666,11 +11247,8 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H473" t="s">
-        <v>8</v>
+      <c r="G473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474">
@@ -12692,11 +11270,8 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H474" t="s">
-        <v>8</v>
+      <c r="G474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -12718,11 +11293,8 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H475" t="s">
-        <v>8</v>
+      <c r="G475" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="476">
@@ -12744,11 +11316,8 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H476" t="s">
-        <v>8</v>
+      <c r="G476" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="477">
@@ -12770,11 +11339,8 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H477" t="s">
-        <v>8</v>
+      <c r="G477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478">
@@ -12796,11 +11362,8 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H478" t="s">
-        <v>8</v>
+      <c r="G478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -12822,11 +11385,8 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H479" t="s">
-        <v>8</v>
+      <c r="G479" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="480">
@@ -12848,11 +11408,8 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H480" t="s">
-        <v>8</v>
+      <c r="G480" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="481">
@@ -12874,11 +11431,8 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H481" t="s">
-        <v>8</v>
+      <c r="G481" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -12900,11 +11454,8 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H482" t="s">
-        <v>8</v>
+      <c r="G482" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -12926,11 +11477,8 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H483" t="s">
-        <v>8</v>
+      <c r="G483" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -12952,11 +11500,8 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="n">
-        <v>0.0158159993588924</v>
-      </c>
-      <c r="H484" t="s">
-        <v>8</v>
+      <c r="G484" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="485">
@@ -12978,11 +11523,8 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H485" t="s">
-        <v>8</v>
+      <c r="G485" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="486">
@@ -13004,11 +11546,8 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H486" t="s">
-        <v>8</v>
+      <c r="G486" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -13030,11 +11569,8 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H487" t="s">
-        <v>8</v>
+      <c r="G487" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="488">
@@ -13056,11 +11592,8 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H488" t="s">
-        <v>8</v>
+      <c r="G488" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -13082,11 +11615,8 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H489" t="s">
-        <v>8</v>
+      <c r="G489" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="490">
@@ -13108,11 +11638,8 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H490" t="s">
-        <v>8</v>
+      <c r="G490" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -13134,11 +11661,8 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H491" t="s">
-        <v>8</v>
+      <c r="G491" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -13160,11 +11684,8 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H492" t="s">
-        <v>8</v>
+      <c r="G492" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="493">
@@ -13186,11 +11707,8 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H493" t="s">
-        <v>8</v>
+      <c r="G493" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="494">
@@ -13212,11 +11730,8 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H494" t="s">
-        <v>8</v>
+      <c r="G494" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="495">
@@ -13238,11 +11753,8 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H495" t="s">
-        <v>8</v>
+      <c r="G495" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="496">
@@ -13264,11 +11776,8 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H496" t="s">
-        <v>8</v>
+      <c r="G496" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -13290,11 +11799,8 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H497" t="s">
-        <v>8</v>
+      <c r="G497" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -13316,11 +11822,8 @@
       <c r="F498" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G498" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H498" t="s">
-        <v>8</v>
+      <c r="G498" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="499">
@@ -13342,11 +11845,8 @@
       <c r="F499" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G499" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H499" t="s">
-        <v>8</v>
+      <c r="G499" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -13368,11 +11868,8 @@
       <c r="F500" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G500" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H500" t="s">
-        <v>8</v>
+      <c r="G500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -13394,11 +11891,8 @@
       <c r="F501" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G501" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H501" t="s">
-        <v>8</v>
+      <c r="G501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502">
@@ -13420,11 +11914,8 @@
       <c r="F502" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G502" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H502" t="s">
-        <v>8</v>
+      <c r="G502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -13446,11 +11937,8 @@
       <c r="F503" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G503" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H503" t="s">
-        <v>8</v>
+      <c r="G503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -13472,11 +11960,8 @@
       <c r="F504" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G504" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H504" t="s">
-        <v>8</v>
+      <c r="G504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505">
@@ -13498,11 +11983,8 @@
       <c r="F505" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G505" t="n">
-        <v>0.0157140009105206</v>
-      </c>
-      <c r="H505" t="s">
-        <v>8</v>
+      <c r="G505" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -13524,11 +12006,8 @@
       <c r="F506" t="n">
         <v>0.0154079999774694</v>
       </c>
-      <c r="G506" t="n">
-        <v>0.0154079999774694</v>
-      </c>
-      <c r="H506" t="s">
-        <v>8</v>
+      <c r="G506" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="507">
@@ -13550,11 +12029,8 @@
       <c r="F507" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G507" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H507" t="s">
-        <v>8</v>
+      <c r="G507" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -13576,11 +12052,8 @@
       <c r="F508" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G508" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H508" t="s">
-        <v>8</v>
+      <c r="G508" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -13602,11 +12075,8 @@
       <c r="F509" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G509" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H509" t="s">
-        <v>8</v>
+      <c r="G509" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="510">
@@ -13628,11 +12098,8 @@
       <c r="F510" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G510" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H510" t="s">
-        <v>8</v>
+      <c r="G510" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="511">
@@ -13654,11 +12121,8 @@
       <c r="F511" t="n">
         <v>0.0153059996664524</v>
       </c>
-      <c r="G511" t="n">
-        <v>0.0153059996664524</v>
-      </c>
-      <c r="H511" t="s">
-        <v>8</v>
+      <c r="G511" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -13680,11 +12144,8 @@
       <c r="F512" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G512" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H512" t="s">
-        <v>8</v>
+      <c r="G512" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="513">
@@ -13706,11 +12167,8 @@
       <c r="F513" t="n">
         <v>0.0151019999757409</v>
       </c>
-      <c r="G513" t="n">
-        <v>0.0151019999757409</v>
-      </c>
-      <c r="H513" t="s">
-        <v>8</v>
+      <c r="G513" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -13732,11 +12190,8 @@
       <c r="F514" t="n">
         <v>0.0152040002867579</v>
       </c>
-      <c r="G514" t="n">
-        <v>0.0152040002867579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>8</v>
+      <c r="G514" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -13758,11 +12213,8 @@
       <c r="F515" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G515" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H515" t="s">
-        <v>8</v>
+      <c r="G515" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -13784,11 +12236,8 @@
       <c r="F516" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G516" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H516" t="s">
-        <v>8</v>
+      <c r="G516" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="517">
@@ -13810,11 +12259,8 @@
       <c r="F517" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G517" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H517" t="s">
-        <v>8</v>
+      <c r="G517" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -13836,11 +12282,8 @@
       <c r="F518" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G518" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H518" t="s">
-        <v>8</v>
+      <c r="G518" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -13862,11 +12305,8 @@
       <c r="F519" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G519" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H519" t="s">
-        <v>8</v>
+      <c r="G519" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -13888,11 +12328,8 @@
       <c r="F520" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G520" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H520" t="s">
-        <v>8</v>
+      <c r="G520" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -13914,11 +12351,8 @@
       <c r="F521" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G521" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H521" t="s">
-        <v>8</v>
+      <c r="G521" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="522">
@@ -13940,11 +12374,8 @@
       <c r="F522" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G522" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H522" t="s">
-        <v>8</v>
+      <c r="G522" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -13966,11 +12397,8 @@
       <c r="F523" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G523" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H523" t="s">
-        <v>8</v>
+      <c r="G523" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -13992,11 +12420,8 @@
       <c r="F524" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G524" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H524" t="s">
-        <v>8</v>
+      <c r="G524" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="525">
@@ -14018,11 +12443,8 @@
       <c r="F525" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G525" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H525" t="s">
-        <v>8</v>
+      <c r="G525" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -14044,11 +12466,8 @@
       <c r="F526" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G526" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H526" t="s">
-        <v>8</v>
+      <c r="G526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527">
@@ -14070,11 +12489,8 @@
       <c r="F527" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G527" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H527" t="s">
-        <v>8</v>
+      <c r="G527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528">
@@ -14096,11 +12512,8 @@
       <c r="F528" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G528" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H528" t="s">
-        <v>8</v>
+      <c r="G528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529">
@@ -14122,11 +12535,8 @@
       <c r="F529" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G529" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H529" t="s">
-        <v>8</v>
+      <c r="G529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -14148,11 +12558,8 @@
       <c r="F530" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G530" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H530" t="s">
-        <v>8</v>
+      <c r="G530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -14174,11 +12581,8 @@
       <c r="F531" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G531" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H531" t="s">
-        <v>8</v>
+      <c r="G531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532">
@@ -14200,11 +12604,8 @@
       <c r="F532" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G532" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H532" t="s">
-        <v>8</v>
+      <c r="G532" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="533">
@@ -14226,11 +12627,8 @@
       <c r="F533" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G533" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H533" t="s">
-        <v>8</v>
+      <c r="G533" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -14252,11 +12650,8 @@
       <c r="F534" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G534" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H534" t="s">
-        <v>8</v>
+      <c r="G534" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="535">
@@ -14278,11 +12673,8 @@
       <c r="F535" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G535" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H535" t="s">
-        <v>8</v>
+      <c r="G535" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -14304,11 +12696,8 @@
       <c r="F536" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G536" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H536" t="s">
-        <v>8</v>
+      <c r="G536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537">
@@ -14330,11 +12719,8 @@
       <c r="F537" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G537" t="n">
-        <v>0.0171419996768236</v>
-      </c>
-      <c r="H537" t="s">
-        <v>8</v>
+      <c r="G537" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="538">
@@ -14356,11 +12742,8 @@
       <c r="F538" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G538" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H538" t="s">
-        <v>8</v>
+      <c r="G538" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="539">
@@ -14382,11 +12765,8 @@
       <c r="F539" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G539" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H539" t="s">
-        <v>8</v>
+      <c r="G539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540">
@@ -14408,11 +12788,8 @@
       <c r="F540" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G540" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H540" t="s">
-        <v>8</v>
+      <c r="G540" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -14434,11 +12811,8 @@
       <c r="F541" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G541" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H541" t="s">
-        <v>8</v>
+      <c r="G541" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="542">
@@ -14460,11 +12834,8 @@
       <c r="F542" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G542" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H542" t="s">
-        <v>8</v>
+      <c r="G542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -14486,11 +12857,8 @@
       <c r="F543" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G543" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H543" t="s">
-        <v>8</v>
+      <c r="G543" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -14512,11 +12880,8 @@
       <c r="F544" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G544" t="n">
-        <v>0.0161220002919436</v>
-      </c>
-      <c r="H544" t="s">
-        <v>8</v>
+      <c r="G544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545">
@@ -14538,11 +12903,8 @@
       <c r="F545" t="n">
         <v>0.0155100002884865</v>
       </c>
-      <c r="G545" t="n">
-        <v>0.0155100002884865</v>
-      </c>
-      <c r="H545" t="s">
-        <v>8</v>
+      <c r="G545" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="546">
@@ -14564,11 +12926,8 @@
       <c r="F546" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G546" t="n">
-        <v>0.0156119996681809</v>
-      </c>
-      <c r="H546" t="s">
-        <v>8</v>
+      <c r="G546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547">
@@ -14590,11 +12949,8 @@
       <c r="F547" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G547" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H547" t="s">
-        <v>8</v>
+      <c r="G547" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="548">
@@ -14616,11 +12972,8 @@
       <c r="F548" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G548" t="n">
-        <v>0.0159179996699095</v>
-      </c>
-      <c r="H548" t="s">
-        <v>8</v>
+      <c r="G548" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -14642,11 +12995,8 @@
       <c r="F549" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G549" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H549" t="s">
-        <v>8</v>
+      <c r="G549" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -14668,11 +13018,8 @@
       <c r="F550" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G550" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H550" t="s">
-        <v>8</v>
+      <c r="G550" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -14694,11 +13041,8 @@
       <c r="F551" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G551" t="n">
-        <v>0.0160199999809265</v>
-      </c>
-      <c r="H551" t="s">
-        <v>8</v>
+      <c r="G551" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="552">
@@ -14720,11 +13064,8 @@
       <c r="F552" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G552" t="n">
-        <v>0.0163260009139776</v>
-      </c>
-      <c r="H552" t="s">
-        <v>8</v>
+      <c r="G552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -14746,11 +13087,8 @@
       <c r="F553" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G553" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H553" t="s">
-        <v>8</v>
+      <c r="G553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -14772,11 +13110,8 @@
       <c r="F554" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G554" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H554" t="s">
-        <v>8</v>
+      <c r="G554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -14798,11 +13133,8 @@
       <c r="F555" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G555" t="n">
-        <v>0.0165299996733665</v>
-      </c>
-      <c r="H555" t="s">
-        <v>8</v>
+      <c r="G555" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="556">
@@ -14824,11 +13156,8 @@
       <c r="F556" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G556" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H556" t="s">
-        <v>8</v>
+      <c r="G556" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="557">
@@ -14850,11 +13179,8 @@
       <c r="F557" t="n">
         <v>0.0164279993623495</v>
       </c>
-      <c r="G557" t="n">
-        <v>0.0164279993623495</v>
-      </c>
-      <c r="H557" t="s">
-        <v>8</v>
+      <c r="G557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -14876,11 +13202,8 @@
       <c r="F558" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G558" t="n">
-        <v>0.0170399993658066</v>
-      </c>
-      <c r="H558" t="s">
-        <v>8</v>
+      <c r="G558" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="559">
@@ -14902,11 +13225,8 @@
       <c r="F559" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G559" t="n">
-        <v>0.0166319999843836</v>
-      </c>
-      <c r="H559" t="s">
-        <v>8</v>
+      <c r="G559" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="560">
@@ -14928,11 +13248,8 @@
       <c r="F560" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G560" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H560" t="s">
-        <v>8</v>
+      <c r="G560" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -14954,11 +13271,8 @@
       <c r="F561" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G561" t="n">
-        <v>0.0168360006064177</v>
-      </c>
-      <c r="H561" t="s">
-        <v>8</v>
+      <c r="G561" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="562">
@@ -14980,11 +13294,8 @@
       <c r="F562" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G562" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H562" t="s">
-        <v>8</v>
+      <c r="G562" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="563">
@@ -15006,11 +13317,8 @@
       <c r="F563" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G563" t="n">
-        <v>0.0167340002954006</v>
-      </c>
-      <c r="H563" t="s">
-        <v>8</v>
+      <c r="G563" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="564">
@@ -15032,11 +13340,8 @@
       <c r="F564" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G564" t="n">
-        <v>0.0169380009174347</v>
-      </c>
-      <c r="H564" t="s">
-        <v>8</v>
+      <c r="G564" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -15058,11 +13363,8 @@
       <c r="F565" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G565" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H565" t="s">
-        <v>8</v>
+      <c r="G565" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="566">
@@ -15084,11 +13386,8 @@
       <c r="F566" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G566" t="n">
-        <v>0.0173460002988577</v>
-      </c>
-      <c r="H566" t="s">
-        <v>8</v>
+      <c r="G566" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -15110,11 +13409,8 @@
       <c r="F567" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G567" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H567" t="s">
-        <v>8</v>
+      <c r="G567" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="568">
@@ -15136,11 +13432,8 @@
       <c r="F568" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G568" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H568" t="s">
-        <v>8</v>
+      <c r="G568" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -15162,11 +13455,8 @@
       <c r="F569" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G569" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H569" t="s">
-        <v>8</v>
+      <c r="G569" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="570">
@@ -15188,11 +13478,8 @@
       <c r="F570" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G570" t="n">
-        <v>0.0176529996097088</v>
-      </c>
-      <c r="H570" t="s">
-        <v>8</v>
+      <c r="G570" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -15214,11 +13501,8 @@
       <c r="F571" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G571" t="n">
-        <v>0.0172439999878407</v>
-      </c>
-      <c r="H571" t="s">
-        <v>8</v>
+      <c r="G571" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="572">
@@ -15240,11 +13524,8 @@
       <c r="F572" t="n">
         <v>0.0174480006098747</v>
       </c>
-      <c r="G572" t="n">
-        <v>0.0174480006098747</v>
-      </c>
-      <c r="H572" t="s">
-        <v>8</v>
+      <c r="G572" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -15266,11 +13547,8 @@
       <c r="F573" t="n">
         <v>0.0175509992986917</v>
       </c>
-      <c r="G573" t="n">
-        <v>0.0175509992986917</v>
-      </c>
-      <c r="H573" t="s">
-        <v>8</v>
+      <c r="G573" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="574">
@@ -15292,11 +13570,8 @@
       <c r="F574" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G574" t="n">
-        <v>0.0181629993021488</v>
-      </c>
-      <c r="H574" t="s">
-        <v>8</v>
+      <c r="G574" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -15318,11 +13593,8 @@
       <c r="F575" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G575" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H575" t="s">
-        <v>8</v>
+      <c r="G575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -15344,11 +13616,8 @@
       <c r="F576" t="n">
         <v>0.0177549999207258</v>
       </c>
-      <c r="G576" t="n">
-        <v>0.0177549999207258</v>
-      </c>
-      <c r="H576" t="s">
-        <v>8</v>
+      <c r="G576" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -15370,11 +13639,8 @@
       <c r="F577" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G577" t="n">
-        <v>0.0179590005427599</v>
-      </c>
-      <c r="H577" t="s">
-        <v>8</v>
+      <c r="G577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -15396,11 +13662,8 @@
       <c r="F578" t="n">
         <v>0.0175000000745058</v>
       </c>
-      <c r="G578" t="n">
-        <v>0.0175000000745058</v>
-      </c>
-      <c r="H578" t="s">
-        <v>8</v>
+      <c r="G578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579">
@@ -15422,11 +13685,8 @@
       <c r="F579" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G579" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H579" t="s">
-        <v>8</v>
+      <c r="G579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580">
@@ -15448,11 +13708,8 @@
       <c r="F580" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G580" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H580" t="s">
-        <v>8</v>
+      <c r="G580" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="581">
@@ -15474,11 +13731,8 @@
       <c r="F581" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G581" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H581" t="s">
-        <v>8</v>
+      <c r="G581" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="582">
@@ -15500,11 +13754,8 @@
       <c r="F582" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G582" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H582" t="s">
-        <v>8</v>
+      <c r="G582" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -15526,11 +13777,8 @@
       <c r="F583" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G583" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H583" t="s">
-        <v>8</v>
+      <c r="G583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -15552,11 +13800,8 @@
       <c r="F584" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G584" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H584" t="s">
-        <v>8</v>
+      <c r="G584" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="585">
@@ -15578,11 +13823,8 @@
       <c r="F585" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G585" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H585" t="s">
-        <v>8</v>
+      <c r="G585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586">
@@ -15604,11 +13846,8 @@
       <c r="F586" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G586" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H586" t="s">
-        <v>8</v>
+      <c r="G586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -15630,11 +13869,8 @@
       <c r="F587" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G587" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H587" t="s">
-        <v>8</v>
+      <c r="G587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588">
@@ -15656,11 +13892,8 @@
       <c r="F588" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G588" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H588" t="s">
-        <v>8</v>
+      <c r="G588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589">
@@ -15682,11 +13915,8 @@
       <c r="F589" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G589" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H589" t="s">
-        <v>8</v>
+      <c r="G589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590">
@@ -15708,11 +13938,8 @@
       <c r="F590" t="n">
         <v>0.0171000007539988</v>
       </c>
-      <c r="G590" t="n">
-        <v>0.0171000007539988</v>
-      </c>
-      <c r="H590" t="s">
-        <v>8</v>
+      <c r="G590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591">
@@ -15734,11 +13961,8 @@
       <c r="F591" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G591" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H591" t="s">
-        <v>8</v>
+      <c r="G591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592">
@@ -15760,11 +13984,8 @@
       <c r="F592" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G592" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H592" t="s">
-        <v>8</v>
+      <c r="G592" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="593">
@@ -15786,11 +14007,8 @@
       <c r="F593" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G593" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H593" t="s">
-        <v>8</v>
+      <c r="G593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594">
@@ -15812,11 +14030,8 @@
       <c r="F594" t="n">
         <v>0.0215000007301569</v>
       </c>
-      <c r="G594" t="n">
-        <v>0.0215000007301569</v>
-      </c>
-      <c r="H594" t="s">
-        <v>8</v>
+      <c r="G594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595">
@@ -15838,11 +14053,8 @@
       <c r="F595" t="n">
         <v>0.0203000009059906</v>
       </c>
-      <c r="G595" t="n">
-        <v>0.0203000009059906</v>
-      </c>
-      <c r="H595" t="s">
-        <v>8</v>
+      <c r="G595" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="596">
@@ -15864,11 +14076,8 @@
       <c r="F596" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G596" t="n">
-        <v>0.0199999995529652</v>
-      </c>
-      <c r="H596" t="s">
-        <v>8</v>
+      <c r="G596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597">
@@ -15890,11 +14099,8 @@
       <c r="F597" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G597" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H597" t="s">
-        <v>8</v>
+      <c r="G597" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="598">
@@ -15916,11 +14122,8 @@
       <c r="F598" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G598" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H598" t="s">
-        <v>8</v>
+      <c r="G598" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="599">
@@ -15942,11 +14145,8 @@
       <c r="F599" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G599" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H599" t="s">
-        <v>8</v>
+      <c r="G599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600">
@@ -15968,11 +14168,8 @@
       <c r="F600" t="n">
         <v>0.0183000005781651</v>
       </c>
-      <c r="G600" t="n">
-        <v>0.0183000005781651</v>
-      </c>
-      <c r="H600" t="s">
-        <v>8</v>
+      <c r="G600" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="601">
@@ -15994,11 +14191,8 @@
       <c r="F601" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G601" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H601" t="s">
-        <v>8</v>
+      <c r="G601" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="602">
@@ -16020,11 +14214,8 @@
       <c r="F602" t="n">
         <v>0.0185000002384186</v>
       </c>
-      <c r="G602" t="n">
-        <v>0.0185000002384186</v>
-      </c>
-      <c r="H602" t="s">
-        <v>8</v>
+      <c r="G602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603">
@@ -16046,11 +14237,8 @@
       <c r="F603" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G603" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H603" t="s">
-        <v>8</v>
+      <c r="G603" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="604">
@@ -16072,11 +14260,8 @@
       <c r="F604" t="n">
         <v>0.0196000002324581</v>
       </c>
-      <c r="G604" t="n">
-        <v>0.0196000002324581</v>
-      </c>
-      <c r="H604" t="s">
-        <v>8</v>
+      <c r="G604" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="605">
@@ -16098,11 +14283,8 @@
       <c r="F605" t="n">
         <v>0.0192000009119511</v>
       </c>
-      <c r="G605" t="n">
-        <v>0.0192000009119511</v>
-      </c>
-      <c r="H605" t="s">
-        <v>8</v>
+      <c r="G605" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="606">
@@ -16124,11 +14306,8 @@
       <c r="F606" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G606" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H606" t="s">
-        <v>8</v>
+      <c r="G606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607">
@@ -16150,11 +14329,8 @@
       <c r="F607" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G607" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H607" t="s">
-        <v>8</v>
+      <c r="G607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608">
@@ -16176,11 +14352,8 @@
       <c r="F608" t="n">
         <v>0.0188999995589256</v>
       </c>
-      <c r="G608" t="n">
-        <v>0.0188999995589256</v>
-      </c>
-      <c r="H608" t="s">
-        <v>8</v>
+      <c r="G608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609">
@@ -16202,11 +14375,8 @@
       <c r="F609" t="n">
         <v>0.0181000009179115</v>
       </c>
-      <c r="G609" t="n">
-        <v>0.0181000009179115</v>
-      </c>
-      <c r="H609" t="s">
-        <v>8</v>
+      <c r="G609" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="610">
@@ -16228,11 +14398,8 @@
       <c r="F610" t="n">
         <v>0.0173000004142523</v>
       </c>
-      <c r="G610" t="n">
-        <v>0.0173000004142523</v>
-      </c>
-      <c r="H610" t="s">
-        <v>8</v>
+      <c r="G610" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="611">
@@ -16254,11 +14421,8 @@
       <c r="F611" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G611" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H611" t="s">
-        <v>8</v>
+      <c r="G611" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="612">
@@ -16280,11 +14444,8 @@
       <c r="F612" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G612" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H612" t="s">
-        <v>8</v>
+      <c r="G612" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="613">
@@ -16306,11 +14467,8 @@
       <c r="F613" t="n">
         <v>0.0189999993890524</v>
       </c>
-      <c r="G613" t="n">
-        <v>0.0189999993890524</v>
-      </c>
-      <c r="H613" t="s">
-        <v>8</v>
+      <c r="G613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614">
@@ -16332,11 +14490,8 @@
       <c r="F614" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G614" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H614" t="s">
-        <v>8</v>
+      <c r="G614" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -16358,11 +14513,8 @@
       <c r="F615" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G615" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H615" t="s">
-        <v>8</v>
+      <c r="G615" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="616">
@@ -16384,11 +14536,8 @@
       <c r="F616" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G616" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H616" t="s">
-        <v>8</v>
+      <c r="G616" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -16410,11 +14559,8 @@
       <c r="F617" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G617" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H617" t="s">
-        <v>8</v>
+      <c r="G617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618">
@@ -16436,11 +14582,8 @@
       <c r="F618" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G618" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H618" t="s">
-        <v>8</v>
+      <c r="G618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619">
@@ -16462,11 +14605,8 @@
       <c r="F619" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G619" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H619" t="s">
-        <v>8</v>
+      <c r="G619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620">
@@ -16488,11 +14628,8 @@
       <c r="F620" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G620" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H620" t="s">
-        <v>8</v>
+      <c r="G620" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="621">
@@ -16514,11 +14651,8 @@
       <c r="F621" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G621" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H621" t="s">
-        <v>8</v>
+      <c r="G621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622">
@@ -16540,11 +14674,8 @@
       <c r="F622" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G622" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H622" t="s">
-        <v>8</v>
+      <c r="G622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623">
@@ -16566,11 +14697,8 @@
       <c r="F623" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G623" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H623" t="s">
-        <v>8</v>
+      <c r="G623" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="624">
@@ -16592,11 +14720,8 @@
       <c r="F624" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G624" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H624" t="s">
-        <v>8</v>
+      <c r="G624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625">
@@ -16618,11 +14743,8 @@
       <c r="F625" t="n">
         <v>0.0175999999046326</v>
       </c>
-      <c r="G625" t="n">
-        <v>0.0175999999046326</v>
-      </c>
-      <c r="H625" t="s">
-        <v>8</v>
+      <c r="G625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -16644,11 +14766,8 @@
       <c r="F626" t="n">
         <v>0.0186000000685453</v>
       </c>
-      <c r="G626" t="n">
-        <v>0.0186000000685453</v>
-      </c>
-      <c r="H626" t="s">
-        <v>8</v>
+      <c r="G626" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="627">
@@ -16670,11 +14789,8 @@
       <c r="F627" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G627" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H627" t="s">
-        <v>8</v>
+      <c r="G627" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="628">
@@ -16696,11 +14812,8 @@
       <c r="F628" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G628" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H628" t="s">
-        <v>8</v>
+      <c r="G628" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="629">
@@ -16722,11 +14835,8 @@
       <c r="F629" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G629" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H629" t="s">
-        <v>8</v>
+      <c r="G629" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="630">
@@ -16748,11 +14858,8 @@
       <c r="F630" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G630" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H630" t="s">
-        <v>8</v>
+      <c r="G630" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -16774,11 +14881,8 @@
       <c r="F631" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G631" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H631" t="s">
-        <v>8</v>
+      <c r="G631" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="632">
@@ -16800,11 +14904,8 @@
       <c r="F632" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G632" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H632" t="s">
-        <v>8</v>
+      <c r="G632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633">
@@ -16826,11 +14927,8 @@
       <c r="F633" t="n">
         <v>0.0172000005841255</v>
       </c>
-      <c r="G633" t="n">
-        <v>0.0172000005841255</v>
-      </c>
-      <c r="H633" t="s">
-        <v>8</v>
+      <c r="G633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -16852,11 +14950,8 @@
       <c r="F634" t="n">
         <v>0.017000000923872</v>
       </c>
-      <c r="G634" t="n">
-        <v>0.017000000923872</v>
-      </c>
-      <c r="H634" t="s">
-        <v>8</v>
+      <c r="G634" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -16878,11 +14973,8 @@
       <c r="F635" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G635" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H635" t="s">
-        <v>8</v>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -16904,11 +14996,8 @@
       <c r="F636" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G636" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H636" t="s">
-        <v>8</v>
+      <c r="G636" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="637">
@@ -16930,11 +15019,8 @@
       <c r="F637" t="n">
         <v>0.017400000244379</v>
       </c>
-      <c r="G637" t="n">
-        <v>0.017400000244379</v>
-      </c>
-      <c r="H637" t="s">
-        <v>8</v>
+      <c r="G637" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="638">
@@ -16956,11 +15042,8 @@
       <c r="F638" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G638" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H638" t="s">
-        <v>8</v>
+      <c r="G638" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="639">
@@ -16982,11 +15065,8 @@
       <c r="F639" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G639" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H639" t="s">
-        <v>8</v>
+      <c r="G639" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="640">
@@ -17008,11 +15088,8 @@
       <c r="F640" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G640" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H640" t="s">
-        <v>8</v>
+      <c r="G640" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="641">
@@ -17034,11 +15111,8 @@
       <c r="F641" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G641" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H641" t="s">
-        <v>8</v>
+      <c r="G641" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -17060,11 +15134,8 @@
       <c r="F642" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G642" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H642" t="s">
-        <v>8</v>
+      <c r="G642" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -17086,11 +15157,8 @@
       <c r="F643" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G643" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H643" t="s">
-        <v>8</v>
+      <c r="G643" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="644">
@@ -17112,11 +15180,8 @@
       <c r="F644" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G644" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H644" t="s">
-        <v>8</v>
+      <c r="G644" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -17138,11 +15203,8 @@
       <c r="F645" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G645" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H645" t="s">
-        <v>8</v>
+      <c r="G645" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -17164,11 +15226,8 @@
       <c r="F646" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G646" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H646" t="s">
-        <v>8</v>
+      <c r="G646" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="647">
@@ -17190,11 +15249,8 @@
       <c r="F647" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G647" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H647" t="s">
-        <v>8</v>
+      <c r="G647" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -17216,11 +15272,8 @@
       <c r="F648" t="n">
         <v>0.0177999995648861</v>
       </c>
-      <c r="G648" t="n">
-        <v>0.0177999995648861</v>
-      </c>
-      <c r="H648" t="s">
-        <v>8</v>
+      <c r="G648" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -17242,11 +15295,8 @@
       <c r="F649" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G649" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H649" t="s">
-        <v>8</v>
+      <c r="G649" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="650">
@@ -17268,11 +15318,8 @@
       <c r="F650" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G650" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H650" t="s">
-        <v>8</v>
+      <c r="G650" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="651">
@@ -17294,11 +15341,8 @@
       <c r="F651" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G651" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H651" t="s">
-        <v>8</v>
+      <c r="G651" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="652">
@@ -17320,11 +15364,8 @@
       <c r="F652" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G652" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H652" t="s">
-        <v>8</v>
+      <c r="G652" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="653">
@@ -17346,11 +15387,8 @@
       <c r="F653" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G653" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H653" t="s">
-        <v>8</v>
+      <c r="G653" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -17372,11 +15410,8 @@
       <c r="F654" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G654" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H654" t="s">
-        <v>8</v>
+      <c r="G654" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="655">
@@ -17398,11 +15433,8 @@
       <c r="F655" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G655" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H655" t="s">
-        <v>8</v>
+      <c r="G655" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="656">
@@ -17424,11 +15456,8 @@
       <c r="F656" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G656" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H656" t="s">
-        <v>8</v>
+      <c r="G656" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="657">
@@ -17450,11 +15479,8 @@
       <c r="F657" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G657" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H657" t="s">
-        <v>8</v>
+      <c r="G657" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="658">
@@ -17476,11 +15502,8 @@
       <c r="F658" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G658" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H658" t="s">
-        <v>8</v>
+      <c r="G658" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -17502,11 +15525,8 @@
       <c r="F659" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G659" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H659" t="s">
-        <v>8</v>
+      <c r="G659" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -17528,11 +15548,8 @@
       <c r="F660" t="n">
         <v>0.0179999992251396</v>
       </c>
-      <c r="G660" t="n">
-        <v>0.0179999992251396</v>
-      </c>
-      <c r="H660" t="s">
-        <v>8</v>
+      <c r="G660" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -17554,11 +15571,8 @@
       <c r="F661" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G661" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H661" t="s">
-        <v>8</v>
+      <c r="G661" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="662">
@@ -17580,11 +15594,8 @@
       <c r="F662" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G662" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H662" t="s">
-        <v>8</v>
+      <c r="G662" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="663">
@@ -17606,11 +15617,8 @@
       <c r="F663" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G663" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H663" t="s">
-        <v>8</v>
+      <c r="G663" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="664">
@@ -17632,11 +15640,8 @@
       <c r="F664" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G664" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H664" t="s">
-        <v>8</v>
+      <c r="G664" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="665">
@@ -17658,11 +15663,8 @@
       <c r="F665" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G665" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H665" t="s">
-        <v>8</v>
+      <c r="G665" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="666">
@@ -17684,11 +15686,8 @@
       <c r="F666" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G666" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H666" t="s">
-        <v>8</v>
+      <c r="G666" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="667">
@@ -17710,11 +15709,8 @@
       <c r="F667" t="n">
         <v>0.0182000007480383</v>
       </c>
-      <c r="G667" t="n">
-        <v>0.0182000007480383</v>
-      </c>
-      <c r="H667" t="s">
-        <v>8</v>
+      <c r="G667" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="668">
@@ -17736,11 +15732,8 @@
       <c r="F668" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H668" t="s">
-        <v>8</v>
+      <c r="G668" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="669">
@@ -17762,11 +15755,8 @@
       <c r="F669" t="n">
         <v>0.0184000004082918</v>
       </c>
-      <c r="G669" t="n">
-        <v>0.0184000004082918</v>
-      </c>
-      <c r="H669" t="s">
-        <v>8</v>
+      <c r="G669" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -17788,11 +15778,8 @@
       <c r="F670" t="n">
         <v>0.0197999998927116</v>
       </c>
-      <c r="G670" t="n">
-        <v>0.0197999998927116</v>
-      </c>
-      <c r="H670" t="s">
-        <v>8</v>
+      <c r="G670" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -17814,11 +15801,8 @@
       <c r="F671" t="n">
         <v>0.0204000007361174</v>
       </c>
-      <c r="G671" t="n">
-        <v>0.0204000007361174</v>
-      </c>
-      <c r="H671" t="s">
-        <v>8</v>
+      <c r="G671" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="672">
@@ -17840,11 +15824,8 @@
       <c r="F672" t="n">
         <v>0.0201999992132187</v>
       </c>
-      <c r="G672" t="n">
-        <v>0.0201999992132187</v>
-      </c>
-      <c r="H672" t="s">
-        <v>8</v>
+      <c r="G672" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="673">
@@ -17866,11 +15847,8 @@
       <c r="F673" t="n">
         <v>0.0206000003963709</v>
       </c>
-      <c r="G673" t="n">
-        <v>0.0206000003963709</v>
-      </c>
-      <c r="H673" t="s">
-        <v>8</v>
+      <c r="G673" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="674">
@@ -17892,11 +15870,8 @@
       <c r="F674" t="n">
         <v>0.0208000000566244</v>
       </c>
-      <c r="G674" t="n">
-        <v>0.0208000000566244</v>
-      </c>
-      <c r="H674" t="s">
-        <v>8</v>
+      <c r="G674" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="675">
@@ -17918,11 +15893,8 @@
       <c r="F675" t="n">
         <v>0.0211999993771315</v>
       </c>
-      <c r="G675" t="n">
-        <v>0.0211999993771315</v>
-      </c>
-      <c r="H675" t="s">
-        <v>8</v>
+      <c r="G675" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="676">
@@ -17944,11 +15916,8 @@
       <c r="F676" t="n">
         <v>0.02280000038445</v>
       </c>
-      <c r="G676" t="n">
-        <v>0.02280000038445</v>
-      </c>
-      <c r="H676" t="s">
-        <v>8</v>
+      <c r="G676" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="677">
@@ -17970,11 +15939,8 @@
       <c r="F677" t="n">
         <v>0.0216000005602837</v>
       </c>
-      <c r="G677" t="n">
-        <v>0.0216000005602837</v>
-      </c>
-      <c r="H677" t="s">
-        <v>8</v>
+      <c r="G677" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="678">
@@ -17996,11 +15962,8 @@
       <c r="F678" t="n">
         <v>0.0221999995410442</v>
       </c>
-      <c r="G678" t="n">
-        <v>0.0221999995410442</v>
-      </c>
-      <c r="H678" t="s">
-        <v>8</v>
+      <c r="G678" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="679">
@@ -18022,11 +15985,8 @@
       <c r="F679" t="n">
         <v>0.0233999993652105</v>
       </c>
-      <c r="G679" t="n">
-        <v>0.0233999993652105</v>
-      </c>
-      <c r="H679" t="s">
-        <v>8</v>
+      <c r="G679" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="680">
@@ -18048,11 +16008,8 @@
       <c r="F680" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G680" t="n">
-        <v>0.0243999995291233</v>
-      </c>
-      <c r="H680" t="s">
-        <v>8</v>
+      <c r="G680" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="681">
@@ -18074,11 +16031,8 @@
       <c r="F681" t="n">
         <v>0.0240000002086163</v>
       </c>
-      <c r="G681" t="n">
-        <v>0.0240000002086163</v>
-      </c>
-      <c r="H681" t="s">
-        <v>8</v>
+      <c r="G681" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="682">
@@ -18100,11 +16054,8 @@
       <c r="F682" t="n">
         <v>0.0243999995291233</v>
       </c>
-      <c r="G682" t="n">
-        <v>0.0243999995291233</v>
-      </c>
-      <c r="H682" t="s">
-        <v>8</v>
+      <c r="G682" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="683">
@@ -18126,11 +16077,8 @@
       <c r="F683" t="n">
         <v>0.0253999996930361</v>
       </c>
-      <c r="G683" t="n">
-        <v>0.0253999996930361</v>
-      </c>
-      <c r="H683" t="s">
-        <v>8</v>
+      <c r="G683" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="684">
@@ -18152,11 +16100,8 @@
       <c r="F684" t="n">
         <v>0.0252000000327826</v>
       </c>
-      <c r="G684" t="n">
-        <v>0.0252000000327826</v>
-      </c>
-      <c r="H684" t="s">
-        <v>8</v>
+      <c r="G684" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="685">
@@ -18178,11 +16123,8 @@
       <c r="F685" t="n">
         <v>0.0248000007122755</v>
       </c>
-      <c r="G685" t="n">
-        <v>0.0248000007122755</v>
-      </c>
-      <c r="H685" t="s">
-        <v>8</v>
+      <c r="G685" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="686">
@@ -18204,11 +16146,8 @@
       <c r="F686" t="n">
         <v>0.0238000005483627</v>
       </c>
-      <c r="G686" t="n">
-        <v>0.0238000005483627</v>
-      </c>
-      <c r="H686" t="s">
-        <v>8</v>
+      <c r="G686" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="687">
@@ -18230,11 +16169,8 @@
       <c r="F687" t="n">
         <v>0.0238000005483627</v>
       </c>
-      <c r="G687" t="n">
-        <v>0.0238000005483627</v>
-      </c>
-      <c r="H687" t="s">
-        <v>8</v>
+      <c r="G687" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -16173,6 +16173,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B688" t="n">
+        <v>5153871</v>
+      </c>
+      <c r="C688" t="n">
+        <v>0.0241999998688698</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="E688" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="G688" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/KK.MI.xlsx
+++ b/data/KK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adj_close</t>
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
@@ -394,6 +397,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -414,8 +420,11 @@
       <c r="F2" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -437,8 +446,11 @@
       <c r="F3" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -460,8 +472,11 @@
       <c r="F4" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -483,8 +498,11 @@
       <c r="F5" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -506,8 +524,11 @@
       <c r="F6" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -529,8 +550,11 @@
       <c r="F7" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -552,8 +576,11 @@
       <c r="F8" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -575,8 +602,11 @@
       <c r="F9" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -598,8 +628,11 @@
       <c r="F10" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -621,8 +654,11 @@
       <c r="F11" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +680,11 @@
       <c r="F12" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -667,8 +706,11 @@
       <c r="F13" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -690,8 +732,11 @@
       <c r="F14" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -713,8 +758,11 @@
       <c r="F15" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -736,8 +784,11 @@
       <c r="F16" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -759,8 +810,11 @@
       <c r="F17" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -782,8 +836,11 @@
       <c r="F18" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,8 +862,11 @@
       <c r="F19" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -828,8 +888,11 @@
       <c r="F20" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -851,8 +914,11 @@
       <c r="F21" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -874,8 +940,11 @@
       <c r="F22" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -897,8 +966,11 @@
       <c r="F23" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -920,8 +992,11 @@
       <c r="F24" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -943,8 +1018,11 @@
       <c r="F25" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -966,8 +1044,11 @@
       <c r="F26" t="n">
         <v>0.0203060004860163</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" t="n">
+        <v>0.0203060004860163</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -989,8 +1070,11 @@
       <c r="F27" t="n">
         <v>0.019845999777317</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" t="n">
+        <v>0.019845999777317</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1012,8 +1096,11 @@
       <c r="F28" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1035,8 +1122,11 @@
       <c r="F29" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1058,8 +1148,11 @@
       <c r="F30" t="n">
         <v>0.01923399977386</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
+      <c r="G30" t="n">
+        <v>0.01923399977386</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1081,8 +1174,11 @@
       <c r="F31" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1104,8 +1200,11 @@
       <c r="F32" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1127,8 +1226,11 @@
       <c r="F33" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1150,8 +1252,11 @@
       <c r="F34" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1173,8 +1278,11 @@
       <c r="F35" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1196,8 +1304,11 @@
       <c r="F36" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1219,8 +1330,11 @@
       <c r="F37" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1242,8 +1356,11 @@
       <c r="F38" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1265,8 +1382,11 @@
       <c r="F39" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1288,8 +1408,11 @@
       <c r="F40" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1311,8 +1434,11 @@
       <c r="F41" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1334,8 +1460,11 @@
       <c r="F42" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="G42" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1357,8 +1486,11 @@
       <c r="F43" t="n">
         <v>0.0191319994628429</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>0.0191319994628429</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1380,8 +1512,11 @@
       <c r="F44" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,8 +1538,11 @@
       <c r="F45" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -1426,8 +1564,11 @@
       <c r="F46" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1449,8 +1590,11 @@
       <c r="F47" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1472,8 +1616,11 @@
       <c r="F48" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1495,8 +1642,11 @@
       <c r="F49" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1518,8 +1668,11 @@
       <c r="F50" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1541,8 +1694,11 @@
       <c r="F51" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1564,8 +1720,11 @@
       <c r="F52" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1587,8 +1746,11 @@
       <c r="F53" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -1610,8 +1772,11 @@
       <c r="F54" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1633,8 +1798,11 @@
       <c r="F55" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1656,8 +1824,11 @@
       <c r="F56" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1679,8 +1850,11 @@
       <c r="F57" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -1702,8 +1876,11 @@
       <c r="F58" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1725,8 +1902,11 @@
       <c r="F59" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1748,8 +1928,11 @@
       <c r="F60" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G60" t="s">
-        <v>7</v>
+      <c r="G60" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1771,8 +1954,11 @@
       <c r="F61" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G61" t="s">
-        <v>7</v>
+      <c r="G61" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1794,8 +1980,11 @@
       <c r="F62" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G62" t="s">
-        <v>7</v>
+      <c r="G62" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1817,8 +2006,11 @@
       <c r="F63" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1840,8 +2032,11 @@
       <c r="F64" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -1863,8 +2058,11 @@
       <c r="F65" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -1886,8 +2084,11 @@
       <c r="F66" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1909,8 +2110,11 @@
       <c r="F67" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1932,8 +2136,11 @@
       <c r="F68" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -1955,8 +2162,11 @@
       <c r="F69" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1978,8 +2188,11 @@
       <c r="F70" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -2001,8 +2214,11 @@
       <c r="F71" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2024,8 +2240,11 @@
       <c r="F72" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2047,8 +2266,11 @@
       <c r="F73" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -2070,8 +2292,11 @@
       <c r="F74" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -2093,8 +2318,11 @@
       <c r="F75" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -2116,8 +2344,11 @@
       <c r="F76" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2139,8 +2370,11 @@
       <c r="F77" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -2162,8 +2396,11 @@
       <c r="F78" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -2185,8 +2422,11 @@
       <c r="F79" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2208,8 +2448,11 @@
       <c r="F80" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
+      <c r="G80" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -2231,8 +2474,11 @@
       <c r="F81" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2254,8 +2500,11 @@
       <c r="F82" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2277,8 +2526,11 @@
       <c r="F83" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2300,8 +2552,11 @@
       <c r="F84" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2323,8 +2578,11 @@
       <c r="F85" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2346,8 +2604,11 @@
       <c r="F86" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -2369,8 +2630,11 @@
       <c r="F87" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -2392,8 +2656,11 @@
       <c r="F88" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2415,8 +2682,11 @@
       <c r="F89" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -2438,8 +2708,11 @@
       <c r="F90" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2461,8 +2734,11 @@
       <c r="F91" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2484,8 +2760,11 @@
       <c r="F92" t="n">
         <v>0.0202040001749992</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" t="n">
+        <v>0.0202040001749992</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2507,8 +2786,11 @@
       <c r="F93" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2530,8 +2812,11 @@
       <c r="F94" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2553,8 +2838,11 @@
       <c r="F95" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2576,8 +2864,11 @@
       <c r="F96" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2599,8 +2890,11 @@
       <c r="F97" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G97" t="s">
-        <v>7</v>
+      <c r="G97" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2622,8 +2916,11 @@
       <c r="F98" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G98" t="s">
-        <v>7</v>
+      <c r="G98" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -2645,8 +2942,11 @@
       <c r="F99" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -2668,8 +2968,11 @@
       <c r="F100" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -2691,8 +2994,11 @@
       <c r="F101" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2714,8 +3020,11 @@
       <c r="F102" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2737,8 +3046,11 @@
       <c r="F103" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -2760,8 +3072,11 @@
       <c r="F104" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -2783,8 +3098,11 @@
       <c r="F105" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2806,8 +3124,11 @@
       <c r="F106" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G106" t="s">
-        <v>7</v>
+      <c r="G106" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -2829,8 +3150,11 @@
       <c r="F107" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -2852,8 +3176,11 @@
       <c r="F108" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -2875,8 +3202,11 @@
       <c r="F109" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2898,8 +3228,11 @@
       <c r="F110" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -2921,8 +3254,11 @@
       <c r="F111" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -2944,8 +3280,11 @@
       <c r="F112" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -2967,8 +3306,11 @@
       <c r="F113" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2990,8 +3332,11 @@
       <c r="F114" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3013,8 +3358,11 @@
       <c r="F115" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -3036,8 +3384,11 @@
       <c r="F116" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -3059,8 +3410,11 @@
       <c r="F117" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -3082,8 +3436,11 @@
       <c r="F118" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3105,8 +3462,11 @@
       <c r="F119" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -3128,8 +3488,11 @@
       <c r="F120" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121">
@@ -3151,8 +3514,11 @@
       <c r="F121" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="G121" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3174,8 +3540,11 @@
       <c r="F122" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -3197,8 +3566,11 @@
       <c r="F123" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H123" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3220,8 +3592,11 @@
       <c r="F124" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -3243,8 +3618,11 @@
       <c r="F125" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H125" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3266,8 +3644,11 @@
       <c r="F126" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H126" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -3289,8 +3670,11 @@
       <c r="F127" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H127" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3312,8 +3696,11 @@
       <c r="F128" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H128" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -3335,8 +3722,11 @@
       <c r="F129" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H129" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -3358,8 +3748,11 @@
       <c r="F130" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H130" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -3381,8 +3774,11 @@
       <c r="F131" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H131" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132">
@@ -3404,8 +3800,11 @@
       <c r="F132" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H132" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -3427,8 +3826,11 @@
       <c r="F133" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H133" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134">
@@ -3450,8 +3852,11 @@
       <c r="F134" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -3473,8 +3878,11 @@
       <c r="F135" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G135" t="s">
-        <v>7</v>
+      <c r="G135" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136">
@@ -3496,8 +3904,11 @@
       <c r="F136" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G136" t="s">
-        <v>7</v>
+      <c r="G136" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137">
@@ -3519,8 +3930,11 @@
       <c r="F137" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G137" t="s">
-        <v>7</v>
+      <c r="G137" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -3542,8 +3956,11 @@
       <c r="F138" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3565,8 +3982,11 @@
       <c r="F139" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140">
@@ -3588,8 +4008,11 @@
       <c r="F140" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141">
@@ -3611,8 +4034,11 @@
       <c r="F141" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -3634,8 +4060,11 @@
       <c r="F142" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,8 +4086,11 @@
       <c r="F143" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144">
@@ -3680,8 +4112,11 @@
       <c r="F144" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -3703,8 +4138,11 @@
       <c r="F145" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146">
@@ -3726,8 +4164,11 @@
       <c r="F146" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3749,8 +4190,11 @@
       <c r="F147" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148">
@@ -3772,8 +4216,11 @@
       <c r="F148" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3795,8 +4242,11 @@
       <c r="F149" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
+      <c r="G149" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150">
@@ -3818,8 +4268,11 @@
       <c r="F150" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -3841,8 +4294,11 @@
       <c r="F151" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
@@ -3864,8 +4320,11 @@
       <c r="F152" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G152" t="s">
-        <v>7</v>
+      <c r="G152" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3887,8 +4346,11 @@
       <c r="F153" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G153" t="s">
-        <v>7</v>
+      <c r="G153" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,8 +4372,11 @@
       <c r="F154" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3933,8 +4398,11 @@
       <c r="F155" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156">
@@ -3956,8 +4424,11 @@
       <c r="F156" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -3979,8 +4450,11 @@
       <c r="F157" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158">
@@ -4002,8 +4476,11 @@
       <c r="F158" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -4025,8 +4502,11 @@
       <c r="F159" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
+      <c r="G159" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -4048,8 +4528,11 @@
       <c r="F160" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G160" t="s">
-        <v>7</v>
+      <c r="G160" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161">
@@ -4071,8 +4554,11 @@
       <c r="F161" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G161" t="s">
-        <v>7</v>
+      <c r="G161" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162">
@@ -4094,8 +4580,11 @@
       <c r="F162" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G162" t="s">
-        <v>7</v>
+      <c r="G162" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -4117,8 +4606,11 @@
       <c r="F163" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G163" t="s">
-        <v>7</v>
+      <c r="G163" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -4140,8 +4632,11 @@
       <c r="F164" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G164" t="s">
-        <v>7</v>
+      <c r="G164" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -4163,8 +4658,11 @@
       <c r="F165" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G165" t="s">
-        <v>7</v>
+      <c r="G165" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -4186,8 +4684,11 @@
       <c r="F166" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -4209,8 +4710,11 @@
       <c r="F167" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -4232,8 +4736,11 @@
       <c r="F168" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169">
@@ -4255,8 +4762,11 @@
       <c r="F169" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4278,8 +4788,11 @@
       <c r="F170" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H170" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -4301,8 +4814,11 @@
       <c r="F171" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G171" t="s">
-        <v>7</v>
+      <c r="G171" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4324,8 +4840,11 @@
       <c r="F172" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G172" t="s">
-        <v>7</v>
+      <c r="G172" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H172" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4347,8 +4866,11 @@
       <c r="F173" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H173" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4370,8 +4892,11 @@
       <c r="F174" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
+      <c r="G174" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H174" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -4393,8 +4918,11 @@
       <c r="F175" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
+      <c r="G175" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H175" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176">
@@ -4416,8 +4944,11 @@
       <c r="F176" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G176" t="s">
-        <v>7</v>
+      <c r="G176" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H176" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -4439,8 +4970,11 @@
       <c r="F177" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G177" t="s">
-        <v>7</v>
+      <c r="G177" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H177" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -4462,8 +4996,11 @@
       <c r="F178" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H178" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4485,8 +5022,11 @@
       <c r="F179" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
+      <c r="G179" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H179" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4508,8 +5048,11 @@
       <c r="F180" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G180" t="s">
-        <v>7</v>
+      <c r="G180" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H180" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
@@ -4531,8 +5074,11 @@
       <c r="F181" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G181" t="s">
-        <v>7</v>
+      <c r="G181" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H181" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182">
@@ -4554,8 +5100,11 @@
       <c r="F182" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G182" t="s">
-        <v>7</v>
+      <c r="G182" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H182" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183">
@@ -4577,8 +5126,11 @@
       <c r="F183" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G183" t="s">
-        <v>7</v>
+      <c r="G183" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H183" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
@@ -4600,8 +5152,11 @@
       <c r="F184" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G184" t="s">
-        <v>7</v>
+      <c r="G184" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185">
@@ -4623,8 +5178,11 @@
       <c r="F185" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G185" t="s">
-        <v>7</v>
+      <c r="G185" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H185" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186">
@@ -4646,8 +5204,11 @@
       <c r="F186" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G186" t="s">
-        <v>7</v>
+      <c r="G186" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H186" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187">
@@ -4669,8 +5230,11 @@
       <c r="F187" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G187" t="s">
-        <v>7</v>
+      <c r="G187" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H187" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4692,8 +5256,11 @@
       <c r="F188" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G188" t="s">
-        <v>7</v>
+      <c r="G188" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H188" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189">
@@ -4715,8 +5282,11 @@
       <c r="F189" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G189" t="s">
-        <v>7</v>
+      <c r="G189" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H189" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4738,8 +5308,11 @@
       <c r="F190" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G190" t="s">
-        <v>7</v>
+      <c r="G190" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H190" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4761,8 +5334,11 @@
       <c r="F191" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G191" t="s">
-        <v>7</v>
+      <c r="G191" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H191" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -4784,8 +5360,11 @@
       <c r="F192" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G192" t="s">
-        <v>7</v>
+      <c r="G192" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H192" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4807,8 +5386,11 @@
       <c r="F193" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G193" t="s">
-        <v>7</v>
+      <c r="G193" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H193" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194">
@@ -4830,8 +5412,11 @@
       <c r="F194" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G194" t="s">
-        <v>7</v>
+      <c r="G194" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H194" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195">
@@ -4853,8 +5438,11 @@
       <c r="F195" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G195" t="s">
-        <v>7</v>
+      <c r="G195" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H195" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -4876,8 +5464,11 @@
       <c r="F196" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G196" t="s">
-        <v>7</v>
+      <c r="G196" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H196" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -4899,8 +5490,11 @@
       <c r="F197" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G197" t="s">
-        <v>7</v>
+      <c r="G197" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -4922,8 +5516,11 @@
       <c r="F198" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G198" t="s">
-        <v>7</v>
+      <c r="G198" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H198" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199">
@@ -4945,8 +5542,11 @@
       <c r="F199" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G199" t="s">
-        <v>7</v>
+      <c r="G199" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H199" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -4968,8 +5568,11 @@
       <c r="F200" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G200" t="s">
-        <v>7</v>
+      <c r="G200" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H200" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201">
@@ -4991,8 +5594,11 @@
       <c r="F201" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G201" t="s">
-        <v>7</v>
+      <c r="G201" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H201" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -5014,8 +5620,11 @@
       <c r="F202" t="n">
         <v>0.0187749993056059</v>
       </c>
-      <c r="G202" t="s">
-        <v>7</v>
+      <c r="G202" t="n">
+        <v>0.0187749993056059</v>
+      </c>
+      <c r="H202" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -5037,8 +5646,11 @@
       <c r="F203" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G203" t="s">
-        <v>7</v>
+      <c r="G203" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204">
@@ -5060,8 +5672,11 @@
       <c r="F204" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G204" t="s">
-        <v>7</v>
+      <c r="G204" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H204" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205">
@@ -5083,8 +5698,11 @@
       <c r="F205" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G205" t="s">
-        <v>7</v>
+      <c r="G205" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H205" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206">
@@ -5106,8 +5724,11 @@
       <c r="F206" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G206" t="s">
-        <v>7</v>
+      <c r="G206" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H206" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207">
@@ -5129,8 +5750,11 @@
       <c r="F207" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G207" t="s">
-        <v>7</v>
+      <c r="G207" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H207" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -5152,8 +5776,11 @@
       <c r="F208" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G208" t="s">
-        <v>7</v>
+      <c r="G208" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H208" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209">
@@ -5175,8 +5802,11 @@
       <c r="F209" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G209" t="s">
-        <v>7</v>
+      <c r="G209" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H209" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -5198,8 +5828,11 @@
       <c r="F210" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G210" t="s">
-        <v>7</v>
+      <c r="G210" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H210" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5221,8 +5854,11 @@
       <c r="F211" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G211" t="s">
-        <v>7</v>
+      <c r="G211" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H211" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -5244,8 +5880,11 @@
       <c r="F212" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G212" t="s">
-        <v>7</v>
+      <c r="G212" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H212" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213">
@@ -5267,8 +5906,11 @@
       <c r="F213" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G213" t="s">
-        <v>7</v>
+      <c r="G213" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H213" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214">
@@ -5290,8 +5932,11 @@
       <c r="F214" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G214" t="s">
-        <v>7</v>
+      <c r="G214" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H214" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5313,8 +5958,11 @@
       <c r="F215" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G215" t="s">
-        <v>7</v>
+      <c r="G215" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H215" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5336,8 +5984,11 @@
       <c r="F216" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G216" t="s">
-        <v>7</v>
+      <c r="G216" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H216" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -5359,8 +6010,11 @@
       <c r="F217" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G217" t="s">
-        <v>7</v>
+      <c r="G217" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H217" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5382,8 +6036,11 @@
       <c r="F218" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G218" t="s">
-        <v>7</v>
+      <c r="G218" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H218" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -5405,8 +6062,11 @@
       <c r="F219" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G219" t="s">
-        <v>7</v>
+      <c r="G219" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H219" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -5428,8 +6088,11 @@
       <c r="F220" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G220" t="s">
-        <v>7</v>
+      <c r="G220" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H220" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -5451,8 +6114,11 @@
       <c r="F221" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G221" t="s">
-        <v>7</v>
+      <c r="G221" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H221" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222">
@@ -5474,8 +6140,11 @@
       <c r="F222" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G222" t="s">
-        <v>7</v>
+      <c r="G222" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H222" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -5497,8 +6166,11 @@
       <c r="F223" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G223" t="s">
-        <v>7</v>
+      <c r="G223" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H223" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224">
@@ -5520,8 +6192,11 @@
       <c r="F224" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G224" t="s">
-        <v>7</v>
+      <c r="G224" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H224" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225">
@@ -5543,8 +6218,11 @@
       <c r="F225" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G225" t="s">
-        <v>7</v>
+      <c r="G225" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H225" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -5566,8 +6244,11 @@
       <c r="F226" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G226" t="s">
-        <v>7</v>
+      <c r="G226" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H226" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5589,8 +6270,11 @@
       <c r="F227" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G227" t="s">
-        <v>7</v>
+      <c r="G227" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H227" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5612,8 +6296,11 @@
       <c r="F228" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G228" t="s">
-        <v>7</v>
+      <c r="G228" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H228" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229">
@@ -5635,8 +6322,11 @@
       <c r="F229" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G229" t="s">
-        <v>7</v>
+      <c r="G229" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H229" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5658,8 +6348,11 @@
       <c r="F230" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G230" t="s">
-        <v>7</v>
+      <c r="G230" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H230" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5681,8 +6374,11 @@
       <c r="F231" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G231" t="s">
-        <v>7</v>
+      <c r="G231" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H231" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5704,8 +6400,11 @@
       <c r="F232" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G232" t="s">
-        <v>7</v>
+      <c r="G232" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H232" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5727,8 +6426,11 @@
       <c r="F233" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G233" t="s">
-        <v>7</v>
+      <c r="G233" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H233" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234">
@@ -5750,8 +6452,11 @@
       <c r="F234" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G234" t="s">
-        <v>7</v>
+      <c r="G234" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H234" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -5773,8 +6478,11 @@
       <c r="F235" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G235" t="s">
-        <v>7</v>
+      <c r="G235" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H235" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -5796,8 +6504,11 @@
       <c r="F236" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G236" t="s">
-        <v>7</v>
+      <c r="G236" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H236" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -5819,8 +6530,11 @@
       <c r="F237" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G237" t="s">
-        <v>7</v>
+      <c r="G237" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H237" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -5842,8 +6556,11 @@
       <c r="F238" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G238" t="s">
-        <v>7</v>
+      <c r="G238" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H238" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239">
@@ -5865,8 +6582,11 @@
       <c r="F239" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G239" t="s">
-        <v>7</v>
+      <c r="G239" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H239" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5888,8 +6608,11 @@
       <c r="F240" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G240" t="s">
-        <v>7</v>
+      <c r="G240" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H240" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241">
@@ -5911,8 +6634,11 @@
       <c r="F241" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G241" t="s">
-        <v>7</v>
+      <c r="G241" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H241" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -5934,8 +6660,11 @@
       <c r="F242" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G242" t="s">
-        <v>7</v>
+      <c r="G242" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H242" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5957,8 +6686,11 @@
       <c r="F243" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G243" t="s">
-        <v>7</v>
+      <c r="G243" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H243" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244">
@@ -5980,8 +6712,11 @@
       <c r="F244" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G244" t="s">
-        <v>7</v>
+      <c r="G244" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H244" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245">
@@ -6003,8 +6738,11 @@
       <c r="F245" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G245" t="s">
-        <v>7</v>
+      <c r="G245" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H245" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6026,8 +6764,11 @@
       <c r="F246" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G246" t="s">
-        <v>7</v>
+      <c r="G246" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H246" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -6049,8 +6790,11 @@
       <c r="F247" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G247" t="s">
-        <v>7</v>
+      <c r="G247" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H247" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248">
@@ -6072,8 +6816,11 @@
       <c r="F248" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G248" t="s">
-        <v>7</v>
+      <c r="G248" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H248" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -6095,8 +6842,11 @@
       <c r="F249" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G249" t="s">
-        <v>7</v>
+      <c r="G249" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H249" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -6118,8 +6868,11 @@
       <c r="F250" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G250" t="s">
-        <v>7</v>
+      <c r="G250" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H250" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251">
@@ -6141,8 +6894,11 @@
       <c r="F251" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G251" t="s">
-        <v>7</v>
+      <c r="G251" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H251" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6164,8 +6920,11 @@
       <c r="F252" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G252" t="s">
-        <v>7</v>
+      <c r="G252" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H252" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6187,8 +6946,11 @@
       <c r="F253" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G253" t="s">
-        <v>7</v>
+      <c r="G253" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H253" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6210,8 +6972,11 @@
       <c r="F254" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G254" t="s">
-        <v>7</v>
+      <c r="G254" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H254" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6233,8 +6998,11 @@
       <c r="F255" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G255" t="s">
-        <v>7</v>
+      <c r="G255" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6256,8 +7024,11 @@
       <c r="F256" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G256" t="s">
-        <v>7</v>
+      <c r="G256" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257">
@@ -6279,8 +7050,11 @@
       <c r="F257" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G257" t="s">
-        <v>7</v>
+      <c r="G257" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6302,8 +7076,11 @@
       <c r="F258" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G258" t="s">
-        <v>7</v>
+      <c r="G258" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259">
@@ -6325,8 +7102,11 @@
       <c r="F259" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G259" t="s">
-        <v>7</v>
+      <c r="G259" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H259" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260">
@@ -6348,8 +7128,11 @@
       <c r="F260" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G260" t="s">
-        <v>7</v>
+      <c r="G260" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H260" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261">
@@ -6371,8 +7154,11 @@
       <c r="F261" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G261" t="s">
-        <v>7</v>
+      <c r="G261" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H261" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -6394,8 +7180,11 @@
       <c r="F262" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G262" t="s">
-        <v>7</v>
+      <c r="G262" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H262" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263">
@@ -6417,8 +7206,11 @@
       <c r="F263" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G263" t="s">
-        <v>7</v>
+      <c r="G263" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H263" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264">
@@ -6440,8 +7232,11 @@
       <c r="F264" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G264" t="s">
-        <v>7</v>
+      <c r="G264" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H264" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265">
@@ -6463,8 +7258,11 @@
       <c r="F265" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G265" t="s">
-        <v>7</v>
+      <c r="G265" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H265" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -6486,8 +7284,11 @@
       <c r="F266" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G266" t="s">
-        <v>7</v>
+      <c r="G266" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H266" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6509,8 +7310,11 @@
       <c r="F267" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G267" t="s">
-        <v>7</v>
+      <c r="G267" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H267" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -6532,8 +7336,11 @@
       <c r="F268" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G268" t="s">
-        <v>7</v>
+      <c r="G268" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H268" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -6555,8 +7362,11 @@
       <c r="F269" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G269" t="s">
-        <v>7</v>
+      <c r="G269" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H269" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -6578,8 +7388,11 @@
       <c r="F270" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G270" t="s">
-        <v>7</v>
+      <c r="G270" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H270" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271">
@@ -6601,8 +7414,11 @@
       <c r="F271" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G271" t="s">
-        <v>7</v>
+      <c r="G271" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H271" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -6624,8 +7440,11 @@
       <c r="F272" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G272" t="s">
-        <v>7</v>
+      <c r="G272" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H272" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -6647,8 +7466,11 @@
       <c r="F273" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
+      <c r="G273" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H273" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6670,8 +7492,11 @@
       <c r="F274" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G274" t="s">
-        <v>7</v>
+      <c r="G274" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H274" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -6693,8 +7518,11 @@
       <c r="F275" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G275" t="s">
-        <v>7</v>
+      <c r="G275" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H275" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6716,8 +7544,11 @@
       <c r="F276" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G276" t="s">
-        <v>7</v>
+      <c r="G276" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H276" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6739,8 +7570,11 @@
       <c r="F277" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G277" t="s">
-        <v>7</v>
+      <c r="G277" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H277" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6762,8 +7596,11 @@
       <c r="F278" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G278" t="s">
-        <v>7</v>
+      <c r="G278" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H278" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6785,8 +7622,11 @@
       <c r="F279" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G279" t="s">
-        <v>7</v>
+      <c r="G279" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H279" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280">
@@ -6808,8 +7648,11 @@
       <c r="F280" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G280" t="s">
-        <v>7</v>
+      <c r="G280" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H280" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281">
@@ -6831,8 +7674,11 @@
       <c r="F281" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G281" t="s">
-        <v>7</v>
+      <c r="G281" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H281" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6854,8 +7700,11 @@
       <c r="F282" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G282" t="s">
-        <v>7</v>
+      <c r="G282" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H282" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283">
@@ -6877,8 +7726,11 @@
       <c r="F283" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G283" t="s">
-        <v>7</v>
+      <c r="G283" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H283" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284">
@@ -6900,8 +7752,11 @@
       <c r="F284" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G284" t="s">
-        <v>7</v>
+      <c r="G284" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H284" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -6923,8 +7778,11 @@
       <c r="F285" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G285" t="s">
-        <v>7</v>
+      <c r="G285" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H285" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6946,8 +7804,11 @@
       <c r="F286" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G286" t="s">
-        <v>7</v>
+      <c r="G286" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H286" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6969,8 +7830,11 @@
       <c r="F287" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G287" t="s">
-        <v>7</v>
+      <c r="G287" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H287" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6992,8 +7856,11 @@
       <c r="F288" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G288" t="s">
-        <v>7</v>
+      <c r="G288" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H288" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -7015,8 +7882,11 @@
       <c r="F289" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G289" t="s">
-        <v>7</v>
+      <c r="G289" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H289" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -7038,8 +7908,11 @@
       <c r="F290" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G290" t="s">
-        <v>7</v>
+      <c r="G290" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H290" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7061,8 +7934,11 @@
       <c r="F291" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G291" t="s">
-        <v>7</v>
+      <c r="G291" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H291" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -7084,8 +7960,11 @@
       <c r="F292" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G292" t="s">
-        <v>7</v>
+      <c r="G292" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H292" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -7107,8 +7986,11 @@
       <c r="F293" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G293" t="s">
-        <v>7</v>
+      <c r="G293" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H293" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -7130,8 +8012,11 @@
       <c r="F294" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G294" t="s">
-        <v>7</v>
+      <c r="G294" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H294" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295">
@@ -7153,8 +8038,11 @@
       <c r="F295" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G295" t="s">
-        <v>7</v>
+      <c r="G295" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H295" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -7176,8 +8064,11 @@
       <c r="F296" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G296" t="s">
-        <v>7</v>
+      <c r="G296" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H296" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -7199,8 +8090,11 @@
       <c r="F297" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G297" t="s">
-        <v>7</v>
+      <c r="G297" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H297" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -7222,8 +8116,11 @@
       <c r="F298" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G298" t="s">
-        <v>7</v>
+      <c r="G298" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -7245,8 +8142,11 @@
       <c r="F299" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G299" t="s">
-        <v>7</v>
+      <c r="G299" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H299" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -7268,8 +8168,11 @@
       <c r="F300" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G300" t="s">
-        <v>7</v>
+      <c r="G300" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H300" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -7291,8 +8194,11 @@
       <c r="F301" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G301" t="s">
-        <v>7</v>
+      <c r="G301" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H301" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7314,8 +8220,11 @@
       <c r="F302" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G302" t="s">
-        <v>7</v>
+      <c r="G302" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H302" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -7337,8 +8246,11 @@
       <c r="F303" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G303" t="s">
-        <v>7</v>
+      <c r="G303" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H303" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7360,8 +8272,11 @@
       <c r="F304" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G304" t="s">
-        <v>7</v>
+      <c r="G304" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H304" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305">
@@ -7383,8 +8298,11 @@
       <c r="F305" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G305" t="s">
-        <v>7</v>
+      <c r="G305" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H305" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -7406,8 +8324,11 @@
       <c r="F306" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G306" t="s">
-        <v>7</v>
+      <c r="G306" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H306" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307">
@@ -7429,8 +8350,11 @@
       <c r="F307" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G307" t="s">
-        <v>7</v>
+      <c r="G307" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H307" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308">
@@ -7452,8 +8376,11 @@
       <c r="F308" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G308" t="s">
-        <v>7</v>
+      <c r="G308" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H308" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309">
@@ -7475,8 +8402,11 @@
       <c r="F309" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G309" t="s">
-        <v>7</v>
+      <c r="G309" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H309" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310">
@@ -7498,8 +8428,11 @@
       <c r="F310" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G310" t="s">
-        <v>7</v>
+      <c r="G310" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H310" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -7521,8 +8454,11 @@
       <c r="F311" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G311" t="s">
-        <v>7</v>
+      <c r="G311" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H311" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312">
@@ -7544,8 +8480,11 @@
       <c r="F312" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G312" t="s">
-        <v>7</v>
+      <c r="G312" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H312" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313">
@@ -7567,8 +8506,11 @@
       <c r="F313" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G313" t="s">
-        <v>7</v>
+      <c r="G313" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H313" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7590,8 +8532,11 @@
       <c r="F314" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G314" t="s">
-        <v>7</v>
+      <c r="G314" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H314" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315">
@@ -7613,8 +8558,11 @@
       <c r="F315" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G315" t="s">
-        <v>7</v>
+      <c r="G315" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H315" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -7636,8 +8584,11 @@
       <c r="F316" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G316" t="s">
-        <v>7</v>
+      <c r="G316" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H316" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -7659,8 +8610,11 @@
       <c r="F317" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G317" t="s">
-        <v>7</v>
+      <c r="G317" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H317" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7682,8 +8636,11 @@
       <c r="F318" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G318" t="s">
-        <v>7</v>
+      <c r="G318" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H318" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319">
@@ -7705,8 +8662,11 @@
       <c r="F319" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G319" t="s">
-        <v>7</v>
+      <c r="G319" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H319" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -7728,8 +8688,11 @@
       <c r="F320" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G320" t="s">
-        <v>7</v>
+      <c r="G320" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H320" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -7751,8 +8714,11 @@
       <c r="F321" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G321" t="s">
-        <v>7</v>
+      <c r="G321" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H321" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -7774,8 +8740,11 @@
       <c r="F322" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G322" t="s">
-        <v>7</v>
+      <c r="G322" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H322" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -7797,8 +8766,11 @@
       <c r="F323" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G323" t="s">
-        <v>7</v>
+      <c r="G323" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H323" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7820,8 +8792,11 @@
       <c r="F324" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G324" t="s">
-        <v>7</v>
+      <c r="G324" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H324" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7843,8 +8818,11 @@
       <c r="F325" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G325" t="s">
-        <v>7</v>
+      <c r="G325" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H325" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326">
@@ -7866,8 +8844,11 @@
       <c r="F326" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G326" t="s">
-        <v>7</v>
+      <c r="G326" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H326" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327">
@@ -7889,8 +8870,11 @@
       <c r="F327" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G327" t="s">
-        <v>7</v>
+      <c r="G327" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H327" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7912,8 +8896,11 @@
       <c r="F328" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G328" t="s">
-        <v>7</v>
+      <c r="G328" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H328" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329">
@@ -7935,8 +8922,11 @@
       <c r="F329" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G329" t="s">
-        <v>7</v>
+      <c r="G329" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H329" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7958,8 +8948,11 @@
       <c r="F330" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G330" t="s">
-        <v>7</v>
+      <c r="G330" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H330" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -7981,8 +8974,11 @@
       <c r="F331" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G331" t="s">
-        <v>7</v>
+      <c r="G331" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H331" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332">
@@ -8004,8 +9000,11 @@
       <c r="F332" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G332" t="s">
-        <v>7</v>
+      <c r="G332" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H332" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8027,8 +9026,11 @@
       <c r="F333" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G333" t="s">
-        <v>7</v>
+      <c r="G333" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H333" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -8050,8 +9052,11 @@
       <c r="F334" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G334" t="s">
-        <v>7</v>
+      <c r="G334" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H334" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -8073,8 +9078,11 @@
       <c r="F335" t="n">
         <v>0.0204080007970333</v>
       </c>
-      <c r="G335" t="s">
-        <v>7</v>
+      <c r="G335" t="n">
+        <v>0.0204080007970333</v>
+      </c>
+      <c r="H335" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -8096,8 +9104,11 @@
       <c r="F336" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G336" t="s">
-        <v>7</v>
+      <c r="G336" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H336" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8119,8 +9130,11 @@
       <c r="F337" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G337" t="s">
-        <v>7</v>
+      <c r="G337" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H337" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338">
@@ -8142,8 +9156,11 @@
       <c r="F338" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G338" t="s">
-        <v>7</v>
+      <c r="G338" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H338" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339">
@@ -8165,8 +9182,11 @@
       <c r="F339" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G339" t="s">
-        <v>7</v>
+      <c r="G339" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H339" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -8188,8 +9208,11 @@
       <c r="F340" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G340" t="s">
-        <v>7</v>
+      <c r="G340" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H340" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -8211,8 +9234,11 @@
       <c r="F341" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G341" t="s">
-        <v>7</v>
+      <c r="G341" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H341" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342">
@@ -8234,8 +9260,11 @@
       <c r="F342" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G342" t="s">
-        <v>7</v>
+      <c r="G342" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H342" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343">
@@ -8257,8 +9286,11 @@
       <c r="F343" t="n">
         <v>0.019590999931097</v>
       </c>
-      <c r="G343" t="s">
-        <v>7</v>
+      <c r="G343" t="n">
+        <v>0.019590999931097</v>
+      </c>
+      <c r="H343" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344">
@@ -8280,8 +9312,11 @@
       <c r="F344" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G344" t="s">
-        <v>7</v>
+      <c r="G344" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H344" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -8303,8 +9338,11 @@
       <c r="F345" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G345" t="s">
-        <v>7</v>
+      <c r="G345" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H345" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -8326,8 +9364,11 @@
       <c r="F346" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G346" t="s">
-        <v>7</v>
+      <c r="G346" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H346" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -8349,8 +9390,11 @@
       <c r="F347" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G347" t="s">
-        <v>7</v>
+      <c r="G347" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H347" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348">
@@ -8372,8 +9416,11 @@
       <c r="F348" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G348" t="s">
-        <v>7</v>
+      <c r="G348" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H348" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349">
@@ -8395,8 +9442,11 @@
       <c r="F349" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G349" t="s">
-        <v>7</v>
+      <c r="G349" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H349" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -8418,8 +9468,11 @@
       <c r="F350" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G350" t="s">
-        <v>7</v>
+      <c r="G350" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H350" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351">
@@ -8441,8 +9494,11 @@
       <c r="F351" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G351" t="s">
-        <v>7</v>
+      <c r="G351" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H351" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8464,8 +9520,11 @@
       <c r="F352" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G352" t="s">
-        <v>7</v>
+      <c r="G352" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H352" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -8487,8 +9546,11 @@
       <c r="F353" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G353" t="s">
-        <v>7</v>
+      <c r="G353" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H353" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354">
@@ -8510,8 +9572,11 @@
       <c r="F354" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G354" t="s">
-        <v>7</v>
+      <c r="G354" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H354" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8533,8 +9598,11 @@
       <c r="F355" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G355" t="s">
-        <v>7</v>
+      <c r="G355" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H355" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -8556,8 +9624,11 @@
       <c r="F356" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G356" t="s">
-        <v>7</v>
+      <c r="G356" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H356" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8579,8 +9650,11 @@
       <c r="F357" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G357" t="s">
-        <v>7</v>
+      <c r="G357" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H357" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -8602,8 +9676,11 @@
       <c r="F358" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G358" t="s">
-        <v>7</v>
+      <c r="G358" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H358" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359">
@@ -8625,8 +9702,11 @@
       <c r="F359" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G359" t="s">
-        <v>7</v>
+      <c r="G359" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H359" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8648,8 +9728,11 @@
       <c r="F360" t="n">
         <v>0.0201019998639822</v>
       </c>
-      <c r="G360" t="s">
-        <v>7</v>
+      <c r="G360" t="n">
+        <v>0.0201019998639822</v>
+      </c>
+      <c r="H360" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361">
@@ -8671,8 +9754,11 @@
       <c r="F361" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G361" t="s">
-        <v>7</v>
+      <c r="G361" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H361" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362">
@@ -8694,8 +9780,11 @@
       <c r="F362" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G362" t="s">
-        <v>7</v>
+      <c r="G362" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H362" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -8717,8 +9806,11 @@
       <c r="F363" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G363" t="s">
-        <v>7</v>
+      <c r="G363" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H363" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8740,8 +9832,11 @@
       <c r="F364" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G364" t="s">
-        <v>7</v>
+      <c r="G364" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H364" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8763,8 +9858,11 @@
       <c r="F365" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G365" t="s">
-        <v>7</v>
+      <c r="G365" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H365" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8786,8 +9884,11 @@
       <c r="F366" t="n">
         <v>0.0197950005531311</v>
       </c>
-      <c r="G366" t="s">
-        <v>7</v>
+      <c r="G366" t="n">
+        <v>0.0197950005531311</v>
+      </c>
+      <c r="H366" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8809,8 +9910,11 @@
       <c r="F367" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G367" t="s">
-        <v>7</v>
+      <c r="G367" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H367" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8832,8 +9936,11 @@
       <c r="F368" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G368" t="s">
-        <v>7</v>
+      <c r="G368" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H368" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -8855,8 +9962,11 @@
       <c r="F369" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G369" t="s">
-        <v>7</v>
+      <c r="G369" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H369" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8878,8 +9988,11 @@
       <c r="F370" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G370" t="s">
-        <v>7</v>
+      <c r="G370" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H370" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8901,8 +10014,11 @@
       <c r="F371" t="n">
         <v>0.0192850008606911</v>
       </c>
-      <c r="G371" t="s">
-        <v>7</v>
+      <c r="G371" t="n">
+        <v>0.0192850008606911</v>
+      </c>
+      <c r="H371" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8924,8 +10040,11 @@
       <c r="F372" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G372" t="s">
-        <v>7</v>
+      <c r="G372" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H372" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -8947,8 +10066,11 @@
       <c r="F373" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G373" t="s">
-        <v>7</v>
+      <c r="G373" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H373" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8970,8 +10092,11 @@
       <c r="F374" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G374" t="s">
-        <v>7</v>
+      <c r="G374" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H374" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8993,8 +10118,11 @@
       <c r="F375" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G375" t="s">
-        <v>7</v>
+      <c r="G375" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H375" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -9016,8 +10144,11 @@
       <c r="F376" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G376" t="s">
-        <v>7</v>
+      <c r="G376" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H376" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -9039,8 +10170,11 @@
       <c r="F377" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G377" t="s">
-        <v>7</v>
+      <c r="G377" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H377" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -9062,8 +10196,11 @@
       <c r="F378" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G378" t="s">
-        <v>7</v>
+      <c r="G378" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H378" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -9085,8 +10222,11 @@
       <c r="F379" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G379" t="s">
-        <v>7</v>
+      <c r="G379" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H379" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -9108,8 +10248,11 @@
       <c r="F380" t="n">
         <v>0.019386999309063</v>
       </c>
-      <c r="G380" t="s">
-        <v>7</v>
+      <c r="G380" t="n">
+        <v>0.019386999309063</v>
+      </c>
+      <c r="H380" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -9131,8 +10274,11 @@
       <c r="F381" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G381" t="s">
-        <v>7</v>
+      <c r="G381" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H381" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -9154,8 +10300,11 @@
       <c r="F382" t="n">
         <v>0.0199999995529652</v>
       </c>
-      <c r="G382" t="s">
-        <v>7</v>
+      <c r="G382" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H382" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -9177,8 +10326,11 @@
       <c r="F383" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G383" t="s">
-        <v>7</v>
+      <c r="G383" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H383" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -9200,8 +10352,11 @@
       <c r="F384" t="n">
         <v>0.0198970008641481</v>
       </c>
-      <c r="G384" t="s">
-        <v>7</v>
+      <c r="G384" t="n">
+        <v>0.0198970008641481</v>
+      </c>
+      <c r="H384" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -9223,8 +10378,11 @@
       <c r="F385" t="n">
         <v>0.0196930002421141</v>
       </c>
-      <c r="G385" t="s">
-        <v>7</v>
+      <c r="G385" t="n">
+        <v>0.0196930002421141</v>
+      </c>
+      <c r="H385" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -9246,8 +10404,11 @@
       <c r="F386" t="n">
         <v>0.019183000549674</v>
       </c>
-      <c r="G386" t="s">
-        <v>7</v>
+      <c r="G386" t="n">
+        <v>0.019183000549674</v>
+      </c>
+      <c r="H386" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -9269,8 +10430,11 @@
       <c r="F387" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G387" t="s">
-        <v>7</v>
+      <c r="G387" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H387" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -9292,8 +10456,11 @@
       <c r="F388" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G388" t="s">
-        <v>7</v>
+      <c r="G388" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H388" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -9315,8 +10482,11 @@
       <c r="F389" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G389" t="s">
-        <v>7</v>
+      <c r="G389" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H389" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -9338,8 +10508,11 @@
       <c r="F390" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G390" t="s">
-        <v>7</v>
+      <c r="G390" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H390" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -9361,8 +10534,11 @@
       <c r="F391" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G391" t="s">
-        <v>7</v>
+      <c r="G391" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H391" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -9384,8 +10560,11 @@
       <c r="F392" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G392" t="s">
-        <v>7</v>
+      <c r="G392" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H392" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -9407,8 +10586,11 @@
       <c r="F393" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G393" t="s">
-        <v>7</v>
+      <c r="G393" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H393" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -9430,8 +10612,11 @@
       <c r="F394" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G394" t="s">
-        <v>7</v>
+      <c r="G394" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H394" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -9453,8 +10638,11 @@
       <c r="F395" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G395" t="s">
-        <v>7</v>
+      <c r="G395" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H395" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -9476,8 +10664,11 @@
       <c r="F396" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G396" t="s">
-        <v>7</v>
+      <c r="G396" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H396" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -9499,8 +10690,11 @@
       <c r="F397" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G397" t="s">
-        <v>7</v>
+      <c r="G397" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H397" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -9522,8 +10716,11 @@
       <c r="F398" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G398" t="s">
-        <v>7</v>
+      <c r="G398" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H398" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -9545,8 +10742,11 @@
       <c r="F399" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G399" t="s">
-        <v>7</v>
+      <c r="G399" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H399" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -9568,8 +10768,11 @@
       <c r="F400" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G400" t="s">
-        <v>7</v>
+      <c r="G400" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H400" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -9591,8 +10794,11 @@
       <c r="F401" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G401" t="s">
-        <v>7</v>
+      <c r="G401" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H401" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -9614,8 +10820,11 @@
       <c r="F402" t="n">
         <v>0.01948899962008</v>
       </c>
-      <c r="G402" t="s">
-        <v>7</v>
+      <c r="G402" t="n">
+        <v>0.01948899962008</v>
+      </c>
+      <c r="H402" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9637,8 +10846,11 @@
       <c r="F403" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G403" t="s">
-        <v>7</v>
+      <c r="G403" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H403" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9660,8 +10872,11 @@
       <c r="F404" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G404" t="s">
-        <v>7</v>
+      <c r="G404" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H404" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -9683,8 +10898,11 @@
       <c r="F405" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G405" t="s">
-        <v>7</v>
+      <c r="G405" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H405" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9706,8 +10924,11 @@
       <c r="F406" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G406" t="s">
-        <v>7</v>
+      <c r="G406" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H406" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -9729,8 +10950,11 @@
       <c r="F407" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G407" t="s">
-        <v>7</v>
+      <c r="G407" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H407" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9752,8 +10976,11 @@
       <c r="F408" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G408" t="s">
-        <v>7</v>
+      <c r="G408" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H408" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -9775,8 +11002,11 @@
       <c r="F409" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G409" t="s">
-        <v>7</v>
+      <c r="G409" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H409" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9798,8 +11028,11 @@
       <c r="F410" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G410" t="s">
-        <v>7</v>
+      <c r="G410" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H410" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9821,8 +11054,11 @@
       <c r="F411" t="n">
         <v>0.019081000238657</v>
       </c>
-      <c r="G411" t="s">
-        <v>7</v>
+      <c r="G411" t="n">
+        <v>0.019081000238657</v>
+      </c>
+      <c r="H411" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9844,8 +11080,11 @@
       <c r="F412" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G412" t="s">
-        <v>7</v>
+      <c r="G412" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H412" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9867,8 +11106,11 @@
       <c r="F413" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G413" t="s">
-        <v>7</v>
+      <c r="G413" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H413" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -9890,8 +11132,11 @@
       <c r="F414" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G414" t="s">
-        <v>7</v>
+      <c r="G414" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H414" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9913,8 +11158,11 @@
       <c r="F415" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G415" t="s">
-        <v>7</v>
+      <c r="G415" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H415" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9936,8 +11184,11 @@
       <c r="F416" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G416" t="s">
-        <v>7</v>
+      <c r="G416" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H416" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -9959,8 +11210,11 @@
       <c r="F417" t="n">
         <v>0.01897899992764</v>
       </c>
-      <c r="G417" t="s">
-        <v>7</v>
+      <c r="G417" t="n">
+        <v>0.01897899992764</v>
+      </c>
+      <c r="H417" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -9982,8 +11236,11 @@
       <c r="F418" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G418" t="s">
-        <v>7</v>
+      <c r="G418" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H418" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -10005,8 +11262,11 @@
       <c r="F419" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G419" t="s">
-        <v>7</v>
+      <c r="G419" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H419" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -10028,8 +11288,11 @@
       <c r="F420" t="n">
         <v>0.0188769996166229</v>
       </c>
-      <c r="G420" t="s">
-        <v>7</v>
+      <c r="G420" t="n">
+        <v>0.0188769996166229</v>
+      </c>
+      <c r="H420" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -10051,8 +11314,11 @@
       <c r="F421" t="n">
         <v>0.018673000857234</v>
       </c>
-      <c r="G421" t="s">
-        <v>7</v>
+      <c r="G421" t="n">
+        <v>0.018673000857234</v>
+      </c>
+      <c r="H421" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -10074,8 +11340,11 @@
       <c r="F422" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G422" t="s">
-        <v>7</v>
+      <c r="G422" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H422" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -10097,8 +11366,11 @@
       <c r="F423" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G423" t="s">
-        <v>7</v>
+      <c r="G423" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H423" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -10120,8 +11392,11 @@
       <c r="F424" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G424" t="s">
-        <v>7</v>
+      <c r="G424" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H424" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -10143,8 +11418,11 @@
       <c r="F425" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G425" t="s">
-        <v>7</v>
+      <c r="G425" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H425" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -10166,8 +11444,11 @@
       <c r="F426" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G426" t="s">
-        <v>7</v>
+      <c r="G426" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H426" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -10189,8 +11470,11 @@
       <c r="F427" t="n">
         <v>0.0181629993021488</v>
       </c>
-      <c r="G427" t="s">
-        <v>7</v>
+      <c r="G427" t="n">
+        <v>0.0181629993021488</v>
+      </c>
+      <c r="H427" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -10212,8 +11496,11 @@
       <c r="F428" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G428" t="s">
-        <v>7</v>
+      <c r="G428" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H428" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -10235,8 +11522,11 @@
       <c r="F429" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G429" t="s">
-        <v>7</v>
+      <c r="G429" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H429" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -10258,8 +11548,11 @@
       <c r="F430" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G430" t="s">
-        <v>7</v>
+      <c r="G430" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H430" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -10281,8 +11574,11 @@
       <c r="F431" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G431" t="s">
-        <v>7</v>
+      <c r="G431" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H431" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -10304,8 +11600,11 @@
       <c r="F432" t="n">
         <v>0.018571000546217</v>
       </c>
-      <c r="G432" t="s">
-        <v>7</v>
+      <c r="G432" t="n">
+        <v>0.018571000546217</v>
+      </c>
+      <c r="H432" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -10327,8 +11626,11 @@
       <c r="F433" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G433" t="s">
-        <v>7</v>
+      <c r="G433" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H433" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -10350,8 +11652,11 @@
       <c r="F434" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G434" t="s">
-        <v>7</v>
+      <c r="G434" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H434" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -10373,8 +11678,11 @@
       <c r="F435" t="n">
         <v>0.0183669999241829</v>
       </c>
-      <c r="G435" t="s">
-        <v>7</v>
+      <c r="G435" t="n">
+        <v>0.0183669999241829</v>
+      </c>
+      <c r="H435" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -10396,8 +11704,11 @@
       <c r="F436" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G436" t="s">
-        <v>7</v>
+      <c r="G436" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H436" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -10419,8 +11730,11 @@
       <c r="F437" t="n">
         <v>0.0182649996131659</v>
       </c>
-      <c r="G437" t="s">
-        <v>7</v>
+      <c r="G437" t="n">
+        <v>0.0182649996131659</v>
+      </c>
+      <c r="H437" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -10442,8 +11756,11 @@
       <c r="F438" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G438" t="s">
-        <v>7</v>
+      <c r="G438" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H438" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -10465,8 +11782,11 @@
       <c r="F439" t="n">
         <v>0.0179590005427599</v>
       </c>
-      <c r="G439" t="s">
-        <v>7</v>
+      <c r="G439" t="n">
+        <v>0.0179590005427599</v>
+      </c>
+      <c r="H439" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -10488,8 +11808,11 @@
       <c r="F440" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G440" t="s">
-        <v>7</v>
+      <c r="G440" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H440" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -10511,8 +11834,11 @@
       <c r="F441" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G441" t="s">
-        <v>7</v>
+      <c r="G441" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H441" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -10534,8 +11860,11 @@
       <c r="F442" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G442" t="s">
-        <v>7</v>
+      <c r="G442" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H442" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -10557,8 +11886,11 @@
       <c r="F443" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G443" t="s">
-        <v>7</v>
+      <c r="G443" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H443" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -10580,8 +11912,11 @@
       <c r="F444" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G444" t="s">
-        <v>7</v>
+      <c r="G444" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H444" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -10603,8 +11938,11 @@
       <c r="F445" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G445" t="s">
-        <v>7</v>
+      <c r="G445" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H445" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -10626,8 +11964,11 @@
       <c r="F446" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G446" t="s">
-        <v>7</v>
+      <c r="G446" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H446" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -10649,8 +11990,11 @@
       <c r="F447" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G447" t="s">
-        <v>7</v>
+      <c r="G447" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H447" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -10672,8 +12016,11 @@
       <c r="F448" t="n">
         <v>0.0176529996097088</v>
       </c>
-      <c r="G448" t="s">
-        <v>7</v>
+      <c r="G448" t="n">
+        <v>0.0176529996097088</v>
+      </c>
+      <c r="H448" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -10695,8 +12042,11 @@
       <c r="F449" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G449" t="s">
-        <v>7</v>
+      <c r="G449" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H449" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -10718,8 +12068,11 @@
       <c r="F450" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G450" t="s">
-        <v>7</v>
+      <c r="G450" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H450" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -10741,8 +12094,11 @@
       <c r="F451" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G451" t="s">
-        <v>7</v>
+      <c r="G451" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H451" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10764,8 +12120,11 @@
       <c r="F452" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G452" t="s">
-        <v>7</v>
+      <c r="G452" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H452" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10787,8 +12146,11 @@
       <c r="F453" t="n">
         <v>0.0172439999878407</v>
       </c>
-      <c r="G453" t="s">
-        <v>7</v>
+      <c r="G453" t="n">
+        <v>0.0172439999878407</v>
+      </c>
+      <c r="H453" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -10810,8 +12172,11 @@
       <c r="F454" t="n">
         <v>0.0170399993658066</v>
       </c>
-      <c r="G454" t="s">
-        <v>7</v>
+      <c r="G454" t="n">
+        <v>0.0170399993658066</v>
+      </c>
+      <c r="H454" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10833,8 +12198,11 @@
       <c r="F455" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G455" t="s">
-        <v>7</v>
+      <c r="G455" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H455" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10856,8 +12224,11 @@
       <c r="F456" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G456" t="s">
-        <v>7</v>
+      <c r="G456" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H456" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10879,8 +12250,11 @@
       <c r="F457" t="n">
         <v>0.0163260009139776</v>
       </c>
-      <c r="G457" t="s">
-        <v>7</v>
+      <c r="G457" t="n">
+        <v>0.0163260009139776</v>
+      </c>
+      <c r="H457" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -10902,8 +12276,11 @@
       <c r="F458" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G458" t="s">
-        <v>7</v>
+      <c r="G458" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H458" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -10925,8 +12302,11 @@
       <c r="F459" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G459" t="s">
-        <v>7</v>
+      <c r="G459" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H459" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -10948,8 +12328,11 @@
       <c r="F460" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G460" t="s">
-        <v>7</v>
+      <c r="G460" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H460" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -10971,8 +12354,11 @@
       <c r="F461" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G461" t="s">
-        <v>7</v>
+      <c r="G461" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H461" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10994,8 +12380,11 @@
       <c r="F462" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G462" t="s">
-        <v>7</v>
+      <c r="G462" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H462" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -11017,8 +12406,11 @@
       <c r="F463" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G463" t="s">
-        <v>7</v>
+      <c r="G463" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H463" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -11040,8 +12432,11 @@
       <c r="F464" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G464" t="s">
-        <v>7</v>
+      <c r="G464" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H464" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -11063,8 +12458,11 @@
       <c r="F465" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G465" t="s">
-        <v>7</v>
+      <c r="G465" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H465" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -11086,8 +12484,11 @@
       <c r="F466" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G466" t="s">
-        <v>7</v>
+      <c r="G466" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+      <c r="H466" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -11109,8 +12510,11 @@
       <c r="F467" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G467" t="s">
-        <v>7</v>
+      <c r="G467" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H467" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -11132,8 +12536,11 @@
       <c r="F468" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G468" t="s">
-        <v>7</v>
+      <c r="G468" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H468" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -11155,8 +12562,11 @@
       <c r="F469" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G469" t="s">
-        <v>7</v>
+      <c r="G469" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -11178,8 +12588,11 @@
       <c r="F470" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G470" t="s">
-        <v>7</v>
+      <c r="G470" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H470" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -11201,8 +12614,11 @@
       <c r="F471" t="n">
         <v>0.0168360006064177</v>
       </c>
-      <c r="G471" t="s">
-        <v>7</v>
+      <c r="G471" t="n">
+        <v>0.0168360006064177</v>
+      </c>
+      <c r="H471" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -11224,8 +12640,11 @@
       <c r="F472" t="n">
         <v>0.0160199999809265</v>
       </c>
-      <c r="G472" t="s">
-        <v>7</v>
+      <c r="G472" t="n">
+        <v>0.0160199999809265</v>
+      </c>
+      <c r="H472" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -11247,8 +12666,11 @@
       <c r="F473" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G473" t="s">
-        <v>7</v>
+      <c r="G473" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H473" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -11270,8 +12692,11 @@
       <c r="F474" t="n">
         <v>0.0159179996699095</v>
       </c>
-      <c r="G474" t="s">
-        <v>7</v>
+      <c r="G474" t="n">
+        <v>0.0159179996699095</v>
+      </c>
+      <c r="H474" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -11293,8 +12718,11 @@
       <c r="F475" t="n">
         <v>0.0156119996681809</v>
       </c>
-      <c r="G475" t="s">
-        <v>7</v>
+      <c r="G475" t="n">
+        <v>0.0156119996681809</v>
+      </c>
+      <c r="H475" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -11316,8 +12744,11 @@
       <c r="F476" t="n">
         <v>0.0157140009105206</v>
       </c>
-      <c r="G476" t="s">
-        <v>7</v>
+      <c r="G476" t="n">
+        <v>0.0157140009105206</v>
+      </c>
+      <c r="H476" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -11339,8 +12770,11 @@
       <c r="F477" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G477" t="s">
-        <v>7</v>
+      <c r="G477" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H477" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -11362,8 +12796,11 @@
       <c r="F478" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G478" t="s">
-        <v>7</v>
+      <c r="G478" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H478" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -11385,8 +12822,11 @@
       <c r="F479" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G479" t="s">
-        <v>7</v>
+      <c r="G479" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H479" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -11408,8 +12848,11 @@
       <c r="F480" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G480" t="s">
-        <v>7</v>
+      <c r="G480" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H480" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -11431,8 +12874,11 @@
       <c r="F481" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G481" t="s">
-        <v>7</v>
+      <c r="G481" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H481" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -11454,8 +12900,11 @@
       <c r="F482" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G482" t="s">
-        <v>7</v>
+      <c r="G482" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H482" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -11477,8 +12926,11 @@
       <c r="F483" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G483" t="s">
-        <v>7</v>
+      <c r="G483" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H483" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -11500,8 +12952,11 @@
       <c r="F484" t="n">
         <v>0.0158159993588924</v>
       </c>
-      <c r="G484" t="s">
-        <v>7</v>
+      <c r="G484" t="n">
+        <v>0.0158159993588924</v>
+      </c>
+      <c r="H484" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -11523,8 +12978,11 @@
       <c r="F485" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G485" t="s">
-        <v>7</v>
+      <c r="G485" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H485" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -11546,8 +13004,11 @@
       <c r="F486" t="n">
         <v>0.0171419996768236</v>
       </c>
-      <c r="G486" t="s">
-        <v>7</v>
+      <c r="G486" t="n">
+        <v>0.0171419996768236</v>
+      </c>
+      <c r="H486" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -11569,8 +13030,11 @@
       <c r="F487" t="n">
         <v>0.0165299996733665</v>
       </c>
-      <c r="G487" t="s">
-        <v>7</v>
+      <c r="G487" t="n">
+        <v>0.0165299996733665</v>
+      </c>
+      <c r="H487" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="488">
@@ -11592,8 +13056,11 @@
       <c r="F488" t="n">
         <v>0.0166319999843836</v>
       </c>
-      <c r="G488" t="s">
-        <v>7</v>
+      <c r="G488" t="n">
+        <v>0.0166319999843836</v>
+      </c>
+      <c r="H488" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -11615,8 +13082,11 @@
       <c r="F489" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G489" t="s">
-        <v>7</v>
+      <c r="G489" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H489" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -11638,8 +13108,11 @@
       <c r="F490" t="n">
         <v>0.0173460002988577</v>
       </c>
-      <c r="G490" t="s">
-        <v>7</v>
+      <c r="G490" t="n">
+        <v>0.0173460002988577</v>
+      </c>
+      <c r="H490" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -11661,8 +13134,11 @@
       <c r="F491" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G491" t="s">
-        <v>7</v>
+      <c r="G491" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H491" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -11684,8 +13160,11 @@
       <c r="F492" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G492" t="s">
-        <v>7</v>
+      <c r="G492" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H492" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -11707,8 +13186,11 @@
       <c r="F493" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G493" t="s">
-        <v>7</v>
+      <c r="G493" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H493" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -11730,8 +13212,11 @@
       <c r="F494" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G494" t="s">
-        <v>7</v>
+      <c r="G494" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H494" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -11753,8 +13238,11 @@
       <c r="F495" t="n">
         <v>0.0169380009174347</v>
       </c>
-      <c r="G495" t="s">
-        <v>7</v>
+      <c r="G495" t="n">
+        <v>0.0169380009174347</v>
+      </c>
+      <c r="H495" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="496">
@@ -11776,8 +13264,11 @@
       <c r="F496" t="n">
         <v>0.0167340002954006</v>
       </c>
-      <c r="G496" t="s">
-        <v>7</v>
+      <c r="G496" t="n">
+        <v>0.0167340002954006</v>
+      </c>
+      <c r="H496" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -11799,8 +13290,11 @@
       <c r="F497" t="n">
         <v>0.0161220002919436</v>
       </c>
-      <c r="G497" t="s">
-        <v>7</v>
+      <c r="G497" t="n">
+        <v>0.0161220002919436</v>
+      </c>
+     